--- a/design/tables/Wave.xlsx
+++ b/design/tables/Wave.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wave" sheetId="1" r:id="Rd3a1c38015cd47be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wave" sheetId="1" r:id="R057385c01c0a4954"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -17,7 +17,7 @@
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="0.######"/>
   </x:numFmts>
-  <x:fonts count="3">
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -33,8 +33,19 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Microsoft YaHei"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF24453D"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -51,6 +62,16 @@
         <x:fgColor rgb="FF34564C"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE5EDE7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF335A50"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -58,7 +79,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="9">
+  <x:cellXfs count="15">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -82,6 +103,16 @@
     <x:xf numFmtId="201" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -289,9 +320,10 @@
     <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="32" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="27.5" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="48" customHeight="1">
+    <x:row r="1" ht="54" customHeight="1">
       <x:c r="A1" s="6" t="str">
         <x:v>唯一ID，不可重复</x:v>
       </x:c>
@@ -306,6 +338,9 @@
       </x:c>
       <x:c r="E1" s="6" t="str">
         <x:v>波次提示I18</x:v>
+      </x:c>
+      <x:c r="F1" s="12" t="str">
+        <x:v>仅影响本波怪物血量，基础移速不随关卡/波次改变</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="26" customHeight="1">
@@ -324,6 +359,9 @@
       <x:c r="E2" s="3" t="str">
         <x:v>client</x:v>
       </x:c>
+      <x:c r="F2" s="12" t="str">
+        <x:v>client</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="26" customHeight="1">
       <x:c r="A3" s="3" t="str">
@@ -341,6 +379,9 @@
       <x:c r="E3" s="3" t="str">
         <x:v>string</x:v>
       </x:c>
+      <x:c r="F3" s="12" t="str">
+        <x:v>float</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="40" customHeight="1">
       <x:c r="A4" s="6" t="str">
@@ -358,6 +399,9 @@
       <x:c r="E4" s="6" t="str">
         <x:v>波次提示I18</x:v>
       </x:c>
+      <x:c r="F4" s="12" t="str">
+        <x:v>本波血量倍率</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="30" customHeight="1">
       <x:c r="A5" s="5" t="str">
@@ -375,6 +419,9 @@
       <x:c r="E5" s="5" t="str">
         <x:v>announcement</x:v>
       </x:c>
+      <x:c r="F5" s="14" t="str">
+        <x:v>healthScale</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="7" t="n">
@@ -390,6 +437,9 @@
         <x:v>0.98</x:v>
       </x:c>
       <x:c r="E6" s="2" t="str"/>
+      <x:c r="F6" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="7" t="n">
@@ -405,6 +455,9 @@
         <x:v>0.86</x:v>
       </x:c>
       <x:c r="E7" s="2" t="str"/>
+      <x:c r="F7" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="7" t="n">
@@ -420,6 +473,9 @@
         <x:v>0.72</x:v>
       </x:c>
       <x:c r="E8" s="2" t="str"/>
+      <x:c r="F8" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="7" t="n">
@@ -437,6 +493,9 @@
       <x:c r="E9" s="2" t="str">
         <x:v>wave.104.announcement</x:v>
       </x:c>
+      <x:c r="F9" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="7" t="n">
@@ -452,6 +511,9 @@
         <x:v>0.86</x:v>
       </x:c>
       <x:c r="E10" s="2" t="str"/>
+      <x:c r="F10" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" s="7" t="n">
@@ -467,6 +529,9 @@
         <x:v>0.7</x:v>
       </x:c>
       <x:c r="E11" s="2" t="str"/>
+      <x:c r="F11" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="7" t="n">
@@ -482,6 +547,9 @@
         <x:v>0.58</x:v>
       </x:c>
       <x:c r="E12" s="2" t="str"/>
+      <x:c r="F12" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
       <x:c r="A13" s="7" t="n">
@@ -499,6 +567,9 @@
       <x:c r="E13" s="2" t="str">
         <x:v>wave.204.announcement</x:v>
       </x:c>
+      <x:c r="F13" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
       <x:c r="A14" s="7" t="n">
@@ -514,6 +585,9 @@
         <x:v>0.62</x:v>
       </x:c>
       <x:c r="E14" s="2" t="str"/>
+      <x:c r="F14" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
       <x:c r="A15" s="7" t="n">
@@ -529,6 +603,9 @@
         <x:v>0.54</x:v>
       </x:c>
       <x:c r="E15" s="2" t="str"/>
+      <x:c r="F15" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="16" ht="15" hidden="0" customHeight="1">
       <x:c r="A16" s="7" t="n">
@@ -544,6 +621,9 @@
         <x:v>0.46</x:v>
       </x:c>
       <x:c r="E16" s="2" t="str"/>
+      <x:c r="F16" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
       <x:c r="A17" s="7" t="n">
@@ -561,6 +641,9 @@
       <x:c r="E17" s="2" t="str">
         <x:v>wave.304.announcement</x:v>
       </x:c>
+      <x:c r="F17" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" ht="15" hidden="0" customHeight="1">
       <x:c r="A18" s="7" t="n">
@@ -576,6 +659,9 @@
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="E18" s="2" t="str"/>
+      <x:c r="F18" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" ht="15" hidden="0" customHeight="1">
       <x:c r="A19" s="7" t="n">
@@ -591,6 +677,9 @@
         <x:v>0.66</x:v>
       </x:c>
       <x:c r="E19" s="2" t="str"/>
+      <x:c r="F19" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" ht="15" hidden="0" customHeight="1">
       <x:c r="A20" s="7" t="n">
@@ -606,6 +695,9 @@
         <x:v>0.58</x:v>
       </x:c>
       <x:c r="E20" s="2" t="str"/>
+      <x:c r="F20" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
       <x:c r="A21" s="7" t="n">
@@ -623,6 +715,9 @@
       <x:c r="E21" s="2" t="str">
         <x:v>wave.404.announcement</x:v>
       </x:c>
+      <x:c r="F21" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
       <x:c r="A22" s="7" t="n">
@@ -638,6 +733,9 @@
         <x:v>0.74</x:v>
       </x:c>
       <x:c r="E22" s="2" t="str"/>
+      <x:c r="F22" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" ht="15" hidden="0" customHeight="1">
       <x:c r="A23" s="7" t="n">
@@ -653,6 +751,9 @@
         <x:v>0.64</x:v>
       </x:c>
       <x:c r="E23" s="2" t="str"/>
+      <x:c r="F23" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="24" ht="15" hidden="0" customHeight="1">
       <x:c r="A24" s="7" t="n">
@@ -668,6 +769,9 @@
         <x:v>0.54</x:v>
       </x:c>
       <x:c r="E24" s="2" t="str"/>
+      <x:c r="F24" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="25" ht="15" hidden="0" customHeight="1">
       <x:c r="A25" s="7" t="n">
@@ -685,6 +789,9 @@
       <x:c r="E25" s="2" t="str">
         <x:v>wave.504.announcement</x:v>
       </x:c>
+      <x:c r="F25" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="26" ht="15" hidden="0" customHeight="1">
       <x:c r="A26" s="7" t="n">
@@ -700,6 +807,9 @@
         <x:v>0.7</x:v>
       </x:c>
       <x:c r="E26" s="2" t="str"/>
+      <x:c r="F26" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="27" ht="15" hidden="0" customHeight="1">
       <x:c r="A27" s="7" t="n">
@@ -715,6 +825,9 @@
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="E27" s="2" t="str"/>
+      <x:c r="F27" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="28" ht="15" hidden="0" customHeight="1">
       <x:c r="A28" s="7" t="n">
@@ -730,6 +843,9 @@
         <x:v>0.51</x:v>
       </x:c>
       <x:c r="E28" s="2" t="str"/>
+      <x:c r="F28" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="29" ht="15" hidden="0" customHeight="1">
       <x:c r="A29" s="7" t="n">
@@ -747,6 +863,9 @@
       <x:c r="E29" s="2" t="str">
         <x:v>wave.604.announcement</x:v>
       </x:c>
+      <x:c r="F29" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="30" ht="15" hidden="0" customHeight="1">
       <x:c r="A30" s="7" t="n">
@@ -762,6 +881,9 @@
         <x:v>0.68</x:v>
       </x:c>
       <x:c r="E30" s="2" t="str"/>
+      <x:c r="F30" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="31" ht="15" hidden="0" customHeight="1">
       <x:c r="A31" s="7" t="n">
@@ -777,6 +899,9 @@
         <x:v>0.57</x:v>
       </x:c>
       <x:c r="E31" s="2" t="str"/>
+      <x:c r="F31" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="32" ht="15" hidden="0" customHeight="1">
       <x:c r="A32" s="7" t="n">
@@ -792,6 +917,9 @@
         <x:v>0.49</x:v>
       </x:c>
       <x:c r="E32" s="2" t="str"/>
+      <x:c r="F32" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="33" ht="15" hidden="0" customHeight="1">
       <x:c r="A33" s="7" t="n">
@@ -809,6 +937,9 @@
       <x:c r="E33" s="2" t="str">
         <x:v>wave.704.announcement</x:v>
       </x:c>
+      <x:c r="F33" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="34" ht="15" hidden="0" customHeight="1">
       <x:c r="A34" s="7" t="n">
@@ -824,6 +955,9 @@
         <x:v>0.65</x:v>
       </x:c>
       <x:c r="E34" s="2" t="str"/>
+      <x:c r="F34" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="35" ht="15" hidden="0" customHeight="1">
       <x:c r="A35" s="7" t="n">
@@ -839,6 +973,9 @@
         <x:v>0.55</x:v>
       </x:c>
       <x:c r="E35" s="2" t="str"/>
+      <x:c r="F35" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="36" ht="15" hidden="0" customHeight="1">
       <x:c r="A36" s="7" t="n">
@@ -854,6 +991,9 @@
         <x:v>0.47</x:v>
       </x:c>
       <x:c r="E36" s="2" t="str"/>
+      <x:c r="F36" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="37" ht="15" hidden="0" customHeight="1">
       <x:c r="A37" s="7" t="n">
@@ -871,6 +1011,9 @@
       <x:c r="E37" s="2" t="str">
         <x:v>wave.804.announcement</x:v>
       </x:c>
+      <x:c r="F37" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="38" ht="15" hidden="0" customHeight="1">
       <x:c r="A38" s="7" t="n">
@@ -886,6 +1029,9 @@
         <x:v>0.62</x:v>
       </x:c>
       <x:c r="E38" s="2" t="str"/>
+      <x:c r="F38" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="39" ht="15" hidden="0" customHeight="1">
       <x:c r="A39" s="7" t="n">
@@ -901,6 +1047,9 @@
         <x:v>0.53</x:v>
       </x:c>
       <x:c r="E39" s="2" t="str"/>
+      <x:c r="F39" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="40" ht="15" hidden="0" customHeight="1">
       <x:c r="A40" s="7" t="n">
@@ -916,6 +1065,9 @@
         <x:v>0.45</x:v>
       </x:c>
       <x:c r="E40" s="2" t="str"/>
+      <x:c r="F40" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="41" ht="15" hidden="0" customHeight="1">
       <x:c r="A41" s="7" t="n">
@@ -933,6 +1085,9 @@
       <x:c r="E41" s="2" t="str">
         <x:v>wave.904.announcement</x:v>
       </x:c>
+      <x:c r="F41" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="42" ht="15" hidden="0" customHeight="1">
       <x:c r="A42" s="7" t="n">
@@ -948,6 +1103,9 @@
         <x:v>0.62</x:v>
       </x:c>
       <x:c r="E42" s="2" t="str"/>
+      <x:c r="F42" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="43" ht="15" hidden="0" customHeight="1">
       <x:c r="A43" s="7" t="n">
@@ -963,6 +1121,9 @@
         <x:v>0.54</x:v>
       </x:c>
       <x:c r="E43" s="2" t="str"/>
+      <x:c r="F43" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="44" ht="15" hidden="0" customHeight="1">
       <x:c r="A44" s="7" t="n">
@@ -978,6 +1139,9 @@
         <x:v>0.47</x:v>
       </x:c>
       <x:c r="E44" s="2" t="str"/>
+      <x:c r="F44" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="45" ht="15" hidden="0" customHeight="1">
       <x:c r="A45" s="7" t="n">
@@ -993,6 +1157,9 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="E45" s="2" t="str"/>
+      <x:c r="F45" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="46" ht="15" hidden="0" customHeight="1">
       <x:c r="A46" s="7" t="n">
@@ -1010,6 +1177,9 @@
       <x:c r="E46" s="2" t="str">
         <x:v>wave.1005.announcement</x:v>
       </x:c>
+      <x:c r="F46" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="47" ht="15" hidden="0" customHeight="1">
       <x:c r="A47" s="7" t="n">
@@ -1027,6 +1197,9 @@
       <x:c r="E47" s="2" t="str">
         <x:v>wave.1101.announcement</x:v>
       </x:c>
+      <x:c r="F47" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="48" ht="15" hidden="0" customHeight="1">
       <x:c r="A48" s="7" t="n">
@@ -1042,6 +1215,9 @@
         <x:v>0.595</x:v>
       </x:c>
       <x:c r="E48" s="2" t="str"/>
+      <x:c r="F48" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="49" ht="15" hidden="0" customHeight="1">
       <x:c r="A49" s="7" t="n">
@@ -1057,6 +1233,9 @@
         <x:v>0.53</x:v>
       </x:c>
       <x:c r="E49" s="2" t="str"/>
+      <x:c r="F49" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="50" ht="15" hidden="0" customHeight="1">
       <x:c r="A50" s="7" t="n">
@@ -1072,6 +1251,9 @@
         <x:v>0.465</x:v>
       </x:c>
       <x:c r="E50" s="2" t="str"/>
+      <x:c r="F50" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="51" ht="15" hidden="0" customHeight="1">
       <x:c r="A51" s="7" t="n">
@@ -1089,6 +1271,9 @@
       <x:c r="E51" s="2" t="str">
         <x:v>wave.1201.announcement</x:v>
       </x:c>
+      <x:c r="F51" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="52" ht="15" hidden="0" customHeight="1">
       <x:c r="A52" s="7" t="n">
@@ -1104,6 +1289,9 @@
         <x:v>0.589</x:v>
       </x:c>
       <x:c r="E52" s="2" t="str"/>
+      <x:c r="F52" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="53" ht="15" hidden="0" customHeight="1">
       <x:c r="A53" s="7" t="n">
@@ -1119,6 +1307,9 @@
         <x:v>0.524</x:v>
       </x:c>
       <x:c r="E53" s="2" t="str"/>
+      <x:c r="F53" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="54" ht="15" hidden="0" customHeight="1">
       <x:c r="A54" s="7" t="n">
@@ -1134,6 +1325,9 @@
         <x:v>0.459</x:v>
       </x:c>
       <x:c r="E54" s="2" t="str"/>
+      <x:c r="F54" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="55" ht="15" hidden="0" customHeight="1">
       <x:c r="A55" s="7" t="n">
@@ -1151,6 +1345,9 @@
       <x:c r="E55" s="2" t="str">
         <x:v>wave.1301.announcement</x:v>
       </x:c>
+      <x:c r="F55" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="56" ht="15" hidden="0" customHeight="1">
       <x:c r="A56" s="7" t="n">
@@ -1166,6 +1363,9 @@
         <x:v>0.583</x:v>
       </x:c>
       <x:c r="E56" s="2" t="str"/>
+      <x:c r="F56" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="57" ht="15" hidden="0" customHeight="1">
       <x:c r="A57" s="7" t="n">
@@ -1181,6 +1381,9 @@
         <x:v>0.518</x:v>
       </x:c>
       <x:c r="E57" s="2" t="str"/>
+      <x:c r="F57" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="58" ht="15" hidden="0" customHeight="1">
       <x:c r="A58" s="7" t="n">
@@ -1196,6 +1399,9 @@
         <x:v>0.453</x:v>
       </x:c>
       <x:c r="E58" s="2" t="str"/>
+      <x:c r="F58" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="59" ht="15" hidden="0" customHeight="1">
       <x:c r="A59" s="7" t="n">
@@ -1213,6 +1419,9 @@
       <x:c r="E59" s="2" t="str">
         <x:v>wave.1401.announcement</x:v>
       </x:c>
+      <x:c r="F59" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="60" ht="15" hidden="0" customHeight="1">
       <x:c r="A60" s="7" t="n">
@@ -1228,6 +1437,9 @@
         <x:v>0.577</x:v>
       </x:c>
       <x:c r="E60" s="2" t="str"/>
+      <x:c r="F60" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="61" ht="15" hidden="0" customHeight="1">
       <x:c r="A61" s="7" t="n">
@@ -1243,6 +1455,9 @@
         <x:v>0.512</x:v>
       </x:c>
       <x:c r="E61" s="2" t="str"/>
+      <x:c r="F61" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="62" ht="15" hidden="0" customHeight="1">
       <x:c r="A62" s="7" t="n">
@@ -1258,6 +1473,9 @@
         <x:v>0.447</x:v>
       </x:c>
       <x:c r="E62" s="2" t="str"/>
+      <x:c r="F62" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="63" ht="15" hidden="0" customHeight="1">
       <x:c r="A63" s="7" t="n">
@@ -1275,6 +1493,9 @@
       <x:c r="E63" s="2" t="str">
         <x:v>wave.1501.announcement</x:v>
       </x:c>
+      <x:c r="F63" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="64" ht="15" hidden="0" customHeight="1">
       <x:c r="A64" s="7" t="n">
@@ -1290,6 +1511,9 @@
         <x:v>0.571</x:v>
       </x:c>
       <x:c r="E64" s="2" t="str"/>
+      <x:c r="F64" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="65" ht="15" hidden="0" customHeight="1">
       <x:c r="A65" s="7" t="n">
@@ -1305,6 +1529,9 @@
         <x:v>0.506</x:v>
       </x:c>
       <x:c r="E65" s="2" t="str"/>
+      <x:c r="F65" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="66" ht="15" hidden="0" customHeight="1">
       <x:c r="A66" s="7" t="n">
@@ -1320,6 +1547,9 @@
         <x:v>0.441</x:v>
       </x:c>
       <x:c r="E66" s="2" t="str"/>
+      <x:c r="F66" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="67" ht="15" hidden="0" customHeight="1">
       <x:c r="A67" s="7" t="n">
@@ -1337,6 +1567,9 @@
       <x:c r="E67" s="2" t="str">
         <x:v>wave.1505.announcement</x:v>
       </x:c>
+      <x:c r="F67" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="68" ht="15" hidden="0" customHeight="1">
       <x:c r="A68" s="7" t="n">
@@ -1354,6 +1587,9 @@
       <x:c r="E68" s="2" t="str">
         <x:v>wave.1601.announcement</x:v>
       </x:c>
+      <x:c r="F68" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
     </x:row>
     <x:row r="69" ht="15" hidden="0" customHeight="1">
       <x:c r="A69" s="7" t="n">
@@ -1369,6 +1605,9 @@
         <x:v>0.565</x:v>
       </x:c>
       <x:c r="E69" s="2" t="str"/>
+      <x:c r="F69" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="70" ht="15" hidden="0" customHeight="1">
       <x:c r="A70" s="7" t="n">
@@ -1384,6 +1623,9 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="E70" s="2" t="str"/>
+      <x:c r="F70" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="71" ht="15" hidden="0" customHeight="1">
       <x:c r="A71" s="7" t="n">
@@ -1399,6 +1641,9 @@
         <x:v>0.435</x:v>
       </x:c>
       <x:c r="E71" s="2" t="str"/>
+      <x:c r="F71" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="72" ht="15" hidden="0" customHeight="1">
       <x:c r="A72" s="7" t="n">
@@ -1416,6 +1661,9 @@
       <x:c r="E72" s="2" t="str">
         <x:v>wave.1701.announcement</x:v>
       </x:c>
+      <x:c r="F72" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
     </x:row>
     <x:row r="73" ht="15" hidden="0" customHeight="1">
       <x:c r="A73" s="7" t="n">
@@ -1431,6 +1679,9 @@
         <x:v>0.559</x:v>
       </x:c>
       <x:c r="E73" s="2" t="str"/>
+      <x:c r="F73" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="74" ht="15" hidden="0" customHeight="1">
       <x:c r="A74" s="7" t="n">
@@ -1446,6 +1697,9 @@
         <x:v>0.494</x:v>
       </x:c>
       <x:c r="E74" s="2" t="str"/>
+      <x:c r="F74" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="75" ht="15" hidden="0" customHeight="1">
       <x:c r="A75" s="7" t="n">
@@ -1461,6 +1715,9 @@
         <x:v>0.429</x:v>
       </x:c>
       <x:c r="E75" s="2" t="str"/>
+      <x:c r="F75" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="76" ht="15" hidden="0" customHeight="1">
       <x:c r="A76" s="7" t="n">
@@ -1478,6 +1735,9 @@
       <x:c r="E76" s="2" t="str">
         <x:v>wave.1801.announcement</x:v>
       </x:c>
+      <x:c r="F76" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="77" ht="15" hidden="0" customHeight="1">
       <x:c r="A77" s="7" t="n">
@@ -1493,6 +1753,9 @@
         <x:v>0.553</x:v>
       </x:c>
       <x:c r="E77" s="2" t="str"/>
+      <x:c r="F77" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="78" ht="15" hidden="0" customHeight="1">
       <x:c r="A78" s="7" t="n">
@@ -1508,6 +1771,9 @@
         <x:v>0.488</x:v>
       </x:c>
       <x:c r="E78" s="2" t="str"/>
+      <x:c r="F78" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="79" ht="15" hidden="0" customHeight="1">
       <x:c r="A79" s="7" t="n">
@@ -1523,6 +1789,9 @@
         <x:v>0.423</x:v>
       </x:c>
       <x:c r="E79" s="2" t="str"/>
+      <x:c r="F79" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="80" ht="15" hidden="0" customHeight="1">
       <x:c r="A80" s="7" t="n">
@@ -1540,6 +1809,9 @@
       <x:c r="E80" s="2" t="str">
         <x:v>wave.1901.announcement</x:v>
       </x:c>
+      <x:c r="F80" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="81" ht="15" hidden="0" customHeight="1">
       <x:c r="A81" s="7" t="n">
@@ -1555,6 +1827,9 @@
         <x:v>0.547</x:v>
       </x:c>
       <x:c r="E81" s="2" t="str"/>
+      <x:c r="F81" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="82" ht="15" hidden="0" customHeight="1">
       <x:c r="A82" s="7" t="n">
@@ -1570,6 +1845,9 @@
         <x:v>0.482</x:v>
       </x:c>
       <x:c r="E82" s="2" t="str"/>
+      <x:c r="F82" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="83" ht="15" hidden="0" customHeight="1">
       <x:c r="A83" s="7" t="n">
@@ -1585,6 +1863,9 @@
         <x:v>0.417</x:v>
       </x:c>
       <x:c r="E83" s="2" t="str"/>
+      <x:c r="F83" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="84" ht="15" hidden="0" customHeight="1">
       <x:c r="A84" s="7" t="n">
@@ -1602,6 +1883,9 @@
       <x:c r="E84" s="2" t="str">
         <x:v>wave.2001.announcement</x:v>
       </x:c>
+      <x:c r="F84" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="85" ht="15" hidden="0" customHeight="1">
       <x:c r="A85" s="7" t="n">
@@ -1617,6 +1901,9 @@
         <x:v>0.541</x:v>
       </x:c>
       <x:c r="E85" s="2" t="str"/>
+      <x:c r="F85" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="86" ht="15" hidden="0" customHeight="1">
       <x:c r="A86" s="7" t="n">
@@ -1632,6 +1919,9 @@
         <x:v>0.476</x:v>
       </x:c>
       <x:c r="E86" s="2" t="str"/>
+      <x:c r="F86" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="87" ht="15" hidden="0" customHeight="1">
       <x:c r="A87" s="7" t="n">
@@ -1647,6 +1937,9 @@
         <x:v>0.411</x:v>
       </x:c>
       <x:c r="E87" s="2" t="str"/>
+      <x:c r="F87" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="88" ht="15" hidden="0" customHeight="1">
       <x:c r="A88" s="7" t="n">
@@ -1664,6 +1957,415 @@
       <x:c r="E88" s="2" t="str">
         <x:v>wave.2005.announcement</x:v>
       </x:c>
+      <x:c r="F88" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" t="n">
+        <x:v>2006</x:v>
+      </x:c>
+      <x:c r="B89" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C89" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D89" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="E89" t="str"/>
+      <x:c r="F89" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" t="n">
+        <x:v>2007</x:v>
+      </x:c>
+      <x:c r="B90" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C90" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D90" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="E90" t="str"/>
+      <x:c r="F90" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" t="n">
+        <x:v>2008</x:v>
+      </x:c>
+      <x:c r="B91" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C91" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D91" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="E91" t="str"/>
+      <x:c r="F91" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" t="n">
+        <x:v>2009</x:v>
+      </x:c>
+      <x:c r="B92" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C92" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D92" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="E92" t="str"/>
+      <x:c r="F92" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" t="n">
+        <x:v>2010</x:v>
+      </x:c>
+      <x:c r="B93" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C93" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D93" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="E93" t="str"/>
+      <x:c r="F93" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" t="n">
+        <x:v>2011</x:v>
+      </x:c>
+      <x:c r="B94" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C94" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D94" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="E94" t="str"/>
+      <x:c r="F94" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" t="n">
+        <x:v>2012</x:v>
+      </x:c>
+      <x:c r="B95" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C95" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D95" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="E95" t="str"/>
+      <x:c r="F95" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" t="n">
+        <x:v>2013</x:v>
+      </x:c>
+      <x:c r="B96" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C96" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D96" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="E96" t="str"/>
+      <x:c r="F96" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" t="n">
+        <x:v>2014</x:v>
+      </x:c>
+      <x:c r="B97" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C97" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D97" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="E97" t="str"/>
+      <x:c r="F97" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" t="n">
+        <x:v>2015</x:v>
+      </x:c>
+      <x:c r="B98" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C98" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D98" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="E98" t="str"/>
+      <x:c r="F98" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" t="n">
+        <x:v>2016</x:v>
+      </x:c>
+      <x:c r="B99" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C99" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D99" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="E99" t="str"/>
+      <x:c r="F99" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" t="n">
+        <x:v>2017</x:v>
+      </x:c>
+      <x:c r="B100" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C100" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D100" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="E100" t="str"/>
+      <x:c r="F100" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" t="n">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="B101" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C101" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D101" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="E101" t="str"/>
+      <x:c r="F101" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" t="n">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c r="B102" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C102" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D102" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="E102" t="str">
+        <x:v>challenge.bossWave</x:v>
+      </x:c>
+      <x:c r="F102" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" t="n">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c r="B103" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C103" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D103" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="E103" t="str"/>
+      <x:c r="F103" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" t="n">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="B104" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C104" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D104" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="E104" t="str"/>
+      <x:c r="F104" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" t="n">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="B105" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C105" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D105" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="E105" t="str"/>
+      <x:c r="F105" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106" t="n">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c r="B106" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C106" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D106" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="E106" t="str"/>
+      <x:c r="F106" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107">
+      <x:c r="A107" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="B107" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C107" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D107" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="E107" t="str"/>
+      <x:c r="F107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108">
+      <x:c r="A108" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="B108" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C108" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D108" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="E108" t="str"/>
+      <x:c r="F108" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109">
+      <x:c r="A109" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="B109" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C109" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D109" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="E109" t="str">
+        <x:v>challenge.bossWave</x:v>
+      </x:c>
+      <x:c r="F109" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110">
+      <x:c r="A110"/>
+      <x:c r="B110"/>
+      <x:c r="C110"/>
+      <x:c r="D110"/>
+      <x:c r="E110"/>
+      <x:c r="F110"/>
+    </x:row>
+    <x:row r="111">
+      <x:c r="A111"/>
+      <x:c r="B111"/>
+      <x:c r="C111"/>
+      <x:c r="D111"/>
+      <x:c r="E111"/>
+      <x:c r="F111"/>
+    </x:row>
+    <x:row r="112">
+      <x:c r="A112"/>
+      <x:c r="B112"/>
+      <x:c r="C112"/>
+      <x:c r="D112"/>
+      <x:c r="E112"/>
+      <x:c r="F112"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/design/tables/Wave.xlsx
+++ b/design/tables/Wave.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wave" sheetId="1" r:id="R94d17e4e2a0c4bff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wave" sheetId="1" r:id="R03164f2be7f44e3c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -389,6 +389,9 @@
       <x:c r="F1" s="12" t="str">
         <x:v>仅影响本波怪物血量，基础移速不随关卡/波次改变</x:v>
       </x:c>
+      <x:c r="G1" t="str">
+        <x:v>挑战首领生命倍率</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="26" customHeight="1">
       <x:c r="A2" s="3" t="str">
@@ -409,6 +412,9 @@
       <x:c r="F2" s="12" t="str">
         <x:v>client</x:v>
       </x:c>
+      <x:c r="G2" t="str">
+        <x:v>client</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="26" customHeight="1">
       <x:c r="A3" s="3" t="str">
@@ -429,6 +435,9 @@
       <x:c r="F3" s="12" t="str">
         <x:v>float</x:v>
       </x:c>
+      <x:c r="G3" t="str">
+        <x:v>float</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="40" customHeight="1">
       <x:c r="A4" s="6" t="str">
@@ -449,6 +458,9 @@
       <x:c r="F4" s="12" t="str">
         <x:v>本波血量倍率</x:v>
       </x:c>
+      <x:c r="G4" t="str">
+        <x:v>首领生命倍率</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="30" customHeight="1">
       <x:c r="A5" s="5" t="str">
@@ -469,6 +481,9 @@
       <x:c r="F5" s="14" t="str">
         <x:v>healthScale</x:v>
       </x:c>
+      <x:c r="G5" t="str">
+        <x:v>bossHealthScale</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="48" hidden="0" customHeight="1">
       <x:c r="A6" s="23" t="n">
@@ -487,6 +502,9 @@
       <x:c r="F6" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G6" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="48" hidden="0" customHeight="1">
       <x:c r="A7" s="23" t="n">
@@ -505,6 +523,9 @@
       <x:c r="F7" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G7" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="48" hidden="0" customHeight="1">
       <x:c r="A8" s="23" t="n">
@@ -523,6 +544,9 @@
       <x:c r="F8" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G8" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="48" hidden="0" customHeight="1">
       <x:c r="A9" s="23" t="n">
@@ -543,6 +567,9 @@
       <x:c r="F9" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G9" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="48" hidden="0" customHeight="1">
       <x:c r="A10" s="23" t="n">
@@ -561,6 +588,9 @@
       <x:c r="F10" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G10" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="48" hidden="0" customHeight="1">
       <x:c r="A11" s="23" t="n">
@@ -579,6 +609,9 @@
       <x:c r="F11" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G11" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="48" hidden="0" customHeight="1">
       <x:c r="A12" s="23" t="n">
@@ -597,6 +630,9 @@
       <x:c r="F12" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G12" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="48" hidden="0" customHeight="1">
       <x:c r="A13" s="23" t="n">
@@ -617,6 +653,9 @@
       <x:c r="F13" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G13" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="48" hidden="0" customHeight="1">
       <x:c r="A14" s="23" t="n">
@@ -635,6 +674,9 @@
       <x:c r="F14" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G14" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" ht="48" hidden="0" customHeight="1">
       <x:c r="A15" s="23" t="n">
@@ -653,6 +695,9 @@
       <x:c r="F15" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G15" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="16" ht="48" hidden="0" customHeight="1">
       <x:c r="A16" s="23" t="n">
@@ -671,6 +716,9 @@
       <x:c r="F16" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G16" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" ht="48" hidden="0" customHeight="1">
       <x:c r="A17" s="23" t="n">
@@ -691,6 +739,9 @@
       <x:c r="F17" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G17" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" ht="48" hidden="0" customHeight="1">
       <x:c r="A18" s="23" t="n">
@@ -709,6 +760,9 @@
       <x:c r="F18" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G18" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" ht="48" hidden="0" customHeight="1">
       <x:c r="A19" s="23" t="n">
@@ -727,6 +781,9 @@
       <x:c r="F19" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G19" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" ht="48" hidden="0" customHeight="1">
       <x:c r="A20" s="23" t="n">
@@ -745,6 +802,9 @@
       <x:c r="F20" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G20" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" ht="48" hidden="0" customHeight="1">
       <x:c r="A21" s="23" t="n">
@@ -765,6 +825,9 @@
       <x:c r="F21" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G21" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" ht="48" hidden="0" customHeight="1">
       <x:c r="A22" s="23" t="n">
@@ -783,6 +846,9 @@
       <x:c r="F22" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G22" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" ht="48" hidden="0" customHeight="1">
       <x:c r="A23" s="23" t="n">
@@ -801,6 +867,9 @@
       <x:c r="F23" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G23" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="24" ht="48" hidden="0" customHeight="1">
       <x:c r="A24" s="23" t="n">
@@ -819,6 +888,9 @@
       <x:c r="F24" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G24" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="25" ht="48" hidden="0" customHeight="1">
       <x:c r="A25" s="23" t="n">
@@ -839,6 +911,9 @@
       <x:c r="F25" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G25" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="26" ht="48" hidden="0" customHeight="1">
       <x:c r="A26" s="23" t="n">
@@ -857,6 +932,9 @@
       <x:c r="F26" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G26" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="27" ht="48" hidden="0" customHeight="1">
       <x:c r="A27" s="23" t="n">
@@ -875,6 +953,9 @@
       <x:c r="F27" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G27" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="28" ht="48" hidden="0" customHeight="1">
       <x:c r="A28" s="23" t="n">
@@ -893,6 +974,9 @@
       <x:c r="F28" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G28" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="29" ht="48" hidden="0" customHeight="1">
       <x:c r="A29" s="23" t="n">
@@ -913,6 +997,9 @@
       <x:c r="F29" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G29" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="30" ht="48" hidden="0" customHeight="1">
       <x:c r="A30" s="23" t="n">
@@ -931,6 +1018,9 @@
       <x:c r="F30" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G30" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="31" ht="48" hidden="0" customHeight="1">
       <x:c r="A31" s="23" t="n">
@@ -949,6 +1039,9 @@
       <x:c r="F31" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G31" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="32" ht="48" hidden="0" customHeight="1">
       <x:c r="A32" s="23" t="n">
@@ -967,6 +1060,9 @@
       <x:c r="F32" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G32" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="33" ht="48" hidden="0" customHeight="1">
       <x:c r="A33" s="23" t="n">
@@ -987,6 +1083,9 @@
       <x:c r="F33" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G33" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="34" ht="48" hidden="0" customHeight="1">
       <x:c r="A34" s="23" t="n">
@@ -1007,6 +1106,9 @@
       <x:c r="F34" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G34" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="35" ht="48" hidden="0" customHeight="1">
       <x:c r="A35" s="23" t="n">
@@ -1025,6 +1127,9 @@
       <x:c r="F35" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G35" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="36" ht="48" hidden="0" customHeight="1">
       <x:c r="A36" s="23" t="n">
@@ -1045,6 +1150,9 @@
       <x:c r="F36" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G36" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="37" ht="48" hidden="0" customHeight="1">
       <x:c r="A37" s="23" t="n">
@@ -1065,6 +1173,9 @@
       <x:c r="F37" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G37" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="38" ht="48" hidden="0" customHeight="1">
       <x:c r="A38" s="23" t="n">
@@ -1083,6 +1194,9 @@
       <x:c r="F38" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G38" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="39" ht="48" hidden="0" customHeight="1">
       <x:c r="A39" s="23" t="n">
@@ -1101,6 +1215,9 @@
       <x:c r="F39" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G39" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="40" ht="48" hidden="0" customHeight="1">
       <x:c r="A40" s="23" t="n">
@@ -1119,6 +1236,9 @@
       <x:c r="F40" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G40" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="41" ht="48" hidden="0" customHeight="1">
       <x:c r="A41" s="23" t="n">
@@ -1139,6 +1259,9 @@
       <x:c r="F41" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G41" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="42" ht="48" hidden="0" customHeight="1">
       <x:c r="A42" s="23" t="n">
@@ -1157,6 +1280,9 @@
       <x:c r="F42" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G42" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="43" ht="48" hidden="0" customHeight="1">
       <x:c r="A43" s="23" t="n">
@@ -1175,6 +1301,9 @@
       <x:c r="F43" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G43" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="44" ht="48" hidden="0" customHeight="1">
       <x:c r="A44" s="23" t="n">
@@ -1193,6 +1322,9 @@
       <x:c r="F44" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G44" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="45" ht="48" hidden="0" customHeight="1">
       <x:c r="A45" s="23" t="n">
@@ -1211,6 +1343,9 @@
       <x:c r="F45" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G45" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="46" ht="48" hidden="0" customHeight="1">
       <x:c r="A46" s="23" t="n">
@@ -1231,6 +1366,9 @@
       <x:c r="F46" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G46" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="47" ht="48" hidden="0" customHeight="1">
       <x:c r="A47" s="23" t="n">
@@ -1251,6 +1389,9 @@
       <x:c r="F47" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G47" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="48" ht="48" hidden="0" customHeight="1">
       <x:c r="A48" s="23" t="n">
@@ -1269,6 +1410,9 @@
       <x:c r="F48" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G48" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="49" ht="48" hidden="0" customHeight="1">
       <x:c r="A49" s="23" t="n">
@@ -1287,6 +1431,9 @@
       <x:c r="F49" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G49" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="50" ht="48" hidden="0" customHeight="1">
       <x:c r="A50" s="23" t="n">
@@ -1305,6 +1452,9 @@
       <x:c r="F50" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G50" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="51" ht="48" hidden="0" customHeight="1">
       <x:c r="A51" s="23" t="n">
@@ -1325,6 +1475,9 @@
       <x:c r="F51" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G51" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="52" ht="48" hidden="0" customHeight="1">
       <x:c r="A52" s="23" t="n">
@@ -1343,6 +1496,9 @@
       <x:c r="F52" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G52" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="53" ht="48" hidden="0" customHeight="1">
       <x:c r="A53" s="23" t="n">
@@ -1361,6 +1517,9 @@
       <x:c r="F53" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G53" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="54" ht="48" hidden="0" customHeight="1">
       <x:c r="A54" s="23" t="n">
@@ -1379,6 +1538,9 @@
       <x:c r="F54" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G54" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="55" ht="48" hidden="0" customHeight="1">
       <x:c r="A55" s="23" t="n">
@@ -1399,6 +1561,9 @@
       <x:c r="F55" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G55" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="56" ht="48" hidden="0" customHeight="1">
       <x:c r="A56" s="23" t="n">
@@ -1417,6 +1582,9 @@
       <x:c r="F56" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G56" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="57" ht="48" hidden="0" customHeight="1">
       <x:c r="A57" s="23" t="n">
@@ -1435,6 +1603,9 @@
       <x:c r="F57" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G57" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="58" ht="48" hidden="0" customHeight="1">
       <x:c r="A58" s="23" t="n">
@@ -1453,6 +1624,9 @@
       <x:c r="F58" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G58" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="59" ht="48" hidden="0" customHeight="1">
       <x:c r="A59" s="23" t="n">
@@ -1473,6 +1647,9 @@
       <x:c r="F59" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G59" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="60" ht="48" hidden="0" customHeight="1">
       <x:c r="A60" s="23" t="n">
@@ -1491,6 +1668,9 @@
       <x:c r="F60" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G60" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="61" ht="48" hidden="0" customHeight="1">
       <x:c r="A61" s="23" t="n">
@@ -1509,6 +1689,9 @@
       <x:c r="F61" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G61" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="62" ht="48" hidden="0" customHeight="1">
       <x:c r="A62" s="23" t="n">
@@ -1527,6 +1710,9 @@
       <x:c r="F62" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G62" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="63" ht="48" hidden="0" customHeight="1">
       <x:c r="A63" s="23" t="n">
@@ -1547,6 +1733,9 @@
       <x:c r="F63" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G63" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="64" ht="48" hidden="0" customHeight="1">
       <x:c r="A64" s="23" t="n">
@@ -1565,6 +1754,9 @@
       <x:c r="F64" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G64" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="65" ht="48" hidden="0" customHeight="1">
       <x:c r="A65" s="23" t="n">
@@ -1585,6 +1777,9 @@
       <x:c r="F65" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G65" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="66" ht="48" hidden="0" customHeight="1">
       <x:c r="A66" s="23" t="n">
@@ -1603,6 +1798,9 @@
       <x:c r="F66" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G66" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="67" ht="48" hidden="0" customHeight="1">
       <x:c r="A67" s="23" t="n">
@@ -1623,6 +1821,9 @@
       <x:c r="F67" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G67" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="68" ht="48" hidden="0" customHeight="1">
       <x:c r="A68" s="23" t="n">
@@ -1643,6 +1844,9 @@
       <x:c r="F68" s="26" t="n">
         <x:v>0.8</x:v>
       </x:c>
+      <x:c r="G68" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="69" ht="48" hidden="0" customHeight="1">
       <x:c r="A69" s="23" t="n">
@@ -1661,6 +1865,9 @@
       <x:c r="F69" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G69" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="70" ht="48" hidden="0" customHeight="1">
       <x:c r="A70" s="23" t="n">
@@ -1679,6 +1886,9 @@
       <x:c r="F70" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G70" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="71" ht="48" hidden="0" customHeight="1">
       <x:c r="A71" s="23" t="n">
@@ -1697,6 +1907,9 @@
       <x:c r="F71" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G71" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="72" ht="48" hidden="0" customHeight="1">
       <x:c r="A72" s="23" t="n">
@@ -1717,6 +1930,9 @@
       <x:c r="F72" s="26" t="n">
         <x:v>0.8</x:v>
       </x:c>
+      <x:c r="G72" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="73" ht="48" hidden="0" customHeight="1">
       <x:c r="A73" s="23" t="n">
@@ -1735,6 +1951,9 @@
       <x:c r="F73" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G73" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="74" ht="48" hidden="0" customHeight="1">
       <x:c r="A74" s="23" t="n">
@@ -1753,6 +1972,9 @@
       <x:c r="F74" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G74" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="75" ht="48" hidden="0" customHeight="1">
       <x:c r="A75" s="23" t="n">
@@ -1771,6 +1993,9 @@
       <x:c r="F75" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G75" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="76" ht="48" hidden="0" customHeight="1">
       <x:c r="A76" s="23" t="n">
@@ -1791,6 +2016,9 @@
       <x:c r="F76" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G76" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="77" ht="48" hidden="0" customHeight="1">
       <x:c r="A77" s="23" t="n">
@@ -1809,6 +2037,9 @@
       <x:c r="F77" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G77" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="78" ht="48" hidden="0" customHeight="1">
       <x:c r="A78" s="23" t="n">
@@ -1827,6 +2058,9 @@
       <x:c r="F78" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G78" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="79" ht="48" hidden="0" customHeight="1">
       <x:c r="A79" s="23" t="n">
@@ -1845,6 +2079,9 @@
       <x:c r="F79" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G79" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="80" ht="48" hidden="0" customHeight="1">
       <x:c r="A80" s="23" t="n">
@@ -1865,6 +2102,9 @@
       <x:c r="F80" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G80" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="81" ht="48" hidden="0" customHeight="1">
       <x:c r="A81" s="23" t="n">
@@ -1883,6 +2123,9 @@
       <x:c r="F81" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G81" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="82" ht="48" hidden="0" customHeight="1">
       <x:c r="A82" s="23" t="n">
@@ -1901,6 +2144,9 @@
       <x:c r="F82" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G82" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="83" ht="48" hidden="0" customHeight="1">
       <x:c r="A83" s="23" t="n">
@@ -1919,6 +2165,9 @@
       <x:c r="F83" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G83" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="84" ht="48" hidden="0" customHeight="1">
       <x:c r="A84" s="23" t="n">
@@ -1939,6 +2188,9 @@
       <x:c r="F84" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G84" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="85" ht="48" hidden="0" customHeight="1">
       <x:c r="A85" s="23" t="n">
@@ -1959,6 +2211,9 @@
       <x:c r="F85" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G85" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="86" ht="48" hidden="0" customHeight="1">
       <x:c r="A86" s="23" t="n">
@@ -1979,6 +2234,9 @@
       <x:c r="F86" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G86" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="87" ht="48" hidden="0" customHeight="1">
       <x:c r="A87" s="23" t="n">
@@ -1997,6 +2255,9 @@
       <x:c r="F87" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G87" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="88" ht="48" hidden="0" customHeight="1">
       <x:c r="A88" s="23" t="n">
@@ -2017,10 +2278,13 @@
       <x:c r="F88" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G88" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="89" ht="48" customHeight="1">
       <x:c r="A89" s="26" t="n">
-        <x:v>2006</x:v>
+        <x:v>2101</x:v>
       </x:c>
       <x:c r="B89" s="26" t="n">
         <x:v>21</x:v>
@@ -2029,16 +2293,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D89" s="26" t="n">
-        <x:v>0.3</x:v>
+        <x:v>0.95</x:v>
       </x:c>
       <x:c r="E89" s="26" t="str"/>
       <x:c r="F89" s="26" t="n">
-        <x:v>0.6</x:v>
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="G89" t="n">
+        <x:v>1.8</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="48" customHeight="1">
       <x:c r="A90" s="26" t="n">
-        <x:v>2007</x:v>
+        <x:v>2102</x:v>
       </x:c>
       <x:c r="B90" s="26" t="n">
         <x:v>21</x:v>
@@ -2047,16 +2314,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D90" s="26" t="n">
-        <x:v>0.3</x:v>
+        <x:v>0.9</x:v>
       </x:c>
       <x:c r="E90" s="26" t="str"/>
       <x:c r="F90" s="26" t="n">
-        <x:v>0.6</x:v>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G90" t="n">
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="48" customHeight="1">
       <x:c r="A91" s="26" t="n">
-        <x:v>2008</x:v>
+        <x:v>2103</x:v>
       </x:c>
       <x:c r="B91" s="26" t="n">
         <x:v>21</x:v>
@@ -2065,16 +2335,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D91" s="26" t="n">
-        <x:v>0.3</x:v>
+        <x:v>0.85</x:v>
       </x:c>
       <x:c r="E91" s="26" t="str"/>
       <x:c r="F91" s="26" t="n">
-        <x:v>0.6</x:v>
+        <x:v>2.3</x:v>
+      </x:c>
+      <x:c r="G91" t="n">
+        <x:v>2.3</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="48" customHeight="1">
       <x:c r="A92" s="26" t="n">
-        <x:v>2009</x:v>
+        <x:v>2104</x:v>
       </x:c>
       <x:c r="B92" s="26" t="n">
         <x:v>21</x:v>
@@ -2083,16 +2356,19 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D92" s="26" t="n">
-        <x:v>0.3</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="E92" s="26" t="str"/>
       <x:c r="F92" s="26" t="n">
-        <x:v>0.8</x:v>
+        <x:v>2.6</x:v>
+      </x:c>
+      <x:c r="G92" t="n">
+        <x:v>2.6</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="48" customHeight="1">
       <x:c r="A93" s="26" t="n">
-        <x:v>2010</x:v>
+        <x:v>2105</x:v>
       </x:c>
       <x:c r="B93" s="26" t="n">
         <x:v>21</x:v>
@@ -2101,16 +2377,21 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D93" s="26" t="n">
-        <x:v>0.3</x:v>
-      </x:c>
-      <x:c r="E93" s="26" t="str"/>
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="E93" s="26" t="str">
+        <x:v>challenge.bossWave</x:v>
+      </x:c>
       <x:c r="F93" s="26" t="n">
-        <x:v>0.8</x:v>
+        <x:v>2.9</x:v>
+      </x:c>
+      <x:c r="G93" t="n">
+        <x:v>2.5</x:v>
       </x:c>
     </x:row>
     <x:row r="94" ht="48" customHeight="1">
       <x:c r="A94" s="26" t="n">
-        <x:v>2011</x:v>
+        <x:v>2106</x:v>
       </x:c>
       <x:c r="B94" s="26" t="n">
         <x:v>21</x:v>
@@ -2119,16 +2400,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="D94" s="26" t="n">
-        <x:v>0.3</x:v>
+        <x:v>0.75</x:v>
       </x:c>
       <x:c r="E94" s="26" t="str"/>
       <x:c r="F94" s="26" t="n">
-        <x:v>0.8</x:v>
+        <x:v>3.3</x:v>
+      </x:c>
+      <x:c r="G94" t="n">
+        <x:v>3.3</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="48" customHeight="1">
       <x:c r="A95" s="26" t="n">
-        <x:v>2012</x:v>
+        <x:v>2107</x:v>
       </x:c>
       <x:c r="B95" s="26" t="n">
         <x:v>21</x:v>
@@ -2137,16 +2421,19 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D95" s="26" t="n">
-        <x:v>0.3</x:v>
+        <x:v>0.7</x:v>
       </x:c>
       <x:c r="E95" s="26" t="str"/>
       <x:c r="F95" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>3.7</x:v>
+      </x:c>
+      <x:c r="G95" t="n">
+        <x:v>3.7</x:v>
       </x:c>
     </x:row>
     <x:row r="96" ht="48" customHeight="1">
       <x:c r="A96" s="26" t="n">
-        <x:v>2013</x:v>
+        <x:v>2108</x:v>
       </x:c>
       <x:c r="B96" s="26" t="n">
         <x:v>21</x:v>
@@ -2155,16 +2442,19 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D96" s="26" t="n">
-        <x:v>0.3</x:v>
+        <x:v>0.65</x:v>
       </x:c>
       <x:c r="E96" s="26" t="str"/>
       <x:c r="F96" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>4.1</x:v>
+      </x:c>
+      <x:c r="G96" t="n">
+        <x:v>4.1</x:v>
       </x:c>
     </x:row>
     <x:row r="97" ht="48" customHeight="1">
       <x:c r="A97" s="26" t="n">
-        <x:v>2014</x:v>
+        <x:v>2109</x:v>
       </x:c>
       <x:c r="B97" s="26" t="n">
         <x:v>21</x:v>
@@ -2173,16 +2463,19 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D97" s="26" t="n">
-        <x:v>0.3</x:v>
+        <x:v>0.7</x:v>
       </x:c>
       <x:c r="E97" s="26" t="str"/>
       <x:c r="F97" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>4.5</x:v>
+      </x:c>
+      <x:c r="G97" t="n">
+        <x:v>4.5</x:v>
       </x:c>
     </x:row>
     <x:row r="98" ht="48" customHeight="1">
       <x:c r="A98" s="26" t="n">
-        <x:v>2015</x:v>
+        <x:v>2110</x:v>
       </x:c>
       <x:c r="B98" s="26" t="n">
         <x:v>21</x:v>
@@ -2191,16 +2484,21 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D98" s="26" t="n">
-        <x:v>0.3</x:v>
-      </x:c>
-      <x:c r="E98" s="26" t="str"/>
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="E98" s="26" t="str">
+        <x:v>challenge.bossWave</x:v>
+      </x:c>
       <x:c r="F98" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G98" t="n">
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="99" ht="48" customHeight="1">
       <x:c r="A99" s="26" t="n">
-        <x:v>2016</x:v>
+        <x:v>2111</x:v>
       </x:c>
       <x:c r="B99" s="26" t="n">
         <x:v>21</x:v>
@@ -2209,16 +2507,19 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D99" s="26" t="n">
-        <x:v>0.3</x:v>
+        <x:v>0.65</x:v>
       </x:c>
       <x:c r="E99" s="26" t="str"/>
       <x:c r="F99" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>5.6</x:v>
+      </x:c>
+      <x:c r="G99" t="n">
+        <x:v>5.6</x:v>
       </x:c>
     </x:row>
     <x:row r="100" ht="48" customHeight="1">
       <x:c r="A100" s="26" t="n">
-        <x:v>2017</x:v>
+        <x:v>2112</x:v>
       </x:c>
       <x:c r="B100" s="26" t="n">
         <x:v>21</x:v>
@@ -2227,16 +2528,19 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D100" s="26" t="n">
-        <x:v>0.3</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="E100" s="26" t="str"/>
       <x:c r="F100" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>6.2</x:v>
+      </x:c>
+      <x:c r="G100" t="n">
+        <x:v>6.2</x:v>
       </x:c>
     </x:row>
     <x:row r="101" ht="48" customHeight="1">
       <x:c r="A101" s="26" t="n">
-        <x:v>2018</x:v>
+        <x:v>2113</x:v>
       </x:c>
       <x:c r="B101" s="26" t="n">
         <x:v>21</x:v>
@@ -2245,16 +2549,19 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="D101" s="26" t="n">
-        <x:v>0.3</x:v>
+        <x:v>0.65</x:v>
       </x:c>
       <x:c r="E101" s="26" t="str"/>
       <x:c r="F101" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>6.9</x:v>
+      </x:c>
+      <x:c r="G101" t="n">
+        <x:v>6.9</x:v>
       </x:c>
     </x:row>
     <x:row r="102" ht="48" customHeight="1">
       <x:c r="A102" s="26" t="n">
-        <x:v>2019</x:v>
+        <x:v>2114</x:v>
       </x:c>
       <x:c r="B102" s="26" t="n">
         <x:v>21</x:v>
@@ -2263,18 +2570,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D102" s="26" t="n">
-        <x:v>0.3</x:v>
-      </x:c>
-      <x:c r="E102" s="26" t="str">
-        <x:v>challenge.bossWave</x:v>
-      </x:c>
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="E102" s="26" t="str"/>
       <x:c r="F102" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>7.6</x:v>
+      </x:c>
+      <x:c r="G102" t="n">
+        <x:v>7.6</x:v>
       </x:c>
     </x:row>
     <x:row r="103" ht="48" customHeight="1">
       <x:c r="A103" s="26" t="n">
-        <x:v>2020</x:v>
+        <x:v>2115</x:v>
       </x:c>
       <x:c r="B103" s="26" t="n">
         <x:v>21</x:v>
@@ -2283,122 +2591,65 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="D103" s="26" t="n">
-        <x:v>0.3</x:v>
-      </x:c>
-      <x:c r="E103" s="26" t="str"/>
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="E103" s="26" t="str">
+        <x:v>challenge.bossWave</x:v>
+      </x:c>
       <x:c r="F103" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>8.5</x:v>
+      </x:c>
+      <x:c r="G103" t="n">
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="104" ht="48" customHeight="1">
-      <x:c r="A104" s="26" t="n">
-        <x:v>2021</x:v>
-      </x:c>
-      <x:c r="B104" s="26" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C104" s="26" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D104" s="26" t="n">
-        <x:v>0.3</x:v>
-      </x:c>
-      <x:c r="E104" s="26" t="str"/>
-      <x:c r="F104" s="26" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="A104" s="26"/>
+      <x:c r="B104" s="26"/>
+      <x:c r="C104" s="26"/>
+      <x:c r="D104" s="26"/>
+      <x:c r="E104" s="26"/>
+      <x:c r="F104" s="26"/>
     </x:row>
     <x:row r="105" ht="48" customHeight="1">
-      <x:c r="A105" s="26" t="n">
-        <x:v>2022</x:v>
-      </x:c>
-      <x:c r="B105" s="26" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C105" s="26" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D105" s="26" t="n">
-        <x:v>0.3</x:v>
-      </x:c>
-      <x:c r="E105" s="26" t="str"/>
-      <x:c r="F105" s="26" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="A105" s="26"/>
+      <x:c r="B105" s="26"/>
+      <x:c r="C105" s="26"/>
+      <x:c r="D105" s="26"/>
+      <x:c r="E105" s="26"/>
+      <x:c r="F105" s="26"/>
     </x:row>
     <x:row r="106" ht="48" customHeight="1">
-      <x:c r="A106" s="26" t="n">
-        <x:v>2023</x:v>
-      </x:c>
-      <x:c r="B106" s="26" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C106" s="26" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D106" s="26" t="n">
-        <x:v>0.3</x:v>
-      </x:c>
-      <x:c r="E106" s="26" t="str"/>
-      <x:c r="F106" s="26" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="A106" s="26"/>
+      <x:c r="B106" s="26"/>
+      <x:c r="C106" s="26"/>
+      <x:c r="D106" s="26"/>
+      <x:c r="E106" s="26"/>
+      <x:c r="F106" s="26"/>
     </x:row>
     <x:row r="107" ht="48" customHeight="1">
-      <x:c r="A107" s="26" t="n">
-        <x:v>2024</x:v>
-      </x:c>
-      <x:c r="B107" s="26" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C107" s="26" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D107" s="26" t="n">
-        <x:v>0.3</x:v>
-      </x:c>
-      <x:c r="E107" s="26" t="str"/>
-      <x:c r="F107" s="26" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="A107" s="26"/>
+      <x:c r="B107" s="26"/>
+      <x:c r="C107" s="26"/>
+      <x:c r="D107" s="26"/>
+      <x:c r="E107" s="26"/>
+      <x:c r="F107" s="26"/>
     </x:row>
     <x:row r="108" ht="48" customHeight="1">
-      <x:c r="A108" s="26" t="n">
-        <x:v>2025</x:v>
-      </x:c>
-      <x:c r="B108" s="26" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C108" s="26" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D108" s="26" t="n">
-        <x:v>0.3</x:v>
-      </x:c>
-      <x:c r="E108" s="26" t="str"/>
-      <x:c r="F108" s="26" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="A108" s="26"/>
+      <x:c r="B108" s="26"/>
+      <x:c r="C108" s="26"/>
+      <x:c r="D108" s="26"/>
+      <x:c r="E108" s="26"/>
+      <x:c r="F108" s="26"/>
     </x:row>
     <x:row r="109" ht="48" customHeight="1">
-      <x:c r="A109" s="26" t="n">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="B109" s="26" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C109" s="26" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D109" s="26" t="n">
-        <x:v>0.3</x:v>
-      </x:c>
-      <x:c r="E109" s="26" t="str">
-        <x:v>challenge.bossWave</x:v>
-      </x:c>
-      <x:c r="F109" s="26" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="A109" s="26"/>
+      <x:c r="B109" s="26"/>
+      <x:c r="C109" s="26"/>
+      <x:c r="D109" s="26"/>
+      <x:c r="E109" s="26"/>
+      <x:c r="F109" s="26"/>
     </x:row>
     <x:row r="110">
       <x:c r="A110"/>

--- a/design/tables/Wave.xlsx
+++ b/design/tables/Wave.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wave" sheetId="1" r:id="R03164f2be7f44e3c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wave" sheetId="1" r:id="R26eca255db9b46ca"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2604,76 +2604,1609 @@
       </x:c>
     </x:row>
     <x:row r="104" ht="48" customHeight="1">
-      <x:c r="A104" s="26"/>
-      <x:c r="B104" s="26"/>
-      <x:c r="C104" s="26"/>
-      <x:c r="D104" s="26"/>
-      <x:c r="E104" s="26"/>
-      <x:c r="F104" s="26"/>
+      <x:c r="A104" s="26" t="n">
+        <x:v>2201</x:v>
+      </x:c>
+      <x:c r="B104" s="26" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C104" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D104" s="26" t="n">
+        <x:v>0.912</x:v>
+      </x:c>
+      <x:c r="E104" s="26" t="str"/>
+      <x:c r="F104" s="26" t="n">
+        <x:v>1.71</x:v>
+      </x:c>
+      <x:c r="G104" t="n">
+        <x:v>1.71</x:v>
+      </x:c>
     </x:row>
     <x:row r="105" ht="48" customHeight="1">
-      <x:c r="A105" s="26"/>
-      <x:c r="B105" s="26"/>
-      <x:c r="C105" s="26"/>
-      <x:c r="D105" s="26"/>
-      <x:c r="E105" s="26"/>
-      <x:c r="F105" s="26"/>
+      <x:c r="A105" s="26" t="n">
+        <x:v>2202</x:v>
+      </x:c>
+      <x:c r="B105" s="26" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C105" s="26" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D105" s="26" t="n">
+        <x:v>0.864</x:v>
+      </x:c>
+      <x:c r="E105" s="26" t="str"/>
+      <x:c r="F105" s="26" t="n">
+        <x:v>1.9</x:v>
+      </x:c>
+      <x:c r="G105" t="n">
+        <x:v>1.9</x:v>
+      </x:c>
     </x:row>
     <x:row r="106" ht="48" customHeight="1">
-      <x:c r="A106" s="26"/>
-      <x:c r="B106" s="26"/>
-      <x:c r="C106" s="26"/>
-      <x:c r="D106" s="26"/>
-      <x:c r="E106" s="26"/>
-      <x:c r="F106" s="26"/>
+      <x:c r="A106" s="26" t="n">
+        <x:v>2203</x:v>
+      </x:c>
+      <x:c r="B106" s="26" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C106" s="26" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D106" s="26" t="n">
+        <x:v>0.816</x:v>
+      </x:c>
+      <x:c r="E106" s="26" t="str"/>
+      <x:c r="F106" s="26" t="n">
+        <x:v>2.185</x:v>
+      </x:c>
+      <x:c r="G106" t="n">
+        <x:v>2.185</x:v>
+      </x:c>
     </x:row>
     <x:row r="107" ht="48" customHeight="1">
-      <x:c r="A107" s="26"/>
-      <x:c r="B107" s="26"/>
-      <x:c r="C107" s="26"/>
-      <x:c r="D107" s="26"/>
-      <x:c r="E107" s="26"/>
-      <x:c r="F107" s="26"/>
+      <x:c r="A107" s="26" t="n">
+        <x:v>2204</x:v>
+      </x:c>
+      <x:c r="B107" s="26" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C107" s="26" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D107" s="26" t="n">
+        <x:v>0.768</x:v>
+      </x:c>
+      <x:c r="E107" s="26" t="str"/>
+      <x:c r="F107" s="26" t="n">
+        <x:v>2.47</x:v>
+      </x:c>
+      <x:c r="G107" t="n">
+        <x:v>2.47</x:v>
+      </x:c>
     </x:row>
     <x:row r="108" ht="48" customHeight="1">
-      <x:c r="A108" s="26"/>
-      <x:c r="B108" s="26"/>
-      <x:c r="C108" s="26"/>
-      <x:c r="D108" s="26"/>
-      <x:c r="E108" s="26"/>
-      <x:c r="F108" s="26"/>
+      <x:c r="A108" s="26" t="n">
+        <x:v>2205</x:v>
+      </x:c>
+      <x:c r="B108" s="26" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C108" s="26" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D108" s="26" t="n">
+        <x:v>0.816</x:v>
+      </x:c>
+      <x:c r="E108" s="26" t="str">
+        <x:v>challenge.bossWave</x:v>
+      </x:c>
+      <x:c r="F108" s="26" t="n">
+        <x:v>2.755</x:v>
+      </x:c>
+      <x:c r="G108" t="n">
+        <x:v>2.375</x:v>
+      </x:c>
     </x:row>
     <x:row r="109" ht="48" customHeight="1">
-      <x:c r="A109" s="26"/>
-      <x:c r="B109" s="26"/>
-      <x:c r="C109" s="26"/>
-      <x:c r="D109" s="26"/>
-      <x:c r="E109" s="26"/>
-      <x:c r="F109" s="26"/>
+      <x:c r="A109" s="26" t="n">
+        <x:v>2206</x:v>
+      </x:c>
+      <x:c r="B109" s="26" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C109" s="26" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D109" s="26" t="n">
+        <x:v>0.72</x:v>
+      </x:c>
+      <x:c r="E109" s="26" t="str"/>
+      <x:c r="F109" s="26" t="n">
+        <x:v>3.135</x:v>
+      </x:c>
+      <x:c r="G109" t="n">
+        <x:v>3.135</x:v>
+      </x:c>
     </x:row>
     <x:row r="110">
-      <x:c r="A110"/>
-      <x:c r="B110"/>
-      <x:c r="C110"/>
-      <x:c r="D110"/>
-      <x:c r="E110"/>
-      <x:c r="F110"/>
+      <x:c r="A110" t="n">
+        <x:v>2207</x:v>
+      </x:c>
+      <x:c r="B110" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C110" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D110" t="n">
+        <x:v>0.672</x:v>
+      </x:c>
+      <x:c r="E110" t="str"/>
+      <x:c r="F110" t="n">
+        <x:v>3.515</x:v>
+      </x:c>
+      <x:c r="G110" t="n">
+        <x:v>3.515</x:v>
+      </x:c>
     </x:row>
     <x:row r="111">
-      <x:c r="A111"/>
-      <x:c r="B111"/>
-      <x:c r="C111"/>
-      <x:c r="D111"/>
-      <x:c r="E111"/>
-      <x:c r="F111"/>
+      <x:c r="A111" t="n">
+        <x:v>2208</x:v>
+      </x:c>
+      <x:c r="B111" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C111" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D111" t="n">
+        <x:v>0.624</x:v>
+      </x:c>
+      <x:c r="E111" t="str"/>
+      <x:c r="F111" t="n">
+        <x:v>3.895</x:v>
+      </x:c>
+      <x:c r="G111" t="n">
+        <x:v>3.895</x:v>
+      </x:c>
     </x:row>
     <x:row r="112">
-      <x:c r="A112"/>
-      <x:c r="B112"/>
-      <x:c r="C112"/>
-      <x:c r="D112"/>
-      <x:c r="E112"/>
-      <x:c r="F112"/>
+      <x:c r="A112" t="n">
+        <x:v>2209</x:v>
+      </x:c>
+      <x:c r="B112" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C112" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D112" t="n">
+        <x:v>0.672</x:v>
+      </x:c>
+      <x:c r="E112" t="str"/>
+      <x:c r="F112" t="n">
+        <x:v>4.275</x:v>
+      </x:c>
+      <x:c r="G112" t="n">
+        <x:v>4.275</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113">
+      <x:c r="A113" t="n">
+        <x:v>2210</x:v>
+      </x:c>
+      <x:c r="B113" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C113" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D113" t="n">
+        <x:v>0.768</x:v>
+      </x:c>
+      <x:c r="E113" t="str">
+        <x:v>challenge.bossWave</x:v>
+      </x:c>
+      <x:c r="F113" t="n">
+        <x:v>4.75</x:v>
+      </x:c>
+      <x:c r="G113" t="n">
+        <x:v>5.7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114">
+      <x:c r="A114" t="n">
+        <x:v>2211</x:v>
+      </x:c>
+      <x:c r="B114" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C114" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D114" t="n">
+        <x:v>0.624</x:v>
+      </x:c>
+      <x:c r="E114" t="str"/>
+      <x:c r="F114" t="n">
+        <x:v>5.32</x:v>
+      </x:c>
+      <x:c r="G114" t="n">
+        <x:v>5.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115">
+      <x:c r="A115" t="n">
+        <x:v>2212</x:v>
+      </x:c>
+      <x:c r="B115" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C115" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D115" t="n">
+        <x:v>0.576</x:v>
+      </x:c>
+      <x:c r="E115" t="str"/>
+      <x:c r="F115" t="n">
+        <x:v>5.89</x:v>
+      </x:c>
+      <x:c r="G115" t="n">
+        <x:v>5.89</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116">
+      <x:c r="A116" t="n">
+        <x:v>2213</x:v>
+      </x:c>
+      <x:c r="B116" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C116" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D116" t="n">
+        <x:v>0.624</x:v>
+      </x:c>
+      <x:c r="E116" t="str"/>
+      <x:c r="F116" t="n">
+        <x:v>6.555</x:v>
+      </x:c>
+      <x:c r="G116" t="n">
+        <x:v>6.555</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117">
+      <x:c r="A117" t="n">
+        <x:v>2214</x:v>
+      </x:c>
+      <x:c r="B117" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C117" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D117" t="n">
+        <x:v>0.528</x:v>
+      </x:c>
+      <x:c r="E117" t="str"/>
+      <x:c r="F117" t="n">
+        <x:v>7.22</x:v>
+      </x:c>
+      <x:c r="G117" t="n">
+        <x:v>7.22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118">
+      <x:c r="A118" t="n">
+        <x:v>2215</x:v>
+      </x:c>
+      <x:c r="B118" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C118" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D118" t="n">
+        <x:v>0.624</x:v>
+      </x:c>
+      <x:c r="E118" t="str">
+        <x:v>challenge.bossWave</x:v>
+      </x:c>
+      <x:c r="F118" t="n">
+        <x:v>8.075</x:v>
+      </x:c>
+      <x:c r="G118" t="n">
+        <x:v>9.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119">
+      <x:c r="A119" t="n">
+        <x:v>2301</x:v>
+      </x:c>
+      <x:c r="B119" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C119" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D119" t="n">
+        <x:v>0.95</x:v>
+      </x:c>
+      <x:c r="E119" t="str"/>
+      <x:c r="F119" t="n">
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="G119" t="n">
+        <x:v>1.8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120">
+      <x:c r="A120" t="n">
+        <x:v>2302</x:v>
+      </x:c>
+      <x:c r="B120" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C120" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D120" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="E120" t="str"/>
+      <x:c r="F120" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G120" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121">
+      <x:c r="A121" t="n">
+        <x:v>2303</x:v>
+      </x:c>
+      <x:c r="B121" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C121" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D121" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="E121" t="str"/>
+      <x:c r="F121" t="n">
+        <x:v>2.3</x:v>
+      </x:c>
+      <x:c r="G121" t="n">
+        <x:v>2.3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122">
+      <x:c r="A122" t="n">
+        <x:v>2304</x:v>
+      </x:c>
+      <x:c r="B122" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C122" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D122" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="E122" t="str"/>
+      <x:c r="F122" t="n">
+        <x:v>2.6</x:v>
+      </x:c>
+      <x:c r="G122" t="n">
+        <x:v>2.6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123">
+      <x:c r="A123" t="n">
+        <x:v>2305</x:v>
+      </x:c>
+      <x:c r="B123" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C123" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D123" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="E123" t="str">
+        <x:v>challenge.bossWave</x:v>
+      </x:c>
+      <x:c r="F123" t="n">
+        <x:v>2.9</x:v>
+      </x:c>
+      <x:c r="G123" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124">
+      <x:c r="A124" t="n">
+        <x:v>2306</x:v>
+      </x:c>
+      <x:c r="B124" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C124" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D124" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="E124" t="str"/>
+      <x:c r="F124" t="n">
+        <x:v>3.3</x:v>
+      </x:c>
+      <x:c r="G124" t="n">
+        <x:v>3.3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125">
+      <x:c r="A125" t="n">
+        <x:v>2307</x:v>
+      </x:c>
+      <x:c r="B125" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C125" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D125" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="E125" t="str"/>
+      <x:c r="F125" t="n">
+        <x:v>3.7</x:v>
+      </x:c>
+      <x:c r="G125" t="n">
+        <x:v>3.7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126">
+      <x:c r="A126" t="n">
+        <x:v>2308</x:v>
+      </x:c>
+      <x:c r="B126" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C126" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D126" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="E126" t="str"/>
+      <x:c r="F126" t="n">
+        <x:v>4.1</x:v>
+      </x:c>
+      <x:c r="G126" t="n">
+        <x:v>4.1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127">
+      <x:c r="A127" t="n">
+        <x:v>2309</x:v>
+      </x:c>
+      <x:c r="B127" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C127" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D127" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="E127" t="str"/>
+      <x:c r="F127" t="n">
+        <x:v>4.5</x:v>
+      </x:c>
+      <x:c r="G127" t="n">
+        <x:v>4.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128">
+      <x:c r="A128" t="n">
+        <x:v>2310</x:v>
+      </x:c>
+      <x:c r="B128" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C128" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D128" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="E128" t="str">
+        <x:v>challenge.bossWave</x:v>
+      </x:c>
+      <x:c r="F128" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G128" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129">
+      <x:c r="A129" t="n">
+        <x:v>2311</x:v>
+      </x:c>
+      <x:c r="B129" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C129" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D129" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="E129" t="str"/>
+      <x:c r="F129" t="n">
+        <x:v>5.6</x:v>
+      </x:c>
+      <x:c r="G129" t="n">
+        <x:v>5.6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130">
+      <x:c r="A130" t="n">
+        <x:v>2312</x:v>
+      </x:c>
+      <x:c r="B130" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C130" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D130" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="E130" t="str"/>
+      <x:c r="F130" t="n">
+        <x:v>6.2</x:v>
+      </x:c>
+      <x:c r="G130" t="n">
+        <x:v>6.2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131">
+      <x:c r="A131" t="n">
+        <x:v>2313</x:v>
+      </x:c>
+      <x:c r="B131" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C131" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D131" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="E131" t="str"/>
+      <x:c r="F131" t="n">
+        <x:v>6.9</x:v>
+      </x:c>
+      <x:c r="G131" t="n">
+        <x:v>6.9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132">
+      <x:c r="A132" t="n">
+        <x:v>2314</x:v>
+      </x:c>
+      <x:c r="B132" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C132" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D132" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="E132" t="str"/>
+      <x:c r="F132" t="n">
+        <x:v>7.6</x:v>
+      </x:c>
+      <x:c r="G132" t="n">
+        <x:v>7.6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133">
+      <x:c r="A133" t="n">
+        <x:v>2315</x:v>
+      </x:c>
+      <x:c r="B133" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C133" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D133" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="E133" t="str">
+        <x:v>challenge.bossWave</x:v>
+      </x:c>
+      <x:c r="F133" t="n">
+        <x:v>8.5</x:v>
+      </x:c>
+      <x:c r="G133" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134">
+      <x:c r="A134" t="n">
+        <x:v>2401</x:v>
+      </x:c>
+      <x:c r="B134" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C134" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D134" t="n">
+        <x:v>0.893</x:v>
+      </x:c>
+      <x:c r="E134" t="str"/>
+      <x:c r="F134" t="n">
+        <x:v>1.836</x:v>
+      </x:c>
+      <x:c r="G134" t="n">
+        <x:v>1.836</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135">
+      <x:c r="A135" t="n">
+        <x:v>2402</x:v>
+      </x:c>
+      <x:c r="B135" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C135" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D135" t="n">
+        <x:v>0.846</x:v>
+      </x:c>
+      <x:c r="E135" t="str"/>
+      <x:c r="F135" t="n">
+        <x:v>2.04</x:v>
+      </x:c>
+      <x:c r="G135" t="n">
+        <x:v>2.04</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136">
+      <x:c r="A136" t="n">
+        <x:v>2403</x:v>
+      </x:c>
+      <x:c r="B136" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C136" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D136" t="n">
+        <x:v>0.799</x:v>
+      </x:c>
+      <x:c r="E136" t="str"/>
+      <x:c r="F136" t="n">
+        <x:v>2.346</x:v>
+      </x:c>
+      <x:c r="G136" t="n">
+        <x:v>2.346</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137">
+      <x:c r="A137" t="n">
+        <x:v>2404</x:v>
+      </x:c>
+      <x:c r="B137" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C137" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D137" t="n">
+        <x:v>0.752</x:v>
+      </x:c>
+      <x:c r="E137" t="str"/>
+      <x:c r="F137" t="n">
+        <x:v>2.652</x:v>
+      </x:c>
+      <x:c r="G137" t="n">
+        <x:v>2.652</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138">
+      <x:c r="A138" t="n">
+        <x:v>2405</x:v>
+      </x:c>
+      <x:c r="B138" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C138" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D138" t="n">
+        <x:v>0.799</x:v>
+      </x:c>
+      <x:c r="E138" t="str">
+        <x:v>challenge.bossWave</x:v>
+      </x:c>
+      <x:c r="F138" t="n">
+        <x:v>2.958</x:v>
+      </x:c>
+      <x:c r="G138" t="n">
+        <x:v>2.55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139">
+      <x:c r="A139" t="n">
+        <x:v>2406</x:v>
+      </x:c>
+      <x:c r="B139" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C139" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D139" t="n">
+        <x:v>0.705</x:v>
+      </x:c>
+      <x:c r="E139" t="str"/>
+      <x:c r="F139" t="n">
+        <x:v>3.366</x:v>
+      </x:c>
+      <x:c r="G139" t="n">
+        <x:v>3.366</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140">
+      <x:c r="A140" t="n">
+        <x:v>2407</x:v>
+      </x:c>
+      <x:c r="B140" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C140" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D140" t="n">
+        <x:v>0.658</x:v>
+      </x:c>
+      <x:c r="E140" t="str"/>
+      <x:c r="F140" t="n">
+        <x:v>3.774</x:v>
+      </x:c>
+      <x:c r="G140" t="n">
+        <x:v>3.774</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141">
+      <x:c r="A141" t="n">
+        <x:v>2408</x:v>
+      </x:c>
+      <x:c r="B141" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C141" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D141" t="n">
+        <x:v>0.611</x:v>
+      </x:c>
+      <x:c r="E141" t="str"/>
+      <x:c r="F141" t="n">
+        <x:v>4.182</x:v>
+      </x:c>
+      <x:c r="G141" t="n">
+        <x:v>4.182</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142">
+      <x:c r="A142" t="n">
+        <x:v>2409</x:v>
+      </x:c>
+      <x:c r="B142" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C142" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D142" t="n">
+        <x:v>0.658</x:v>
+      </x:c>
+      <x:c r="E142" t="str"/>
+      <x:c r="F142" t="n">
+        <x:v>4.59</x:v>
+      </x:c>
+      <x:c r="G142" t="n">
+        <x:v>4.59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143">
+      <x:c r="A143" t="n">
+        <x:v>2410</x:v>
+      </x:c>
+      <x:c r="B143" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C143" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D143" t="n">
+        <x:v>0.752</x:v>
+      </x:c>
+      <x:c r="E143" t="str">
+        <x:v>challenge.bossWave</x:v>
+      </x:c>
+      <x:c r="F143" t="n">
+        <x:v>5.1</x:v>
+      </x:c>
+      <x:c r="G143" t="n">
+        <x:v>6.12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144">
+      <x:c r="A144" t="n">
+        <x:v>2411</x:v>
+      </x:c>
+      <x:c r="B144" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C144" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D144" t="n">
+        <x:v>0.611</x:v>
+      </x:c>
+      <x:c r="E144" t="str"/>
+      <x:c r="F144" t="n">
+        <x:v>5.712</x:v>
+      </x:c>
+      <x:c r="G144" t="n">
+        <x:v>5.712</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145">
+      <x:c r="A145" t="n">
+        <x:v>2412</x:v>
+      </x:c>
+      <x:c r="B145" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C145" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D145" t="n">
+        <x:v>0.564</x:v>
+      </x:c>
+      <x:c r="E145" t="str"/>
+      <x:c r="F145" t="n">
+        <x:v>6.324</x:v>
+      </x:c>
+      <x:c r="G145" t="n">
+        <x:v>6.324</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146">
+      <x:c r="A146" t="n">
+        <x:v>2413</x:v>
+      </x:c>
+      <x:c r="B146" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C146" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D146" t="n">
+        <x:v>0.611</x:v>
+      </x:c>
+      <x:c r="E146" t="str"/>
+      <x:c r="F146" t="n">
+        <x:v>7.038</x:v>
+      </x:c>
+      <x:c r="G146" t="n">
+        <x:v>7.038</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147">
+      <x:c r="A147" t="n">
+        <x:v>2414</x:v>
+      </x:c>
+      <x:c r="B147" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C147" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D147" t="n">
+        <x:v>0.517</x:v>
+      </x:c>
+      <x:c r="E147" t="str"/>
+      <x:c r="F147" t="n">
+        <x:v>7.752</x:v>
+      </x:c>
+      <x:c r="G147" t="n">
+        <x:v>7.752</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148">
+      <x:c r="A148" t="n">
+        <x:v>2415</x:v>
+      </x:c>
+      <x:c r="B148" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C148" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D148" t="n">
+        <x:v>0.611</x:v>
+      </x:c>
+      <x:c r="E148" t="str">
+        <x:v>challenge.bossWave</x:v>
+      </x:c>
+      <x:c r="F148" t="n">
+        <x:v>8.67</x:v>
+      </x:c>
+      <x:c r="G148" t="n">
+        <x:v>10.2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149">
+      <x:c r="A149" t="n">
+        <x:v>2501</x:v>
+      </x:c>
+      <x:c r="B149" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C149" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D149" t="n">
+        <x:v>0.912</x:v>
+      </x:c>
+      <x:c r="E149" t="str"/>
+      <x:c r="F149" t="n">
+        <x:v>1.854</x:v>
+      </x:c>
+      <x:c r="G149" t="n">
+        <x:v>1.854</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150">
+      <x:c r="A150" t="n">
+        <x:v>2502</x:v>
+      </x:c>
+      <x:c r="B150" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C150" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D150" t="n">
+        <x:v>0.864</x:v>
+      </x:c>
+      <x:c r="E150" t="str"/>
+      <x:c r="F150" t="n">
+        <x:v>2.06</x:v>
+      </x:c>
+      <x:c r="G150" t="n">
+        <x:v>2.06</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151">
+      <x:c r="A151" t="n">
+        <x:v>2503</x:v>
+      </x:c>
+      <x:c r="B151" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C151" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D151" t="n">
+        <x:v>0.816</x:v>
+      </x:c>
+      <x:c r="E151" t="str"/>
+      <x:c r="F151" t="n">
+        <x:v>2.369</x:v>
+      </x:c>
+      <x:c r="G151" t="n">
+        <x:v>2.369</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152">
+      <x:c r="A152" t="n">
+        <x:v>2504</x:v>
+      </x:c>
+      <x:c r="B152" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C152" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D152" t="n">
+        <x:v>0.768</x:v>
+      </x:c>
+      <x:c r="E152" t="str"/>
+      <x:c r="F152" t="n">
+        <x:v>2.678</x:v>
+      </x:c>
+      <x:c r="G152" t="n">
+        <x:v>2.678</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153">
+      <x:c r="A153" t="n">
+        <x:v>2505</x:v>
+      </x:c>
+      <x:c r="B153" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C153" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D153" t="n">
+        <x:v>0.816</x:v>
+      </x:c>
+      <x:c r="E153" t="str">
+        <x:v>challenge.bossWave</x:v>
+      </x:c>
+      <x:c r="F153" t="n">
+        <x:v>2.987</x:v>
+      </x:c>
+      <x:c r="G153" t="n">
+        <x:v>2.575</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154">
+      <x:c r="A154" t="n">
+        <x:v>2506</x:v>
+      </x:c>
+      <x:c r="B154" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C154" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D154" t="n">
+        <x:v>0.72</x:v>
+      </x:c>
+      <x:c r="E154" t="str"/>
+      <x:c r="F154" t="n">
+        <x:v>3.399</x:v>
+      </x:c>
+      <x:c r="G154" t="n">
+        <x:v>3.399</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155">
+      <x:c r="A155" t="n">
+        <x:v>2507</x:v>
+      </x:c>
+      <x:c r="B155" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C155" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D155" t="n">
+        <x:v>0.672</x:v>
+      </x:c>
+      <x:c r="E155" t="str"/>
+      <x:c r="F155" t="n">
+        <x:v>3.811</x:v>
+      </x:c>
+      <x:c r="G155" t="n">
+        <x:v>3.811</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156">
+      <x:c r="A156" t="n">
+        <x:v>2508</x:v>
+      </x:c>
+      <x:c r="B156" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C156" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D156" t="n">
+        <x:v>0.624</x:v>
+      </x:c>
+      <x:c r="E156" t="str"/>
+      <x:c r="F156" t="n">
+        <x:v>4.223</x:v>
+      </x:c>
+      <x:c r="G156" t="n">
+        <x:v>4.223</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157">
+      <x:c r="A157" t="n">
+        <x:v>2509</x:v>
+      </x:c>
+      <x:c r="B157" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C157" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D157" t="n">
+        <x:v>0.672</x:v>
+      </x:c>
+      <x:c r="E157" t="str"/>
+      <x:c r="F157" t="n">
+        <x:v>4.635</x:v>
+      </x:c>
+      <x:c r="G157" t="n">
+        <x:v>4.635</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158">
+      <x:c r="A158" t="n">
+        <x:v>2510</x:v>
+      </x:c>
+      <x:c r="B158" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C158" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D158" t="n">
+        <x:v>0.768</x:v>
+      </x:c>
+      <x:c r="E158" t="str">
+        <x:v>challenge.bossWave</x:v>
+      </x:c>
+      <x:c r="F158" t="n">
+        <x:v>5.15</x:v>
+      </x:c>
+      <x:c r="G158" t="n">
+        <x:v>6.18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159">
+      <x:c r="A159" t="n">
+        <x:v>2511</x:v>
+      </x:c>
+      <x:c r="B159" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C159" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D159" t="n">
+        <x:v>0.624</x:v>
+      </x:c>
+      <x:c r="E159" t="str"/>
+      <x:c r="F159" t="n">
+        <x:v>5.768</x:v>
+      </x:c>
+      <x:c r="G159" t="n">
+        <x:v>5.768</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160">
+      <x:c r="A160" t="n">
+        <x:v>2512</x:v>
+      </x:c>
+      <x:c r="B160" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C160" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D160" t="n">
+        <x:v>0.576</x:v>
+      </x:c>
+      <x:c r="E160" t="str"/>
+      <x:c r="F160" t="n">
+        <x:v>6.386</x:v>
+      </x:c>
+      <x:c r="G160" t="n">
+        <x:v>6.386</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161">
+      <x:c r="A161" t="n">
+        <x:v>2513</x:v>
+      </x:c>
+      <x:c r="B161" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C161" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D161" t="n">
+        <x:v>0.624</x:v>
+      </x:c>
+      <x:c r="E161" t="str"/>
+      <x:c r="F161" t="n">
+        <x:v>7.107</x:v>
+      </x:c>
+      <x:c r="G161" t="n">
+        <x:v>7.107</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162">
+      <x:c r="A162" t="n">
+        <x:v>2514</x:v>
+      </x:c>
+      <x:c r="B162" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C162" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D162" t="n">
+        <x:v>0.528</x:v>
+      </x:c>
+      <x:c r="E162" t="str"/>
+      <x:c r="F162" t="n">
+        <x:v>7.828</x:v>
+      </x:c>
+      <x:c r="G162" t="n">
+        <x:v>7.828</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163">
+      <x:c r="A163" t="n">
+        <x:v>2515</x:v>
+      </x:c>
+      <x:c r="B163" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C163" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D163" t="n">
+        <x:v>0.624</x:v>
+      </x:c>
+      <x:c r="E163" t="str">
+        <x:v>challenge.bossWave</x:v>
+      </x:c>
+      <x:c r="F163" t="n">
+        <x:v>8.755</x:v>
+      </x:c>
+      <x:c r="G163" t="n">
+        <x:v>10.3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164">
+      <x:c r="A164" t="n">
+        <x:v>2601</x:v>
+      </x:c>
+      <x:c r="B164" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C164" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D164" t="n">
+        <x:v>0.95</x:v>
+      </x:c>
+      <x:c r="E164" t="str"/>
+      <x:c r="F164" t="n">
+        <x:v>1.908</x:v>
+      </x:c>
+      <x:c r="G164" t="n">
+        <x:v>1.908</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165">
+      <x:c r="A165" t="n">
+        <x:v>2602</x:v>
+      </x:c>
+      <x:c r="B165" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C165" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D165" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="E165" t="str"/>
+      <x:c r="F165" t="n">
+        <x:v>2.12</x:v>
+      </x:c>
+      <x:c r="G165" t="n">
+        <x:v>2.12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166">
+      <x:c r="A166" t="n">
+        <x:v>2603</x:v>
+      </x:c>
+      <x:c r="B166" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C166" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D166" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="E166" t="str"/>
+      <x:c r="F166" t="n">
+        <x:v>2.438</x:v>
+      </x:c>
+      <x:c r="G166" t="n">
+        <x:v>2.438</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167">
+      <x:c r="A167" t="n">
+        <x:v>2604</x:v>
+      </x:c>
+      <x:c r="B167" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C167" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D167" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="E167" t="str"/>
+      <x:c r="F167" t="n">
+        <x:v>2.756</x:v>
+      </x:c>
+      <x:c r="G167" t="n">
+        <x:v>2.756</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168">
+      <x:c r="A168" t="n">
+        <x:v>2605</x:v>
+      </x:c>
+      <x:c r="B168" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C168" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D168" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="E168" t="str">
+        <x:v>challenge.bossWave</x:v>
+      </x:c>
+      <x:c r="F168" t="n">
+        <x:v>3.074</x:v>
+      </x:c>
+      <x:c r="G168" t="n">
+        <x:v>2.65</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169">
+      <x:c r="A169" t="n">
+        <x:v>2606</x:v>
+      </x:c>
+      <x:c r="B169" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C169" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D169" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="E169" t="str"/>
+      <x:c r="F169" t="n">
+        <x:v>3.498</x:v>
+      </x:c>
+      <x:c r="G169" t="n">
+        <x:v>3.498</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170">
+      <x:c r="A170" t="n">
+        <x:v>2607</x:v>
+      </x:c>
+      <x:c r="B170" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C170" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D170" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="E170" t="str"/>
+      <x:c r="F170" t="n">
+        <x:v>3.922</x:v>
+      </x:c>
+      <x:c r="G170" t="n">
+        <x:v>3.922</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171">
+      <x:c r="A171" t="n">
+        <x:v>2608</x:v>
+      </x:c>
+      <x:c r="B171" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C171" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D171" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="E171" t="str"/>
+      <x:c r="F171" t="n">
+        <x:v>4.346</x:v>
+      </x:c>
+      <x:c r="G171" t="n">
+        <x:v>4.346</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172">
+      <x:c r="A172" t="n">
+        <x:v>2609</x:v>
+      </x:c>
+      <x:c r="B172" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C172" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D172" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="E172" t="str"/>
+      <x:c r="F172" t="n">
+        <x:v>4.77</x:v>
+      </x:c>
+      <x:c r="G172" t="n">
+        <x:v>4.77</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173">
+      <x:c r="A173" t="n">
+        <x:v>2610</x:v>
+      </x:c>
+      <x:c r="B173" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C173" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D173" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="E173" t="str">
+        <x:v>challenge.bossWave</x:v>
+      </x:c>
+      <x:c r="F173" t="n">
+        <x:v>5.3</x:v>
+      </x:c>
+      <x:c r="G173" t="n">
+        <x:v>6.36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174">
+      <x:c r="A174" t="n">
+        <x:v>2611</x:v>
+      </x:c>
+      <x:c r="B174" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C174" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D174" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="E174" t="str"/>
+      <x:c r="F174" t="n">
+        <x:v>5.936</x:v>
+      </x:c>
+      <x:c r="G174" t="n">
+        <x:v>5.936</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175">
+      <x:c r="A175" t="n">
+        <x:v>2612</x:v>
+      </x:c>
+      <x:c r="B175" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C175" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D175" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="E175" t="str"/>
+      <x:c r="F175" t="n">
+        <x:v>6.572</x:v>
+      </x:c>
+      <x:c r="G175" t="n">
+        <x:v>6.572</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="176">
+      <x:c r="A176" t="n">
+        <x:v>2613</x:v>
+      </x:c>
+      <x:c r="B176" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C176" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D176" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="E176" t="str"/>
+      <x:c r="F176" t="n">
+        <x:v>7.314</x:v>
+      </x:c>
+      <x:c r="G176" t="n">
+        <x:v>7.314</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177">
+      <x:c r="A177" t="n">
+        <x:v>2614</x:v>
+      </x:c>
+      <x:c r="B177" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C177" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D177" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="E177" t="str"/>
+      <x:c r="F177" t="n">
+        <x:v>8.056</x:v>
+      </x:c>
+      <x:c r="G177" t="n">
+        <x:v>8.056</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178">
+      <x:c r="A178" t="n">
+        <x:v>2615</x:v>
+      </x:c>
+      <x:c r="B178" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C178" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D178" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="E178" t="str">
+        <x:v>challenge.bossWave</x:v>
+      </x:c>
+      <x:c r="F178" t="n">
+        <x:v>9.01</x:v>
+      </x:c>
+      <x:c r="G178" t="n">
+        <x:v>10.6</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/design/tables/Wave.xlsx
+++ b/design/tables/Wave.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wave" sheetId="1" r:id="R26eca255db9b46ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wave" sheetId="1" r:id="R9292f1c4c5964cb0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2293,14 +2293,14 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D89" s="26" t="n">
-        <x:v>0.95</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E89" s="26" t="str"/>
       <x:c r="F89" s="26" t="n">
-        <x:v>1.8</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="G89" t="n">
-        <x:v>1.8</x:v>
+        <x:v>1.98</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="48" customHeight="1">
@@ -2314,14 +2314,14 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D90" s="26" t="n">
-        <x:v>0.9</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E90" s="26" t="str"/>
       <x:c r="F90" s="26" t="n">
-        <x:v>2</x:v>
+        <x:v>0.6276</x:v>
       </x:c>
       <x:c r="G90" t="n">
-        <x:v>2</x:v>
+        <x:v>2.2</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="48" customHeight="1">
@@ -2335,14 +2335,14 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D91" s="26" t="n">
-        <x:v>0.85</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E91" s="26" t="str"/>
       <x:c r="F91" s="26" t="n">
-        <x:v>2.3</x:v>
+        <x:v>0.7102</x:v>
       </x:c>
       <x:c r="G91" t="n">
-        <x:v>2.3</x:v>
+        <x:v>2.53</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="48" customHeight="1">
@@ -2356,14 +2356,14 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D92" s="26" t="n">
-        <x:v>0.8</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E92" s="26" t="str"/>
       <x:c r="F92" s="26" t="n">
-        <x:v>2.6</x:v>
+        <x:v>0.848</x:v>
       </x:c>
       <x:c r="G92" t="n">
-        <x:v>2.6</x:v>
+        <x:v>2.86</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="48" customHeight="1">
@@ -2377,16 +2377,16 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D93" s="26" t="n">
-        <x:v>0.85</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E93" s="26" t="str">
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F93" s="26" t="n">
-        <x:v>2.9</x:v>
+        <x:v>1.0408</x:v>
       </x:c>
       <x:c r="G93" t="n">
-        <x:v>2.5</x:v>
+        <x:v>2.75</x:v>
       </x:c>
     </x:row>
     <x:row r="94" ht="48" customHeight="1">
@@ -2400,14 +2400,14 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="D94" s="26" t="n">
-        <x:v>0.75</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E94" s="26" t="str"/>
       <x:c r="F94" s="26" t="n">
-        <x:v>3.3</x:v>
+        <x:v>1.2888</x:v>
       </x:c>
       <x:c r="G94" t="n">
-        <x:v>3.3</x:v>
+        <x:v>3.63</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="48" customHeight="1">
@@ -2421,14 +2421,14 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D95" s="26" t="n">
-        <x:v>0.7</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E95" s="26" t="str"/>
       <x:c r="F95" s="26" t="n">
-        <x:v>3.7</x:v>
+        <x:v>1.5918</x:v>
       </x:c>
       <x:c r="G95" t="n">
-        <x:v>3.7</x:v>
+        <x:v>4.07</x:v>
       </x:c>
     </x:row>
     <x:row r="96" ht="48" customHeight="1">
@@ -2442,14 +2442,14 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D96" s="26" t="n">
-        <x:v>0.65</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E96" s="26" t="str"/>
       <x:c r="F96" s="26" t="n">
-        <x:v>4.1</x:v>
+        <x:v>1.95</x:v>
       </x:c>
       <x:c r="G96" t="n">
-        <x:v>4.1</x:v>
+        <x:v>4.51</x:v>
       </x:c>
     </x:row>
     <x:row r="97" ht="48" customHeight="1">
@@ -2463,14 +2463,14 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D97" s="26" t="n">
-        <x:v>0.7</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E97" s="26" t="str"/>
       <x:c r="F97" s="26" t="n">
-        <x:v>4.5</x:v>
+        <x:v>2.3633</x:v>
       </x:c>
       <x:c r="G97" t="n">
-        <x:v>4.5</x:v>
+        <x:v>4.95</x:v>
       </x:c>
     </x:row>
     <x:row r="98" ht="48" customHeight="1">
@@ -2484,16 +2484,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D98" s="26" t="n">
-        <x:v>0.8</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E98" s="26" t="str">
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F98" s="26" t="n">
-        <x:v>5</x:v>
+        <x:v>2.8316</x:v>
       </x:c>
       <x:c r="G98" t="n">
-        <x:v>6</x:v>
+        <x:v>6.6</x:v>
       </x:c>
     </x:row>
     <x:row r="99" ht="48" customHeight="1">
@@ -2507,14 +2507,14 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D99" s="26" t="n">
-        <x:v>0.65</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E99" s="26" t="str"/>
       <x:c r="F99" s="26" t="n">
-        <x:v>5.6</x:v>
+        <x:v>3.3551</x:v>
       </x:c>
       <x:c r="G99" t="n">
-        <x:v>5.6</x:v>
+        <x:v>6.16</x:v>
       </x:c>
     </x:row>
     <x:row r="100" ht="48" customHeight="1">
@@ -2528,14 +2528,14 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D100" s="26" t="n">
-        <x:v>0.6</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E100" s="26" t="str"/>
       <x:c r="F100" s="26" t="n">
-        <x:v>6.2</x:v>
+        <x:v>3.9337</x:v>
       </x:c>
       <x:c r="G100" t="n">
-        <x:v>6.2</x:v>
+        <x:v>6.82</x:v>
       </x:c>
     </x:row>
     <x:row r="101" ht="48" customHeight="1">
@@ -2549,14 +2549,14 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="D101" s="26" t="n">
-        <x:v>0.65</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E101" s="26" t="str"/>
       <x:c r="F101" s="26" t="n">
-        <x:v>6.9</x:v>
+        <x:v>4.5673</x:v>
       </x:c>
       <x:c r="G101" t="n">
-        <x:v>6.9</x:v>
+        <x:v>7.59</x:v>
       </x:c>
     </x:row>
     <x:row r="102" ht="48" customHeight="1">
@@ -2570,14 +2570,14 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D102" s="26" t="n">
-        <x:v>0.55</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E102" s="26" t="str"/>
       <x:c r="F102" s="26" t="n">
-        <x:v>7.6</x:v>
+        <x:v>5.2561</x:v>
       </x:c>
       <x:c r="G102" t="n">
-        <x:v>7.6</x:v>
+        <x:v>8.36</x:v>
       </x:c>
     </x:row>
     <x:row r="103" ht="48" customHeight="1">
@@ -2591,16 +2591,16 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="D103" s="26" t="n">
-        <x:v>0.65</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E103" s="26" t="str">
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F103" s="26" t="n">
-        <x:v>8.5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G103" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="104" ht="48" customHeight="1">
@@ -2614,14 +2614,14 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D104" s="26" t="n">
-        <x:v>0.912</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E104" s="26" t="str"/>
       <x:c r="F104" s="26" t="n">
-        <x:v>1.71</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="G104" t="n">
-        <x:v>1.71</x:v>
+        <x:v>1.881</x:v>
       </x:c>
     </x:row>
     <x:row r="105" ht="48" customHeight="1">
@@ -2635,14 +2635,14 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D105" s="26" t="n">
-        <x:v>0.864</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E105" s="26" t="str"/>
       <x:c r="F105" s="26" t="n">
-        <x:v>1.9</x:v>
+        <x:v>0.5138</x:v>
       </x:c>
       <x:c r="G105" t="n">
-        <x:v>1.9</x:v>
+        <x:v>2.09</x:v>
       </x:c>
     </x:row>
     <x:row r="106" ht="48" customHeight="1">
@@ -2656,14 +2656,14 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D106" s="26" t="n">
-        <x:v>0.816</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E106" s="26" t="str"/>
       <x:c r="F106" s="26" t="n">
-        <x:v>2.185</x:v>
+        <x:v>0.5551</x:v>
       </x:c>
       <x:c r="G106" t="n">
-        <x:v>2.185</x:v>
+        <x:v>2.4035</x:v>
       </x:c>
     </x:row>
     <x:row r="107" ht="48" customHeight="1">
@@ -2677,14 +2677,14 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D107" s="26" t="n">
-        <x:v>0.768</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E107" s="26" t="str"/>
       <x:c r="F107" s="26" t="n">
-        <x:v>2.47</x:v>
+        <x:v>0.624</x:v>
       </x:c>
       <x:c r="G107" t="n">
-        <x:v>2.47</x:v>
+        <x:v>2.717</x:v>
       </x:c>
     </x:row>
     <x:row r="108" ht="48" customHeight="1">
@@ -2698,16 +2698,16 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D108" s="26" t="n">
-        <x:v>0.816</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E108" s="26" t="str">
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F108" s="26" t="n">
-        <x:v>2.755</x:v>
+        <x:v>0.7204</x:v>
       </x:c>
       <x:c r="G108" t="n">
-        <x:v>2.375</x:v>
+        <x:v>2.6125</x:v>
       </x:c>
     </x:row>
     <x:row r="109" ht="48" customHeight="1">
@@ -2721,14 +2721,14 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="D109" s="26" t="n">
-        <x:v>0.72</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E109" s="26" t="str"/>
       <x:c r="F109" s="26" t="n">
-        <x:v>3.135</x:v>
+        <x:v>0.8444</x:v>
       </x:c>
       <x:c r="G109" t="n">
-        <x:v>3.135</x:v>
+        <x:v>3.4485</x:v>
       </x:c>
     </x:row>
     <x:row r="110">
@@ -2742,14 +2742,14 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D110" t="n">
-        <x:v>0.672</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E110" t="str"/>
       <x:c r="F110" t="n">
-        <x:v>3.515</x:v>
+        <x:v>0.9959</x:v>
       </x:c>
       <x:c r="G110" t="n">
-        <x:v>3.515</x:v>
+        <x:v>3.8665</x:v>
       </x:c>
     </x:row>
     <x:row r="111">
@@ -2763,14 +2763,14 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D111" t="n">
-        <x:v>0.624</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E111" t="str"/>
       <x:c r="F111" t="n">
-        <x:v>3.895</x:v>
+        <x:v>1.175</x:v>
       </x:c>
       <x:c r="G111" t="n">
-        <x:v>3.895</x:v>
+        <x:v>4.2845</x:v>
       </x:c>
     </x:row>
     <x:row r="112">
@@ -2784,14 +2784,14 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D112" t="n">
-        <x:v>0.672</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E112" t="str"/>
       <x:c r="F112" t="n">
-        <x:v>4.275</x:v>
+        <x:v>1.3816</x:v>
       </x:c>
       <x:c r="G112" t="n">
-        <x:v>4.275</x:v>
+        <x:v>4.7025</x:v>
       </x:c>
     </x:row>
     <x:row r="113">
@@ -2805,16 +2805,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D113" t="n">
-        <x:v>0.768</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E113" t="str">
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F113" t="n">
-        <x:v>4.75</x:v>
+        <x:v>1.6158</x:v>
       </x:c>
       <x:c r="G113" t="n">
-        <x:v>5.7</x:v>
+        <x:v>6.27</x:v>
       </x:c>
     </x:row>
     <x:row r="114">
@@ -2828,14 +2828,14 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D114" t="n">
-        <x:v>0.624</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E114" t="str"/>
       <x:c r="F114" t="n">
-        <x:v>5.32</x:v>
+        <x:v>1.8776</x:v>
       </x:c>
       <x:c r="G114" t="n">
-        <x:v>5.32</x:v>
+        <x:v>5.852</x:v>
       </x:c>
     </x:row>
     <x:row r="115">
@@ -2849,14 +2849,14 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D115" t="n">
-        <x:v>0.576</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E115" t="str"/>
       <x:c r="F115" t="n">
-        <x:v>5.89</x:v>
+        <x:v>2.1668</x:v>
       </x:c>
       <x:c r="G115" t="n">
-        <x:v>5.89</x:v>
+        <x:v>6.479</x:v>
       </x:c>
     </x:row>
     <x:row r="116">
@@ -2870,14 +2870,14 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="D116" t="n">
-        <x:v>0.624</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E116" t="str"/>
       <x:c r="F116" t="n">
-        <x:v>6.555</x:v>
+        <x:v>2.4837</x:v>
       </x:c>
       <x:c r="G116" t="n">
-        <x:v>6.555</x:v>
+        <x:v>7.2105</x:v>
       </x:c>
     </x:row>
     <x:row r="117">
@@ -2891,14 +2891,14 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D117" t="n">
-        <x:v>0.528</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E117" t="str"/>
       <x:c r="F117" t="n">
-        <x:v>7.22</x:v>
+        <x:v>2.8281</x:v>
       </x:c>
       <x:c r="G117" t="n">
-        <x:v>7.22</x:v>
+        <x:v>7.942</x:v>
       </x:c>
     </x:row>
     <x:row r="118">
@@ -2912,16 +2912,16 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="D118" t="n">
-        <x:v>0.624</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E118" t="str">
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F118" t="n">
-        <x:v>8.075</x:v>
+        <x:v>3.2</x:v>
       </x:c>
       <x:c r="G118" t="n">
-        <x:v>9.5</x:v>
+        <x:v>10.45</x:v>
       </x:c>
     </x:row>
     <x:row r="119">
@@ -2935,14 +2935,14 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D119" t="n">
-        <x:v>0.95</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E119" t="str"/>
       <x:c r="F119" t="n">
-        <x:v>1.8</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="G119" t="n">
-        <x:v>1.8</x:v>
+        <x:v>1.98</x:v>
       </x:c>
     </x:row>
     <x:row r="120">
@@ -2956,14 +2956,14 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D120" t="n">
-        <x:v>0.9</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E120" t="str"/>
       <x:c r="F120" t="n">
-        <x:v>2</x:v>
+        <x:v>0.6276</x:v>
       </x:c>
       <x:c r="G120" t="n">
-        <x:v>2</x:v>
+        <x:v>2.2</x:v>
       </x:c>
     </x:row>
     <x:row r="121">
@@ -2977,14 +2977,14 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D121" t="n">
-        <x:v>0.85</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E121" t="str"/>
       <x:c r="F121" t="n">
-        <x:v>2.3</x:v>
+        <x:v>0.7102</x:v>
       </x:c>
       <x:c r="G121" t="n">
-        <x:v>2.3</x:v>
+        <x:v>2.53</x:v>
       </x:c>
     </x:row>
     <x:row r="122">
@@ -2998,14 +2998,14 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D122" t="n">
-        <x:v>0.8</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E122" t="str"/>
       <x:c r="F122" t="n">
-        <x:v>2.6</x:v>
+        <x:v>0.848</x:v>
       </x:c>
       <x:c r="G122" t="n">
-        <x:v>2.6</x:v>
+        <x:v>2.86</x:v>
       </x:c>
     </x:row>
     <x:row r="123">
@@ -3019,16 +3019,16 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D123" t="n">
-        <x:v>0.85</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E123" t="str">
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F123" t="n">
-        <x:v>2.9</x:v>
+        <x:v>1.0408</x:v>
       </x:c>
       <x:c r="G123" t="n">
-        <x:v>2.5</x:v>
+        <x:v>2.75</x:v>
       </x:c>
     </x:row>
     <x:row r="124">
@@ -3042,14 +3042,14 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="D124" t="n">
-        <x:v>0.75</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E124" t="str"/>
       <x:c r="F124" t="n">
-        <x:v>3.3</x:v>
+        <x:v>1.2888</x:v>
       </x:c>
       <x:c r="G124" t="n">
-        <x:v>3.3</x:v>
+        <x:v>3.63</x:v>
       </x:c>
     </x:row>
     <x:row r="125">
@@ -3063,14 +3063,14 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D125" t="n">
-        <x:v>0.7</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E125" t="str"/>
       <x:c r="F125" t="n">
-        <x:v>3.7</x:v>
+        <x:v>1.5918</x:v>
       </x:c>
       <x:c r="G125" t="n">
-        <x:v>3.7</x:v>
+        <x:v>4.07</x:v>
       </x:c>
     </x:row>
     <x:row r="126">
@@ -3084,14 +3084,14 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D126" t="n">
-        <x:v>0.65</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E126" t="str"/>
       <x:c r="F126" t="n">
-        <x:v>4.1</x:v>
+        <x:v>1.95</x:v>
       </x:c>
       <x:c r="G126" t="n">
-        <x:v>4.1</x:v>
+        <x:v>4.51</x:v>
       </x:c>
     </x:row>
     <x:row r="127">
@@ -3105,14 +3105,14 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D127" t="n">
-        <x:v>0.7</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E127" t="str"/>
       <x:c r="F127" t="n">
-        <x:v>4.5</x:v>
+        <x:v>2.3633</x:v>
       </x:c>
       <x:c r="G127" t="n">
-        <x:v>4.5</x:v>
+        <x:v>4.95</x:v>
       </x:c>
     </x:row>
     <x:row r="128">
@@ -3126,16 +3126,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D128" t="n">
-        <x:v>0.8</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E128" t="str">
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F128" t="n">
-        <x:v>5</x:v>
+        <x:v>2.8316</x:v>
       </x:c>
       <x:c r="G128" t="n">
-        <x:v>6</x:v>
+        <x:v>6.6</x:v>
       </x:c>
     </x:row>
     <x:row r="129">
@@ -3149,14 +3149,14 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D129" t="n">
-        <x:v>0.65</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E129" t="str"/>
       <x:c r="F129" t="n">
-        <x:v>5.6</x:v>
+        <x:v>3.3551</x:v>
       </x:c>
       <x:c r="G129" t="n">
-        <x:v>5.6</x:v>
+        <x:v>6.16</x:v>
       </x:c>
     </x:row>
     <x:row r="130">
@@ -3170,14 +3170,14 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D130" t="n">
-        <x:v>0.6</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E130" t="str"/>
       <x:c r="F130" t="n">
-        <x:v>6.2</x:v>
+        <x:v>3.9337</x:v>
       </x:c>
       <x:c r="G130" t="n">
-        <x:v>6.2</x:v>
+        <x:v>6.82</x:v>
       </x:c>
     </x:row>
     <x:row r="131">
@@ -3191,14 +3191,14 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="D131" t="n">
-        <x:v>0.65</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E131" t="str"/>
       <x:c r="F131" t="n">
-        <x:v>6.9</x:v>
+        <x:v>4.5673</x:v>
       </x:c>
       <x:c r="G131" t="n">
-        <x:v>6.9</x:v>
+        <x:v>7.59</x:v>
       </x:c>
     </x:row>
     <x:row r="132">
@@ -3212,14 +3212,14 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D132" t="n">
-        <x:v>0.55</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E132" t="str"/>
       <x:c r="F132" t="n">
-        <x:v>7.6</x:v>
+        <x:v>5.2561</x:v>
       </x:c>
       <x:c r="G132" t="n">
-        <x:v>7.6</x:v>
+        <x:v>8.36</x:v>
       </x:c>
     </x:row>
     <x:row r="133">
@@ -3233,16 +3233,16 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="D133" t="n">
-        <x:v>0.65</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E133" t="str">
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F133" t="n">
-        <x:v>8.5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G133" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="134">
@@ -3256,14 +3256,14 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D134" t="n">
-        <x:v>0.893</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E134" t="str"/>
       <x:c r="F134" t="n">
-        <x:v>1.836</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="G134" t="n">
-        <x:v>1.836</x:v>
+        <x:v>2.0196</x:v>
       </x:c>
     </x:row>
     <x:row r="135">
@@ -3277,14 +3277,14 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D135" t="n">
-        <x:v>0.846</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E135" t="str"/>
       <x:c r="F135" t="n">
-        <x:v>2.04</x:v>
+        <x:v>0.3128</x:v>
       </x:c>
       <x:c r="G135" t="n">
-        <x:v>2.04</x:v>
+        <x:v>2.244</x:v>
       </x:c>
     </x:row>
     <x:row r="136">
@@ -3298,14 +3298,14 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D136" t="n">
-        <x:v>0.799</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E136" t="str"/>
       <x:c r="F136" t="n">
-        <x:v>2.346</x:v>
+        <x:v>0.351</x:v>
       </x:c>
       <x:c r="G136" t="n">
-        <x:v>2.346</x:v>
+        <x:v>2.5806</x:v>
       </x:c>
     </x:row>
     <x:row r="137">
@@ -3319,14 +3319,14 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D137" t="n">
-        <x:v>0.752</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E137" t="str"/>
       <x:c r="F137" t="n">
-        <x:v>2.652</x:v>
+        <x:v>0.4148</x:v>
       </x:c>
       <x:c r="G137" t="n">
-        <x:v>2.652</x:v>
+        <x:v>2.9172</x:v>
       </x:c>
     </x:row>
     <x:row r="138">
@@ -3340,16 +3340,16 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D138" t="n">
-        <x:v>0.799</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E138" t="str">
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F138" t="n">
-        <x:v>2.958</x:v>
+        <x:v>0.5041</x:v>
       </x:c>
       <x:c r="G138" t="n">
-        <x:v>2.55</x:v>
+        <x:v>2.805</x:v>
       </x:c>
     </x:row>
     <x:row r="139">
@@ -3363,14 +3363,14 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="D139" t="n">
-        <x:v>0.705</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E139" t="str"/>
       <x:c r="F139" t="n">
-        <x:v>3.366</x:v>
+        <x:v>0.6189</x:v>
       </x:c>
       <x:c r="G139" t="n">
-        <x:v>3.366</x:v>
+        <x:v>3.7026</x:v>
       </x:c>
     </x:row>
     <x:row r="140">
@@ -3384,14 +3384,14 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D140" t="n">
-        <x:v>0.658</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E140" t="str"/>
       <x:c r="F140" t="n">
-        <x:v>3.774</x:v>
+        <x:v>0.7592</x:v>
       </x:c>
       <x:c r="G140" t="n">
-        <x:v>3.774</x:v>
+        <x:v>4.1514</x:v>
       </x:c>
     </x:row>
     <x:row r="141">
@@ -3405,14 +3405,14 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D141" t="n">
-        <x:v>0.611</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E141" t="str"/>
       <x:c r="F141" t="n">
-        <x:v>4.182</x:v>
+        <x:v>0.925</x:v>
       </x:c>
       <x:c r="G141" t="n">
-        <x:v>4.182</x:v>
+        <x:v>4.6002</x:v>
       </x:c>
     </x:row>
     <x:row r="142">
@@ -3426,14 +3426,14 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D142" t="n">
-        <x:v>0.658</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E142" t="str"/>
       <x:c r="F142" t="n">
-        <x:v>4.59</x:v>
+        <x:v>1.1163</x:v>
       </x:c>
       <x:c r="G142" t="n">
-        <x:v>4.59</x:v>
+        <x:v>5.049</x:v>
       </x:c>
     </x:row>
     <x:row r="143">
@@ -3447,16 +3447,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D143" t="n">
-        <x:v>0.752</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E143" t="str">
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F143" t="n">
-        <x:v>5.1</x:v>
+        <x:v>1.3332</x:v>
       </x:c>
       <x:c r="G143" t="n">
-        <x:v>6.12</x:v>
+        <x:v>6.732</x:v>
       </x:c>
     </x:row>
     <x:row r="144">
@@ -3470,14 +3470,14 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D144" t="n">
-        <x:v>0.611</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E144" t="str"/>
       <x:c r="F144" t="n">
-        <x:v>5.712</x:v>
+        <x:v>1.5755</x:v>
       </x:c>
       <x:c r="G144" t="n">
-        <x:v>5.712</x:v>
+        <x:v>6.2832</x:v>
       </x:c>
     </x:row>
     <x:row r="145">
@@ -3491,14 +3491,14 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D145" t="n">
-        <x:v>0.564</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E145" t="str"/>
       <x:c r="F145" t="n">
-        <x:v>6.324</x:v>
+        <x:v>1.8434</x:v>
       </x:c>
       <x:c r="G145" t="n">
-        <x:v>6.324</x:v>
+        <x:v>6.9564</x:v>
       </x:c>
     </x:row>
     <x:row r="146">
@@ -3512,14 +3512,14 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="D146" t="n">
-        <x:v>0.611</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E146" t="str"/>
       <x:c r="F146" t="n">
-        <x:v>7.038</x:v>
+        <x:v>2.1367</x:v>
       </x:c>
       <x:c r="G146" t="n">
-        <x:v>7.038</x:v>
+        <x:v>7.7418</x:v>
       </x:c>
     </x:row>
     <x:row r="147">
@@ -3533,14 +3533,14 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D147" t="n">
-        <x:v>0.517</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E147" t="str"/>
       <x:c r="F147" t="n">
-        <x:v>7.752</x:v>
+        <x:v>2.4556</x:v>
       </x:c>
       <x:c r="G147" t="n">
-        <x:v>7.752</x:v>
+        <x:v>8.5272</x:v>
       </x:c>
     </x:row>
     <x:row r="148">
@@ -3554,16 +3554,16 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="D148" t="n">
-        <x:v>0.611</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E148" t="str">
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F148" t="n">
-        <x:v>8.67</x:v>
+        <x:v>2.8</x:v>
       </x:c>
       <x:c r="G148" t="n">
-        <x:v>10.2</x:v>
+        <x:v>11.22</x:v>
       </x:c>
     </x:row>
     <x:row r="149">
@@ -3577,14 +3577,14 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D149" t="n">
-        <x:v>0.912</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E149" t="str"/>
       <x:c r="F149" t="n">
-        <x:v>1.854</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="G149" t="n">
-        <x:v>1.854</x:v>
+        <x:v>2.0394</x:v>
       </x:c>
     </x:row>
     <x:row r="150">
@@ -3598,14 +3598,14 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D150" t="n">
-        <x:v>0.864</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E150" t="str"/>
       <x:c r="F150" t="n">
-        <x:v>2.06</x:v>
+        <x:v>0.648</x:v>
       </x:c>
       <x:c r="G150" t="n">
-        <x:v>2.06</x:v>
+        <x:v>2.266</x:v>
       </x:c>
     </x:row>
     <x:row r="151">
@@ -3619,14 +3619,14 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D151" t="n">
-        <x:v>0.816</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E151" t="str"/>
       <x:c r="F151" t="n">
-        <x:v>2.369</x:v>
+        <x:v>0.7918</x:v>
       </x:c>
       <x:c r="G151" t="n">
-        <x:v>2.369</x:v>
+        <x:v>2.6059</x:v>
       </x:c>
     </x:row>
     <x:row r="152">
@@ -3640,14 +3640,14 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D152" t="n">
-        <x:v>0.768</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E152" t="str"/>
       <x:c r="F152" t="n">
-        <x:v>2.678</x:v>
+        <x:v>1.0316</x:v>
       </x:c>
       <x:c r="G152" t="n">
-        <x:v>2.678</x:v>
+        <x:v>2.9458</x:v>
       </x:c>
     </x:row>
     <x:row r="153">
@@ -3661,16 +3661,16 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D153" t="n">
-        <x:v>0.816</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E153" t="str">
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F153" t="n">
-        <x:v>2.987</x:v>
+        <x:v>1.3673</x:v>
       </x:c>
       <x:c r="G153" t="n">
-        <x:v>2.575</x:v>
+        <x:v>2.8325</x:v>
       </x:c>
     </x:row>
     <x:row r="154">
@@ -3684,14 +3684,14 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="D154" t="n">
-        <x:v>0.72</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E154" t="str"/>
       <x:c r="F154" t="n">
-        <x:v>3.399</x:v>
+        <x:v>1.799</x:v>
       </x:c>
       <x:c r="G154" t="n">
-        <x:v>3.399</x:v>
+        <x:v>3.7389</x:v>
       </x:c>
     </x:row>
     <x:row r="155">
@@ -3705,14 +3705,14 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D155" t="n">
-        <x:v>0.672</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E155" t="str"/>
       <x:c r="F155" t="n">
-        <x:v>3.811</x:v>
+        <x:v>2.3265</x:v>
       </x:c>
       <x:c r="G155" t="n">
-        <x:v>3.811</x:v>
+        <x:v>4.1921</x:v>
       </x:c>
     </x:row>
     <x:row r="156">
@@ -3726,14 +3726,14 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D156" t="n">
-        <x:v>0.624</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E156" t="str"/>
       <x:c r="F156" t="n">
-        <x:v>4.223</x:v>
+        <x:v>2.95</x:v>
       </x:c>
       <x:c r="G156" t="n">
-        <x:v>4.223</x:v>
+        <x:v>4.6453</x:v>
       </x:c>
     </x:row>
     <x:row r="157">
@@ -3747,14 +3747,14 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D157" t="n">
-        <x:v>0.672</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E157" t="str"/>
       <x:c r="F157" t="n">
-        <x:v>4.635</x:v>
+        <x:v>3.6694</x:v>
       </x:c>
       <x:c r="G157" t="n">
-        <x:v>4.635</x:v>
+        <x:v>5.0985</x:v>
       </x:c>
     </x:row>
     <x:row r="158">
@@ -3768,16 +3768,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D158" t="n">
-        <x:v>0.768</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E158" t="str">
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F158" t="n">
-        <x:v>5.15</x:v>
+        <x:v>4.4847</x:v>
       </x:c>
       <x:c r="G158" t="n">
-        <x:v>6.18</x:v>
+        <x:v>6.798</x:v>
       </x:c>
     </x:row>
     <x:row r="159">
@@ -3791,14 +3791,14 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D159" t="n">
-        <x:v>0.624</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E159" t="str"/>
       <x:c r="F159" t="n">
-        <x:v>5.768</x:v>
+        <x:v>5.3959</x:v>
       </x:c>
       <x:c r="G159" t="n">
-        <x:v>5.768</x:v>
+        <x:v>6.3448</x:v>
       </x:c>
     </x:row>
     <x:row r="160">
@@ -3812,14 +3812,14 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D160" t="n">
-        <x:v>0.576</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E160" t="str"/>
       <x:c r="F160" t="n">
-        <x:v>6.386</x:v>
+        <x:v>6.4031</x:v>
       </x:c>
       <x:c r="G160" t="n">
-        <x:v>6.386</x:v>
+        <x:v>7.0246</x:v>
       </x:c>
     </x:row>
     <x:row r="161">
@@ -3833,14 +3833,14 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="D161" t="n">
-        <x:v>0.624</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E161" t="str"/>
       <x:c r="F161" t="n">
-        <x:v>7.107</x:v>
+        <x:v>7.5061</x:v>
       </x:c>
       <x:c r="G161" t="n">
-        <x:v>7.107</x:v>
+        <x:v>7.8177</x:v>
       </x:c>
     </x:row>
     <x:row r="162">
@@ -3854,14 +3854,14 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D162" t="n">
-        <x:v>0.528</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E162" t="str"/>
       <x:c r="F162" t="n">
-        <x:v>7.828</x:v>
+        <x:v>8.7051</x:v>
       </x:c>
       <x:c r="G162" t="n">
-        <x:v>7.828</x:v>
+        <x:v>8.6108</x:v>
       </x:c>
     </x:row>
     <x:row r="163">
@@ -3875,16 +3875,16 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="D163" t="n">
-        <x:v>0.624</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E163" t="str">
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F163" t="n">
-        <x:v>8.755</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G163" t="n">
-        <x:v>10.3</x:v>
+        <x:v>11.33</x:v>
       </x:c>
     </x:row>
     <x:row r="164">
@@ -3898,14 +3898,14 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D164" t="n">
-        <x:v>0.95</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E164" t="str"/>
       <x:c r="F164" t="n">
-        <x:v>1.908</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="G164" t="n">
-        <x:v>1.908</x:v>
+        <x:v>2.0988</x:v>
       </x:c>
     </x:row>
     <x:row r="165">
@@ -3919,14 +3919,14 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D165" t="n">
-        <x:v>0.9</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E165" t="str"/>
       <x:c r="F165" t="n">
-        <x:v>2.12</x:v>
+        <x:v>0.6276</x:v>
       </x:c>
       <x:c r="G165" t="n">
-        <x:v>2.12</x:v>
+        <x:v>2.332</x:v>
       </x:c>
     </x:row>
     <x:row r="166">
@@ -3940,14 +3940,14 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D166" t="n">
-        <x:v>0.85</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E166" t="str"/>
       <x:c r="F166" t="n">
-        <x:v>2.438</x:v>
+        <x:v>0.7102</x:v>
       </x:c>
       <x:c r="G166" t="n">
-        <x:v>2.438</x:v>
+        <x:v>2.6818</x:v>
       </x:c>
     </x:row>
     <x:row r="167">
@@ -3961,14 +3961,14 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D167" t="n">
-        <x:v>0.8</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E167" t="str"/>
       <x:c r="F167" t="n">
-        <x:v>2.756</x:v>
+        <x:v>0.848</x:v>
       </x:c>
       <x:c r="G167" t="n">
-        <x:v>2.756</x:v>
+        <x:v>3.0316</x:v>
       </x:c>
     </x:row>
     <x:row r="168">
@@ -3982,16 +3982,16 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D168" t="n">
-        <x:v>0.85</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E168" t="str">
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F168" t="n">
-        <x:v>3.074</x:v>
+        <x:v>1.0408</x:v>
       </x:c>
       <x:c r="G168" t="n">
-        <x:v>2.65</x:v>
+        <x:v>2.915</x:v>
       </x:c>
     </x:row>
     <x:row r="169">
@@ -4005,14 +4005,14 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="D169" t="n">
-        <x:v>0.75</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E169" t="str"/>
       <x:c r="F169" t="n">
-        <x:v>3.498</x:v>
+        <x:v>1.2888</x:v>
       </x:c>
       <x:c r="G169" t="n">
-        <x:v>3.498</x:v>
+        <x:v>3.8478</x:v>
       </x:c>
     </x:row>
     <x:row r="170">
@@ -4026,14 +4026,14 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D170" t="n">
-        <x:v>0.7</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E170" t="str"/>
       <x:c r="F170" t="n">
-        <x:v>3.922</x:v>
+        <x:v>1.5918</x:v>
       </x:c>
       <x:c r="G170" t="n">
-        <x:v>3.922</x:v>
+        <x:v>4.3142</x:v>
       </x:c>
     </x:row>
     <x:row r="171">
@@ -4047,14 +4047,14 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D171" t="n">
-        <x:v>0.65</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E171" t="str"/>
       <x:c r="F171" t="n">
-        <x:v>4.346</x:v>
+        <x:v>1.95</x:v>
       </x:c>
       <x:c r="G171" t="n">
-        <x:v>4.346</x:v>
+        <x:v>4.7806</x:v>
       </x:c>
     </x:row>
     <x:row r="172">
@@ -4068,14 +4068,14 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D172" t="n">
-        <x:v>0.7</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E172" t="str"/>
       <x:c r="F172" t="n">
-        <x:v>4.77</x:v>
+        <x:v>2.3633</x:v>
       </x:c>
       <x:c r="G172" t="n">
-        <x:v>4.77</x:v>
+        <x:v>5.247</x:v>
       </x:c>
     </x:row>
     <x:row r="173">
@@ -4089,16 +4089,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D173" t="n">
-        <x:v>0.8</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E173" t="str">
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F173" t="n">
-        <x:v>5.3</x:v>
+        <x:v>2.8316</x:v>
       </x:c>
       <x:c r="G173" t="n">
-        <x:v>6.36</x:v>
+        <x:v>6.996</x:v>
       </x:c>
     </x:row>
     <x:row r="174">
@@ -4112,14 +4112,14 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D174" t="n">
-        <x:v>0.65</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E174" t="str"/>
       <x:c r="F174" t="n">
-        <x:v>5.936</x:v>
+        <x:v>3.3551</x:v>
       </x:c>
       <x:c r="G174" t="n">
-        <x:v>5.936</x:v>
+        <x:v>6.5296</x:v>
       </x:c>
     </x:row>
     <x:row r="175">
@@ -4133,14 +4133,14 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D175" t="n">
-        <x:v>0.6</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E175" t="str"/>
       <x:c r="F175" t="n">
-        <x:v>6.572</x:v>
+        <x:v>3.9337</x:v>
       </x:c>
       <x:c r="G175" t="n">
-        <x:v>6.572</x:v>
+        <x:v>7.2292</x:v>
       </x:c>
     </x:row>
     <x:row r="176">
@@ -4154,14 +4154,14 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="D176" t="n">
-        <x:v>0.65</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E176" t="str"/>
       <x:c r="F176" t="n">
-        <x:v>7.314</x:v>
+        <x:v>4.5673</x:v>
       </x:c>
       <x:c r="G176" t="n">
-        <x:v>7.314</x:v>
+        <x:v>8.0454</x:v>
       </x:c>
     </x:row>
     <x:row r="177">
@@ -4175,14 +4175,14 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D177" t="n">
-        <x:v>0.55</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E177" t="str"/>
       <x:c r="F177" t="n">
-        <x:v>8.056</x:v>
+        <x:v>5.2561</x:v>
       </x:c>
       <x:c r="G177" t="n">
-        <x:v>8.056</x:v>
+        <x:v>8.8616</x:v>
       </x:c>
     </x:row>
     <x:row r="178">
@@ -4196,16 +4196,16 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="D178" t="n">
-        <x:v>0.65</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E178" t="str">
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F178" t="n">
-        <x:v>9.01</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G178" t="n">
-        <x:v>10.6</x:v>
+        <x:v>11.66</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/design/tables/Wave.xlsx
+++ b/design/tables/Wave.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wave" sheetId="1" r:id="R9292f1c4c5964cb0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wave" sheetId="1" r:id="R38cb25b1bf8c4816"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2293,14 +2293,14 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D89" s="26" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.65</x:v>
       </x:c>
       <x:c r="E89" s="26" t="str"/>
       <x:c r="F89" s="26" t="n">
-        <x:v>0.6</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="G89" t="n">
-        <x:v>1.98</x:v>
+        <x:v>3.168</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="48" customHeight="1">
@@ -2314,14 +2314,14 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D90" s="26" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.6336</x:v>
       </x:c>
       <x:c r="E90" s="26" t="str"/>
       <x:c r="F90" s="26" t="n">
-        <x:v>0.6276</x:v>
+        <x:v>0.4286</x:v>
       </x:c>
       <x:c r="G90" t="n">
-        <x:v>2.2</x:v>
+        <x:v>3.52</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="48" customHeight="1">
@@ -2335,14 +2335,14 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D91" s="26" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.6171</x:v>
       </x:c>
       <x:c r="E91" s="26" t="str"/>
       <x:c r="F91" s="26" t="n">
-        <x:v>0.7102</x:v>
+        <x:v>0.5143</x:v>
       </x:c>
       <x:c r="G91" t="n">
-        <x:v>2.53</x:v>
+        <x:v>4.048</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="48" customHeight="1">
@@ -2356,14 +2356,14 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D92" s="26" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.6007</x:v>
       </x:c>
       <x:c r="E92" s="26" t="str"/>
       <x:c r="F92" s="26" t="n">
-        <x:v>0.848</x:v>
+        <x:v>0.6571</x:v>
       </x:c>
       <x:c r="G92" t="n">
-        <x:v>2.86</x:v>
+        <x:v>4.576</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="48" customHeight="1">
@@ -2377,16 +2377,16 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D93" s="26" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.5843</x:v>
       </x:c>
       <x:c r="E93" s="26" t="str">
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F93" s="26" t="n">
-        <x:v>1.0408</x:v>
+        <x:v>0.8571</x:v>
       </x:c>
       <x:c r="G93" t="n">
-        <x:v>2.75</x:v>
+        <x:v>4.4</x:v>
       </x:c>
     </x:row>
     <x:row r="94" ht="48" customHeight="1">
@@ -2400,14 +2400,14 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="D94" s="26" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.5679</x:v>
       </x:c>
       <x:c r="E94" s="26" t="str"/>
       <x:c r="F94" s="26" t="n">
-        <x:v>1.2888</x:v>
+        <x:v>1.1143</x:v>
       </x:c>
       <x:c r="G94" t="n">
-        <x:v>3.63</x:v>
+        <x:v>5.808</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="48" customHeight="1">
@@ -2421,14 +2421,14 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D95" s="26" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.5514</x:v>
       </x:c>
       <x:c r="E95" s="26" t="str"/>
       <x:c r="F95" s="26" t="n">
-        <x:v>1.5918</x:v>
+        <x:v>1.4286</x:v>
       </x:c>
       <x:c r="G95" t="n">
-        <x:v>4.07</x:v>
+        <x:v>6.512</x:v>
       </x:c>
     </x:row>
     <x:row r="96" ht="48" customHeight="1">
@@ -2442,14 +2442,14 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D96" s="26" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.535</x:v>
       </x:c>
       <x:c r="E96" s="26" t="str"/>
       <x:c r="F96" s="26" t="n">
-        <x:v>1.95</x:v>
+        <x:v>1.8</x:v>
       </x:c>
       <x:c r="G96" t="n">
-        <x:v>4.51</x:v>
+        <x:v>7.216</x:v>
       </x:c>
     </x:row>
     <x:row r="97" ht="48" customHeight="1">
@@ -2463,14 +2463,14 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D97" s="26" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.5186</x:v>
       </x:c>
       <x:c r="E97" s="26" t="str"/>
       <x:c r="F97" s="26" t="n">
-        <x:v>2.3633</x:v>
+        <x:v>2.2286</x:v>
       </x:c>
       <x:c r="G97" t="n">
-        <x:v>4.95</x:v>
+        <x:v>7.92</x:v>
       </x:c>
     </x:row>
     <x:row r="98" ht="48" customHeight="1">
@@ -2484,16 +2484,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D98" s="26" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.5021</x:v>
       </x:c>
       <x:c r="E98" s="26" t="str">
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F98" s="26" t="n">
-        <x:v>2.8316</x:v>
+        <x:v>2.7143</x:v>
       </x:c>
       <x:c r="G98" t="n">
-        <x:v>6.6</x:v>
+        <x:v>10.56</x:v>
       </x:c>
     </x:row>
     <x:row r="99" ht="48" customHeight="1">
@@ -2507,14 +2507,14 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D99" s="26" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.4857</x:v>
       </x:c>
       <x:c r="E99" s="26" t="str"/>
       <x:c r="F99" s="26" t="n">
-        <x:v>3.3551</x:v>
+        <x:v>3.2571</x:v>
       </x:c>
       <x:c r="G99" t="n">
-        <x:v>6.16</x:v>
+        <x:v>9.856</x:v>
       </x:c>
     </x:row>
     <x:row r="100" ht="48" customHeight="1">
@@ -2528,14 +2528,14 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D100" s="26" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.4693</x:v>
       </x:c>
       <x:c r="E100" s="26" t="str"/>
       <x:c r="F100" s="26" t="n">
-        <x:v>3.9337</x:v>
+        <x:v>3.8571</x:v>
       </x:c>
       <x:c r="G100" t="n">
-        <x:v>6.82</x:v>
+        <x:v>10.912</x:v>
       </x:c>
     </x:row>
     <x:row r="101" ht="48" customHeight="1">
@@ -2549,14 +2549,14 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="D101" s="26" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.4529</x:v>
       </x:c>
       <x:c r="E101" s="26" t="str"/>
       <x:c r="F101" s="26" t="n">
-        <x:v>4.5673</x:v>
+        <x:v>4.5143</x:v>
       </x:c>
       <x:c r="G101" t="n">
-        <x:v>7.59</x:v>
+        <x:v>12.144</x:v>
       </x:c>
     </x:row>
     <x:row r="102" ht="48" customHeight="1">
@@ -2570,14 +2570,14 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D102" s="26" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.4364</x:v>
       </x:c>
       <x:c r="E102" s="26" t="str"/>
       <x:c r="F102" s="26" t="n">
-        <x:v>5.2561</x:v>
+        <x:v>5.2286</x:v>
       </x:c>
       <x:c r="G102" t="n">
-        <x:v>8.36</x:v>
+        <x:v>13.376</x:v>
       </x:c>
     </x:row>
     <x:row r="103" ht="48" customHeight="1">
@@ -2591,7 +2591,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="D103" s="26" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.42</x:v>
       </x:c>
       <x:c r="E103" s="26" t="str">
         <x:v>challenge.bossWave</x:v>
@@ -2600,7 +2600,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="G103" t="n">
-        <x:v>11</x:v>
+        <x:v>17.6</x:v>
       </x:c>
     </x:row>
     <x:row r="104" ht="48" customHeight="1">
@@ -2614,14 +2614,14 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D104" s="26" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.65</x:v>
       </x:c>
       <x:c r="E104" s="26" t="str"/>
       <x:c r="F104" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="G104" t="n">
-        <x:v>1.881</x:v>
+        <x:v>3.0096</x:v>
       </x:c>
     </x:row>
     <x:row r="105" ht="48" customHeight="1">
@@ -2635,14 +2635,14 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D105" s="26" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.6336</x:v>
       </x:c>
       <x:c r="E105" s="26" t="str"/>
       <x:c r="F105" s="26" t="n">
-        <x:v>0.5138</x:v>
+        <x:v>0.4031</x:v>
       </x:c>
       <x:c r="G105" t="n">
-        <x:v>2.09</x:v>
+        <x:v>3.3477</x:v>
       </x:c>
     </x:row>
     <x:row r="106" ht="48" customHeight="1">
@@ -2656,14 +2656,14 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D106" s="26" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.6171</x:v>
       </x:c>
       <x:c r="E106" s="26" t="str"/>
       <x:c r="F106" s="26" t="n">
-        <x:v>0.5551</x:v>
+        <x:v>0.4251</x:v>
       </x:c>
       <x:c r="G106" t="n">
-        <x:v>2.4035</x:v>
+        <x:v>3.8792</x:v>
       </x:c>
     </x:row>
     <x:row r="107" ht="48" customHeight="1">
@@ -2677,14 +2677,14 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D107" s="26" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.6007</x:v>
       </x:c>
       <x:c r="E107" s="26" t="str"/>
       <x:c r="F107" s="26" t="n">
-        <x:v>0.624</x:v>
+        <x:v>0.4846</x:v>
       </x:c>
       <x:c r="G107" t="n">
-        <x:v>2.717</x:v>
+        <x:v>4.4755</x:v>
       </x:c>
     </x:row>
     <x:row r="108" ht="48" customHeight="1">
@@ -2698,16 +2698,16 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D108" s="26" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.5843</x:v>
       </x:c>
       <x:c r="E108" s="26" t="str">
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F108" s="26" t="n">
-        <x:v>0.7204</x:v>
+        <x:v>0.6006</x:v>
       </x:c>
       <x:c r="G108" t="n">
-        <x:v>2.6125</x:v>
+        <x:v>4.4725</x:v>
       </x:c>
     </x:row>
     <x:row r="109" ht="48" customHeight="1">
@@ -2721,14 +2721,14 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="D109" s="26" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.5679</x:v>
       </x:c>
       <x:c r="E109" s="26" t="str"/>
       <x:c r="F109" s="26" t="n">
-        <x:v>0.8444</x:v>
+        <x:v>0.7918</x:v>
       </x:c>
       <x:c r="G109" t="n">
-        <x:v>3.4485</x:v>
+        <x:v>6.2716</x:v>
       </x:c>
     </x:row>
     <x:row r="110">
@@ -2742,14 +2742,14 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D110" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.5514</x:v>
       </x:c>
       <x:c r="E110" t="str"/>
       <x:c r="F110" t="n">
-        <x:v>0.9959</x:v>
+        <x:v>1.077</x:v>
       </x:c>
       <x:c r="G110" t="n">
-        <x:v>3.8665</x:v>
+        <x:v>7.6473</x:v>
       </x:c>
     </x:row>
     <x:row r="111">
@@ -2763,14 +2763,14 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D111" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.535</x:v>
       </x:c>
       <x:c r="E111" t="str"/>
       <x:c r="F111" t="n">
-        <x:v>1.175</x:v>
+        <x:v>1.475</x:v>
       </x:c>
       <x:c r="G111" t="n">
-        <x:v>4.2845</x:v>
+        <x:v>9.4259</x:v>
       </x:c>
     </x:row>
     <x:row r="112">
@@ -2784,14 +2784,14 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D112" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.5186</x:v>
       </x:c>
       <x:c r="E112" t="str"/>
       <x:c r="F112" t="n">
-        <x:v>1.3816</x:v>
+        <x:v>2.0047</x:v>
       </x:c>
       <x:c r="G112" t="n">
-        <x:v>4.7025</x:v>
+        <x:v>11.7357</x:v>
       </x:c>
     </x:row>
     <x:row r="113">
@@ -2805,16 +2805,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D113" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.5021</x:v>
       </x:c>
       <x:c r="E113" t="str">
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F113" t="n">
-        <x:v>1.6158</x:v>
+        <x:v>2.6848</x:v>
       </x:c>
       <x:c r="G113" t="n">
-        <x:v>6.27</x:v>
+        <x:v>18.0276</x:v>
       </x:c>
     </x:row>
     <x:row r="114">
@@ -2828,14 +2828,14 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D114" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.4857</x:v>
       </x:c>
       <x:c r="E114" t="str"/>
       <x:c r="F114" t="n">
-        <x:v>1.8776</x:v>
+        <x:v>3.5341</x:v>
       </x:c>
       <x:c r="G114" t="n">
-        <x:v>5.852</x:v>
+        <x:v>19.5999</x:v>
       </x:c>
     </x:row>
     <x:row r="115">
@@ -2849,14 +2849,14 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D115" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.4693</x:v>
       </x:c>
       <x:c r="E115" t="str"/>
       <x:c r="F115" t="n">
-        <x:v>2.1668</x:v>
+        <x:v>4.5715</x:v>
       </x:c>
       <x:c r="G115" t="n">
-        <x:v>6.479</x:v>
+        <x:v>25.4513</x:v>
       </x:c>
     </x:row>
     <x:row r="116">
@@ -2870,14 +2870,14 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="D116" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.4529</x:v>
       </x:c>
       <x:c r="E116" t="str"/>
       <x:c r="F116" t="n">
-        <x:v>2.4837</x:v>
+        <x:v>5.8157</x:v>
       </x:c>
       <x:c r="G116" t="n">
-        <x:v>7.2105</x:v>
+        <x:v>33.3323</x:v>
       </x:c>
     </x:row>
     <x:row r="117">
@@ -2891,14 +2891,14 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D117" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.4364</x:v>
       </x:c>
       <x:c r="E117" t="str"/>
       <x:c r="F117" t="n">
-        <x:v>2.8281</x:v>
+        <x:v>7.2856</x:v>
       </x:c>
       <x:c r="G117" t="n">
-        <x:v>7.942</x:v>
+        <x:v>43.2295</x:v>
       </x:c>
     </x:row>
     <x:row r="118">
@@ -2912,16 +2912,16 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="D118" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.42</x:v>
       </x:c>
       <x:c r="E118" t="str">
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F118" t="n">
-        <x:v>3.2</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G118" t="n">
-        <x:v>10.45</x:v>
+        <x:v>66.88</x:v>
       </x:c>
     </x:row>
     <x:row r="119">
@@ -2935,14 +2935,14 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D119" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.65</x:v>
       </x:c>
       <x:c r="E119" t="str"/>
       <x:c r="F119" t="n">
-        <x:v>0.6</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="G119" t="n">
-        <x:v>1.98</x:v>
+        <x:v>3.168</x:v>
       </x:c>
     </x:row>
     <x:row r="120">
@@ -2956,14 +2956,14 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D120" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.6336</x:v>
       </x:c>
       <x:c r="E120" t="str"/>
       <x:c r="F120" t="n">
-        <x:v>0.6276</x:v>
+        <x:v>0.4286</x:v>
       </x:c>
       <x:c r="G120" t="n">
-        <x:v>2.2</x:v>
+        <x:v>3.52</x:v>
       </x:c>
     </x:row>
     <x:row r="121">
@@ -2977,14 +2977,14 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D121" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.6171</x:v>
       </x:c>
       <x:c r="E121" t="str"/>
       <x:c r="F121" t="n">
-        <x:v>0.7102</x:v>
+        <x:v>0.5143</x:v>
       </x:c>
       <x:c r="G121" t="n">
-        <x:v>2.53</x:v>
+        <x:v>4.048</x:v>
       </x:c>
     </x:row>
     <x:row r="122">
@@ -2998,14 +2998,14 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D122" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.6007</x:v>
       </x:c>
       <x:c r="E122" t="str"/>
       <x:c r="F122" t="n">
-        <x:v>0.848</x:v>
+        <x:v>0.6571</x:v>
       </x:c>
       <x:c r="G122" t="n">
-        <x:v>2.86</x:v>
+        <x:v>4.576</x:v>
       </x:c>
     </x:row>
     <x:row r="123">
@@ -3019,16 +3019,16 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D123" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.5843</x:v>
       </x:c>
       <x:c r="E123" t="str">
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F123" t="n">
-        <x:v>1.0408</x:v>
+        <x:v>0.8571</x:v>
       </x:c>
       <x:c r="G123" t="n">
-        <x:v>2.75</x:v>
+        <x:v>4.4</x:v>
       </x:c>
     </x:row>
     <x:row r="124">
@@ -3042,14 +3042,14 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="D124" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.5679</x:v>
       </x:c>
       <x:c r="E124" t="str"/>
       <x:c r="F124" t="n">
-        <x:v>1.2888</x:v>
+        <x:v>1.1143</x:v>
       </x:c>
       <x:c r="G124" t="n">
-        <x:v>3.63</x:v>
+        <x:v>5.808</x:v>
       </x:c>
     </x:row>
     <x:row r="125">
@@ -3063,14 +3063,14 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D125" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.5514</x:v>
       </x:c>
       <x:c r="E125" t="str"/>
       <x:c r="F125" t="n">
-        <x:v>1.5918</x:v>
+        <x:v>1.4286</x:v>
       </x:c>
       <x:c r="G125" t="n">
-        <x:v>4.07</x:v>
+        <x:v>6.512</x:v>
       </x:c>
     </x:row>
     <x:row r="126">
@@ -3084,14 +3084,14 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D126" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.535</x:v>
       </x:c>
       <x:c r="E126" t="str"/>
       <x:c r="F126" t="n">
-        <x:v>1.95</x:v>
+        <x:v>1.8</x:v>
       </x:c>
       <x:c r="G126" t="n">
-        <x:v>4.51</x:v>
+        <x:v>7.216</x:v>
       </x:c>
     </x:row>
     <x:row r="127">
@@ -3105,14 +3105,14 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D127" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.5186</x:v>
       </x:c>
       <x:c r="E127" t="str"/>
       <x:c r="F127" t="n">
-        <x:v>2.3633</x:v>
+        <x:v>2.2286</x:v>
       </x:c>
       <x:c r="G127" t="n">
-        <x:v>4.95</x:v>
+        <x:v>7.92</x:v>
       </x:c>
     </x:row>
     <x:row r="128">
@@ -3126,16 +3126,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D128" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.5021</x:v>
       </x:c>
       <x:c r="E128" t="str">
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F128" t="n">
-        <x:v>2.8316</x:v>
+        <x:v>2.7143</x:v>
       </x:c>
       <x:c r="G128" t="n">
-        <x:v>6.6</x:v>
+        <x:v>10.56</x:v>
       </x:c>
     </x:row>
     <x:row r="129">
@@ -3149,14 +3149,14 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D129" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.4857</x:v>
       </x:c>
       <x:c r="E129" t="str"/>
       <x:c r="F129" t="n">
-        <x:v>3.3551</x:v>
+        <x:v>3.2571</x:v>
       </x:c>
       <x:c r="G129" t="n">
-        <x:v>6.16</x:v>
+        <x:v>9.856</x:v>
       </x:c>
     </x:row>
     <x:row r="130">
@@ -3170,14 +3170,14 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D130" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.4693</x:v>
       </x:c>
       <x:c r="E130" t="str"/>
       <x:c r="F130" t="n">
-        <x:v>3.9337</x:v>
+        <x:v>3.8571</x:v>
       </x:c>
       <x:c r="G130" t="n">
-        <x:v>6.82</x:v>
+        <x:v>10.912</x:v>
       </x:c>
     </x:row>
     <x:row r="131">
@@ -3191,14 +3191,14 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="D131" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.4529</x:v>
       </x:c>
       <x:c r="E131" t="str"/>
       <x:c r="F131" t="n">
-        <x:v>4.5673</x:v>
+        <x:v>4.5143</x:v>
       </x:c>
       <x:c r="G131" t="n">
-        <x:v>7.59</x:v>
+        <x:v>12.144</x:v>
       </x:c>
     </x:row>
     <x:row r="132">
@@ -3212,14 +3212,14 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D132" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.4364</x:v>
       </x:c>
       <x:c r="E132" t="str"/>
       <x:c r="F132" t="n">
-        <x:v>5.2561</x:v>
+        <x:v>5.2286</x:v>
       </x:c>
       <x:c r="G132" t="n">
-        <x:v>8.36</x:v>
+        <x:v>13.376</x:v>
       </x:c>
     </x:row>
     <x:row r="133">
@@ -3233,7 +3233,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="D133" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.42</x:v>
       </x:c>
       <x:c r="E133" t="str">
         <x:v>challenge.bossWave</x:v>
@@ -3242,7 +3242,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="G133" t="n">
-        <x:v>11</x:v>
+        <x:v>17.6</x:v>
       </x:c>
     </x:row>
     <x:row r="134">
@@ -3256,14 +3256,14 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D134" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.65</x:v>
       </x:c>
       <x:c r="E134" t="str"/>
       <x:c r="F134" t="n">
-        <x:v>0.3</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="G134" t="n">
-        <x:v>2.0196</x:v>
+        <x:v>3.2314</x:v>
       </x:c>
     </x:row>
     <x:row r="135">
@@ -3277,14 +3277,14 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D135" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.6336</x:v>
       </x:c>
       <x:c r="E135" t="str"/>
       <x:c r="F135" t="n">
-        <x:v>0.3128</x:v>
+        <x:v>0.4122</x:v>
       </x:c>
       <x:c r="G135" t="n">
-        <x:v>2.244</x:v>
+        <x:v>3.5904</x:v>
       </x:c>
     </x:row>
     <x:row r="136">
@@ -3298,14 +3298,14 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D136" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.6171</x:v>
       </x:c>
       <x:c r="E136" t="str"/>
       <x:c r="F136" t="n">
-        <x:v>0.351</x:v>
+        <x:v>0.449</x:v>
       </x:c>
       <x:c r="G136" t="n">
-        <x:v>2.5806</x:v>
+        <x:v>4.129</x:v>
       </x:c>
     </x:row>
     <x:row r="137">
@@ -3319,14 +3319,14 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D137" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.6007</x:v>
       </x:c>
       <x:c r="E137" t="str"/>
       <x:c r="F137" t="n">
-        <x:v>0.4148</x:v>
+        <x:v>0.5102</x:v>
       </x:c>
       <x:c r="G137" t="n">
-        <x:v>2.9172</x:v>
+        <x:v>4.6675</x:v>
       </x:c>
     </x:row>
     <x:row r="138">
@@ -3340,16 +3340,16 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D138" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.5843</x:v>
       </x:c>
       <x:c r="E138" t="str">
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F138" t="n">
-        <x:v>0.5041</x:v>
+        <x:v>0.5959</x:v>
       </x:c>
       <x:c r="G138" t="n">
-        <x:v>2.805</x:v>
+        <x:v>4.488</x:v>
       </x:c>
     </x:row>
     <x:row r="139">
@@ -3363,14 +3363,14 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="D139" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.5679</x:v>
       </x:c>
       <x:c r="E139" t="str"/>
       <x:c r="F139" t="n">
-        <x:v>0.6189</x:v>
+        <x:v>0.7061</x:v>
       </x:c>
       <x:c r="G139" t="n">
-        <x:v>3.7026</x:v>
+        <x:v>5.9242</x:v>
       </x:c>
     </x:row>
     <x:row r="140">
@@ -3384,14 +3384,14 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D140" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.5514</x:v>
       </x:c>
       <x:c r="E140" t="str"/>
       <x:c r="F140" t="n">
-        <x:v>0.7592</x:v>
+        <x:v>0.8408</x:v>
       </x:c>
       <x:c r="G140" t="n">
-        <x:v>4.1514</x:v>
+        <x:v>6.6422</x:v>
       </x:c>
     </x:row>
     <x:row r="141">
@@ -3405,14 +3405,14 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D141" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.535</x:v>
       </x:c>
       <x:c r="E141" t="str"/>
       <x:c r="F141" t="n">
-        <x:v>0.925</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G141" t="n">
-        <x:v>4.6002</x:v>
+        <x:v>7.3603</x:v>
       </x:c>
     </x:row>
     <x:row r="142">
@@ -3426,14 +3426,14 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D142" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.5186</x:v>
       </x:c>
       <x:c r="E142" t="str"/>
       <x:c r="F142" t="n">
-        <x:v>1.1163</x:v>
+        <x:v>1.1837</x:v>
       </x:c>
       <x:c r="G142" t="n">
-        <x:v>5.049</x:v>
+        <x:v>8.0784</x:v>
       </x:c>
     </x:row>
     <x:row r="143">
@@ -3447,16 +3447,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D143" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.5021</x:v>
       </x:c>
       <x:c r="E143" t="str">
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F143" t="n">
-        <x:v>1.3332</x:v>
+        <x:v>1.3918</x:v>
       </x:c>
       <x:c r="G143" t="n">
-        <x:v>6.732</x:v>
+        <x:v>10.7712</x:v>
       </x:c>
     </x:row>
     <x:row r="144">
@@ -3470,14 +3470,14 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D144" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.4857</x:v>
       </x:c>
       <x:c r="E144" t="str"/>
       <x:c r="F144" t="n">
-        <x:v>1.5755</x:v>
+        <x:v>1.6245</x:v>
       </x:c>
       <x:c r="G144" t="n">
-        <x:v>6.2832</x:v>
+        <x:v>10.0531</x:v>
       </x:c>
     </x:row>
     <x:row r="145">
@@ -3491,14 +3491,14 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D145" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.4693</x:v>
       </x:c>
       <x:c r="E145" t="str"/>
       <x:c r="F145" t="n">
-        <x:v>1.8434</x:v>
+        <x:v>1.8816</x:v>
       </x:c>
       <x:c r="G145" t="n">
-        <x:v>6.9564</x:v>
+        <x:v>11.1302</x:v>
       </x:c>
     </x:row>
     <x:row r="146">
@@ -3512,14 +3512,14 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="D146" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.4529</x:v>
       </x:c>
       <x:c r="E146" t="str"/>
       <x:c r="F146" t="n">
-        <x:v>2.1367</x:v>
+        <x:v>2.1633</x:v>
       </x:c>
       <x:c r="G146" t="n">
-        <x:v>7.7418</x:v>
+        <x:v>12.3869</x:v>
       </x:c>
     </x:row>
     <x:row r="147">
@@ -3533,14 +3533,14 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D147" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.4364</x:v>
       </x:c>
       <x:c r="E147" t="str"/>
       <x:c r="F147" t="n">
-        <x:v>2.4556</x:v>
+        <x:v>2.4694</x:v>
       </x:c>
       <x:c r="G147" t="n">
-        <x:v>8.5272</x:v>
+        <x:v>13.6435</x:v>
       </x:c>
     </x:row>
     <x:row r="148">
@@ -3554,7 +3554,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="D148" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.42</x:v>
       </x:c>
       <x:c r="E148" t="str">
         <x:v>challenge.bossWave</x:v>
@@ -3563,7 +3563,7 @@
         <x:v>2.8</x:v>
       </x:c>
       <x:c r="G148" t="n">
-        <x:v>11.22</x:v>
+        <x:v>17.952</x:v>
       </x:c>
     </x:row>
     <x:row r="149">
@@ -3577,14 +3577,14 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D149" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.65</x:v>
       </x:c>
       <x:c r="E149" t="str"/>
       <x:c r="F149" t="n">
-        <x:v>0.6</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="G149" t="n">
-        <x:v>2.0394</x:v>
+        <x:v>3.263</x:v>
       </x:c>
     </x:row>
     <x:row r="150">
@@ -3598,14 +3598,14 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D150" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.6336</x:v>
       </x:c>
       <x:c r="E150" t="str"/>
       <x:c r="F150" t="n">
-        <x:v>0.648</x:v>
+        <x:v>0.449</x:v>
       </x:c>
       <x:c r="G150" t="n">
-        <x:v>2.266</x:v>
+        <x:v>3.6256</x:v>
       </x:c>
     </x:row>
     <x:row r="151">
@@ -3619,14 +3619,14 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D151" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.6171</x:v>
       </x:c>
       <x:c r="E151" t="str"/>
       <x:c r="F151" t="n">
-        <x:v>0.7918</x:v>
+        <x:v>0.5959</x:v>
       </x:c>
       <x:c r="G151" t="n">
-        <x:v>2.6059</x:v>
+        <x:v>4.1694</x:v>
       </x:c>
     </x:row>
     <x:row r="152">
@@ -3640,14 +3640,14 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D152" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.6007</x:v>
       </x:c>
       <x:c r="E152" t="str"/>
       <x:c r="F152" t="n">
-        <x:v>1.0316</x:v>
+        <x:v>0.8408</x:v>
       </x:c>
       <x:c r="G152" t="n">
-        <x:v>2.9458</x:v>
+        <x:v>4.7133</x:v>
       </x:c>
     </x:row>
     <x:row r="153">
@@ -3661,16 +3661,16 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D153" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.5843</x:v>
       </x:c>
       <x:c r="E153" t="str">
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F153" t="n">
-        <x:v>1.3673</x:v>
+        <x:v>1.1837</x:v>
       </x:c>
       <x:c r="G153" t="n">
-        <x:v>2.8325</x:v>
+        <x:v>4.532</x:v>
       </x:c>
     </x:row>
     <x:row r="154">
@@ -3684,14 +3684,14 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="D154" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.5679</x:v>
       </x:c>
       <x:c r="E154" t="str"/>
       <x:c r="F154" t="n">
-        <x:v>1.799</x:v>
+        <x:v>1.6245</x:v>
       </x:c>
       <x:c r="G154" t="n">
-        <x:v>3.7389</x:v>
+        <x:v>5.9822</x:v>
       </x:c>
     </x:row>
     <x:row r="155">
@@ -3705,14 +3705,14 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D155" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.5514</x:v>
       </x:c>
       <x:c r="E155" t="str"/>
       <x:c r="F155" t="n">
-        <x:v>2.3265</x:v>
+        <x:v>2.1633</x:v>
       </x:c>
       <x:c r="G155" t="n">
-        <x:v>4.1921</x:v>
+        <x:v>6.7074</x:v>
       </x:c>
     </x:row>
     <x:row r="156">
@@ -3726,14 +3726,14 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D156" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.535</x:v>
       </x:c>
       <x:c r="E156" t="str"/>
       <x:c r="F156" t="n">
-        <x:v>2.95</x:v>
+        <x:v>2.8</x:v>
       </x:c>
       <x:c r="G156" t="n">
-        <x:v>4.6453</x:v>
+        <x:v>7.4325</x:v>
       </x:c>
     </x:row>
     <x:row r="157">
@@ -3747,14 +3747,14 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D157" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.5186</x:v>
       </x:c>
       <x:c r="E157" t="str"/>
       <x:c r="F157" t="n">
-        <x:v>3.6694</x:v>
+        <x:v>3.5347</x:v>
       </x:c>
       <x:c r="G157" t="n">
-        <x:v>5.0985</x:v>
+        <x:v>8.1576</x:v>
       </x:c>
     </x:row>
     <x:row r="158">
@@ -3768,16 +3768,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D158" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.5021</x:v>
       </x:c>
       <x:c r="E158" t="str">
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F158" t="n">
-        <x:v>4.4847</x:v>
+        <x:v>4.3673</x:v>
       </x:c>
       <x:c r="G158" t="n">
-        <x:v>6.798</x:v>
+        <x:v>10.8768</x:v>
       </x:c>
     </x:row>
     <x:row r="159">
@@ -3791,14 +3791,14 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D159" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.4857</x:v>
       </x:c>
       <x:c r="E159" t="str"/>
       <x:c r="F159" t="n">
-        <x:v>5.3959</x:v>
+        <x:v>5.298</x:v>
       </x:c>
       <x:c r="G159" t="n">
-        <x:v>6.3448</x:v>
+        <x:v>10.1517</x:v>
       </x:c>
     </x:row>
     <x:row r="160">
@@ -3812,14 +3812,14 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D160" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.4693</x:v>
       </x:c>
       <x:c r="E160" t="str"/>
       <x:c r="F160" t="n">
-        <x:v>6.4031</x:v>
+        <x:v>6.3265</x:v>
       </x:c>
       <x:c r="G160" t="n">
-        <x:v>7.0246</x:v>
+        <x:v>11.2394</x:v>
       </x:c>
     </x:row>
     <x:row r="161">
@@ -3833,14 +3833,14 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="D161" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.4529</x:v>
       </x:c>
       <x:c r="E161" t="str"/>
       <x:c r="F161" t="n">
-        <x:v>7.5061</x:v>
+        <x:v>7.4531</x:v>
       </x:c>
       <x:c r="G161" t="n">
-        <x:v>7.8177</x:v>
+        <x:v>12.5083</x:v>
       </x:c>
     </x:row>
     <x:row r="162">
@@ -3854,14 +3854,14 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D162" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.4364</x:v>
       </x:c>
       <x:c r="E162" t="str"/>
       <x:c r="F162" t="n">
-        <x:v>8.7051</x:v>
+        <x:v>8.6776</x:v>
       </x:c>
       <x:c r="G162" t="n">
-        <x:v>8.6108</x:v>
+        <x:v>13.7773</x:v>
       </x:c>
     </x:row>
     <x:row r="163">
@@ -3875,7 +3875,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="D163" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.42</x:v>
       </x:c>
       <x:c r="E163" t="str">
         <x:v>challenge.bossWave</x:v>
@@ -3884,7 +3884,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G163" t="n">
-        <x:v>11.33</x:v>
+        <x:v>18.128</x:v>
       </x:c>
     </x:row>
     <x:row r="164">
@@ -3898,14 +3898,14 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D164" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.65</x:v>
       </x:c>
       <x:c r="E164" t="str"/>
       <x:c r="F164" t="n">
-        <x:v>0.6</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="G164" t="n">
-        <x:v>2.0988</x:v>
+        <x:v>3.3581</x:v>
       </x:c>
     </x:row>
     <x:row r="165">
@@ -3919,14 +3919,14 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D165" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.6336</x:v>
       </x:c>
       <x:c r="E165" t="str"/>
       <x:c r="F165" t="n">
-        <x:v>0.6276</x:v>
+        <x:v>0.4286</x:v>
       </x:c>
       <x:c r="G165" t="n">
-        <x:v>2.332</x:v>
+        <x:v>3.7312</x:v>
       </x:c>
     </x:row>
     <x:row r="166">
@@ -3940,14 +3940,14 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D166" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.6171</x:v>
       </x:c>
       <x:c r="E166" t="str"/>
       <x:c r="F166" t="n">
-        <x:v>0.7102</x:v>
+        <x:v>0.5143</x:v>
       </x:c>
       <x:c r="G166" t="n">
-        <x:v>2.6818</x:v>
+        <x:v>4.2909</x:v>
       </x:c>
     </x:row>
     <x:row r="167">
@@ -3961,14 +3961,14 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D167" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.6007</x:v>
       </x:c>
       <x:c r="E167" t="str"/>
       <x:c r="F167" t="n">
-        <x:v>0.848</x:v>
+        <x:v>0.6571</x:v>
       </x:c>
       <x:c r="G167" t="n">
-        <x:v>3.0316</x:v>
+        <x:v>4.8506</x:v>
       </x:c>
     </x:row>
     <x:row r="168">
@@ -3982,16 +3982,16 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D168" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.5843</x:v>
       </x:c>
       <x:c r="E168" t="str">
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F168" t="n">
-        <x:v>1.0408</x:v>
+        <x:v>0.8571</x:v>
       </x:c>
       <x:c r="G168" t="n">
-        <x:v>2.915</x:v>
+        <x:v>4.664</x:v>
       </x:c>
     </x:row>
     <x:row r="169">
@@ -4005,14 +4005,14 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="D169" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.5679</x:v>
       </x:c>
       <x:c r="E169" t="str"/>
       <x:c r="F169" t="n">
-        <x:v>1.2888</x:v>
+        <x:v>1.1143</x:v>
       </x:c>
       <x:c r="G169" t="n">
-        <x:v>3.8478</x:v>
+        <x:v>6.1565</x:v>
       </x:c>
     </x:row>
     <x:row r="170">
@@ -4026,14 +4026,14 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D170" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.5514</x:v>
       </x:c>
       <x:c r="E170" t="str"/>
       <x:c r="F170" t="n">
-        <x:v>1.5918</x:v>
+        <x:v>1.4286</x:v>
       </x:c>
       <x:c r="G170" t="n">
-        <x:v>4.3142</x:v>
+        <x:v>6.9027</x:v>
       </x:c>
     </x:row>
     <x:row r="171">
@@ -4047,14 +4047,14 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D171" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.535</x:v>
       </x:c>
       <x:c r="E171" t="str"/>
       <x:c r="F171" t="n">
-        <x:v>1.95</x:v>
+        <x:v>1.8</x:v>
       </x:c>
       <x:c r="G171" t="n">
-        <x:v>4.7806</x:v>
+        <x:v>7.649</x:v>
       </x:c>
     </x:row>
     <x:row r="172">
@@ -4068,14 +4068,14 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D172" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.5186</x:v>
       </x:c>
       <x:c r="E172" t="str"/>
       <x:c r="F172" t="n">
-        <x:v>2.3633</x:v>
+        <x:v>2.2286</x:v>
       </x:c>
       <x:c r="G172" t="n">
-        <x:v>5.247</x:v>
+        <x:v>8.3952</x:v>
       </x:c>
     </x:row>
     <x:row r="173">
@@ -4089,16 +4089,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D173" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.5021</x:v>
       </x:c>
       <x:c r="E173" t="str">
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F173" t="n">
-        <x:v>2.8316</x:v>
+        <x:v>2.7143</x:v>
       </x:c>
       <x:c r="G173" t="n">
-        <x:v>6.996</x:v>
+        <x:v>11.1936</x:v>
       </x:c>
     </x:row>
     <x:row r="174">
@@ -4112,14 +4112,14 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D174" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.4857</x:v>
       </x:c>
       <x:c r="E174" t="str"/>
       <x:c r="F174" t="n">
-        <x:v>3.3551</x:v>
+        <x:v>3.2571</x:v>
       </x:c>
       <x:c r="G174" t="n">
-        <x:v>6.5296</x:v>
+        <x:v>10.4474</x:v>
       </x:c>
     </x:row>
     <x:row r="175">
@@ -4133,14 +4133,14 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D175" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.4693</x:v>
       </x:c>
       <x:c r="E175" t="str"/>
       <x:c r="F175" t="n">
-        <x:v>3.9337</x:v>
+        <x:v>3.8571</x:v>
       </x:c>
       <x:c r="G175" t="n">
-        <x:v>7.2292</x:v>
+        <x:v>11.5667</x:v>
       </x:c>
     </x:row>
     <x:row r="176">
@@ -4154,14 +4154,14 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="D176" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.4529</x:v>
       </x:c>
       <x:c r="E176" t="str"/>
       <x:c r="F176" t="n">
-        <x:v>4.5673</x:v>
+        <x:v>4.5143</x:v>
       </x:c>
       <x:c r="G176" t="n">
-        <x:v>8.0454</x:v>
+        <x:v>12.8726</x:v>
       </x:c>
     </x:row>
     <x:row r="177">
@@ -4175,14 +4175,14 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D177" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.4364</x:v>
       </x:c>
       <x:c r="E177" t="str"/>
       <x:c r="F177" t="n">
-        <x:v>5.2561</x:v>
+        <x:v>5.2286</x:v>
       </x:c>
       <x:c r="G177" t="n">
-        <x:v>8.8616</x:v>
+        <x:v>14.1786</x:v>
       </x:c>
     </x:row>
     <x:row r="178">
@@ -4196,7 +4196,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="D178" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.42</x:v>
       </x:c>
       <x:c r="E178" t="str">
         <x:v>challenge.bossWave</x:v>
@@ -4205,7 +4205,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="G178" t="n">
-        <x:v>11.66</x:v>
+        <x:v>18.656</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/design/tables/Wave.xlsx
+++ b/design/tables/Wave.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wave" sheetId="1" r:id="R38cb25b1bf8c4816"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wave" sheetId="1" r:id="R0140135cd8584715"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2297,7 +2297,7 @@
       </x:c>
       <x:c r="E89" s="26" t="str"/>
       <x:c r="F89" s="26" t="n">
-        <x:v>0.4</x:v>
+        <x:v>0.65</x:v>
       </x:c>
       <x:c r="G89" t="n">
         <x:v>3.168</x:v>
@@ -2318,7 +2318,7 @@
       </x:c>
       <x:c r="E90" s="26" t="str"/>
       <x:c r="F90" s="26" t="n">
-        <x:v>0.4286</x:v>
+        <x:v>0.6834</x:v>
       </x:c>
       <x:c r="G90" t="n">
         <x:v>3.52</x:v>
@@ -2339,7 +2339,7 @@
       </x:c>
       <x:c r="E91" s="26" t="str"/>
       <x:c r="F91" s="26" t="n">
-        <x:v>0.5143</x:v>
+        <x:v>0.7837</x:v>
       </x:c>
       <x:c r="G91" t="n">
         <x:v>4.048</x:v>
@@ -2360,7 +2360,7 @@
       </x:c>
       <x:c r="E92" s="26" t="str"/>
       <x:c r="F92" s="26" t="n">
-        <x:v>0.6571</x:v>
+        <x:v>0.9508</x:v>
       </x:c>
       <x:c r="G92" t="n">
         <x:v>4.576</x:v>
@@ -2383,7 +2383,7 @@
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F93" s="26" t="n">
-        <x:v>0.8571</x:v>
+        <x:v>1.1847</x:v>
       </x:c>
       <x:c r="G93" t="n">
         <x:v>4.4</x:v>
@@ -2404,7 +2404,7 @@
       </x:c>
       <x:c r="E94" s="26" t="str"/>
       <x:c r="F94" s="26" t="n">
-        <x:v>1.1143</x:v>
+        <x:v>1.4855</x:v>
       </x:c>
       <x:c r="G94" t="n">
         <x:v>5.808</x:v>
@@ -2425,7 +2425,7 @@
       </x:c>
       <x:c r="E95" s="26" t="str"/>
       <x:c r="F95" s="26" t="n">
-        <x:v>1.4286</x:v>
+        <x:v>1.8531</x:v>
       </x:c>
       <x:c r="G95" t="n">
         <x:v>6.512</x:v>
@@ -2446,7 +2446,7 @@
       </x:c>
       <x:c r="E96" s="26" t="str"/>
       <x:c r="F96" s="26" t="n">
-        <x:v>1.8</x:v>
+        <x:v>2.2875</x:v>
       </x:c>
       <x:c r="G96" t="n">
         <x:v>7.216</x:v>
@@ -2467,7 +2467,7 @@
       </x:c>
       <x:c r="E97" s="26" t="str"/>
       <x:c r="F97" s="26" t="n">
-        <x:v>2.2286</x:v>
+        <x:v>2.7888</x:v>
       </x:c>
       <x:c r="G97" t="n">
         <x:v>7.92</x:v>
@@ -2490,7 +2490,7 @@
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F98" s="26" t="n">
-        <x:v>2.7143</x:v>
+        <x:v>3.3569</x:v>
       </x:c>
       <x:c r="G98" t="n">
         <x:v>10.56</x:v>
@@ -2511,7 +2511,7 @@
       </x:c>
       <x:c r="E99" s="26" t="str"/>
       <x:c r="F99" s="26" t="n">
-        <x:v>3.2571</x:v>
+        <x:v>3.9918</x:v>
       </x:c>
       <x:c r="G99" t="n">
         <x:v>9.856</x:v>
@@ -2532,7 +2532,7 @@
       </x:c>
       <x:c r="E100" s="26" t="str"/>
       <x:c r="F100" s="26" t="n">
-        <x:v>3.8571</x:v>
+        <x:v>4.6936</x:v>
       </x:c>
       <x:c r="G100" t="n">
         <x:v>10.912</x:v>
@@ -2553,7 +2553,7 @@
       </x:c>
       <x:c r="E101" s="26" t="str"/>
       <x:c r="F101" s="26" t="n">
-        <x:v>4.5143</x:v>
+        <x:v>5.4622</x:v>
       </x:c>
       <x:c r="G101" t="n">
         <x:v>12.144</x:v>
@@ -2574,7 +2574,7 @@
       </x:c>
       <x:c r="E102" s="26" t="str"/>
       <x:c r="F102" s="26" t="n">
-        <x:v>5.2286</x:v>
+        <x:v>6.2977</x:v>
       </x:c>
       <x:c r="G102" t="n">
         <x:v>13.376</x:v>
@@ -2597,7 +2597,7 @@
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F103" s="26" t="n">
-        <x:v>6</x:v>
+        <x:v>7.2</x:v>
       </x:c>
       <x:c r="G103" t="n">
         <x:v>17.6</x:v>
@@ -2618,7 +2618,7 @@
       </x:c>
       <x:c r="E104" s="26" t="str"/>
       <x:c r="F104" s="26" t="n">
-        <x:v>0.4</x:v>
+        <x:v>0.55</x:v>
       </x:c>
       <x:c r="G104" t="n">
         <x:v>3.0096</x:v>
@@ -2639,7 +2639,7 @@
       </x:c>
       <x:c r="E105" s="26" t="str"/>
       <x:c r="F105" s="26" t="n">
-        <x:v>0.4031</x:v>
+        <x:v>0.5558</x:v>
       </x:c>
       <x:c r="G105" t="n">
         <x:v>3.3477</x:v>
@@ -2660,7 +2660,7 @@
       </x:c>
       <x:c r="E106" s="26" t="str"/>
       <x:c r="F106" s="26" t="n">
-        <x:v>0.4251</x:v>
+        <x:v>0.5902</x:v>
       </x:c>
       <x:c r="G106" t="n">
         <x:v>3.8792</x:v>
@@ -2681,7 +2681,7 @@
       </x:c>
       <x:c r="E107" s="26" t="str"/>
       <x:c r="F107" s="26" t="n">
-        <x:v>0.4846</x:v>
+        <x:v>0.6752</x:v>
       </x:c>
       <x:c r="G107" t="n">
         <x:v>4.4755</x:v>
@@ -2704,7 +2704,7 @@
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F108" s="26" t="n">
-        <x:v>0.6006</x:v>
+        <x:v>0.8302</x:v>
       </x:c>
       <x:c r="G108" t="n">
         <x:v>4.4725</x:v>
@@ -2725,7 +2725,7 @@
       </x:c>
       <x:c r="E109" s="26" t="str"/>
       <x:c r="F109" s="26" t="n">
-        <x:v>0.7918</x:v>
+        <x:v>1.0733</x:v>
       </x:c>
       <x:c r="G109" t="n">
         <x:v>6.2716</x:v>
@@ -2746,7 +2746,7 @@
       </x:c>
       <x:c r="E110" t="str"/>
       <x:c r="F110" t="n">
-        <x:v>1.077</x:v>
+        <x:v>1.4219</x:v>
       </x:c>
       <x:c r="G110" t="n">
         <x:v>7.6473</x:v>
@@ -2767,7 +2767,7 @@
       </x:c>
       <x:c r="E111" t="str"/>
       <x:c r="F111" t="n">
-        <x:v>1.475</x:v>
+        <x:v>1.8925</x:v>
       </x:c>
       <x:c r="G111" t="n">
         <x:v>9.4259</x:v>
@@ -2788,7 +2788,7 @@
       </x:c>
       <x:c r="E112" t="str"/>
       <x:c r="F112" t="n">
-        <x:v>2.0047</x:v>
+        <x:v>2.5012</x:v>
       </x:c>
       <x:c r="G112" t="n">
         <x:v>11.7357</x:v>
@@ -2811,7 +2811,7 @@
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F113" t="n">
-        <x:v>2.6848</x:v>
+        <x:v>3.2635</x:v>
       </x:c>
       <x:c r="G113" t="n">
         <x:v>18.0276</x:v>
@@ -2832,7 +2832,7 @@
       </x:c>
       <x:c r="E114" t="str"/>
       <x:c r="F114" t="n">
-        <x:v>3.5341</x:v>
+        <x:v>4.1946</x:v>
       </x:c>
       <x:c r="G114" t="n">
         <x:v>19.5999</x:v>
@@ -2853,7 +2853,7 @@
       </x:c>
       <x:c r="E115" t="str"/>
       <x:c r="F115" t="n">
-        <x:v>4.5715</x:v>
+        <x:v>5.3094</x:v>
       </x:c>
       <x:c r="G115" t="n">
         <x:v>25.4513</x:v>
@@ -2874,7 +2874,7 @@
       </x:c>
       <x:c r="E116" t="str"/>
       <x:c r="F116" t="n">
-        <x:v>5.8157</x:v>
+        <x:v>6.6224</x:v>
       </x:c>
       <x:c r="G116" t="n">
         <x:v>33.3323</x:v>
@@ -2895,7 +2895,7 @@
       </x:c>
       <x:c r="E117" t="str"/>
       <x:c r="F117" t="n">
-        <x:v>7.2856</x:v>
+        <x:v>8.1479</x:v>
       </x:c>
       <x:c r="G117" t="n">
         <x:v>43.2295</x:v>
@@ -2918,7 +2918,7 @@
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F118" t="n">
-        <x:v>9</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="G118" t="n">
         <x:v>66.88</x:v>
@@ -2939,7 +2939,7 @@
       </x:c>
       <x:c r="E119" t="str"/>
       <x:c r="F119" t="n">
-        <x:v>0.4</x:v>
+        <x:v>0.65</x:v>
       </x:c>
       <x:c r="G119" t="n">
         <x:v>3.168</x:v>
@@ -2960,7 +2960,7 @@
       </x:c>
       <x:c r="E120" t="str"/>
       <x:c r="F120" t="n">
-        <x:v>0.4286</x:v>
+        <x:v>0.6834</x:v>
       </x:c>
       <x:c r="G120" t="n">
         <x:v>3.52</x:v>
@@ -2981,7 +2981,7 @@
       </x:c>
       <x:c r="E121" t="str"/>
       <x:c r="F121" t="n">
-        <x:v>0.5143</x:v>
+        <x:v>0.7837</x:v>
       </x:c>
       <x:c r="G121" t="n">
         <x:v>4.048</x:v>
@@ -3002,7 +3002,7 @@
       </x:c>
       <x:c r="E122" t="str"/>
       <x:c r="F122" t="n">
-        <x:v>0.6571</x:v>
+        <x:v>0.9508</x:v>
       </x:c>
       <x:c r="G122" t="n">
         <x:v>4.576</x:v>
@@ -3025,7 +3025,7 @@
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F123" t="n">
-        <x:v>0.8571</x:v>
+        <x:v>1.1847</x:v>
       </x:c>
       <x:c r="G123" t="n">
         <x:v>4.4</x:v>
@@ -3046,7 +3046,7 @@
       </x:c>
       <x:c r="E124" t="str"/>
       <x:c r="F124" t="n">
-        <x:v>1.1143</x:v>
+        <x:v>1.4855</x:v>
       </x:c>
       <x:c r="G124" t="n">
         <x:v>5.808</x:v>
@@ -3067,7 +3067,7 @@
       </x:c>
       <x:c r="E125" t="str"/>
       <x:c r="F125" t="n">
-        <x:v>1.4286</x:v>
+        <x:v>1.8531</x:v>
       </x:c>
       <x:c r="G125" t="n">
         <x:v>6.512</x:v>
@@ -3088,7 +3088,7 @@
       </x:c>
       <x:c r="E126" t="str"/>
       <x:c r="F126" t="n">
-        <x:v>1.8</x:v>
+        <x:v>2.2875</x:v>
       </x:c>
       <x:c r="G126" t="n">
         <x:v>7.216</x:v>
@@ -3109,7 +3109,7 @@
       </x:c>
       <x:c r="E127" t="str"/>
       <x:c r="F127" t="n">
-        <x:v>2.2286</x:v>
+        <x:v>2.7888</x:v>
       </x:c>
       <x:c r="G127" t="n">
         <x:v>7.92</x:v>
@@ -3132,7 +3132,7 @@
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F128" t="n">
-        <x:v>2.7143</x:v>
+        <x:v>3.3569</x:v>
       </x:c>
       <x:c r="G128" t="n">
         <x:v>10.56</x:v>
@@ -3153,7 +3153,7 @@
       </x:c>
       <x:c r="E129" t="str"/>
       <x:c r="F129" t="n">
-        <x:v>3.2571</x:v>
+        <x:v>3.9918</x:v>
       </x:c>
       <x:c r="G129" t="n">
         <x:v>9.856</x:v>
@@ -3174,7 +3174,7 @@
       </x:c>
       <x:c r="E130" t="str"/>
       <x:c r="F130" t="n">
-        <x:v>3.8571</x:v>
+        <x:v>4.6936</x:v>
       </x:c>
       <x:c r="G130" t="n">
         <x:v>10.912</x:v>
@@ -3195,7 +3195,7 @@
       </x:c>
       <x:c r="E131" t="str"/>
       <x:c r="F131" t="n">
-        <x:v>4.5143</x:v>
+        <x:v>5.4622</x:v>
       </x:c>
       <x:c r="G131" t="n">
         <x:v>12.144</x:v>
@@ -3216,7 +3216,7 @@
       </x:c>
       <x:c r="E132" t="str"/>
       <x:c r="F132" t="n">
-        <x:v>5.2286</x:v>
+        <x:v>6.2977</x:v>
       </x:c>
       <x:c r="G132" t="n">
         <x:v>13.376</x:v>
@@ -3239,7 +3239,7 @@
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F133" t="n">
-        <x:v>6</x:v>
+        <x:v>7.2</x:v>
       </x:c>
       <x:c r="G133" t="n">
         <x:v>17.6</x:v>
@@ -3260,7 +3260,7 @@
       </x:c>
       <x:c r="E134" t="str"/>
       <x:c r="F134" t="n">
-        <x:v>0.4</x:v>
+        <x:v>0.55</x:v>
       </x:c>
       <x:c r="G134" t="n">
         <x:v>3.2314</x:v>
@@ -3281,7 +3281,7 @@
       </x:c>
       <x:c r="E135" t="str"/>
       <x:c r="F135" t="n">
-        <x:v>0.4122</x:v>
+        <x:v>0.5737</x:v>
       </x:c>
       <x:c r="G135" t="n">
         <x:v>3.5904</x:v>
@@ -3302,7 +3302,7 @@
       </x:c>
       <x:c r="E136" t="str"/>
       <x:c r="F136" t="n">
-        <x:v>0.449</x:v>
+        <x:v>0.6449</x:v>
       </x:c>
       <x:c r="G136" t="n">
         <x:v>4.129</x:v>
@@ -3323,7 +3323,7 @@
       </x:c>
       <x:c r="E137" t="str"/>
       <x:c r="F137" t="n">
-        <x:v>0.5102</x:v>
+        <x:v>0.7635</x:v>
       </x:c>
       <x:c r="G137" t="n">
         <x:v>4.6675</x:v>
@@ -3346,7 +3346,7 @@
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F138" t="n">
-        <x:v>0.5959</x:v>
+        <x:v>0.9296</x:v>
       </x:c>
       <x:c r="G138" t="n">
         <x:v>4.488</x:v>
@@ -3367,7 +3367,7 @@
       </x:c>
       <x:c r="E139" t="str"/>
       <x:c r="F139" t="n">
-        <x:v>0.7061</x:v>
+        <x:v>1.1431</x:v>
       </x:c>
       <x:c r="G139" t="n">
         <x:v>5.9242</x:v>
@@ -3388,7 +3388,7 @@
       </x:c>
       <x:c r="E140" t="str"/>
       <x:c r="F140" t="n">
-        <x:v>0.8408</x:v>
+        <x:v>1.4041</x:v>
       </x:c>
       <x:c r="G140" t="n">
         <x:v>6.6422</x:v>
@@ -3409,7 +3409,7 @@
       </x:c>
       <x:c r="E141" t="str"/>
       <x:c r="F141" t="n">
-        <x:v>1</x:v>
+        <x:v>1.7125</x:v>
       </x:c>
       <x:c r="G141" t="n">
         <x:v>7.3603</x:v>
@@ -3430,7 +3430,7 @@
       </x:c>
       <x:c r="E142" t="str"/>
       <x:c r="F142" t="n">
-        <x:v>1.1837</x:v>
+        <x:v>2.0684</x:v>
       </x:c>
       <x:c r="G142" t="n">
         <x:v>8.0784</x:v>
@@ -3453,7 +3453,7 @@
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F143" t="n">
-        <x:v>1.3918</x:v>
+        <x:v>2.4717</x:v>
       </x:c>
       <x:c r="G143" t="n">
         <x:v>10.7712</x:v>
@@ -3474,7 +3474,7 @@
       </x:c>
       <x:c r="E144" t="str"/>
       <x:c r="F144" t="n">
-        <x:v>1.6245</x:v>
+        <x:v>2.9224</x:v>
       </x:c>
       <x:c r="G144" t="n">
         <x:v>10.0531</x:v>
@@ -3495,7 +3495,7 @@
       </x:c>
       <x:c r="E145" t="str"/>
       <x:c r="F145" t="n">
-        <x:v>1.8816</x:v>
+        <x:v>3.4207</x:v>
       </x:c>
       <x:c r="G145" t="n">
         <x:v>11.1302</x:v>
@@ -3516,7 +3516,7 @@
       </x:c>
       <x:c r="E146" t="str"/>
       <x:c r="F146" t="n">
-        <x:v>2.1633</x:v>
+        <x:v>3.9663</x:v>
       </x:c>
       <x:c r="G146" t="n">
         <x:v>12.3869</x:v>
@@ -3537,7 +3537,7 @@
       </x:c>
       <x:c r="E147" t="str"/>
       <x:c r="F147" t="n">
-        <x:v>2.4694</x:v>
+        <x:v>4.5594</x:v>
       </x:c>
       <x:c r="G147" t="n">
         <x:v>13.6435</x:v>
@@ -3560,7 +3560,7 @@
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F148" t="n">
-        <x:v>2.8</x:v>
+        <x:v>5.2</x:v>
       </x:c>
       <x:c r="G148" t="n">
         <x:v>17.952</x:v>
@@ -3581,7 +3581,7 @@
       </x:c>
       <x:c r="E149" t="str"/>
       <x:c r="F149" t="n">
-        <x:v>0.4</x:v>
+        <x:v>0.55</x:v>
       </x:c>
       <x:c r="G149" t="n">
         <x:v>3.263</x:v>
@@ -3602,7 +3602,7 @@
       </x:c>
       <x:c r="E150" t="str"/>
       <x:c r="F150" t="n">
-        <x:v>0.449</x:v>
+        <x:v>0.5815</x:v>
       </x:c>
       <x:c r="G150" t="n">
         <x:v>3.6256</x:v>
@@ -3623,7 +3623,7 @@
       </x:c>
       <x:c r="E151" t="str"/>
       <x:c r="F151" t="n">
-        <x:v>0.5959</x:v>
+        <x:v>0.6945</x:v>
       </x:c>
       <x:c r="G151" t="n">
         <x:v>4.1694</x:v>
@@ -3644,7 +3644,7 @@
       </x:c>
       <x:c r="E152" t="str"/>
       <x:c r="F152" t="n">
-        <x:v>0.8408</x:v>
+        <x:v>0.9026</x:v>
       </x:c>
       <x:c r="G152" t="n">
         <x:v>4.7133</x:v>
@@ -3667,7 +3667,7 @@
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F153" t="n">
-        <x:v>1.1837</x:v>
+        <x:v>1.214</x:v>
       </x:c>
       <x:c r="G153" t="n">
         <x:v>4.532</x:v>
@@ -3688,7 +3688,7 @@
       </x:c>
       <x:c r="E154" t="str"/>
       <x:c r="F154" t="n">
-        <x:v>1.6245</x:v>
+        <x:v>1.6348</x:v>
       </x:c>
       <x:c r="G154" t="n">
         <x:v>5.9822</x:v>
@@ -3709,7 +3709,7 @@
       </x:c>
       <x:c r="E155" t="str"/>
       <x:c r="F155" t="n">
-        <x:v>2.1633</x:v>
+        <x:v>2.1702</x:v>
       </x:c>
       <x:c r="G155" t="n">
         <x:v>6.7074</x:v>
@@ -3730,7 +3730,7 @@
       </x:c>
       <x:c r="E156" t="str"/>
       <x:c r="F156" t="n">
-        <x:v>2.8</x:v>
+        <x:v>2.8243</x:v>
       </x:c>
       <x:c r="G156" t="n">
         <x:v>7.4325</x:v>
@@ -3751,7 +3751,7 @@
       </x:c>
       <x:c r="E157" t="str"/>
       <x:c r="F157" t="n">
-        <x:v>3.5347</x:v>
+        <x:v>3.6009</x:v>
       </x:c>
       <x:c r="G157" t="n">
         <x:v>8.1576</x:v>
@@ -3774,7 +3774,7 @@
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F158" t="n">
-        <x:v>4.3673</x:v>
+        <x:v>4.5034</x:v>
       </x:c>
       <x:c r="G158" t="n">
         <x:v>10.8768</x:v>
@@ -3795,7 +3795,7 @@
       </x:c>
       <x:c r="E159" t="str"/>
       <x:c r="F159" t="n">
-        <x:v>5.298</x:v>
+        <x:v>5.5346</x:v>
       </x:c>
       <x:c r="G159" t="n">
         <x:v>10.1517</x:v>
@@ -3816,7 +3816,7 @@
       </x:c>
       <x:c r="E160" t="str"/>
       <x:c r="F160" t="n">
-        <x:v>6.3265</x:v>
+        <x:v>6.6975</x:v>
       </x:c>
       <x:c r="G160" t="n">
         <x:v>11.2394</x:v>
@@ -3837,7 +3837,7 @@
       </x:c>
       <x:c r="E161" t="str"/>
       <x:c r="F161" t="n">
-        <x:v>7.4531</x:v>
+        <x:v>7.9945</x:v>
       </x:c>
       <x:c r="G161" t="n">
         <x:v>12.5083</x:v>
@@ -3858,7 +3858,7 @@
       </x:c>
       <x:c r="E162" t="str"/>
       <x:c r="F162" t="n">
-        <x:v>8.6776</x:v>
+        <x:v>9.4279</x:v>
       </x:c>
       <x:c r="G162" t="n">
         <x:v>13.7773</x:v>
@@ -3881,7 +3881,7 @@
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F163" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G163" t="n">
         <x:v>18.128</x:v>
@@ -3902,7 +3902,7 @@
       </x:c>
       <x:c r="E164" t="str"/>
       <x:c r="F164" t="n">
-        <x:v>0.4</x:v>
+        <x:v>0.9</x:v>
       </x:c>
       <x:c r="G164" t="n">
         <x:v>3.3581</x:v>
@@ -3923,7 +3923,7 @@
       </x:c>
       <x:c r="E165" t="str"/>
       <x:c r="F165" t="n">
-        <x:v>0.4286</x:v>
+        <x:v>0.9321</x:v>
       </x:c>
       <x:c r="G165" t="n">
         <x:v>3.7312</x:v>
@@ -3944,7 +3944,7 @@
       </x:c>
       <x:c r="E166" t="str"/>
       <x:c r="F166" t="n">
-        <x:v>0.5143</x:v>
+        <x:v>1.0286</x:v>
       </x:c>
       <x:c r="G166" t="n">
         <x:v>4.2909</x:v>
@@ -3965,7 +3965,7 @@
       </x:c>
       <x:c r="E167" t="str"/>
       <x:c r="F167" t="n">
-        <x:v>0.6571</x:v>
+        <x:v>1.1893</x:v>
       </x:c>
       <x:c r="G167" t="n">
         <x:v>4.8506</x:v>
@@ -3988,7 +3988,7 @@
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F168" t="n">
-        <x:v>0.8571</x:v>
+        <x:v>1.4143</x:v>
       </x:c>
       <x:c r="G168" t="n">
         <x:v>4.664</x:v>
@@ -4009,7 +4009,7 @@
       </x:c>
       <x:c r="E169" t="str"/>
       <x:c r="F169" t="n">
-        <x:v>1.1143</x:v>
+        <x:v>1.7036</x:v>
       </x:c>
       <x:c r="G169" t="n">
         <x:v>6.1565</x:v>
@@ -4030,7 +4030,7 @@
       </x:c>
       <x:c r="E170" t="str"/>
       <x:c r="F170" t="n">
-        <x:v>1.4286</x:v>
+        <x:v>2.0571</x:v>
       </x:c>
       <x:c r="G170" t="n">
         <x:v>6.9027</x:v>
@@ -4051,7 +4051,7 @@
       </x:c>
       <x:c r="E171" t="str"/>
       <x:c r="F171" t="n">
-        <x:v>1.8</x:v>
+        <x:v>2.475</x:v>
       </x:c>
       <x:c r="G171" t="n">
         <x:v>7.649</x:v>
@@ -4072,7 +4072,7 @@
       </x:c>
       <x:c r="E172" t="str"/>
       <x:c r="F172" t="n">
-        <x:v>2.2286</x:v>
+        <x:v>2.9571</x:v>
       </x:c>
       <x:c r="G172" t="n">
         <x:v>8.3952</x:v>
@@ -4095,7 +4095,7 @@
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F173" t="n">
-        <x:v>2.7143</x:v>
+        <x:v>3.5036</x:v>
       </x:c>
       <x:c r="G173" t="n">
         <x:v>11.1936</x:v>
@@ -4116,7 +4116,7 @@
       </x:c>
       <x:c r="E174" t="str"/>
       <x:c r="F174" t="n">
-        <x:v>3.2571</x:v>
+        <x:v>4.1143</x:v>
       </x:c>
       <x:c r="G174" t="n">
         <x:v>10.4474</x:v>
@@ -4137,7 +4137,7 @@
       </x:c>
       <x:c r="E175" t="str"/>
       <x:c r="F175" t="n">
-        <x:v>3.8571</x:v>
+        <x:v>4.7893</x:v>
       </x:c>
       <x:c r="G175" t="n">
         <x:v>11.5667</x:v>
@@ -4158,7 +4158,7 @@
       </x:c>
       <x:c r="E176" t="str"/>
       <x:c r="F176" t="n">
-        <x:v>4.5143</x:v>
+        <x:v>5.5286</x:v>
       </x:c>
       <x:c r="G176" t="n">
         <x:v>12.8726</x:v>
@@ -4179,7 +4179,7 @@
       </x:c>
       <x:c r="E177" t="str"/>
       <x:c r="F177" t="n">
-        <x:v>5.2286</x:v>
+        <x:v>6.3321</x:v>
       </x:c>
       <x:c r="G177" t="n">
         <x:v>14.1786</x:v>
@@ -4202,7 +4202,7 @@
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F178" t="n">
-        <x:v>6</x:v>
+        <x:v>7.2</x:v>
       </x:c>
       <x:c r="G178" t="n">
         <x:v>18.656</x:v>

--- a/design/tables/Wave.xlsx
+++ b/design/tables/Wave.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wave" sheetId="1" r:id="R0140135cd8584715"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wave" sheetId="1" r:id="Rfd30d0af2cc6424a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -368,6 +368,9 @@
     <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="32" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="27.5" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="21.8799991607666" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="21.8799991607666" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="21.8799991607666" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="54" customHeight="1">
@@ -392,6 +395,15 @@
       <x:c r="G1" t="str">
         <x:v>挑战首领生命倍率</x:v>
       </x:c>
+      <x:c r="H1" t="str">
+        <x:v>普通波末新生血量增幅</x:v>
+      </x:c>
+      <x:c r="I1" t="str">
+        <x:v>普通波内出生成长指数</x:v>
+      </x:c>
+      <x:c r="J1" t="str">
+        <x:v>挑战精英独立基础血量倍率</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="26" customHeight="1">
       <x:c r="A2" s="3" t="str">
@@ -415,6 +427,15 @@
       <x:c r="G2" t="str">
         <x:v>client</x:v>
       </x:c>
+      <x:c r="H2" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="I2" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="J2" t="str">
+        <x:v>client</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="26" customHeight="1">
       <x:c r="A3" s="3" t="str">
@@ -438,6 +459,15 @@
       <x:c r="G3" t="str">
         <x:v>float</x:v>
       </x:c>
+      <x:c r="H3" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="I3" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="J3" t="str">
+        <x:v>float</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="40" customHeight="1">
       <x:c r="A4" s="6" t="str">
@@ -461,6 +491,15 @@
       <x:c r="G4" t="str">
         <x:v>首领生命倍率</x:v>
       </x:c>
+      <x:c r="H4" t="str">
+        <x:v>spawnHealthGrowth</x:v>
+      </x:c>
+      <x:c r="I4" t="str">
+        <x:v>spawnGrowthPower</x:v>
+      </x:c>
+      <x:c r="J4" t="str">
+        <x:v>eliteBaseHealthScale</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="30" customHeight="1">
       <x:c r="A5" s="5" t="str">
@@ -484,6 +523,15 @@
       <x:c r="G5" t="str">
         <x:v>bossHealthScale</x:v>
       </x:c>
+      <x:c r="H5" t="str">
+        <x:v>spawnHealthGrowth</x:v>
+      </x:c>
+      <x:c r="I5" t="str">
+        <x:v>spawnGrowthPower</x:v>
+      </x:c>
+      <x:c r="J5" t="str">
+        <x:v>eliteBaseHealthScale</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="48" hidden="0" customHeight="1">
       <x:c r="A6" s="23" t="n">
@@ -505,6 +553,15 @@
       <x:c r="G6" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="H6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I6" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J6" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="48" hidden="0" customHeight="1">
       <x:c r="A7" s="23" t="n">
@@ -526,6 +583,15 @@
       <x:c r="G7" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="H7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I7" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J7" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="48" hidden="0" customHeight="1">
       <x:c r="A8" s="23" t="n">
@@ -547,6 +613,15 @@
       <x:c r="G8" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="H8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I8" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J8" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="48" hidden="0" customHeight="1">
       <x:c r="A9" s="23" t="n">
@@ -570,6 +645,15 @@
       <x:c r="G9" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="H9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I9" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J9" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="48" hidden="0" customHeight="1">
       <x:c r="A10" s="23" t="n">
@@ -591,6 +675,15 @@
       <x:c r="G10" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="H10" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I10" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J10" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="48" hidden="0" customHeight="1">
       <x:c r="A11" s="23" t="n">
@@ -612,6 +705,15 @@
       <x:c r="G11" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="H11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I11" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J11" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="48" hidden="0" customHeight="1">
       <x:c r="A12" s="23" t="n">
@@ -633,6 +735,15 @@
       <x:c r="G12" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="H12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I12" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J12" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="48" hidden="0" customHeight="1">
       <x:c r="A13" s="23" t="n">
@@ -656,6 +767,15 @@
       <x:c r="G13" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="H13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I13" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J13" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="48" hidden="0" customHeight="1">
       <x:c r="A14" s="23" t="n">
@@ -677,6 +797,15 @@
       <x:c r="G14" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="H14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I14" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J14" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" ht="48" hidden="0" customHeight="1">
       <x:c r="A15" s="23" t="n">
@@ -698,6 +827,15 @@
       <x:c r="G15" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="H15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I15" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J15" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="16" ht="48" hidden="0" customHeight="1">
       <x:c r="A16" s="23" t="n">
@@ -719,6 +857,15 @@
       <x:c r="G16" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="H16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I16" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J16" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" ht="48" hidden="0" customHeight="1">
       <x:c r="A17" s="23" t="n">
@@ -742,6 +889,15 @@
       <x:c r="G17" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="H17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I17" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J17" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" ht="48" hidden="0" customHeight="1">
       <x:c r="A18" s="23" t="n">
@@ -763,6 +919,15 @@
       <x:c r="G18" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="H18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I18" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J18" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" ht="48" hidden="0" customHeight="1">
       <x:c r="A19" s="23" t="n">
@@ -779,9 +944,18 @@
       </x:c>
       <x:c r="E19" s="25" t="str"/>
       <x:c r="F19" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.05</x:v>
       </x:c>
       <x:c r="G19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H19" t="n">
+        <x:v>0.06666666666666667</x:v>
+      </x:c>
+      <x:c r="I19" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J19" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -800,9 +974,18 @@
       </x:c>
       <x:c r="E20" s="25" t="str"/>
       <x:c r="F20" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.1</x:v>
       </x:c>
       <x:c r="G20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H20" t="n">
+        <x:v>0.13333333333333333</x:v>
+      </x:c>
+      <x:c r="I20" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J20" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -823,9 +1006,18 @@
         <x:v>wave.404.announcement</x:v>
       </x:c>
       <x:c r="F21" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.15</x:v>
       </x:c>
       <x:c r="G21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H21" t="n">
+        <x:v>0.20000000000000004</x:v>
+      </x:c>
+      <x:c r="I21" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J21" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -849,6 +1041,15 @@
       <x:c r="G22" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="H22" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I22" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J22" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" ht="48" hidden="0" customHeight="1">
       <x:c r="A23" s="23" t="n">
@@ -865,9 +1066,18 @@
       </x:c>
       <x:c r="E23" s="25" t="str"/>
       <x:c r="F23" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.05</x:v>
       </x:c>
       <x:c r="G23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H23" t="n">
+        <x:v>0.06666666666666667</x:v>
+      </x:c>
+      <x:c r="I23" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J23" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -886,9 +1096,18 @@
       </x:c>
       <x:c r="E24" s="25" t="str"/>
       <x:c r="F24" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.1</x:v>
       </x:c>
       <x:c r="G24" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H24" t="n">
+        <x:v>0.13333333333333333</x:v>
+      </x:c>
+      <x:c r="I24" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -909,9 +1128,18 @@
         <x:v>wave.504.announcement</x:v>
       </x:c>
       <x:c r="F25" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.15</x:v>
       </x:c>
       <x:c r="G25" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H25" t="n">
+        <x:v>0.20000000000000004</x:v>
+      </x:c>
+      <x:c r="I25" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -935,6 +1163,15 @@
       <x:c r="G26" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="H26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I26" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J26" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="27" ht="48" hidden="0" customHeight="1">
       <x:c r="A27" s="23" t="n">
@@ -951,9 +1188,18 @@
       </x:c>
       <x:c r="E27" s="25" t="str"/>
       <x:c r="F27" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.025</x:v>
       </x:c>
       <x:c r="G27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H27" t="n">
+        <x:v>0.03333333333333333</x:v>
+      </x:c>
+      <x:c r="I27" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -972,9 +1218,18 @@
       </x:c>
       <x:c r="E28" s="25" t="str"/>
       <x:c r="F28" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.05</x:v>
       </x:c>
       <x:c r="G28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H28" t="n">
+        <x:v>0.06666666666666667</x:v>
+      </x:c>
+      <x:c r="I28" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -995,9 +1250,18 @@
         <x:v>wave.604.announcement</x:v>
       </x:c>
       <x:c r="F29" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.075</x:v>
       </x:c>
       <x:c r="G29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H29" t="n">
+        <x:v>0.10000000000000002</x:v>
+      </x:c>
+      <x:c r="I29" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1021,6 +1285,15 @@
       <x:c r="G30" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="H30" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I30" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J30" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="31" ht="48" hidden="0" customHeight="1">
       <x:c r="A31" s="23" t="n">
@@ -1037,9 +1310,18 @@
       </x:c>
       <x:c r="E31" s="25" t="str"/>
       <x:c r="F31" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.05</x:v>
       </x:c>
       <x:c r="G31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H31" t="n">
+        <x:v>0.06666666666666667</x:v>
+      </x:c>
+      <x:c r="I31" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1058,9 +1340,18 @@
       </x:c>
       <x:c r="E32" s="25" t="str"/>
       <x:c r="F32" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.1</x:v>
       </x:c>
       <x:c r="G32" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H32" t="n">
+        <x:v>0.13333333333333333</x:v>
+      </x:c>
+      <x:c r="I32" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J32" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1081,9 +1372,18 @@
         <x:v>wave.704.announcement</x:v>
       </x:c>
       <x:c r="F33" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.15</x:v>
       </x:c>
       <x:c r="G33" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H33" t="n">
+        <x:v>0.20000000000000004</x:v>
+      </x:c>
+      <x:c r="I33" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J33" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1109,6 +1409,15 @@
       <x:c r="G34" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="H34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I34" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J34" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="35" ht="48" hidden="0" customHeight="1">
       <x:c r="A35" s="23" t="n">
@@ -1125,9 +1434,18 @@
       </x:c>
       <x:c r="E35" s="25" t="str"/>
       <x:c r="F35" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.08</x:v>
       </x:c>
       <x:c r="G35" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H35" t="n">
+        <x:v>0.09999999999999999</x:v>
+      </x:c>
+      <x:c r="I35" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J35" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1148,9 +1466,18 @@
         <x:v>wave.803.announcement</x:v>
       </x:c>
       <x:c r="F36" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.16</x:v>
       </x:c>
       <x:c r="G36" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H36" t="n">
+        <x:v>0.19999999999999998</x:v>
+      </x:c>
+      <x:c r="I36" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J36" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1171,9 +1498,18 @@
         <x:v>wave.804.announcement</x:v>
       </x:c>
       <x:c r="F37" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.24</x:v>
       </x:c>
       <x:c r="G37" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H37" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="I37" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J37" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1197,6 +1533,15 @@
       <x:c r="G38" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="H38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I38" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J38" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="39" ht="48" hidden="0" customHeight="1">
       <x:c r="A39" s="23" t="n">
@@ -1213,9 +1558,18 @@
       </x:c>
       <x:c r="E39" s="25" t="str"/>
       <x:c r="F39" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.08</x:v>
       </x:c>
       <x:c r="G39" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H39" t="n">
+        <x:v>0.09999999999999999</x:v>
+      </x:c>
+      <x:c r="I39" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J39" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1234,9 +1588,18 @@
       </x:c>
       <x:c r="E40" s="25" t="str"/>
       <x:c r="F40" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.16</x:v>
       </x:c>
       <x:c r="G40" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H40" t="n">
+        <x:v>0.19999999999999998</x:v>
+      </x:c>
+      <x:c r="I40" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J40" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1257,9 +1620,18 @@
         <x:v>wave.904.announcement</x:v>
       </x:c>
       <x:c r="F41" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.24</x:v>
       </x:c>
       <x:c r="G41" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H41" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="I41" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J41" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1283,6 +1655,15 @@
       <x:c r="G42" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="H42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I42" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J42" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="43" ht="48" hidden="0" customHeight="1">
       <x:c r="A43" s="23" t="n">
@@ -1299,9 +1680,18 @@
       </x:c>
       <x:c r="E43" s="25" t="str"/>
       <x:c r="F43" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.08</x:v>
       </x:c>
       <x:c r="G43" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H43" t="n">
+        <x:v>0.075</x:v>
+      </x:c>
+      <x:c r="I43" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J43" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1320,9 +1710,18 @@
       </x:c>
       <x:c r="E44" s="25" t="str"/>
       <x:c r="F44" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.16</x:v>
       </x:c>
       <x:c r="G44" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H44" t="n">
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="I44" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J44" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1341,9 +1740,18 @@
       </x:c>
       <x:c r="E45" s="25" t="str"/>
       <x:c r="F45" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.24</x:v>
       </x:c>
       <x:c r="G45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H45" t="n">
+        <x:v>0.22499999999999998</x:v>
+      </x:c>
+      <x:c r="I45" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J45" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1364,9 +1772,18 @@
         <x:v>wave.1005.announcement</x:v>
       </x:c>
       <x:c r="F46" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.32</x:v>
       </x:c>
       <x:c r="G46" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H46" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="I46" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J46" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1392,6 +1809,15 @@
       <x:c r="G47" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="H47" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I47" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J47" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="48" ht="48" hidden="0" customHeight="1">
       <x:c r="A48" s="23" t="n">
@@ -1408,9 +1834,18 @@
       </x:c>
       <x:c r="E48" s="25" t="str"/>
       <x:c r="F48" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.08</x:v>
       </x:c>
       <x:c r="G48" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H48" t="n">
+        <x:v>0.09999999999999999</x:v>
+      </x:c>
+      <x:c r="I48" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J48" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1429,9 +1864,18 @@
       </x:c>
       <x:c r="E49" s="25" t="str"/>
       <x:c r="F49" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.16</x:v>
       </x:c>
       <x:c r="G49" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H49" t="n">
+        <x:v>0.19999999999999998</x:v>
+      </x:c>
+      <x:c r="I49" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J49" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1450,9 +1894,18 @@
       </x:c>
       <x:c r="E50" s="25" t="str"/>
       <x:c r="F50" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.24</x:v>
       </x:c>
       <x:c r="G50" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H50" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="I50" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J50" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1478,6 +1931,15 @@
       <x:c r="G51" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="H51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I51" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J51" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="52" ht="48" hidden="0" customHeight="1">
       <x:c r="A52" s="23" t="n">
@@ -1494,9 +1956,18 @@
       </x:c>
       <x:c r="E52" s="25" t="str"/>
       <x:c r="F52" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.08</x:v>
       </x:c>
       <x:c r="G52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H52" t="n">
+        <x:v>0.09999999999999999</x:v>
+      </x:c>
+      <x:c r="I52" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J52" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1515,9 +1986,18 @@
       </x:c>
       <x:c r="E53" s="25" t="str"/>
       <x:c r="F53" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.16</x:v>
       </x:c>
       <x:c r="G53" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H53" t="n">
+        <x:v>0.19999999999999998</x:v>
+      </x:c>
+      <x:c r="I53" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J53" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1536,9 +2016,18 @@
       </x:c>
       <x:c r="E54" s="25" t="str"/>
       <x:c r="F54" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.24</x:v>
       </x:c>
       <x:c r="G54" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H54" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="I54" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J54" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1564,6 +2053,15 @@
       <x:c r="G55" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="H55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I55" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J55" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="56" ht="48" hidden="0" customHeight="1">
       <x:c r="A56" s="23" t="n">
@@ -1580,9 +2078,18 @@
       </x:c>
       <x:c r="E56" s="25" t="str"/>
       <x:c r="F56" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.04</x:v>
       </x:c>
       <x:c r="G56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H56" t="n">
+        <x:v>0.049999999999999996</x:v>
+      </x:c>
+      <x:c r="I56" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J56" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1601,9 +2108,18 @@
       </x:c>
       <x:c r="E57" s="25" t="str"/>
       <x:c r="F57" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.08</x:v>
       </x:c>
       <x:c r="G57" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H57" t="n">
+        <x:v>0.09999999999999999</x:v>
+      </x:c>
+      <x:c r="I57" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J57" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1622,9 +2138,18 @@
       </x:c>
       <x:c r="E58" s="25" t="str"/>
       <x:c r="F58" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.12</x:v>
       </x:c>
       <x:c r="G58" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H58" t="n">
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="I58" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J58" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1650,6 +2175,15 @@
       <x:c r="G59" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="H59" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I59" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J59" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="60" ht="48" hidden="0" customHeight="1">
       <x:c r="A60" s="23" t="n">
@@ -1666,9 +2200,18 @@
       </x:c>
       <x:c r="E60" s="25" t="str"/>
       <x:c r="F60" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.08</x:v>
       </x:c>
       <x:c r="G60" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H60" t="n">
+        <x:v>0.09999999999999999</x:v>
+      </x:c>
+      <x:c r="I60" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J60" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1687,9 +2230,18 @@
       </x:c>
       <x:c r="E61" s="25" t="str"/>
       <x:c r="F61" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.16</x:v>
       </x:c>
       <x:c r="G61" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H61" t="n">
+        <x:v>0.19999999999999998</x:v>
+      </x:c>
+      <x:c r="I61" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J61" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1708,9 +2260,18 @@
       </x:c>
       <x:c r="E62" s="25" t="str"/>
       <x:c r="F62" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.24</x:v>
       </x:c>
       <x:c r="G62" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H62" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="I62" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J62" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1736,6 +2297,15 @@
       <x:c r="G63" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="H63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I63" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J63" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="64" ht="48" hidden="0" customHeight="1">
       <x:c r="A64" s="23" t="n">
@@ -1752,9 +2322,18 @@
       </x:c>
       <x:c r="E64" s="25" t="str"/>
       <x:c r="F64" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.13</x:v>
       </x:c>
       <x:c r="G64" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H64" t="n">
+        <x:v>0.105</x:v>
+      </x:c>
+      <x:c r="I64" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J64" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1775,9 +2354,18 @@
         <x:v>wave.1503.announcement</x:v>
       </x:c>
       <x:c r="F65" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.26</x:v>
       </x:c>
       <x:c r="G65" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H65" t="n">
+        <x:v>0.21</x:v>
+      </x:c>
+      <x:c r="I65" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J65" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1796,9 +2384,18 @@
       </x:c>
       <x:c r="E66" s="25" t="str"/>
       <x:c r="F66" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.39</x:v>
       </x:c>
       <x:c r="G66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H66" t="n">
+        <x:v>0.315</x:v>
+      </x:c>
+      <x:c r="I66" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J66" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1819,9 +2416,18 @@
         <x:v>wave.1505.announcement</x:v>
       </x:c>
       <x:c r="F67" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.52</x:v>
       </x:c>
       <x:c r="G67" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H67" t="n">
+        <x:v>0.42</x:v>
+      </x:c>
+      <x:c r="I67" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J67" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1847,6 +2453,15 @@
       <x:c r="G68" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="H68" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I68" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J68" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="69" ht="48" hidden="0" customHeight="1">
       <x:c r="A69" s="23" t="n">
@@ -1863,9 +2478,18 @@
       </x:c>
       <x:c r="E69" s="25" t="str"/>
       <x:c r="F69" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.13</x:v>
       </x:c>
       <x:c r="G69" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H69" t="n">
+        <x:v>0.13999999999999999</x:v>
+      </x:c>
+      <x:c r="I69" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J69" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1884,9 +2508,18 @@
       </x:c>
       <x:c r="E70" s="25" t="str"/>
       <x:c r="F70" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.26</x:v>
       </x:c>
       <x:c r="G70" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H70" t="n">
+        <x:v>0.27999999999999997</x:v>
+      </x:c>
+      <x:c r="I70" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J70" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1905,9 +2538,18 @@
       </x:c>
       <x:c r="E71" s="25" t="str"/>
       <x:c r="F71" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.39</x:v>
       </x:c>
       <x:c r="G71" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H71" t="n">
+        <x:v>0.42</x:v>
+      </x:c>
+      <x:c r="I71" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J71" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1933,6 +2575,15 @@
       <x:c r="G72" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="H72" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I72" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J72" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="73" ht="48" hidden="0" customHeight="1">
       <x:c r="A73" s="23" t="n">
@@ -1949,9 +2600,18 @@
       </x:c>
       <x:c r="E73" s="25" t="str"/>
       <x:c r="F73" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.13</x:v>
       </x:c>
       <x:c r="G73" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H73" t="n">
+        <x:v>0.13999999999999999</x:v>
+      </x:c>
+      <x:c r="I73" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J73" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1970,9 +2630,18 @@
       </x:c>
       <x:c r="E74" s="25" t="str"/>
       <x:c r="F74" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.26</x:v>
       </x:c>
       <x:c r="G74" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H74" t="n">
+        <x:v>0.27999999999999997</x:v>
+      </x:c>
+      <x:c r="I74" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J74" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1991,9 +2660,18 @@
       </x:c>
       <x:c r="E75" s="25" t="str"/>
       <x:c r="F75" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.39</x:v>
       </x:c>
       <x:c r="G75" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H75" t="n">
+        <x:v>0.42</x:v>
+      </x:c>
+      <x:c r="I75" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J75" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2019,6 +2697,15 @@
       <x:c r="G76" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="H76" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I76" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J76" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="77" ht="48" hidden="0" customHeight="1">
       <x:c r="A77" s="23" t="n">
@@ -2035,9 +2722,18 @@
       </x:c>
       <x:c r="E77" s="25" t="str"/>
       <x:c r="F77" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.13</x:v>
       </x:c>
       <x:c r="G77" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H77" t="n">
+        <x:v>0.13999999999999999</x:v>
+      </x:c>
+      <x:c r="I77" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J77" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2056,9 +2752,18 @@
       </x:c>
       <x:c r="E78" s="25" t="str"/>
       <x:c r="F78" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.26</x:v>
       </x:c>
       <x:c r="G78" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H78" t="n">
+        <x:v>0.27999999999999997</x:v>
+      </x:c>
+      <x:c r="I78" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J78" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2077,9 +2782,18 @@
       </x:c>
       <x:c r="E79" s="25" t="str"/>
       <x:c r="F79" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.39</x:v>
       </x:c>
       <x:c r="G79" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H79" t="n">
+        <x:v>0.42</x:v>
+      </x:c>
+      <x:c r="I79" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J79" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2105,6 +2819,15 @@
       <x:c r="G80" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="H80" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I80" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J80" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="81" ht="48" hidden="0" customHeight="1">
       <x:c r="A81" s="23" t="n">
@@ -2121,9 +2844,18 @@
       </x:c>
       <x:c r="E81" s="25" t="str"/>
       <x:c r="F81" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.035</x:v>
       </x:c>
       <x:c r="G81" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H81" t="n">
+        <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="I81" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J81" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2142,9 +2874,18 @@
       </x:c>
       <x:c r="E82" s="25" t="str"/>
       <x:c r="F82" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.07</x:v>
       </x:c>
       <x:c r="G82" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H82" t="n">
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="I82" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J82" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2163,9 +2904,18 @@
       </x:c>
       <x:c r="E83" s="25" t="str"/>
       <x:c r="F83" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.105</x:v>
       </x:c>
       <x:c r="G83" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H83" t="n">
+        <x:v>0.12</x:v>
+      </x:c>
+      <x:c r="I83" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J83" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2191,6 +2941,15 @@
       <x:c r="G84" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="H84" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I84" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J84" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="85" ht="48" hidden="0" customHeight="1">
       <x:c r="A85" s="23" t="n">
@@ -2209,9 +2968,18 @@
         <x:v>wave.2002.announcement</x:v>
       </x:c>
       <x:c r="F85" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.13</x:v>
       </x:c>
       <x:c r="G85" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H85" t="n">
+        <x:v>0.105</x:v>
+      </x:c>
+      <x:c r="I85" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J85" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2232,9 +3000,18 @@
         <x:v>wave.2003.announcement</x:v>
       </x:c>
       <x:c r="F86" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.26</x:v>
       </x:c>
       <x:c r="G86" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H86" t="n">
+        <x:v>0.21</x:v>
+      </x:c>
+      <x:c r="I86" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J86" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2253,9 +3030,18 @@
       </x:c>
       <x:c r="E87" s="25" t="str"/>
       <x:c r="F87" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.39</x:v>
       </x:c>
       <x:c r="G87" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H87" t="n">
+        <x:v>0.315</x:v>
+      </x:c>
+      <x:c r="I87" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J87" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2276,9 +3062,18 @@
         <x:v>wave.2005.announcement</x:v>
       </x:c>
       <x:c r="F88" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.52</x:v>
       </x:c>
       <x:c r="G88" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H88" t="n">
+        <x:v>0.42</x:v>
+      </x:c>
+      <x:c r="I88" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J88" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2297,10 +3092,19 @@
       </x:c>
       <x:c r="E89" s="26" t="str"/>
       <x:c r="F89" s="26" t="n">
-        <x:v>0.65</x:v>
+        <x:v>1.1</x:v>
       </x:c>
       <x:c r="G89" t="n">
         <x:v>3.168</x:v>
+      </x:c>
+      <x:c r="H89" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I89" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J89" t="n">
+        <x:v>0.65</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="48" customHeight="1">
@@ -2318,10 +3122,19 @@
       </x:c>
       <x:c r="E90" s="26" t="str"/>
       <x:c r="F90" s="26" t="n">
-        <x:v>0.6834</x:v>
+        <x:v>1.6</x:v>
       </x:c>
       <x:c r="G90" t="n">
         <x:v>3.52</x:v>
+      </x:c>
+      <x:c r="H90" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I90" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J90" t="n">
+        <x:v>0.6834</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="48" customHeight="1">
@@ -2339,10 +3152,19 @@
       </x:c>
       <x:c r="E91" s="26" t="str"/>
       <x:c r="F91" s="26" t="n">
-        <x:v>0.7837</x:v>
+        <x:v>2.4</x:v>
       </x:c>
       <x:c r="G91" t="n">
         <x:v>4.048</x:v>
+      </x:c>
+      <x:c r="H91" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I91" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J91" t="n">
+        <x:v>0.7837</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="48" customHeight="1">
@@ -2360,10 +3182,19 @@
       </x:c>
       <x:c r="E92" s="26" t="str"/>
       <x:c r="F92" s="26" t="n">
-        <x:v>0.9508</x:v>
+        <x:v>3.4</x:v>
       </x:c>
       <x:c r="G92" t="n">
         <x:v>4.576</x:v>
+      </x:c>
+      <x:c r="H92" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I92" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J92" t="n">
+        <x:v>0.9508</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="48" customHeight="1">
@@ -2383,10 +3214,19 @@
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F93" s="26" t="n">
-        <x:v>1.1847</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G93" t="n">
         <x:v>4.4</x:v>
+      </x:c>
+      <x:c r="H93" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I93" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J93" t="n">
+        <x:v>1.1847</x:v>
       </x:c>
     </x:row>
     <x:row r="94" ht="48" customHeight="1">
@@ -2404,10 +3244,19 @@
       </x:c>
       <x:c r="E94" s="26" t="str"/>
       <x:c r="F94" s="26" t="n">
-        <x:v>1.4855</x:v>
+        <x:v>5.5</x:v>
       </x:c>
       <x:c r="G94" t="n">
         <x:v>5.808</x:v>
+      </x:c>
+      <x:c r="H94" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I94" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J94" t="n">
+        <x:v>1.4855</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="48" customHeight="1">
@@ -2425,10 +3274,19 @@
       </x:c>
       <x:c r="E95" s="26" t="str"/>
       <x:c r="F95" s="26" t="n">
-        <x:v>1.8531</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G95" t="n">
         <x:v>6.512</x:v>
+      </x:c>
+      <x:c r="H95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I95" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J95" t="n">
+        <x:v>1.8531</x:v>
       </x:c>
     </x:row>
     <x:row r="96" ht="48" customHeight="1">
@@ -2446,10 +3304,19 @@
       </x:c>
       <x:c r="E96" s="26" t="str"/>
       <x:c r="F96" s="26" t="n">
-        <x:v>2.2875</x:v>
+        <x:v>6.5</x:v>
       </x:c>
       <x:c r="G96" t="n">
         <x:v>7.216</x:v>
+      </x:c>
+      <x:c r="H96" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I96" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J96" t="n">
+        <x:v>2.2875</x:v>
       </x:c>
     </x:row>
     <x:row r="97" ht="48" customHeight="1">
@@ -2467,10 +3334,19 @@
       </x:c>
       <x:c r="E97" s="26" t="str"/>
       <x:c r="F97" s="26" t="n">
-        <x:v>2.7888</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G97" t="n">
         <x:v>7.92</x:v>
+      </x:c>
+      <x:c r="H97" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I97" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J97" t="n">
+        <x:v>2.7888</x:v>
       </x:c>
     </x:row>
     <x:row r="98" ht="48" customHeight="1">
@@ -2490,10 +3366,19 @@
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F98" s="26" t="n">
-        <x:v>3.3569</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G98" t="n">
         <x:v>10.56</x:v>
+      </x:c>
+      <x:c r="H98" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I98" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J98" t="n">
+        <x:v>3.3569</x:v>
       </x:c>
     </x:row>
     <x:row r="99" ht="48" customHeight="1">
@@ -2511,10 +3396,19 @@
       </x:c>
       <x:c r="E99" s="26" t="str"/>
       <x:c r="F99" s="26" t="n">
-        <x:v>3.9918</x:v>
+        <x:v>9.2</x:v>
       </x:c>
       <x:c r="G99" t="n">
         <x:v>9.856</x:v>
+      </x:c>
+      <x:c r="H99" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I99" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J99" t="n">
+        <x:v>3.9918</x:v>
       </x:c>
     </x:row>
     <x:row r="100" ht="48" customHeight="1">
@@ -2532,10 +3426,19 @@
       </x:c>
       <x:c r="E100" s="26" t="str"/>
       <x:c r="F100" s="26" t="n">
-        <x:v>4.6936</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G100" t="n">
         <x:v>10.912</x:v>
+      </x:c>
+      <x:c r="H100" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I100" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J100" t="n">
+        <x:v>4.6936</x:v>
       </x:c>
     </x:row>
     <x:row r="101" ht="48" customHeight="1">
@@ -2553,10 +3456,19 @@
       </x:c>
       <x:c r="E101" s="26" t="str"/>
       <x:c r="F101" s="26" t="n">
-        <x:v>5.4622</x:v>
+        <x:v>10.7</x:v>
       </x:c>
       <x:c r="G101" t="n">
         <x:v>12.144</x:v>
+      </x:c>
+      <x:c r="H101" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I101" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J101" t="n">
+        <x:v>5.4622</x:v>
       </x:c>
     </x:row>
     <x:row r="102" ht="48" customHeight="1">
@@ -2574,10 +3486,19 @@
       </x:c>
       <x:c r="E102" s="26" t="str"/>
       <x:c r="F102" s="26" t="n">
-        <x:v>6.2977</x:v>
+        <x:v>11.4</x:v>
       </x:c>
       <x:c r="G102" t="n">
         <x:v>13.376</x:v>
+      </x:c>
+      <x:c r="H102" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I102" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J102" t="n">
+        <x:v>6.2977</x:v>
       </x:c>
     </x:row>
     <x:row r="103" ht="48" customHeight="1">
@@ -2597,10 +3518,19 @@
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F103" s="26" t="n">
-        <x:v>7.2</x:v>
+        <x:v>12.2</x:v>
       </x:c>
       <x:c r="G103" t="n">
         <x:v>17.6</x:v>
+      </x:c>
+      <x:c r="H103" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I103" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J103" t="n">
+        <x:v>7.2</x:v>
       </x:c>
     </x:row>
     <x:row r="104" ht="48" customHeight="1">
@@ -2618,10 +3548,19 @@
       </x:c>
       <x:c r="E104" s="26" t="str"/>
       <x:c r="F104" s="26" t="n">
-        <x:v>0.55</x:v>
+        <x:v>1.21</x:v>
       </x:c>
       <x:c r="G104" t="n">
         <x:v>3.0096</x:v>
+      </x:c>
+      <x:c r="H104" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I104" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J104" t="n">
+        <x:v>0.55</x:v>
       </x:c>
     </x:row>
     <x:row r="105" ht="48" customHeight="1">
@@ -2639,10 +3578,19 @@
       </x:c>
       <x:c r="E105" s="26" t="str"/>
       <x:c r="F105" s="26" t="n">
-        <x:v>0.5558</x:v>
+        <x:v>1.76</x:v>
       </x:c>
       <x:c r="G105" t="n">
         <x:v>3.3477</x:v>
+      </x:c>
+      <x:c r="H105" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I105" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J105" t="n">
+        <x:v>0.5558</x:v>
       </x:c>
     </x:row>
     <x:row r="106" ht="48" customHeight="1">
@@ -2660,10 +3608,19 @@
       </x:c>
       <x:c r="E106" s="26" t="str"/>
       <x:c r="F106" s="26" t="n">
-        <x:v>0.5902</x:v>
+        <x:v>2.64</x:v>
       </x:c>
       <x:c r="G106" t="n">
         <x:v>3.8792</x:v>
+      </x:c>
+      <x:c r="H106" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I106" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J106" t="n">
+        <x:v>0.5902</x:v>
       </x:c>
     </x:row>
     <x:row r="107" ht="48" customHeight="1">
@@ -2681,10 +3638,19 @@
       </x:c>
       <x:c r="E107" s="26" t="str"/>
       <x:c r="F107" s="26" t="n">
-        <x:v>0.6752</x:v>
+        <x:v>3.74</x:v>
       </x:c>
       <x:c r="G107" t="n">
         <x:v>4.4755</x:v>
+      </x:c>
+      <x:c r="H107" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J107" t="n">
+        <x:v>0.6752</x:v>
       </x:c>
     </x:row>
     <x:row r="108" ht="48" customHeight="1">
@@ -2704,10 +3670,19 @@
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F108" s="26" t="n">
-        <x:v>0.8302</x:v>
+        <x:v>4.4</x:v>
       </x:c>
       <x:c r="G108" t="n">
         <x:v>4.4725</x:v>
+      </x:c>
+      <x:c r="H108" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I108" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J108" t="n">
+        <x:v>0.8302</x:v>
       </x:c>
     </x:row>
     <x:row r="109" ht="48" customHeight="1">
@@ -2725,10 +3700,19 @@
       </x:c>
       <x:c r="E109" s="26" t="str"/>
       <x:c r="F109" s="26" t="n">
-        <x:v>1.0733</x:v>
+        <x:v>6.05</x:v>
       </x:c>
       <x:c r="G109" t="n">
         <x:v>6.2716</x:v>
+      </x:c>
+      <x:c r="H109" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I109" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J109" t="n">
+        <x:v>1.0733</x:v>
       </x:c>
     </x:row>
     <x:row r="110">
@@ -2746,10 +3730,19 @@
       </x:c>
       <x:c r="E110" t="str"/>
       <x:c r="F110" t="n">
-        <x:v>1.4219</x:v>
+        <x:v>6.6</x:v>
       </x:c>
       <x:c r="G110" t="n">
         <x:v>7.6473</x:v>
+      </x:c>
+      <x:c r="H110" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I110" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J110" t="n">
+        <x:v>1.4219</x:v>
       </x:c>
     </x:row>
     <x:row r="111">
@@ -2767,10 +3760,19 @@
       </x:c>
       <x:c r="E111" t="str"/>
       <x:c r="F111" t="n">
-        <x:v>1.8925</x:v>
+        <x:v>7.15</x:v>
       </x:c>
       <x:c r="G111" t="n">
         <x:v>9.4259</x:v>
+      </x:c>
+      <x:c r="H111" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I111" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J111" t="n">
+        <x:v>1.8925</x:v>
       </x:c>
     </x:row>
     <x:row r="112">
@@ -2788,10 +3790,19 @@
       </x:c>
       <x:c r="E112" t="str"/>
       <x:c r="F112" t="n">
-        <x:v>2.5012</x:v>
+        <x:v>7.7</x:v>
       </x:c>
       <x:c r="G112" t="n">
         <x:v>11.7357</x:v>
+      </x:c>
+      <x:c r="H112" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I112" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J112" t="n">
+        <x:v>2.5012</x:v>
       </x:c>
     </x:row>
     <x:row r="113">
@@ -2811,10 +3822,19 @@
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F113" t="n">
-        <x:v>3.2635</x:v>
+        <x:v>8.8</x:v>
       </x:c>
       <x:c r="G113" t="n">
         <x:v>18.0276</x:v>
+      </x:c>
+      <x:c r="H113" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I113" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J113" t="n">
+        <x:v>3.2635</x:v>
       </x:c>
     </x:row>
     <x:row r="114">
@@ -2832,10 +3852,19 @@
       </x:c>
       <x:c r="E114" t="str"/>
       <x:c r="F114" t="n">
-        <x:v>4.1946</x:v>
+        <x:v>10.12</x:v>
       </x:c>
       <x:c r="G114" t="n">
         <x:v>19.5999</x:v>
+      </x:c>
+      <x:c r="H114" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I114" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J114" t="n">
+        <x:v>4.1946</x:v>
       </x:c>
     </x:row>
     <x:row r="115">
@@ -2853,10 +3882,19 @@
       </x:c>
       <x:c r="E115" t="str"/>
       <x:c r="F115" t="n">
-        <x:v>5.3094</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G115" t="n">
         <x:v>25.4513</x:v>
+      </x:c>
+      <x:c r="H115" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I115" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J115" t="n">
+        <x:v>5.3094</x:v>
       </x:c>
     </x:row>
     <x:row r="116">
@@ -2874,10 +3912,19 @@
       </x:c>
       <x:c r="E116" t="str"/>
       <x:c r="F116" t="n">
-        <x:v>6.6224</x:v>
+        <x:v>11.77</x:v>
       </x:c>
       <x:c r="G116" t="n">
         <x:v>33.3323</x:v>
+      </x:c>
+      <x:c r="H116" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I116" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J116" t="n">
+        <x:v>6.6224</x:v>
       </x:c>
     </x:row>
     <x:row r="117">
@@ -2895,10 +3942,19 @@
       </x:c>
       <x:c r="E117" t="str"/>
       <x:c r="F117" t="n">
-        <x:v>8.1479</x:v>
+        <x:v>12.54</x:v>
       </x:c>
       <x:c r="G117" t="n">
         <x:v>43.2295</x:v>
+      </x:c>
+      <x:c r="H117" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I117" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J117" t="n">
+        <x:v>8.1479</x:v>
       </x:c>
     </x:row>
     <x:row r="118">
@@ -2918,10 +3974,19 @@
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F118" t="n">
-        <x:v>9.9</x:v>
+        <x:v>13.42</x:v>
       </x:c>
       <x:c r="G118" t="n">
         <x:v>66.88</x:v>
+      </x:c>
+      <x:c r="H118" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I118" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J118" t="n">
+        <x:v>9.9</x:v>
       </x:c>
     </x:row>
     <x:row r="119">
@@ -2939,10 +4004,19 @@
       </x:c>
       <x:c r="E119" t="str"/>
       <x:c r="F119" t="n">
-        <x:v>0.65</x:v>
+        <x:v>0.715</x:v>
       </x:c>
       <x:c r="G119" t="n">
         <x:v>3.168</x:v>
+      </x:c>
+      <x:c r="H119" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I119" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J119" t="n">
+        <x:v>0.65</x:v>
       </x:c>
     </x:row>
     <x:row r="120">
@@ -2960,10 +4034,19 @@
       </x:c>
       <x:c r="E120" t="str"/>
       <x:c r="F120" t="n">
-        <x:v>0.6834</x:v>
+        <x:v>1.04</x:v>
       </x:c>
       <x:c r="G120" t="n">
         <x:v>3.52</x:v>
+      </x:c>
+      <x:c r="H120" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I120" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J120" t="n">
+        <x:v>0.6834</x:v>
       </x:c>
     </x:row>
     <x:row r="121">
@@ -2981,10 +4064,19 @@
       </x:c>
       <x:c r="E121" t="str"/>
       <x:c r="F121" t="n">
-        <x:v>0.7837</x:v>
+        <x:v>1.56</x:v>
       </x:c>
       <x:c r="G121" t="n">
         <x:v>4.048</x:v>
+      </x:c>
+      <x:c r="H121" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I121" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J121" t="n">
+        <x:v>0.7837</x:v>
       </x:c>
     </x:row>
     <x:row r="122">
@@ -3002,10 +4094,19 @@
       </x:c>
       <x:c r="E122" t="str"/>
       <x:c r="F122" t="n">
-        <x:v>0.9508</x:v>
+        <x:v>2.21</x:v>
       </x:c>
       <x:c r="G122" t="n">
         <x:v>4.576</x:v>
+      </x:c>
+      <x:c r="H122" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I122" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J122" t="n">
+        <x:v>0.9508</x:v>
       </x:c>
     </x:row>
     <x:row r="123">
@@ -3025,10 +4126,19 @@
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F123" t="n">
-        <x:v>1.1847</x:v>
+        <x:v>2.6</x:v>
       </x:c>
       <x:c r="G123" t="n">
         <x:v>4.4</x:v>
+      </x:c>
+      <x:c r="H123" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I123" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J123" t="n">
+        <x:v>1.1847</x:v>
       </x:c>
     </x:row>
     <x:row r="124">
@@ -3046,10 +4156,19 @@
       </x:c>
       <x:c r="E124" t="str"/>
       <x:c r="F124" t="n">
-        <x:v>1.4855</x:v>
+        <x:v>3.575</x:v>
       </x:c>
       <x:c r="G124" t="n">
         <x:v>5.808</x:v>
+      </x:c>
+      <x:c r="H124" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I124" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J124" t="n">
+        <x:v>1.4855</x:v>
       </x:c>
     </x:row>
     <x:row r="125">
@@ -3067,10 +4186,19 @@
       </x:c>
       <x:c r="E125" t="str"/>
       <x:c r="F125" t="n">
-        <x:v>1.8531</x:v>
+        <x:v>3.9</x:v>
       </x:c>
       <x:c r="G125" t="n">
         <x:v>6.512</x:v>
+      </x:c>
+      <x:c r="H125" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I125" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J125" t="n">
+        <x:v>1.8531</x:v>
       </x:c>
     </x:row>
     <x:row r="126">
@@ -3088,10 +4216,19 @@
       </x:c>
       <x:c r="E126" t="str"/>
       <x:c r="F126" t="n">
-        <x:v>2.2875</x:v>
+        <x:v>4.225</x:v>
       </x:c>
       <x:c r="G126" t="n">
         <x:v>7.216</x:v>
+      </x:c>
+      <x:c r="H126" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I126" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J126" t="n">
+        <x:v>2.2875</x:v>
       </x:c>
     </x:row>
     <x:row r="127">
@@ -3109,10 +4246,19 @@
       </x:c>
       <x:c r="E127" t="str"/>
       <x:c r="F127" t="n">
-        <x:v>2.7888</x:v>
+        <x:v>4.55</x:v>
       </x:c>
       <x:c r="G127" t="n">
         <x:v>7.92</x:v>
+      </x:c>
+      <x:c r="H127" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I127" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J127" t="n">
+        <x:v>2.7888</x:v>
       </x:c>
     </x:row>
     <x:row r="128">
@@ -3132,10 +4278,19 @@
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F128" t="n">
-        <x:v>3.3569</x:v>
+        <x:v>5.2</x:v>
       </x:c>
       <x:c r="G128" t="n">
         <x:v>10.56</x:v>
+      </x:c>
+      <x:c r="H128" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I128" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J128" t="n">
+        <x:v>3.3569</x:v>
       </x:c>
     </x:row>
     <x:row r="129">
@@ -3153,10 +4308,19 @@
       </x:c>
       <x:c r="E129" t="str"/>
       <x:c r="F129" t="n">
-        <x:v>3.9918</x:v>
+        <x:v>5.98</x:v>
       </x:c>
       <x:c r="G129" t="n">
         <x:v>9.856</x:v>
+      </x:c>
+      <x:c r="H129" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I129" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J129" t="n">
+        <x:v>3.9918</x:v>
       </x:c>
     </x:row>
     <x:row r="130">
@@ -3174,10 +4338,19 @@
       </x:c>
       <x:c r="E130" t="str"/>
       <x:c r="F130" t="n">
-        <x:v>4.6936</x:v>
+        <x:v>6.5</x:v>
       </x:c>
       <x:c r="G130" t="n">
         <x:v>10.912</x:v>
+      </x:c>
+      <x:c r="H130" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I130" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J130" t="n">
+        <x:v>4.6936</x:v>
       </x:c>
     </x:row>
     <x:row r="131">
@@ -3195,10 +4368,19 @@
       </x:c>
       <x:c r="E131" t="str"/>
       <x:c r="F131" t="n">
-        <x:v>5.4622</x:v>
+        <x:v>6.955</x:v>
       </x:c>
       <x:c r="G131" t="n">
         <x:v>12.144</x:v>
+      </x:c>
+      <x:c r="H131" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I131" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J131" t="n">
+        <x:v>5.4622</x:v>
       </x:c>
     </x:row>
     <x:row r="132">
@@ -3216,10 +4398,19 @@
       </x:c>
       <x:c r="E132" t="str"/>
       <x:c r="F132" t="n">
-        <x:v>6.2977</x:v>
+        <x:v>7.41</x:v>
       </x:c>
       <x:c r="G132" t="n">
         <x:v>13.376</x:v>
+      </x:c>
+      <x:c r="H132" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I132" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J132" t="n">
+        <x:v>6.2977</x:v>
       </x:c>
     </x:row>
     <x:row r="133">
@@ -3239,10 +4430,19 @@
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F133" t="n">
-        <x:v>7.2</x:v>
+        <x:v>7.93</x:v>
       </x:c>
       <x:c r="G133" t="n">
         <x:v>17.6</x:v>
+      </x:c>
+      <x:c r="H133" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I133" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J133" t="n">
+        <x:v>7.2</x:v>
       </x:c>
     </x:row>
     <x:row r="134">
@@ -3260,10 +4460,19 @@
       </x:c>
       <x:c r="E134" t="str"/>
       <x:c r="F134" t="n">
-        <x:v>0.55</x:v>
+        <x:v>0.715</x:v>
       </x:c>
       <x:c r="G134" t="n">
         <x:v>3.2314</x:v>
+      </x:c>
+      <x:c r="H134" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I134" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J134" t="n">
+        <x:v>0.55</x:v>
       </x:c>
     </x:row>
     <x:row r="135">
@@ -3281,10 +4490,19 @@
       </x:c>
       <x:c r="E135" t="str"/>
       <x:c r="F135" t="n">
-        <x:v>0.5737</x:v>
+        <x:v>1.04</x:v>
       </x:c>
       <x:c r="G135" t="n">
         <x:v>3.5904</x:v>
+      </x:c>
+      <x:c r="H135" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I135" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J135" t="n">
+        <x:v>0.5737</x:v>
       </x:c>
     </x:row>
     <x:row r="136">
@@ -3302,10 +4520,19 @@
       </x:c>
       <x:c r="E136" t="str"/>
       <x:c r="F136" t="n">
-        <x:v>0.6449</x:v>
+        <x:v>1.56</x:v>
       </x:c>
       <x:c r="G136" t="n">
         <x:v>4.129</x:v>
+      </x:c>
+      <x:c r="H136" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I136" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J136" t="n">
+        <x:v>0.6449</x:v>
       </x:c>
     </x:row>
     <x:row r="137">
@@ -3323,10 +4550,19 @@
       </x:c>
       <x:c r="E137" t="str"/>
       <x:c r="F137" t="n">
-        <x:v>0.7635</x:v>
+        <x:v>2.21</x:v>
       </x:c>
       <x:c r="G137" t="n">
         <x:v>4.6675</x:v>
+      </x:c>
+      <x:c r="H137" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I137" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J137" t="n">
+        <x:v>0.7635</x:v>
       </x:c>
     </x:row>
     <x:row r="138">
@@ -3346,10 +4582,19 @@
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F138" t="n">
-        <x:v>0.9296</x:v>
+        <x:v>2.6</x:v>
       </x:c>
       <x:c r="G138" t="n">
         <x:v>4.488</x:v>
+      </x:c>
+      <x:c r="H138" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I138" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J138" t="n">
+        <x:v>0.9296</x:v>
       </x:c>
     </x:row>
     <x:row r="139">
@@ -3367,10 +4612,19 @@
       </x:c>
       <x:c r="E139" t="str"/>
       <x:c r="F139" t="n">
-        <x:v>1.1431</x:v>
+        <x:v>3.575</x:v>
       </x:c>
       <x:c r="G139" t="n">
         <x:v>5.9242</x:v>
+      </x:c>
+      <x:c r="H139" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I139" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J139" t="n">
+        <x:v>1.1431</x:v>
       </x:c>
     </x:row>
     <x:row r="140">
@@ -3388,10 +4642,19 @@
       </x:c>
       <x:c r="E140" t="str"/>
       <x:c r="F140" t="n">
-        <x:v>1.4041</x:v>
+        <x:v>3.9</x:v>
       </x:c>
       <x:c r="G140" t="n">
         <x:v>6.6422</x:v>
+      </x:c>
+      <x:c r="H140" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I140" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J140" t="n">
+        <x:v>1.4041</x:v>
       </x:c>
     </x:row>
     <x:row r="141">
@@ -3409,10 +4672,19 @@
       </x:c>
       <x:c r="E141" t="str"/>
       <x:c r="F141" t="n">
-        <x:v>1.7125</x:v>
+        <x:v>4.225</x:v>
       </x:c>
       <x:c r="G141" t="n">
         <x:v>7.3603</x:v>
+      </x:c>
+      <x:c r="H141" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I141" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J141" t="n">
+        <x:v>1.7125</x:v>
       </x:c>
     </x:row>
     <x:row r="142">
@@ -3430,10 +4702,19 @@
       </x:c>
       <x:c r="E142" t="str"/>
       <x:c r="F142" t="n">
-        <x:v>2.0684</x:v>
+        <x:v>4.55</x:v>
       </x:c>
       <x:c r="G142" t="n">
         <x:v>8.0784</x:v>
+      </x:c>
+      <x:c r="H142" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I142" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J142" t="n">
+        <x:v>2.0684</x:v>
       </x:c>
     </x:row>
     <x:row r="143">
@@ -3453,10 +4734,19 @@
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F143" t="n">
-        <x:v>2.4717</x:v>
+        <x:v>5.2</x:v>
       </x:c>
       <x:c r="G143" t="n">
         <x:v>10.7712</x:v>
+      </x:c>
+      <x:c r="H143" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I143" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J143" t="n">
+        <x:v>2.4717</x:v>
       </x:c>
     </x:row>
     <x:row r="144">
@@ -3474,10 +4764,19 @@
       </x:c>
       <x:c r="E144" t="str"/>
       <x:c r="F144" t="n">
-        <x:v>2.9224</x:v>
+        <x:v>5.98</x:v>
       </x:c>
       <x:c r="G144" t="n">
         <x:v>10.0531</x:v>
+      </x:c>
+      <x:c r="H144" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I144" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J144" t="n">
+        <x:v>2.9224</x:v>
       </x:c>
     </x:row>
     <x:row r="145">
@@ -3495,10 +4794,19 @@
       </x:c>
       <x:c r="E145" t="str"/>
       <x:c r="F145" t="n">
-        <x:v>3.4207</x:v>
+        <x:v>6.5</x:v>
       </x:c>
       <x:c r="G145" t="n">
         <x:v>11.1302</x:v>
+      </x:c>
+      <x:c r="H145" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I145" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J145" t="n">
+        <x:v>3.4207</x:v>
       </x:c>
     </x:row>
     <x:row r="146">
@@ -3516,10 +4824,19 @@
       </x:c>
       <x:c r="E146" t="str"/>
       <x:c r="F146" t="n">
-        <x:v>3.9663</x:v>
+        <x:v>6.955</x:v>
       </x:c>
       <x:c r="G146" t="n">
         <x:v>12.3869</x:v>
+      </x:c>
+      <x:c r="H146" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I146" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J146" t="n">
+        <x:v>3.9663</x:v>
       </x:c>
     </x:row>
     <x:row r="147">
@@ -3537,10 +4854,19 @@
       </x:c>
       <x:c r="E147" t="str"/>
       <x:c r="F147" t="n">
-        <x:v>4.5594</x:v>
+        <x:v>7.41</x:v>
       </x:c>
       <x:c r="G147" t="n">
         <x:v>13.6435</x:v>
+      </x:c>
+      <x:c r="H147" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I147" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J147" t="n">
+        <x:v>4.5594</x:v>
       </x:c>
     </x:row>
     <x:row r="148">
@@ -3560,10 +4886,19 @@
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F148" t="n">
-        <x:v>5.2</x:v>
+        <x:v>7.93</x:v>
       </x:c>
       <x:c r="G148" t="n">
         <x:v>17.952</x:v>
+      </x:c>
+      <x:c r="H148" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I148" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J148" t="n">
+        <x:v>5.2</x:v>
       </x:c>
     </x:row>
     <x:row r="149">
@@ -3581,10 +4916,19 @@
       </x:c>
       <x:c r="E149" t="str"/>
       <x:c r="F149" t="n">
-        <x:v>0.55</x:v>
+        <x:v>0.9</x:v>
       </x:c>
       <x:c r="G149" t="n">
         <x:v>3.263</x:v>
+      </x:c>
+      <x:c r="H149" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I149" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J149" t="n">
+        <x:v>0.55</x:v>
       </x:c>
     </x:row>
     <x:row r="150">
@@ -3602,10 +4946,19 @@
       </x:c>
       <x:c r="E150" t="str"/>
       <x:c r="F150" t="n">
-        <x:v>0.5815</x:v>
+        <x:v>1.3</x:v>
       </x:c>
       <x:c r="G150" t="n">
         <x:v>3.6256</x:v>
+      </x:c>
+      <x:c r="H150" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I150" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J150" t="n">
+        <x:v>0.5815</x:v>
       </x:c>
     </x:row>
     <x:row r="151">
@@ -3623,10 +4976,19 @@
       </x:c>
       <x:c r="E151" t="str"/>
       <x:c r="F151" t="n">
-        <x:v>0.6945</x:v>
+        <x:v>1.9</x:v>
       </x:c>
       <x:c r="G151" t="n">
         <x:v>4.1694</x:v>
+      </x:c>
+      <x:c r="H151" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I151" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J151" t="n">
+        <x:v>0.6945</x:v>
       </x:c>
     </x:row>
     <x:row r="152">
@@ -3644,10 +5006,19 @@
       </x:c>
       <x:c r="E152" t="str"/>
       <x:c r="F152" t="n">
-        <x:v>0.9026</x:v>
+        <x:v>2.6</x:v>
       </x:c>
       <x:c r="G152" t="n">
         <x:v>4.7133</x:v>
+      </x:c>
+      <x:c r="H152" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I152" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J152" t="n">
+        <x:v>0.9026</x:v>
       </x:c>
     </x:row>
     <x:row r="153">
@@ -3667,10 +5038,19 @@
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F153" t="n">
-        <x:v>1.214</x:v>
+        <x:v>3.2</x:v>
       </x:c>
       <x:c r="G153" t="n">
         <x:v>4.532</x:v>
+      </x:c>
+      <x:c r="H153" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I153" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J153" t="n">
+        <x:v>1.214</x:v>
       </x:c>
     </x:row>
     <x:row r="154">
@@ -3688,10 +5068,19 @@
       </x:c>
       <x:c r="E154" t="str"/>
       <x:c r="F154" t="n">
-        <x:v>1.6348</x:v>
+        <x:v>4.3</x:v>
       </x:c>
       <x:c r="G154" t="n">
         <x:v>5.9822</x:v>
+      </x:c>
+      <x:c r="H154" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I154" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J154" t="n">
+        <x:v>1.6348</x:v>
       </x:c>
     </x:row>
     <x:row r="155">
@@ -3709,10 +5098,19 @@
       </x:c>
       <x:c r="E155" t="str"/>
       <x:c r="F155" t="n">
-        <x:v>2.1702</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G155" t="n">
         <x:v>6.7074</x:v>
+      </x:c>
+      <x:c r="H155" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I155" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J155" t="n">
+        <x:v>2.1702</x:v>
       </x:c>
     </x:row>
     <x:row r="156">
@@ -3730,10 +5128,19 @@
       </x:c>
       <x:c r="E156" t="str"/>
       <x:c r="F156" t="n">
-        <x:v>2.8243</x:v>
+        <x:v>5.8</x:v>
       </x:c>
       <x:c r="G156" t="n">
         <x:v>7.4325</x:v>
+      </x:c>
+      <x:c r="H156" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I156" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J156" t="n">
+        <x:v>2.8243</x:v>
       </x:c>
     </x:row>
     <x:row r="157">
@@ -3751,10 +5158,19 @@
       </x:c>
       <x:c r="E157" t="str"/>
       <x:c r="F157" t="n">
-        <x:v>3.6009</x:v>
+        <x:v>6.8</x:v>
       </x:c>
       <x:c r="G157" t="n">
         <x:v>8.1576</x:v>
+      </x:c>
+      <x:c r="H157" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I157" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J157" t="n">
+        <x:v>3.6009</x:v>
       </x:c>
     </x:row>
     <x:row r="158">
@@ -3774,10 +5190,19 @@
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F158" t="n">
-        <x:v>4.5034</x:v>
+        <x:v>7.8</x:v>
       </x:c>
       <x:c r="G158" t="n">
         <x:v>10.8768</x:v>
+      </x:c>
+      <x:c r="H158" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I158" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J158" t="n">
+        <x:v>4.5034</x:v>
       </x:c>
     </x:row>
     <x:row r="159">
@@ -3795,10 +5220,19 @@
       </x:c>
       <x:c r="E159" t="str"/>
       <x:c r="F159" t="n">
-        <x:v>5.5346</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G159" t="n">
         <x:v>10.1517</x:v>
+      </x:c>
+      <x:c r="H159" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I159" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J159" t="n">
+        <x:v>5.5346</x:v>
       </x:c>
     </x:row>
     <x:row r="160">
@@ -3816,10 +5250,19 @@
       </x:c>
       <x:c r="E160" t="str"/>
       <x:c r="F160" t="n">
-        <x:v>6.6975</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G160" t="n">
         <x:v>11.2394</x:v>
+      </x:c>
+      <x:c r="H160" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I160" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J160" t="n">
+        <x:v>6.6975</x:v>
       </x:c>
     </x:row>
     <x:row r="161">
@@ -3837,10 +5280,19 @@
       </x:c>
       <x:c r="E161" t="str"/>
       <x:c r="F161" t="n">
-        <x:v>7.9945</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G161" t="n">
         <x:v>12.5083</x:v>
+      </x:c>
+      <x:c r="H161" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I161" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J161" t="n">
+        <x:v>7.9945</x:v>
       </x:c>
     </x:row>
     <x:row r="162">
@@ -3858,10 +5310,19 @@
       </x:c>
       <x:c r="E162" t="str"/>
       <x:c r="F162" t="n">
-        <x:v>9.4279</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G162" t="n">
         <x:v>13.7773</x:v>
+      </x:c>
+      <x:c r="H162" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I162" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J162" t="n">
+        <x:v>9.4279</x:v>
       </x:c>
     </x:row>
     <x:row r="163">
@@ -3881,10 +5342,19 @@
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F163" t="n">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G163" t="n">
         <x:v>18.128</x:v>
+      </x:c>
+      <x:c r="H163" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I163" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J163" t="n">
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="164">
@@ -3907,6 +5377,15 @@
       <x:c r="G164" t="n">
         <x:v>3.3581</x:v>
       </x:c>
+      <x:c r="H164" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I164" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J164" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
     </x:row>
     <x:row r="165">
       <x:c r="A165" t="n">
@@ -3923,10 +5402,19 @@
       </x:c>
       <x:c r="E165" t="str"/>
       <x:c r="F165" t="n">
-        <x:v>0.9321</x:v>
+        <x:v>1.1</x:v>
       </x:c>
       <x:c r="G165" t="n">
         <x:v>3.7312</x:v>
+      </x:c>
+      <x:c r="H165" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I165" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J165" t="n">
+        <x:v>0.9321</x:v>
       </x:c>
     </x:row>
     <x:row r="166">
@@ -3944,10 +5432,19 @@
       </x:c>
       <x:c r="E166" t="str"/>
       <x:c r="F166" t="n">
-        <x:v>1.0286</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="G166" t="n">
         <x:v>4.2909</x:v>
+      </x:c>
+      <x:c r="H166" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I166" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J166" t="n">
+        <x:v>1.0286</x:v>
       </x:c>
     </x:row>
     <x:row r="167">
@@ -3965,10 +5462,19 @@
       </x:c>
       <x:c r="E167" t="str"/>
       <x:c r="F167" t="n">
-        <x:v>1.1893</x:v>
+        <x:v>1.9</x:v>
       </x:c>
       <x:c r="G167" t="n">
         <x:v>4.8506</x:v>
+      </x:c>
+      <x:c r="H167" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I167" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J167" t="n">
+        <x:v>1.1893</x:v>
       </x:c>
     </x:row>
     <x:row r="168">
@@ -3988,10 +5494,19 @@
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F168" t="n">
-        <x:v>1.4143</x:v>
+        <x:v>2.4</x:v>
       </x:c>
       <x:c r="G168" t="n">
         <x:v>4.664</x:v>
+      </x:c>
+      <x:c r="H168" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I168" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J168" t="n">
+        <x:v>1.4143</x:v>
       </x:c>
     </x:row>
     <x:row r="169">
@@ -4009,10 +5524,19 @@
       </x:c>
       <x:c r="E169" t="str"/>
       <x:c r="F169" t="n">
-        <x:v>1.7036</x:v>
+        <x:v>3.2</x:v>
       </x:c>
       <x:c r="G169" t="n">
         <x:v>6.1565</x:v>
+      </x:c>
+      <x:c r="H169" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I169" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J169" t="n">
+        <x:v>1.7036</x:v>
       </x:c>
     </x:row>
     <x:row r="170">
@@ -4030,10 +5554,19 @@
       </x:c>
       <x:c r="E170" t="str"/>
       <x:c r="F170" t="n">
-        <x:v>2.0571</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G170" t="n">
         <x:v>6.9027</x:v>
+      </x:c>
+      <x:c r="H170" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I170" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J170" t="n">
+        <x:v>2.0571</x:v>
       </x:c>
     </x:row>
     <x:row r="171">
@@ -4051,10 +5584,19 @@
       </x:c>
       <x:c r="E171" t="str"/>
       <x:c r="F171" t="n">
-        <x:v>2.475</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G171" t="n">
         <x:v>7.649</x:v>
+      </x:c>
+      <x:c r="H171" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I171" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J171" t="n">
+        <x:v>2.475</x:v>
       </x:c>
     </x:row>
     <x:row r="172">
@@ -4072,10 +5614,19 @@
       </x:c>
       <x:c r="E172" t="str"/>
       <x:c r="F172" t="n">
-        <x:v>2.9571</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G172" t="n">
         <x:v>8.3952</x:v>
+      </x:c>
+      <x:c r="H172" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I172" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J172" t="n">
+        <x:v>2.9571</x:v>
       </x:c>
     </x:row>
     <x:row r="173">
@@ -4095,10 +5646,19 @@
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F173" t="n">
-        <x:v>3.5036</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G173" t="n">
         <x:v>11.1936</x:v>
+      </x:c>
+      <x:c r="H173" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I173" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J173" t="n">
+        <x:v>3.5036</x:v>
       </x:c>
     </x:row>
     <x:row r="174">
@@ -4116,10 +5676,19 @@
       </x:c>
       <x:c r="E174" t="str"/>
       <x:c r="F174" t="n">
-        <x:v>4.1143</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G174" t="n">
         <x:v>10.4474</x:v>
+      </x:c>
+      <x:c r="H174" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I174" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J174" t="n">
+        <x:v>4.1143</x:v>
       </x:c>
     </x:row>
     <x:row r="175">
@@ -4137,10 +5706,19 @@
       </x:c>
       <x:c r="E175" t="str"/>
       <x:c r="F175" t="n">
-        <x:v>4.7893</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G175" t="n">
         <x:v>11.5667</x:v>
+      </x:c>
+      <x:c r="H175" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I175" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J175" t="n">
+        <x:v>4.7893</x:v>
       </x:c>
     </x:row>
     <x:row r="176">
@@ -4158,10 +5736,19 @@
       </x:c>
       <x:c r="E176" t="str"/>
       <x:c r="F176" t="n">
-        <x:v>5.5286</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G176" t="n">
         <x:v>12.8726</x:v>
+      </x:c>
+      <x:c r="H176" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I176" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J176" t="n">
+        <x:v>5.5286</x:v>
       </x:c>
     </x:row>
     <x:row r="177">
@@ -4179,10 +5766,19 @@
       </x:c>
       <x:c r="E177" t="str"/>
       <x:c r="F177" t="n">
-        <x:v>6.3321</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G177" t="n">
         <x:v>14.1786</x:v>
+      </x:c>
+      <x:c r="H177" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I177" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J177" t="n">
+        <x:v>6.3321</x:v>
       </x:c>
     </x:row>
     <x:row r="178">
@@ -4202,10 +5798,19 @@
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F178" t="n">
-        <x:v>7.2</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G178" t="n">
         <x:v>18.656</x:v>
+      </x:c>
+      <x:c r="H178" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I178" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J178" t="n">
+        <x:v>7.2</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/design/tables/Wave.xlsx
+++ b/design/tables/Wave.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wave" sheetId="1" r:id="R97372b130428453a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wave" sheetId="1" r:id="R2084ce9055bd4e5f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -579,7 +579,7 @@
       <x:c r="D6" s="24" t="n">
         <x:v>0.98</x:v>
       </x:c>
-      <x:c r="E6" s="25" t="str"/>
+      <x:c r="E6" s="25"/>
       <x:c r="F6" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -615,7 +615,7 @@
       <x:c r="D7" s="24" t="n">
         <x:v>0.86</x:v>
       </x:c>
-      <x:c r="E7" s="25" t="str"/>
+      <x:c r="E7" s="25"/>
       <x:c r="F7" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -651,7 +651,7 @@
       <x:c r="D8" s="24" t="n">
         <x:v>0.72</x:v>
       </x:c>
-      <x:c r="E8" s="25" t="str"/>
+      <x:c r="E8" s="25"/>
       <x:c r="F8" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -687,7 +687,7 @@
       <x:c r="D9" s="24" t="n">
         <x:v>0.64</x:v>
       </x:c>
-      <x:c r="E9" s="25" t="str"/>
+      <x:c r="E9" s="25"/>
       <x:c r="F9" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -723,7 +723,7 @@
       <x:c r="D10" s="24" t="n">
         <x:v>0.6208</x:v>
       </x:c>
-      <x:c r="E10" s="25" t="str"/>
+      <x:c r="E10" s="25"/>
       <x:c r="F10" s="26" t="n">
         <x:v>1.02838</x:v>
       </x:c>
@@ -759,7 +759,7 @@
       <x:c r="D11" s="24" t="n">
         <x:v>0.6016</x:v>
       </x:c>
-      <x:c r="E11" s="25" t="str"/>
+      <x:c r="E11" s="25"/>
       <x:c r="F11" s="26" t="n">
         <x:v>1.07848</x:v>
       </x:c>
@@ -795,7 +795,7 @@
       <x:c r="D12" s="24" t="n">
         <x:v>0.5824</x:v>
       </x:c>
-      <x:c r="E12" s="25" t="str"/>
+      <x:c r="E12" s="25"/>
       <x:c r="F12" s="26" t="n">
         <x:v>1.13446</x:v>
       </x:c>
@@ -869,7 +869,7 @@
       <x:c r="D14" s="24" t="n">
         <x:v>0.86</x:v>
       </x:c>
-      <x:c r="E14" s="25" t="str"/>
+      <x:c r="E14" s="25"/>
       <x:c r="F14" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -905,7 +905,7 @@
       <x:c r="D15" s="24" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="E15" s="25" t="str"/>
+      <x:c r="E15" s="25"/>
       <x:c r="F15" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -941,7 +941,7 @@
       <x:c r="D16" s="24" t="n">
         <x:v>0.58</x:v>
       </x:c>
-      <x:c r="E16" s="25" t="str"/>
+      <x:c r="E16" s="25"/>
       <x:c r="F16" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -977,7 +977,7 @@
       <x:c r="D17" s="24" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="E17" s="25" t="str"/>
+      <x:c r="E17" s="25"/>
       <x:c r="F17" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -1013,7 +1013,7 @@
       <x:c r="D18" s="24" t="n">
         <x:v>0.49</x:v>
       </x:c>
-      <x:c r="E18" s="25" t="str"/>
+      <x:c r="E18" s="25"/>
       <x:c r="F18" s="26" t="n">
         <x:v>1.00504</x:v>
       </x:c>
@@ -1049,7 +1049,7 @@
       <x:c r="D19" s="24" t="n">
         <x:v>0.48</x:v>
       </x:c>
-      <x:c r="E19" s="25" t="str"/>
+      <x:c r="E19" s="25"/>
       <x:c r="F19" s="26" t="n">
         <x:v>1.02791</x:v>
       </x:c>
@@ -1085,7 +1085,7 @@
       <x:c r="D20" s="24" t="n">
         <x:v>0.47</x:v>
       </x:c>
-      <x:c r="E20" s="25" t="str"/>
+      <x:c r="E20" s="25"/>
       <x:c r="F20" s="26" t="n">
         <x:v>1.05665</x:v>
       </x:c>
@@ -1121,7 +1121,7 @@
       <x:c r="D21" s="24" t="n">
         <x:v>0.46</x:v>
       </x:c>
-      <x:c r="E21" s="25" t="str"/>
+      <x:c r="E21" s="25"/>
       <x:c r="F21" s="26" t="n">
         <x:v>1.08805</x:v>
       </x:c>
@@ -1157,7 +1157,7 @@
       <x:c r="D22" s="24" t="n">
         <x:v>0.45</x:v>
       </x:c>
-      <x:c r="E22" s="25" t="str"/>
+      <x:c r="E22" s="25"/>
       <x:c r="F22" s="26" t="n">
         <x:v>1.12061</x:v>
       </x:c>
@@ -1231,7 +1231,7 @@
       <x:c r="D24" s="24" t="n">
         <x:v>0.62</x:v>
       </x:c>
-      <x:c r="E24" s="25" t="str"/>
+      <x:c r="E24" s="25"/>
       <x:c r="F24" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -1267,7 +1267,7 @@
       <x:c r="D25" s="24" t="n">
         <x:v>0.54</x:v>
       </x:c>
-      <x:c r="E25" s="25" t="str"/>
+      <x:c r="E25" s="25"/>
       <x:c r="F25" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -1303,7 +1303,7 @@
       <x:c r="D26" s="24" t="n">
         <x:v>0.46</x:v>
       </x:c>
-      <x:c r="E26" s="25" t="str"/>
+      <x:c r="E26" s="25"/>
       <x:c r="F26" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -1339,7 +1339,7 @@
       <x:c r="D27" s="24" t="n">
         <x:v>0.4</x:v>
       </x:c>
-      <x:c r="E27" s="25" t="str"/>
+      <x:c r="E27" s="25"/>
       <x:c r="F27" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -1375,7 +1375,7 @@
       <x:c r="D28" s="24" t="n">
         <x:v>0.394</x:v>
       </x:c>
-      <x:c r="E28" s="25" t="str"/>
+      <x:c r="E28" s="25"/>
       <x:c r="F28" s="26" t="n">
         <x:v>0.99362</x:v>
       </x:c>
@@ -1411,7 +1411,7 @@
       <x:c r="D29" s="24" t="n">
         <x:v>0.388</x:v>
       </x:c>
-      <x:c r="E29" s="25" t="str"/>
+      <x:c r="E29" s="25"/>
       <x:c r="F29" s="26" t="n">
         <x:v>1.00318</x:v>
       </x:c>
@@ -1447,7 +1447,7 @@
       <x:c r="D30" s="24" t="n">
         <x:v>0.382</x:v>
       </x:c>
-      <x:c r="E30" s="25" t="str"/>
+      <x:c r="E30" s="25"/>
       <x:c r="F30" s="26" t="n">
         <x:v>1.0186</x:v>
       </x:c>
@@ -1483,7 +1483,7 @@
       <x:c r="D31" s="24" t="n">
         <x:v>0.376</x:v>
       </x:c>
-      <x:c r="E31" s="25" t="str"/>
+      <x:c r="E31" s="25"/>
       <x:c r="F31" s="26" t="n">
         <x:v>1.03706</x:v>
       </x:c>
@@ -1519,7 +1519,7 @@
       <x:c r="D32" s="24" t="n">
         <x:v>0.37</x:v>
       </x:c>
-      <x:c r="E32" s="25" t="str"/>
+      <x:c r="E32" s="25"/>
       <x:c r="F32" s="26" t="n">
         <x:v>1.05721</x:v>
       </x:c>
@@ -1555,7 +1555,7 @@
       <x:c r="D33" s="24" t="n">
         <x:v>0.364</x:v>
       </x:c>
-      <x:c r="E33" s="25" t="str"/>
+      <x:c r="E33" s="25"/>
       <x:c r="F33" s="26" t="n">
         <x:v>1.07826</x:v>
       </x:c>
@@ -1591,7 +1591,7 @@
       <x:c r="D34" s="24" t="n">
         <x:v>0.358</x:v>
       </x:c>
-      <x:c r="E34" s="25" t="str"/>
+      <x:c r="E34" s="25"/>
       <x:c r="F34" s="26" t="n">
         <x:v>1.09971</x:v>
       </x:c>
@@ -1665,7 +1665,7 @@
       <x:c r="D36" s="24" t="n">
         <x:v>0.8</x:v>
       </x:c>
-      <x:c r="E36" s="25" t="str"/>
+      <x:c r="E36" s="25"/>
       <x:c r="F36" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -1701,7 +1701,7 @@
       <x:c r="D37" s="24" t="n">
         <x:v>0.66</x:v>
       </x:c>
-      <x:c r="E37" s="25" t="str"/>
+      <x:c r="E37" s="25"/>
       <x:c r="F37" s="26" t="n">
         <x:v>1.05</x:v>
       </x:c>
@@ -1737,7 +1737,7 @@
       <x:c r="D38" s="24" t="n">
         <x:v>0.58</x:v>
       </x:c>
-      <x:c r="E38" s="25" t="str"/>
+      <x:c r="E38" s="25"/>
       <x:c r="F38" s="26" t="n">
         <x:v>1.1</x:v>
       </x:c>
@@ -1773,7 +1773,7 @@
       <x:c r="D39" s="24" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="E39" s="25" t="str"/>
+      <x:c r="E39" s="25"/>
       <x:c r="F39" s="26" t="n">
         <x:v>1.15</x:v>
       </x:c>
@@ -1809,7 +1809,7 @@
       <x:c r="D40" s="24" t="n">
         <x:v>0.49455</x:v>
       </x:c>
-      <x:c r="E40" s="25" t="str"/>
+      <x:c r="E40" s="25"/>
       <x:c r="F40" s="26" t="n">
         <x:v>1.15326</x:v>
       </x:c>
@@ -1845,7 +1845,7 @@
       <x:c r="D41" s="24" t="n">
         <x:v>0.48909</x:v>
       </x:c>
-      <x:c r="E41" s="25" t="str"/>
+      <x:c r="E41" s="25"/>
       <x:c r="F41" s="26" t="n">
         <x:v>1.1766</x:v>
       </x:c>
@@ -1881,7 +1881,7 @@
       <x:c r="D42" s="24" t="n">
         <x:v>0.48364</x:v>
       </x:c>
-      <x:c r="E42" s="25" t="str"/>
+      <x:c r="E42" s="25"/>
       <x:c r="F42" s="26" t="n">
         <x:v>1.20669</x:v>
       </x:c>
@@ -1917,7 +1917,7 @@
       <x:c r="D43" s="24" t="n">
         <x:v>0.47818</x:v>
       </x:c>
-      <x:c r="E43" s="25" t="str"/>
+      <x:c r="E43" s="25"/>
       <x:c r="F43" s="26" t="n">
         <x:v>1.23992</x:v>
       </x:c>
@@ -1953,7 +1953,7 @@
       <x:c r="D44" s="24" t="n">
         <x:v>0.47273</x:v>
       </x:c>
-      <x:c r="E44" s="25" t="str"/>
+      <x:c r="E44" s="25"/>
       <x:c r="F44" s="26" t="n">
         <x:v>1.2746</x:v>
       </x:c>
@@ -1989,7 +1989,7 @@
       <x:c r="D45" s="24" t="n">
         <x:v>0.46727</x:v>
       </x:c>
-      <x:c r="E45" s="25" t="str"/>
+      <x:c r="E45" s="25"/>
       <x:c r="F45" s="26" t="n">
         <x:v>1.30978</x:v>
       </x:c>
@@ -2025,7 +2025,7 @@
       <x:c r="D46" s="24" t="n">
         <x:v>0.46182</x:v>
       </x:c>
-      <x:c r="E46" s="25" t="str"/>
+      <x:c r="E46" s="25"/>
       <x:c r="F46" s="26" t="n">
         <x:v>1.3449</x:v>
       </x:c>
@@ -2061,7 +2061,7 @@
       <x:c r="D47" s="24" t="n">
         <x:v>0.45636</x:v>
       </x:c>
-      <x:c r="E47" s="25" t="str"/>
+      <x:c r="E47" s="25"/>
       <x:c r="F47" s="26" t="n">
         <x:v>1.37964</x:v>
       </x:c>
@@ -2097,7 +2097,7 @@
       <x:c r="D48" s="24" t="n">
         <x:v>0.45091</x:v>
       </x:c>
-      <x:c r="E48" s="25" t="str"/>
+      <x:c r="E48" s="25"/>
       <x:c r="F48" s="26" t="n">
         <x:v>1.41377</x:v>
       </x:c>
@@ -2133,7 +2133,7 @@
       <x:c r="D49" s="24" t="n">
         <x:v>0.44545</x:v>
       </x:c>
-      <x:c r="E49" s="25" t="str"/>
+      <x:c r="E49" s="25"/>
       <x:c r="F49" s="26" t="n">
         <x:v>1.44719</x:v>
       </x:c>
@@ -2207,7 +2207,7 @@
       <x:c r="D51" s="24" t="n">
         <x:v>0.74</x:v>
       </x:c>
-      <x:c r="E51" s="25" t="str"/>
+      <x:c r="E51" s="25"/>
       <x:c r="F51" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -2243,7 +2243,7 @@
       <x:c r="D52" s="24" t="n">
         <x:v>0.64</x:v>
       </x:c>
-      <x:c r="E52" s="25" t="str"/>
+      <x:c r="E52" s="25"/>
       <x:c r="F52" s="26" t="n">
         <x:v>1.05</x:v>
       </x:c>
@@ -2279,7 +2279,7 @@
       <x:c r="D53" s="24" t="n">
         <x:v>0.54</x:v>
       </x:c>
-      <x:c r="E53" s="25" t="str"/>
+      <x:c r="E53" s="25"/>
       <x:c r="F53" s="26" t="n">
         <x:v>1.1</x:v>
       </x:c>
@@ -2315,7 +2315,7 @@
       <x:c r="D54" s="24" t="n">
         <x:v>0.68</x:v>
       </x:c>
-      <x:c r="E54" s="25" t="str"/>
+      <x:c r="E54" s="25"/>
       <x:c r="F54" s="26" t="n">
         <x:v>1.15</x:v>
       </x:c>
@@ -2351,7 +2351,7 @@
       <x:c r="D55" s="24" t="n">
         <x:v>0.6749</x:v>
       </x:c>
-      <x:c r="E55" s="25" t="str"/>
+      <x:c r="E55" s="25"/>
       <x:c r="F55" s="26" t="n">
         <x:v>1.12684</x:v>
       </x:c>
@@ -2387,7 +2387,7 @@
       <x:c r="D56" s="24" t="n">
         <x:v>0.6698</x:v>
       </x:c>
-      <x:c r="E56" s="25" t="str"/>
+      <x:c r="E56" s="25"/>
       <x:c r="F56" s="26" t="n">
         <x:v>1.11937</x:v>
       </x:c>
@@ -2423,7 +2423,7 @@
       <x:c r="D57" s="24" t="n">
         <x:v>0.6647</x:v>
       </x:c>
-      <x:c r="E57" s="25" t="str"/>
+      <x:c r="E57" s="25"/>
       <x:c r="F57" s="26" t="n">
         <x:v>1.11862</x:v>
       </x:c>
@@ -2459,7 +2459,7 @@
       <x:c r="D58" s="24" t="n">
         <x:v>0.6596</x:v>
       </x:c>
-      <x:c r="E58" s="25" t="str"/>
+      <x:c r="E58" s="25"/>
       <x:c r="F58" s="26" t="n">
         <x:v>1.12193</x:v>
       </x:c>
@@ -2495,7 +2495,7 @@
       <x:c r="D59" s="24" t="n">
         <x:v>0.6545</x:v>
       </x:c>
-      <x:c r="E59" s="25" t="str"/>
+      <x:c r="E59" s="25"/>
       <x:c r="F59" s="26" t="n">
         <x:v>1.1279</x:v>
       </x:c>
@@ -2531,7 +2531,7 @@
       <x:c r="D60" s="24" t="n">
         <x:v>0.6494</x:v>
       </x:c>
-      <x:c r="E60" s="25" t="str"/>
+      <x:c r="E60" s="25"/>
       <x:c r="F60" s="26" t="n">
         <x:v>1.1357</x:v>
       </x:c>
@@ -2567,7 +2567,7 @@
       <x:c r="D61" s="24" t="n">
         <x:v>0.6443</x:v>
       </x:c>
-      <x:c r="E61" s="25" t="str"/>
+      <x:c r="E61" s="25"/>
       <x:c r="F61" s="26" t="n">
         <x:v>1.14476</x:v>
       </x:c>
@@ -2603,7 +2603,7 @@
       <x:c r="D62" s="24" t="n">
         <x:v>0.6392</x:v>
       </x:c>
-      <x:c r="E62" s="25" t="str"/>
+      <x:c r="E62" s="25"/>
       <x:c r="F62" s="26" t="n">
         <x:v>1.1547</x:v>
       </x:c>
@@ -2639,7 +2639,7 @@
       <x:c r="D63" s="24" t="n">
         <x:v>0.6341</x:v>
       </x:c>
-      <x:c r="E63" s="25" t="str"/>
+      <x:c r="E63" s="25"/>
       <x:c r="F63" s="26" t="n">
         <x:v>1.16527</x:v>
       </x:c>
@@ -2675,7 +2675,7 @@
       <x:c r="D64" s="24" t="n">
         <x:v>0.629</x:v>
       </x:c>
-      <x:c r="E64" s="25" t="str"/>
+      <x:c r="E64" s="25"/>
       <x:c r="F64" s="26" t="n">
         <x:v>1.17625</x:v>
       </x:c>
@@ -2711,7 +2711,7 @@
       <x:c r="D65" s="24" t="n">
         <x:v>0.6239</x:v>
       </x:c>
-      <x:c r="E65" s="25" t="str"/>
+      <x:c r="E65" s="25"/>
       <x:c r="F65" s="26" t="n">
         <x:v>1.18751</x:v>
       </x:c>
@@ -2747,7 +2747,7 @@
       <x:c r="D66" s="24" t="n">
         <x:v>0.6188</x:v>
       </x:c>
-      <x:c r="E66" s="25" t="str"/>
+      <x:c r="E66" s="25"/>
       <x:c r="F66" s="26" t="n">
         <x:v>1.19893</x:v>
       </x:c>
@@ -2783,7 +2783,7 @@
       <x:c r="D67" s="24" t="n">
         <x:v>0.6137</x:v>
       </x:c>
-      <x:c r="E67" s="25" t="str"/>
+      <x:c r="E67" s="25"/>
       <x:c r="F67" s="26" t="n">
         <x:v>1.21044</x:v>
       </x:c>
@@ -2819,7 +2819,7 @@
       <x:c r="D68" s="24" t="n">
         <x:v>0.6086</x:v>
       </x:c>
-      <x:c r="E68" s="25" t="str"/>
+      <x:c r="E68" s="25"/>
       <x:c r="F68" s="26" t="n">
         <x:v>1.22197</x:v>
       </x:c>
@@ -2855,7 +2855,7 @@
       <x:c r="D69" s="24" t="n">
         <x:v>0.6035</x:v>
       </x:c>
-      <x:c r="E69" s="25" t="str"/>
+      <x:c r="E69" s="25"/>
       <x:c r="F69" s="26" t="n">
         <x:v>1.23347</x:v>
       </x:c>
@@ -2929,7 +2929,7 @@
       <x:c r="D71" s="24" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="E71" s="25" t="str"/>
+      <x:c r="E71" s="25"/>
       <x:c r="F71" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -2965,7 +2965,7 @@
       <x:c r="D72" s="24" t="n">
         <x:v>0.6</x:v>
       </x:c>
-      <x:c r="E72" s="25" t="str"/>
+      <x:c r="E72" s="25"/>
       <x:c r="F72" s="26" t="n">
         <x:v>1.025</x:v>
       </x:c>
@@ -3001,7 +3001,7 @@
       <x:c r="D73" s="24" t="n">
         <x:v>0.51</x:v>
       </x:c>
-      <x:c r="E73" s="25" t="str"/>
+      <x:c r="E73" s="25"/>
       <x:c r="F73" s="26" t="n">
         <x:v>1.05</x:v>
       </x:c>
@@ -3037,7 +3037,7 @@
       <x:c r="D74" s="24" t="n">
         <x:v>0.44</x:v>
       </x:c>
-      <x:c r="E74" s="25" t="str"/>
+      <x:c r="E74" s="25"/>
       <x:c r="F74" s="26" t="n">
         <x:v>1.075</x:v>
       </x:c>
@@ -3073,7 +3073,7 @@
       <x:c r="D75" s="24" t="n">
         <x:v>0.4352</x:v>
       </x:c>
-      <x:c r="E75" s="25" t="str"/>
+      <x:c r="E75" s="25"/>
       <x:c r="F75" s="26" t="n">
         <x:v>1.07805</x:v>
       </x:c>
@@ -3109,7 +3109,7 @@
       <x:c r="D76" s="24" t="n">
         <x:v>0.4304</x:v>
       </x:c>
-      <x:c r="E76" s="25" t="str"/>
+      <x:c r="E76" s="25"/>
       <x:c r="F76" s="26" t="n">
         <x:v>1.09987</x:v>
       </x:c>
@@ -3145,7 +3145,7 @@
       <x:c r="D77" s="24" t="n">
         <x:v>0.4256</x:v>
       </x:c>
-      <x:c r="E77" s="25" t="str"/>
+      <x:c r="E77" s="25"/>
       <x:c r="F77" s="26" t="n">
         <x:v>1.12799</x:v>
       </x:c>
@@ -3181,7 +3181,7 @@
       <x:c r="D78" s="24" t="n">
         <x:v>0.4208</x:v>
       </x:c>
-      <x:c r="E78" s="25" t="str"/>
+      <x:c r="E78" s="25"/>
       <x:c r="F78" s="26" t="n">
         <x:v>1.15906</x:v>
       </x:c>
@@ -3217,7 +3217,7 @@
       <x:c r="D79" s="24" t="n">
         <x:v>0.416</x:v>
       </x:c>
-      <x:c r="E79" s="25" t="str"/>
+      <x:c r="E79" s="25"/>
       <x:c r="F79" s="26" t="n">
         <x:v>1.19147</x:v>
       </x:c>
@@ -3253,7 +3253,7 @@
       <x:c r="D80" s="24" t="n">
         <x:v>0.4112</x:v>
       </x:c>
-      <x:c r="E80" s="25" t="str"/>
+      <x:c r="E80" s="25"/>
       <x:c r="F80" s="26" t="n">
         <x:v>1.22436</x:v>
       </x:c>
@@ -3289,7 +3289,7 @@
       <x:c r="D81" s="24" t="n">
         <x:v>0.4064</x:v>
       </x:c>
-      <x:c r="E81" s="25" t="str"/>
+      <x:c r="E81" s="25"/>
       <x:c r="F81" s="26" t="n">
         <x:v>1.25719</x:v>
       </x:c>
@@ -3325,7 +3325,7 @@
       <x:c r="D82" s="24" t="n">
         <x:v>0.4016</x:v>
       </x:c>
-      <x:c r="E82" s="25" t="str"/>
+      <x:c r="E82" s="25"/>
       <x:c r="F82" s="26" t="n">
         <x:v>1.28966</x:v>
       </x:c>
@@ -3361,7 +3361,7 @@
       <x:c r="D83" s="24" t="n">
         <x:v>0.3968</x:v>
       </x:c>
-      <x:c r="E83" s="25" t="str"/>
+      <x:c r="E83" s="25"/>
       <x:c r="F83" s="26" t="n">
         <x:v>1.32157</x:v>
       </x:c>
@@ -3397,7 +3397,7 @@
       <x:c r="D84" s="24" t="n">
         <x:v>0.392</x:v>
       </x:c>
-      <x:c r="E84" s="25" t="str"/>
+      <x:c r="E84" s="25"/>
       <x:c r="F84" s="26" t="n">
         <x:v>1.35281</x:v>
       </x:c>
@@ -3471,7 +3471,7 @@
       <x:c r="D86" s="24" t="n">
         <x:v>0.68</x:v>
       </x:c>
-      <x:c r="E86" s="25" t="str"/>
+      <x:c r="E86" s="25"/>
       <x:c r="F86" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -3507,7 +3507,7 @@
       <x:c r="D87" s="24" t="n">
         <x:v>0.57</x:v>
       </x:c>
-      <x:c r="E87" s="25" t="str"/>
+      <x:c r="E87" s="25"/>
       <x:c r="F87" s="26" t="n">
         <x:v>1.05</x:v>
       </x:c>
@@ -3543,7 +3543,7 @@
       <x:c r="D88" s="24" t="n">
         <x:v>0.49</x:v>
       </x:c>
-      <x:c r="E88" s="25" t="str"/>
+      <x:c r="E88" s="25"/>
       <x:c r="F88" s="26" t="n">
         <x:v>1.1</x:v>
       </x:c>
@@ -3579,7 +3579,7 @@
       <x:c r="D89" s="26" t="n">
         <x:v>0.42</x:v>
       </x:c>
-      <x:c r="E89" s="26" t="str"/>
+      <x:c r="E89" s="26"/>
       <x:c r="F89" s="26" t="n">
         <x:v>1.15</x:v>
       </x:c>
@@ -3615,7 +3615,7 @@
       <x:c r="D90" s="26" t="n">
         <x:v>0.41542</x:v>
       </x:c>
-      <x:c r="E90" s="26" t="str"/>
+      <x:c r="E90" s="26"/>
       <x:c r="F90" s="26" t="n">
         <x:v>1.15326</x:v>
       </x:c>
@@ -3651,7 +3651,7 @@
       <x:c r="D91" s="26" t="n">
         <x:v>0.41084</x:v>
       </x:c>
-      <x:c r="E91" s="26" t="str"/>
+      <x:c r="E91" s="26"/>
       <x:c r="F91" s="26" t="n">
         <x:v>1.1766</x:v>
       </x:c>
@@ -3687,7 +3687,7 @@
       <x:c r="D92" s="26" t="n">
         <x:v>0.40625</x:v>
       </x:c>
-      <x:c r="E92" s="26" t="str"/>
+      <x:c r="E92" s="26"/>
       <x:c r="F92" s="26" t="n">
         <x:v>1.20669</x:v>
       </x:c>
@@ -3723,7 +3723,7 @@
       <x:c r="D93" s="26" t="n">
         <x:v>0.40167</x:v>
       </x:c>
-      <x:c r="E93" s="26" t="str"/>
+      <x:c r="E93" s="26"/>
       <x:c r="F93" s="26" t="n">
         <x:v>1.23992</x:v>
       </x:c>
@@ -3759,7 +3759,7 @@
       <x:c r="D94" s="26" t="n">
         <x:v>0.39709</x:v>
       </x:c>
-      <x:c r="E94" s="26" t="str"/>
+      <x:c r="E94" s="26"/>
       <x:c r="F94" s="26" t="n">
         <x:v>1.2746</x:v>
       </x:c>
@@ -3795,7 +3795,7 @@
       <x:c r="D95" s="26" t="n">
         <x:v>0.39251</x:v>
       </x:c>
-      <x:c r="E95" s="26" t="str"/>
+      <x:c r="E95" s="26"/>
       <x:c r="F95" s="26" t="n">
         <x:v>1.30978</x:v>
       </x:c>
@@ -3831,7 +3831,7 @@
       <x:c r="D96" s="26" t="n">
         <x:v>0.38793</x:v>
       </x:c>
-      <x:c r="E96" s="26" t="str"/>
+      <x:c r="E96" s="26"/>
       <x:c r="F96" s="26" t="n">
         <x:v>1.3449</x:v>
       </x:c>
@@ -3867,7 +3867,7 @@
       <x:c r="D97" s="26" t="n">
         <x:v>0.38335</x:v>
       </x:c>
-      <x:c r="E97" s="26" t="str"/>
+      <x:c r="E97" s="26"/>
       <x:c r="F97" s="26" t="n">
         <x:v>1.37964</x:v>
       </x:c>
@@ -3903,7 +3903,7 @@
       <x:c r="D98" s="26" t="n">
         <x:v>0.37876</x:v>
       </x:c>
-      <x:c r="E98" s="26" t="str"/>
+      <x:c r="E98" s="26"/>
       <x:c r="F98" s="26" t="n">
         <x:v>1.41377</x:v>
       </x:c>
@@ -3939,7 +3939,7 @@
       <x:c r="D99" s="26" t="n">
         <x:v>0.37418</x:v>
       </x:c>
-      <x:c r="E99" s="26" t="str"/>
+      <x:c r="E99" s="26"/>
       <x:c r="F99" s="26" t="n">
         <x:v>1.44719</x:v>
       </x:c>
@@ -4051,7 +4051,7 @@
       <x:c r="D102" s="26" t="n">
         <x:v>0.68</x:v>
       </x:c>
-      <x:c r="E102" s="26" t="str"/>
+      <x:c r="E102" s="26"/>
       <x:c r="F102" s="26" t="n">
         <x:v>1.08</x:v>
       </x:c>
@@ -4125,7 +4125,7 @@
       <x:c r="D104" s="26" t="n">
         <x:v>0.43</x:v>
       </x:c>
-      <x:c r="E104" s="26" t="str"/>
+      <x:c r="E104" s="26"/>
       <x:c r="F104" s="26" t="n">
         <x:v>1.24</x:v>
       </x:c>
@@ -4161,7 +4161,7 @@
       <x:c r="D105" s="26" t="n">
         <x:v>0.42531</x:v>
       </x:c>
-      <x:c r="E105" s="26" t="str"/>
+      <x:c r="E105" s="26"/>
       <x:c r="F105" s="26" t="n">
         <x:v>1.24351</x:v>
       </x:c>
@@ -4197,7 +4197,7 @@
       <x:c r="D106" s="26" t="n">
         <x:v>0.42062</x:v>
       </x:c>
-      <x:c r="E106" s="26" t="str"/>
+      <x:c r="E106" s="26"/>
       <x:c r="F106" s="26" t="n">
         <x:v>1.26868</x:v>
       </x:c>
@@ -4233,7 +4233,7 @@
       <x:c r="D107" s="26" t="n">
         <x:v>0.41593</x:v>
       </x:c>
-      <x:c r="E107" s="26" t="str"/>
+      <x:c r="E107" s="26"/>
       <x:c r="F107" s="26" t="n">
         <x:v>1.30112</x:v>
       </x:c>
@@ -4269,7 +4269,7 @@
       <x:c r="D108" s="26" t="n">
         <x:v>0.41124</x:v>
       </x:c>
-      <x:c r="E108" s="26" t="str"/>
+      <x:c r="E108" s="26"/>
       <x:c r="F108" s="26" t="n">
         <x:v>1.33696</x:v>
       </x:c>
@@ -4305,7 +4305,7 @@
       <x:c r="D109" s="26" t="n">
         <x:v>0.40655</x:v>
       </x:c>
-      <x:c r="E109" s="26" t="str"/>
+      <x:c r="E109" s="26"/>
       <x:c r="F109" s="26" t="n">
         <x:v>1.37435</x:v>
       </x:c>
@@ -4341,7 +4341,7 @@
       <x:c r="D110" t="n">
         <x:v>0.40185</x:v>
       </x:c>
-      <x:c r="E110" t="str"/>
+      <x:c r="E110"/>
       <x:c r="F110" t="n">
         <x:v>1.41228</x:v>
       </x:c>
@@ -4377,7 +4377,7 @@
       <x:c r="D111" t="n">
         <x:v>0.39716</x:v>
       </x:c>
-      <x:c r="E111" t="str"/>
+      <x:c r="E111"/>
       <x:c r="F111" t="n">
         <x:v>1.45016</x:v>
       </x:c>
@@ -4413,7 +4413,7 @@
       <x:c r="D112" t="n">
         <x:v>0.39247</x:v>
       </x:c>
-      <x:c r="E112" t="str"/>
+      <x:c r="E112"/>
       <x:c r="F112" t="n">
         <x:v>1.48761</x:v>
       </x:c>
@@ -4449,7 +4449,7 @@
       <x:c r="D113" t="n">
         <x:v>0.38778</x:v>
       </x:c>
-      <x:c r="E113" t="str"/>
+      <x:c r="E113"/>
       <x:c r="F113" t="n">
         <x:v>1.52442</x:v>
       </x:c>
@@ -4485,7 +4485,7 @@
       <x:c r="D114" t="n">
         <x:v>0.38309</x:v>
       </x:c>
-      <x:c r="E114" t="str"/>
+      <x:c r="E114"/>
       <x:c r="F114" t="n">
         <x:v>1.56045</x:v>
       </x:c>
@@ -4559,7 +4559,7 @@
       <x:c r="D116" t="n">
         <x:v>0.62</x:v>
       </x:c>
-      <x:c r="E116" t="str"/>
+      <x:c r="E116"/>
       <x:c r="F116" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -4595,7 +4595,7 @@
       <x:c r="D117" t="n">
         <x:v>0.53</x:v>
       </x:c>
-      <x:c r="E117" t="str"/>
+      <x:c r="E117"/>
       <x:c r="F117" t="n">
         <x:v>1.08</x:v>
       </x:c>
@@ -4631,7 +4631,7 @@
       <x:c r="D118" t="n">
         <x:v>0.45</x:v>
       </x:c>
-      <x:c r="E118" t="str"/>
+      <x:c r="E118"/>
       <x:c r="F118" t="n">
         <x:v>1.16</x:v>
       </x:c>
@@ -4667,7 +4667,7 @@
       <x:c r="D119" t="n">
         <x:v>0.38</x:v>
       </x:c>
-      <x:c r="E119" t="str"/>
+      <x:c r="E119"/>
       <x:c r="F119" t="n">
         <x:v>1.24</x:v>
       </x:c>
@@ -4703,7 +4703,7 @@
       <x:c r="D120" t="n">
         <x:v>0.37585</x:v>
       </x:c>
-      <x:c r="E120" t="str"/>
+      <x:c r="E120"/>
       <x:c r="F120" t="n">
         <x:v>1.24351</x:v>
       </x:c>
@@ -4739,7 +4739,7 @@
       <x:c r="D121" t="n">
         <x:v>0.37171</x:v>
       </x:c>
-      <x:c r="E121" t="str"/>
+      <x:c r="E121"/>
       <x:c r="F121" t="n">
         <x:v>1.26868</x:v>
       </x:c>
@@ -4775,7 +4775,7 @@
       <x:c r="D122" t="n">
         <x:v>0.36756</x:v>
       </x:c>
-      <x:c r="E122" t="str"/>
+      <x:c r="E122"/>
       <x:c r="F122" t="n">
         <x:v>1.30112</x:v>
       </x:c>
@@ -4811,7 +4811,7 @@
       <x:c r="D123" t="n">
         <x:v>0.36342</x:v>
       </x:c>
-      <x:c r="E123" t="str"/>
+      <x:c r="E123"/>
       <x:c r="F123" t="n">
         <x:v>1.33696</x:v>
       </x:c>
@@ -4847,7 +4847,7 @@
       <x:c r="D124" t="n">
         <x:v>0.35927</x:v>
       </x:c>
-      <x:c r="E124" t="str"/>
+      <x:c r="E124"/>
       <x:c r="F124" t="n">
         <x:v>1.37435</x:v>
       </x:c>
@@ -4883,7 +4883,7 @@
       <x:c r="D125" t="n">
         <x:v>0.35513</x:v>
       </x:c>
-      <x:c r="E125" t="str"/>
+      <x:c r="E125"/>
       <x:c r="F125" t="n">
         <x:v>1.41228</x:v>
       </x:c>
@@ -4919,7 +4919,7 @@
       <x:c r="D126" t="n">
         <x:v>0.35098</x:v>
       </x:c>
-      <x:c r="E126" t="str"/>
+      <x:c r="E126"/>
       <x:c r="F126" t="n">
         <x:v>1.45016</x:v>
       </x:c>
@@ -4955,7 +4955,7 @@
       <x:c r="D127" t="n">
         <x:v>0.34684</x:v>
       </x:c>
-      <x:c r="E127" t="str"/>
+      <x:c r="E127"/>
       <x:c r="F127" t="n">
         <x:v>1.48761</x:v>
       </x:c>
@@ -4991,7 +4991,7 @@
       <x:c r="D128" t="n">
         <x:v>0.34269</x:v>
       </x:c>
-      <x:c r="E128" t="str"/>
+      <x:c r="E128"/>
       <x:c r="F128" t="n">
         <x:v>1.52442</x:v>
       </x:c>
@@ -5027,7 +5027,7 @@
       <x:c r="D129" t="n">
         <x:v>0.33855</x:v>
       </x:c>
-      <x:c r="E129" t="str"/>
+      <x:c r="E129"/>
       <x:c r="F129" t="n">
         <x:v>1.56045</x:v>
       </x:c>
@@ -5101,7 +5101,7 @@
       <x:c r="D131" t="n">
         <x:v>0.62</x:v>
       </x:c>
-      <x:c r="E131" t="str"/>
+      <x:c r="E131"/>
       <x:c r="F131" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -5137,7 +5137,7 @@
       <x:c r="D132" t="n">
         <x:v>0.58</x:v>
       </x:c>
-      <x:c r="E132" t="str"/>
+      <x:c r="E132"/>
       <x:c r="F132" t="n">
         <x:v>1.08</x:v>
       </x:c>
@@ -5173,7 +5173,7 @@
       <x:c r="D133" t="n">
         <x:v>0.47</x:v>
       </x:c>
-      <x:c r="E133" t="str"/>
+      <x:c r="E133"/>
       <x:c r="F133" t="n">
         <x:v>1.16</x:v>
       </x:c>
@@ -5209,7 +5209,7 @@
       <x:c r="D134" t="n">
         <x:v>0.48</x:v>
       </x:c>
-      <x:c r="E134" t="str"/>
+      <x:c r="E134"/>
       <x:c r="F134" t="n">
         <x:v>1.24</x:v>
       </x:c>
@@ -5245,7 +5245,7 @@
       <x:c r="D135" t="n">
         <x:v>0.6</x:v>
       </x:c>
-      <x:c r="E135" t="str"/>
+      <x:c r="E135"/>
       <x:c r="F135" t="n">
         <x:v>1.32</x:v>
       </x:c>
@@ -5281,7 +5281,7 @@
       <x:c r="D136" t="n">
         <x:v>0.5952</x:v>
       </x:c>
-      <x:c r="E136" t="str"/>
+      <x:c r="E136"/>
       <x:c r="F136" t="n">
         <x:v>1.3025</x:v>
       </x:c>
@@ -5317,7 +5317,7 @@
       <x:c r="D137" t="n">
         <x:v>0.5904</x:v>
       </x:c>
-      <x:c r="E137" t="str"/>
+      <x:c r="E137"/>
       <x:c r="F137" t="n">
         <x:v>1.30319</x:v>
       </x:c>
@@ -5353,7 +5353,7 @@
       <x:c r="D138" t="n">
         <x:v>0.5856</x:v>
       </x:c>
-      <x:c r="E138" t="str"/>
+      <x:c r="E138"/>
       <x:c r="F138" t="n">
         <x:v>1.31121</x:v>
       </x:c>
@@ -5389,7 +5389,7 @@
       <x:c r="D139" t="n">
         <x:v>0.5808</x:v>
       </x:c>
-      <x:c r="E139" t="str"/>
+      <x:c r="E139"/>
       <x:c r="F139" t="n">
         <x:v>1.32344</x:v>
       </x:c>
@@ -5425,7 +5425,7 @@
       <x:c r="D140" t="n">
         <x:v>0.576</x:v>
       </x:c>
-      <x:c r="E140" t="str"/>
+      <x:c r="E140"/>
       <x:c r="F140" t="n">
         <x:v>1.3383</x:v>
       </x:c>
@@ -5461,7 +5461,7 @@
       <x:c r="D141" t="n">
         <x:v>0.5712</x:v>
       </x:c>
-      <x:c r="E141" t="str"/>
+      <x:c r="E141"/>
       <x:c r="F141" t="n">
         <x:v>1.35484</x:v>
       </x:c>
@@ -5497,7 +5497,7 @@
       <x:c r="D142" t="n">
         <x:v>0.5664</x:v>
       </x:c>
-      <x:c r="E142" t="str"/>
+      <x:c r="E142"/>
       <x:c r="F142" t="n">
         <x:v>1.37244</x:v>
       </x:c>
@@ -5533,7 +5533,7 @@
       <x:c r="D143" t="n">
         <x:v>0.5616</x:v>
       </x:c>
-      <x:c r="E143" t="str"/>
+      <x:c r="E143"/>
       <x:c r="F143" t="n">
         <x:v>1.39071</x:v>
       </x:c>
@@ -5569,7 +5569,7 @@
       <x:c r="D144" t="n">
         <x:v>0.5568</x:v>
       </x:c>
-      <x:c r="E144" t="str"/>
+      <x:c r="E144"/>
       <x:c r="F144" t="n">
         <x:v>1.40936</x:v>
       </x:c>
@@ -5605,7 +5605,7 @@
       <x:c r="D145" t="n">
         <x:v>0.552</x:v>
       </x:c>
-      <x:c r="E145" t="str"/>
+      <x:c r="E145"/>
       <x:c r="F145" t="n">
         <x:v>1.42818</x:v>
       </x:c>
@@ -5641,7 +5641,7 @@
       <x:c r="D146" t="n">
         <x:v>0.5472</x:v>
       </x:c>
-      <x:c r="E146" t="str"/>
+      <x:c r="E146"/>
       <x:c r="F146" t="n">
         <x:v>1.44704</x:v>
       </x:c>
@@ -5677,7 +5677,7 @@
       <x:c r="D147" t="n">
         <x:v>0.5424</x:v>
       </x:c>
-      <x:c r="E147" t="str"/>
+      <x:c r="E147"/>
       <x:c r="F147" t="n">
         <x:v>1.46583</x:v>
       </x:c>
@@ -5713,7 +5713,7 @@
       <x:c r="D148" t="n">
         <x:v>0.5376</x:v>
       </x:c>
-      <x:c r="E148" t="str"/>
+      <x:c r="E148"/>
       <x:c r="F148" t="n">
         <x:v>1.48448</x:v>
       </x:c>
@@ -5749,7 +5749,7 @@
       <x:c r="D149" t="n">
         <x:v>0.5328</x:v>
       </x:c>
-      <x:c r="E149" t="str"/>
+      <x:c r="E149"/>
       <x:c r="F149" t="n">
         <x:v>1.50293</x:v>
       </x:c>
@@ -5861,7 +5861,7 @@
       <x:c r="D152" t="n">
         <x:v>0.595</x:v>
       </x:c>
-      <x:c r="E152" t="str"/>
+      <x:c r="E152"/>
       <x:c r="F152" t="n">
         <x:v>1.08</x:v>
       </x:c>
@@ -5897,7 +5897,7 @@
       <x:c r="D153" t="n">
         <x:v>0.53</x:v>
       </x:c>
-      <x:c r="E153" t="str"/>
+      <x:c r="E153"/>
       <x:c r="F153" t="n">
         <x:v>1.16</x:v>
       </x:c>
@@ -5933,7 +5933,7 @@
       <x:c r="D154" t="n">
         <x:v>0.465</x:v>
       </x:c>
-      <x:c r="E154" t="str"/>
+      <x:c r="E154"/>
       <x:c r="F154" t="n">
         <x:v>1.24</x:v>
       </x:c>
@@ -5969,7 +5969,7 @@
       <x:c r="D155" t="n">
         <x:v>0.45993</x:v>
       </x:c>
-      <x:c r="E155" t="str"/>
+      <x:c r="E155"/>
       <x:c r="F155" t="n">
         <x:v>1.24351</x:v>
       </x:c>
@@ -6005,7 +6005,7 @@
       <x:c r="D156" t="n">
         <x:v>0.45485</x:v>
       </x:c>
-      <x:c r="E156" t="str"/>
+      <x:c r="E156"/>
       <x:c r="F156" t="n">
         <x:v>1.26868</x:v>
       </x:c>
@@ -6041,7 +6041,7 @@
       <x:c r="D157" t="n">
         <x:v>0.44978</x:v>
       </x:c>
-      <x:c r="E157" t="str"/>
+      <x:c r="E157"/>
       <x:c r="F157" t="n">
         <x:v>1.30112</x:v>
       </x:c>
@@ -6077,7 +6077,7 @@
       <x:c r="D158" t="n">
         <x:v>0.44471</x:v>
       </x:c>
-      <x:c r="E158" t="str"/>
+      <x:c r="E158"/>
       <x:c r="F158" t="n">
         <x:v>1.33696</x:v>
       </x:c>
@@ -6113,7 +6113,7 @@
       <x:c r="D159" t="n">
         <x:v>0.43964</x:v>
       </x:c>
-      <x:c r="E159" t="str"/>
+      <x:c r="E159"/>
       <x:c r="F159" t="n">
         <x:v>1.37435</x:v>
       </x:c>
@@ -6149,7 +6149,7 @@
       <x:c r="D160" t="n">
         <x:v>0.43456</x:v>
       </x:c>
-      <x:c r="E160" t="str"/>
+      <x:c r="E160"/>
       <x:c r="F160" t="n">
         <x:v>1.41228</x:v>
       </x:c>
@@ -6185,7 +6185,7 @@
       <x:c r="D161" t="n">
         <x:v>0.42949</x:v>
       </x:c>
-      <x:c r="E161" t="str"/>
+      <x:c r="E161"/>
       <x:c r="F161" t="n">
         <x:v>1.45016</x:v>
       </x:c>
@@ -6221,7 +6221,7 @@
       <x:c r="D162" t="n">
         <x:v>0.42442</x:v>
       </x:c>
-      <x:c r="E162" t="str"/>
+      <x:c r="E162"/>
       <x:c r="F162" t="n">
         <x:v>1.48761</x:v>
       </x:c>
@@ -6257,7 +6257,7 @@
       <x:c r="D163" t="n">
         <x:v>0.41935</x:v>
       </x:c>
-      <x:c r="E163" t="str"/>
+      <x:c r="E163"/>
       <x:c r="F163" t="n">
         <x:v>1.52442</x:v>
       </x:c>
@@ -6293,7 +6293,7 @@
       <x:c r="D164" t="n">
         <x:v>0.41427</x:v>
       </x:c>
-      <x:c r="E164" t="str"/>
+      <x:c r="E164"/>
       <x:c r="F164" t="n">
         <x:v>1.56045</x:v>
       </x:c>
@@ -6329,7 +6329,7 @@
       <x:c r="D165" t="n">
         <x:v>0.4092</x:v>
       </x:c>
-      <x:c r="E165" t="str"/>
+      <x:c r="E165"/>
       <x:c r="F165" t="n">
         <x:v>1.59562</x:v>
       </x:c>
@@ -6403,7 +6403,7 @@
       <x:c r="D167" t="n">
         <x:v>0.589</x:v>
       </x:c>
-      <x:c r="E167" t="str"/>
+      <x:c r="E167"/>
       <x:c r="F167" t="n">
         <x:v>1.08</x:v>
       </x:c>
@@ -6439,7 +6439,7 @@
       <x:c r="D168" t="n">
         <x:v>0.524</x:v>
       </x:c>
-      <x:c r="E168" t="str"/>
+      <x:c r="E168"/>
       <x:c r="F168" t="n">
         <x:v>1.16</x:v>
       </x:c>
@@ -6475,7 +6475,7 @@
       <x:c r="D169" t="n">
         <x:v>0.459</x:v>
       </x:c>
-      <x:c r="E169" t="str"/>
+      <x:c r="E169"/>
       <x:c r="F169" t="n">
         <x:v>1.24</x:v>
       </x:c>
@@ -6511,7 +6511,7 @@
       <x:c r="D170" t="n">
         <x:v>0.45399</x:v>
       </x:c>
-      <x:c r="E170" t="str"/>
+      <x:c r="E170"/>
       <x:c r="F170" t="n">
         <x:v>1.24351</x:v>
       </x:c>
@@ -6547,7 +6547,7 @@
       <x:c r="D171" t="n">
         <x:v>0.44899</x:v>
       </x:c>
-      <x:c r="E171" t="str"/>
+      <x:c r="E171"/>
       <x:c r="F171" t="n">
         <x:v>1.26868</x:v>
       </x:c>
@@ -6583,7 +6583,7 @@
       <x:c r="D172" t="n">
         <x:v>0.44398</x:v>
       </x:c>
-      <x:c r="E172" t="str"/>
+      <x:c r="E172"/>
       <x:c r="F172" t="n">
         <x:v>1.30112</x:v>
       </x:c>
@@ -6619,7 +6619,7 @@
       <x:c r="D173" t="n">
         <x:v>0.43897</x:v>
       </x:c>
-      <x:c r="E173" t="str"/>
+      <x:c r="E173"/>
       <x:c r="F173" t="n">
         <x:v>1.33696</x:v>
       </x:c>
@@ -6655,7 +6655,7 @@
       <x:c r="D174" t="n">
         <x:v>0.43396</x:v>
       </x:c>
-      <x:c r="E174" t="str"/>
+      <x:c r="E174"/>
       <x:c r="F174" t="n">
         <x:v>1.37435</x:v>
       </x:c>
@@ -6691,7 +6691,7 @@
       <x:c r="D175" t="n">
         <x:v>0.42896</x:v>
       </x:c>
-      <x:c r="E175" t="str"/>
+      <x:c r="E175"/>
       <x:c r="F175" t="n">
         <x:v>1.41228</x:v>
       </x:c>
@@ -6727,7 +6727,7 @@
       <x:c r="D176" t="n">
         <x:v>0.42395</x:v>
       </x:c>
-      <x:c r="E176" t="str"/>
+      <x:c r="E176"/>
       <x:c r="F176" t="n">
         <x:v>1.45016</x:v>
       </x:c>
@@ -6763,7 +6763,7 @@
       <x:c r="D177" t="n">
         <x:v>0.41894</x:v>
       </x:c>
-      <x:c r="E177" t="str"/>
+      <x:c r="E177"/>
       <x:c r="F177" t="n">
         <x:v>1.48761</x:v>
       </x:c>
@@ -6799,7 +6799,7 @@
       <x:c r="D178" t="n">
         <x:v>0.41393</x:v>
       </x:c>
-      <x:c r="E178" t="str"/>
+      <x:c r="E178"/>
       <x:c r="F178" t="n">
         <x:v>1.52442</x:v>
       </x:c>
@@ -6835,7 +6835,7 @@
       <x:c r="D179" s="24" t="n">
         <x:v>0.40893</x:v>
       </x:c>
-      <x:c r="E179" s="25" t="str"/>
+      <x:c r="E179" s="25"/>
       <x:c r="F179" s="26" t="n">
         <x:v>1.56045</x:v>
       </x:c>
@@ -6871,7 +6871,7 @@
       <x:c r="D180" s="24" t="n">
         <x:v>0.40392</x:v>
       </x:c>
-      <x:c r="E180" s="25" t="str"/>
+      <x:c r="E180" s="25"/>
       <x:c r="F180" s="26" t="n">
         <x:v>1.59562</x:v>
       </x:c>
@@ -6945,7 +6945,7 @@
       <x:c r="D182" s="24" t="n">
         <x:v>0.583</x:v>
       </x:c>
-      <x:c r="E182" s="25" t="str"/>
+      <x:c r="E182" s="25"/>
       <x:c r="F182" s="26" t="n">
         <x:v>1.04</x:v>
       </x:c>
@@ -6981,7 +6981,7 @@
       <x:c r="D183" s="24" t="n">
         <x:v>0.518</x:v>
       </x:c>
-      <x:c r="E183" s="25" t="str"/>
+      <x:c r="E183" s="25"/>
       <x:c r="F183" s="26" t="n">
         <x:v>1.08</x:v>
       </x:c>
@@ -7017,7 +7017,7 @@
       <x:c r="D184" s="24" t="n">
         <x:v>0.453</x:v>
       </x:c>
-      <x:c r="E184" s="25" t="str"/>
+      <x:c r="E184" s="25"/>
       <x:c r="F184" s="26" t="n">
         <x:v>1.12</x:v>
       </x:c>
@@ -7053,7 +7053,7 @@
       <x:c r="D185" s="24" t="n">
         <x:v>0.44806</x:v>
       </x:c>
-      <x:c r="E185" s="25" t="str"/>
+      <x:c r="E185" s="25"/>
       <x:c r="F185" s="26" t="n">
         <x:v>1.12317</x:v>
       </x:c>
@@ -7089,7 +7089,7 @@
       <x:c r="D186" s="24" t="n">
         <x:v>0.44312</x:v>
       </x:c>
-      <x:c r="E186" s="25" t="str"/>
+      <x:c r="E186" s="25"/>
       <x:c r="F186" s="26" t="n">
         <x:v>1.14591</x:v>
       </x:c>
@@ -7125,7 +7125,7 @@
       <x:c r="D187" s="24" t="n">
         <x:v>0.43817</x:v>
       </x:c>
-      <x:c r="E187" s="25" t="str"/>
+      <x:c r="E187" s="25"/>
       <x:c r="F187" s="26" t="n">
         <x:v>1.17521</x:v>
       </x:c>
@@ -7161,7 +7161,7 @@
       <x:c r="D188" s="24" t="n">
         <x:v>0.43323</x:v>
       </x:c>
-      <x:c r="E188" s="25" t="str"/>
+      <x:c r="E188" s="25"/>
       <x:c r="F188" s="26" t="n">
         <x:v>1.20758</x:v>
       </x:c>
@@ -7197,7 +7197,7 @@
       <x:c r="D189" s="24" t="n">
         <x:v>0.42829</x:v>
       </x:c>
-      <x:c r="E189" s="25" t="str"/>
+      <x:c r="E189" s="25"/>
       <x:c r="F189" s="26" t="n">
         <x:v>1.24135</x:v>
       </x:c>
@@ -7233,7 +7233,7 @@
       <x:c r="D190" s="24" t="n">
         <x:v>0.42335</x:v>
       </x:c>
-      <x:c r="E190" s="25" t="str"/>
+      <x:c r="E190" s="25"/>
       <x:c r="F190" s="26" t="n">
         <x:v>1.27561</x:v>
       </x:c>
@@ -7269,7 +7269,7 @@
       <x:c r="D191" s="24" t="n">
         <x:v>0.41841</x:v>
       </x:c>
-      <x:c r="E191" s="25" t="str"/>
+      <x:c r="E191" s="25"/>
       <x:c r="F191" s="26" t="n">
         <x:v>1.30982</x:v>
       </x:c>
@@ -7305,7 +7305,7 @@
       <x:c r="D192" s="24" t="n">
         <x:v>0.41347</x:v>
       </x:c>
-      <x:c r="E192" s="25" t="str"/>
+      <x:c r="E192" s="25"/>
       <x:c r="F192" s="26" t="n">
         <x:v>1.34365</x:v>
       </x:c>
@@ -7341,7 +7341,7 @@
       <x:c r="D193" s="24" t="n">
         <x:v>0.40852</x:v>
       </x:c>
-      <x:c r="E193" s="25" t="str"/>
+      <x:c r="E193" s="25"/>
       <x:c r="F193" s="26" t="n">
         <x:v>1.37689</x:v>
       </x:c>
@@ -7377,7 +7377,7 @@
       <x:c r="D194" s="24" t="n">
         <x:v>0.40358</x:v>
       </x:c>
-      <x:c r="E194" s="25" t="str"/>
+      <x:c r="E194" s="25"/>
       <x:c r="F194" s="26" t="n">
         <x:v>1.40944</x:v>
       </x:c>
@@ -7413,7 +7413,7 @@
       <x:c r="D195" s="24" t="n">
         <x:v>0.39864</x:v>
       </x:c>
-      <x:c r="E195" s="25" t="str"/>
+      <x:c r="E195" s="25"/>
       <x:c r="F195" s="26" t="n">
         <x:v>1.44121</x:v>
       </x:c>
@@ -7487,7 +7487,7 @@
       <x:c r="D197" s="24" t="n">
         <x:v>0.577</x:v>
       </x:c>
-      <x:c r="E197" s="25" t="str"/>
+      <x:c r="E197" s="25"/>
       <x:c r="F197" s="26" t="n">
         <x:v>1.08</x:v>
       </x:c>
@@ -7523,7 +7523,7 @@
       <x:c r="D198" s="24" t="n">
         <x:v>0.512</x:v>
       </x:c>
-      <x:c r="E198" s="25" t="str"/>
+      <x:c r="E198" s="25"/>
       <x:c r="F198" s="26" t="n">
         <x:v>1.16</x:v>
       </x:c>
@@ -7559,7 +7559,7 @@
       <x:c r="D199" s="24" t="n">
         <x:v>0.447</x:v>
       </x:c>
-      <x:c r="E199" s="25" t="str"/>
+      <x:c r="E199" s="25"/>
       <x:c r="F199" s="26" t="n">
         <x:v>1.24</x:v>
       </x:c>
@@ -7595,7 +7595,7 @@
       <x:c r="D200" s="24" t="n">
         <x:v>0.44212</x:v>
       </x:c>
-      <x:c r="E200" s="25" t="str"/>
+      <x:c r="E200" s="25"/>
       <x:c r="F200" s="26" t="n">
         <x:v>1.24351</x:v>
       </x:c>
@@ -7631,7 +7631,7 @@
       <x:c r="D201" s="24" t="n">
         <x:v>0.43725</x:v>
       </x:c>
-      <x:c r="E201" s="25" t="str"/>
+      <x:c r="E201" s="25"/>
       <x:c r="F201" s="26" t="n">
         <x:v>1.26868</x:v>
       </x:c>
@@ -7667,7 +7667,7 @@
       <x:c r="D202" s="24" t="n">
         <x:v>0.43237</x:v>
       </x:c>
-      <x:c r="E202" s="25" t="str"/>
+      <x:c r="E202" s="25"/>
       <x:c r="F202" s="26" t="n">
         <x:v>1.30112</x:v>
       </x:c>
@@ -7703,7 +7703,7 @@
       <x:c r="D203" s="24" t="n">
         <x:v>0.42749</x:v>
       </x:c>
-      <x:c r="E203" s="25" t="str"/>
+      <x:c r="E203" s="25"/>
       <x:c r="F203" s="26" t="n">
         <x:v>1.33696</x:v>
       </x:c>
@@ -7739,7 +7739,7 @@
       <x:c r="D204" s="24" t="n">
         <x:v>0.42262</x:v>
       </x:c>
-      <x:c r="E204" s="25" t="str"/>
+      <x:c r="E204" s="25"/>
       <x:c r="F204" s="26" t="n">
         <x:v>1.37435</x:v>
       </x:c>
@@ -7775,7 +7775,7 @@
       <x:c r="D205" s="24" t="n">
         <x:v>0.41774</x:v>
       </x:c>
-      <x:c r="E205" s="25" t="str"/>
+      <x:c r="E205" s="25"/>
       <x:c r="F205" s="26" t="n">
         <x:v>1.41228</x:v>
       </x:c>
@@ -7811,7 +7811,7 @@
       <x:c r="D206" s="24" t="n">
         <x:v>0.41287</x:v>
       </x:c>
-      <x:c r="E206" s="25" t="str"/>
+      <x:c r="E206" s="25"/>
       <x:c r="F206" s="26" t="n">
         <x:v>1.45016</x:v>
       </x:c>
@@ -7847,7 +7847,7 @@
       <x:c r="D207" s="24" t="n">
         <x:v>0.40799</x:v>
       </x:c>
-      <x:c r="E207" s="25" t="str"/>
+      <x:c r="E207" s="25"/>
       <x:c r="F207" s="26" t="n">
         <x:v>1.48761</x:v>
       </x:c>
@@ -7883,7 +7883,7 @@
       <x:c r="D208" s="24" t="n">
         <x:v>0.40311</x:v>
       </x:c>
-      <x:c r="E208" s="25" t="str"/>
+      <x:c r="E208" s="25"/>
       <x:c r="F208" s="26" t="n">
         <x:v>1.52442</x:v>
       </x:c>
@@ -7919,7 +7919,7 @@
       <x:c r="D209" s="24" t="n">
         <x:v>0.39824</x:v>
       </x:c>
-      <x:c r="E209" s="25" t="str"/>
+      <x:c r="E209" s="25"/>
       <x:c r="F209" s="26" t="n">
         <x:v>1.56045</x:v>
       </x:c>
@@ -7955,7 +7955,7 @@
       <x:c r="D210" s="24" t="n">
         <x:v>0.39336</x:v>
       </x:c>
-      <x:c r="E210" s="25" t="str"/>
+      <x:c r="E210" s="25"/>
       <x:c r="F210" s="26" t="n">
         <x:v>1.59562</x:v>
       </x:c>
@@ -8029,7 +8029,7 @@
       <x:c r="D212" s="24" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="E212" s="25" t="str"/>
+      <x:c r="E212" s="25"/>
       <x:c r="F212" s="26" t="n">
         <x:v>1.13</x:v>
       </x:c>
@@ -8103,7 +8103,7 @@
       <x:c r="D214" s="24" t="n">
         <x:v>0.44</x:v>
       </x:c>
-      <x:c r="E214" s="25" t="str"/>
+      <x:c r="E214" s="25"/>
       <x:c r="F214" s="26" t="n">
         <x:v>1.39</x:v>
       </x:c>
@@ -8139,7 +8139,7 @@
       <x:c r="D215" s="24" t="n">
         <x:v>0.4</x:v>
       </x:c>
-      <x:c r="E215" s="25" t="str"/>
+      <x:c r="E215" s="25"/>
       <x:c r="F215" s="26" t="n">
         <x:v>1.52</x:v>
       </x:c>
@@ -8175,7 +8175,7 @@
       <x:c r="D216" s="24" t="n">
         <x:v>0.3968</x:v>
       </x:c>
-      <x:c r="E216" s="25" t="str"/>
+      <x:c r="E216" s="25"/>
       <x:c r="F216" s="26" t="n">
         <x:v>1.49985</x:v>
       </x:c>
@@ -8211,7 +8211,7 @@
       <x:c r="D217" s="24" t="n">
         <x:v>0.3936</x:v>
       </x:c>
-      <x:c r="E217" s="25" t="str"/>
+      <x:c r="E217" s="25"/>
       <x:c r="F217" s="26" t="n">
         <x:v>1.50064</x:v>
       </x:c>
@@ -8247,7 +8247,7 @@
       <x:c r="D218" s="24" t="n">
         <x:v>0.3904</x:v>
       </x:c>
-      <x:c r="E218" s="25" t="str"/>
+      <x:c r="E218" s="25"/>
       <x:c r="F218" s="26" t="n">
         <x:v>1.50988</x:v>
       </x:c>
@@ -8283,7 +8283,7 @@
       <x:c r="D219" s="24" t="n">
         <x:v>0.3872</x:v>
       </x:c>
-      <x:c r="E219" s="25" t="str"/>
+      <x:c r="E219" s="25"/>
       <x:c r="F219" s="26" t="n">
         <x:v>1.52397</x:v>
       </x:c>
@@ -8319,7 +8319,7 @@
       <x:c r="D220" s="24" t="n">
         <x:v>0.384</x:v>
       </x:c>
-      <x:c r="E220" s="25" t="str"/>
+      <x:c r="E220" s="25"/>
       <x:c r="F220" s="26" t="n">
         <x:v>1.54107</x:v>
       </x:c>
@@ -8355,7 +8355,7 @@
       <x:c r="D221" s="24" t="n">
         <x:v>0.3808</x:v>
       </x:c>
-      <x:c r="E221" s="25" t="str"/>
+      <x:c r="E221" s="25"/>
       <x:c r="F221" s="26" t="n">
         <x:v>1.56012</x:v>
       </x:c>
@@ -8391,7 +8391,7 @@
       <x:c r="D222" s="24" t="n">
         <x:v>0.3776</x:v>
       </x:c>
-      <x:c r="E222" s="25" t="str"/>
+      <x:c r="E222" s="25"/>
       <x:c r="F222" s="26" t="n">
         <x:v>1.58039</x:v>
       </x:c>
@@ -8427,7 +8427,7 @@
       <x:c r="D223" s="24" t="n">
         <x:v>0.3744</x:v>
       </x:c>
-      <x:c r="E223" s="25" t="str"/>
+      <x:c r="E223" s="25"/>
       <x:c r="F223" s="26" t="n">
         <x:v>1.60143</x:v>
       </x:c>
@@ -8463,7 +8463,7 @@
       <x:c r="D224" s="24" t="n">
         <x:v>0.3712</x:v>
       </x:c>
-      <x:c r="E224" s="25" t="str"/>
+      <x:c r="E224" s="25"/>
       <x:c r="F224" s="26" t="n">
         <x:v>1.6229</x:v>
       </x:c>
@@ -8499,7 +8499,7 @@
       <x:c r="D225" s="24" t="n">
         <x:v>0.368</x:v>
       </x:c>
-      <x:c r="E225" s="25" t="str"/>
+      <x:c r="E225" s="25"/>
       <x:c r="F225" s="26" t="n">
         <x:v>1.64457</x:v>
       </x:c>
@@ -8535,7 +8535,7 @@
       <x:c r="D226" s="24" t="n">
         <x:v>0.3648</x:v>
       </x:c>
-      <x:c r="E226" s="25" t="str"/>
+      <x:c r="E226" s="25"/>
       <x:c r="F226" s="26" t="n">
         <x:v>1.66629</x:v>
       </x:c>
@@ -8571,7 +8571,7 @@
       <x:c r="D227" s="24" t="n">
         <x:v>0.3616</x:v>
       </x:c>
-      <x:c r="E227" s="25" t="str"/>
+      <x:c r="E227" s="25"/>
       <x:c r="F227" s="26" t="n">
         <x:v>1.68793</x:v>
       </x:c>
@@ -8607,7 +8607,7 @@
       <x:c r="D228" s="24" t="n">
         <x:v>0.3584</x:v>
       </x:c>
-      <x:c r="E228" s="25" t="str"/>
+      <x:c r="E228" s="25"/>
       <x:c r="F228" s="26" t="n">
         <x:v>1.7094</x:v>
       </x:c>
@@ -8643,7 +8643,7 @@
       <x:c r="D229" s="24" t="n">
         <x:v>0.3552</x:v>
       </x:c>
-      <x:c r="E229" s="25" t="str"/>
+      <x:c r="E229" s="25"/>
       <x:c r="F229" s="26" t="n">
         <x:v>1.73064</x:v>
       </x:c>
@@ -8755,7 +8755,7 @@
       <x:c r="D232" s="24" t="n">
         <x:v>0.565</x:v>
       </x:c>
-      <x:c r="E232" s="25" t="str"/>
+      <x:c r="E232" s="25"/>
       <x:c r="F232" s="26" t="n">
         <x:v>1.13</x:v>
       </x:c>
@@ -8791,7 +8791,7 @@
       <x:c r="D233" s="24" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="E233" s="25" t="str"/>
+      <x:c r="E233" s="25"/>
       <x:c r="F233" s="26" t="n">
         <x:v>1.26</x:v>
       </x:c>
@@ -8827,7 +8827,7 @@
       <x:c r="D234" s="24" t="n">
         <x:v>0.435</x:v>
       </x:c>
-      <x:c r="E234" s="25" t="str"/>
+      <x:c r="E234" s="25"/>
       <x:c r="F234" s="26" t="n">
         <x:v>1.39</x:v>
       </x:c>
@@ -8863,7 +8863,7 @@
       <x:c r="D235" s="24" t="n">
         <x:v>0.43025</x:v>
       </x:c>
-      <x:c r="E235" s="25" t="str"/>
+      <x:c r="E235" s="25"/>
       <x:c r="F235" s="26" t="n">
         <x:v>1.39394</x:v>
       </x:c>
@@ -8899,7 +8899,7 @@
       <x:c r="D236" s="24" t="n">
         <x:v>0.42551</x:v>
       </x:c>
-      <x:c r="E236" s="25" t="str"/>
+      <x:c r="E236" s="25"/>
       <x:c r="F236" s="26" t="n">
         <x:v>1.42215</x:v>
       </x:c>
@@ -8935,7 +8935,7 @@
       <x:c r="D237" s="24" t="n">
         <x:v>0.42076</x:v>
       </x:c>
-      <x:c r="E237" s="25" t="str"/>
+      <x:c r="E237" s="25"/>
       <x:c r="F237" s="26" t="n">
         <x:v>1.45852</x:v>
       </x:c>
@@ -8971,7 +8971,7 @@
       <x:c r="D238" s="24" t="n">
         <x:v>0.41602</x:v>
       </x:c>
-      <x:c r="E238" s="25" t="str"/>
+      <x:c r="E238" s="25"/>
       <x:c r="F238" s="26" t="n">
         <x:v>1.49869</x:v>
       </x:c>
@@ -9007,7 +9007,7 @@
       <x:c r="D239" s="24" t="n">
         <x:v>0.41127</x:v>
       </x:c>
-      <x:c r="E239" s="25" t="str"/>
+      <x:c r="E239" s="25"/>
       <x:c r="F239" s="26" t="n">
         <x:v>1.5406</x:v>
       </x:c>
@@ -9043,7 +9043,7 @@
       <x:c r="D240" s="24" t="n">
         <x:v>0.40653</x:v>
       </x:c>
-      <x:c r="E240" s="25" t="str"/>
+      <x:c r="E240" s="25"/>
       <x:c r="F240" s="26" t="n">
         <x:v>1.58312</x:v>
       </x:c>
@@ -9079,7 +9079,7 @@
       <x:c r="D241" s="24" t="n">
         <x:v>0.40178</x:v>
       </x:c>
-      <x:c r="E241" s="25" t="str"/>
+      <x:c r="E241" s="25"/>
       <x:c r="F241" s="26" t="n">
         <x:v>1.62558</x:v>
       </x:c>
@@ -9115,7 +9115,7 @@
       <x:c r="D242" s="24" t="n">
         <x:v>0.39704</x:v>
       </x:c>
-      <x:c r="E242" s="25" t="str"/>
+      <x:c r="E242" s="25"/>
       <x:c r="F242" s="26" t="n">
         <x:v>1.66756</x:v>
       </x:c>
@@ -9151,7 +9151,7 @@
       <x:c r="D243" s="24" t="n">
         <x:v>0.39229</x:v>
       </x:c>
-      <x:c r="E243" s="25" t="str"/>
+      <x:c r="E243" s="25"/>
       <x:c r="F243" s="26" t="n">
         <x:v>1.70882</x:v>
       </x:c>
@@ -9187,7 +9187,7 @@
       <x:c r="D244" s="24" t="n">
         <x:v>0.38755</x:v>
       </x:c>
-      <x:c r="E244" s="25" t="str"/>
+      <x:c r="E244" s="25"/>
       <x:c r="F244" s="26" t="n">
         <x:v>1.74921</x:v>
       </x:c>
@@ -9223,7 +9223,7 @@
       <x:c r="D245" s="24" t="n">
         <x:v>0.3828</x:v>
       </x:c>
-      <x:c r="E245" s="25" t="str"/>
+      <x:c r="E245" s="25"/>
       <x:c r="F245" s="26" t="n">
         <x:v>1.78864</x:v>
       </x:c>
@@ -9297,7 +9297,7 @@
       <x:c r="D247" s="24" t="n">
         <x:v>0.559</x:v>
       </x:c>
-      <x:c r="E247" s="25" t="str"/>
+      <x:c r="E247" s="25"/>
       <x:c r="F247" s="26" t="n">
         <x:v>1.13</x:v>
       </x:c>
@@ -9333,7 +9333,7 @@
       <x:c r="D248" s="24" t="n">
         <x:v>0.494</x:v>
       </x:c>
-      <x:c r="E248" s="25" t="str"/>
+      <x:c r="E248" s="25"/>
       <x:c r="F248" s="26" t="n">
         <x:v>1.26</x:v>
       </x:c>
@@ -9369,7 +9369,7 @@
       <x:c r="D249" s="24" t="n">
         <x:v>0.429</x:v>
       </x:c>
-      <x:c r="E249" s="25" t="str"/>
+      <x:c r="E249" s="25"/>
       <x:c r="F249" s="26" t="n">
         <x:v>1.39</x:v>
       </x:c>
@@ -9405,7 +9405,7 @@
       <x:c r="D250" s="24" t="n">
         <x:v>0.42432</x:v>
       </x:c>
-      <x:c r="E250" s="25" t="str"/>
+      <x:c r="E250" s="25"/>
       <x:c r="F250" s="26" t="n">
         <x:v>1.25454</x:v>
       </x:c>
@@ -9441,7 +9441,7 @@
       <x:c r="D251" s="24" t="n">
         <x:v>0.41964</x:v>
       </x:c>
-      <x:c r="E251" s="25" t="str"/>
+      <x:c r="E251" s="25"/>
       <x:c r="F251" s="26" t="n">
         <x:v>1.32734</x:v>
       </x:c>
@@ -9477,7 +9477,7 @@
       <x:c r="D252" s="24" t="n">
         <x:v>0.41496</x:v>
       </x:c>
-      <x:c r="E252" s="25" t="str"/>
+      <x:c r="E252" s="25"/>
       <x:c r="F252" s="26" t="n">
         <x:v>1.4099</x:v>
       </x:c>
@@ -9513,7 +9513,7 @@
       <x:c r="D253" s="24" t="n">
         <x:v>0.41028</x:v>
       </x:c>
-      <x:c r="E253" s="25" t="str"/>
+      <x:c r="E253" s="25"/>
       <x:c r="F253" s="26" t="n">
         <x:v>1.49869</x:v>
       </x:c>
@@ -9549,7 +9549,7 @@
       <x:c r="D254" s="24" t="n">
         <x:v>0.4056</x:v>
       </x:c>
-      <x:c r="E254" s="25" t="str"/>
+      <x:c r="E254" s="25"/>
       <x:c r="F254" s="26" t="n">
         <x:v>1.5406</x:v>
       </x:c>
@@ -9585,7 +9585,7 @@
       <x:c r="D255" s="24" t="n">
         <x:v>0.40092</x:v>
       </x:c>
-      <x:c r="E255" s="25" t="str"/>
+      <x:c r="E255" s="25"/>
       <x:c r="F255" s="26" t="n">
         <x:v>1.58312</x:v>
       </x:c>
@@ -9621,7 +9621,7 @@
       <x:c r="D256" s="24" t="n">
         <x:v>0.39624</x:v>
       </x:c>
-      <x:c r="E256" s="25" t="str"/>
+      <x:c r="E256" s="25"/>
       <x:c r="F256" s="26" t="n">
         <x:v>1.62558</x:v>
       </x:c>
@@ -9657,7 +9657,7 @@
       <x:c r="D257" s="24" t="n">
         <x:v>0.39156</x:v>
       </x:c>
-      <x:c r="E257" s="25" t="str"/>
+      <x:c r="E257" s="25"/>
       <x:c r="F257" s="26" t="n">
         <x:v>1.66756</x:v>
       </x:c>
@@ -9693,7 +9693,7 @@
       <x:c r="D258" s="24" t="n">
         <x:v>0.38688</x:v>
       </x:c>
-      <x:c r="E258" s="25" t="str"/>
+      <x:c r="E258" s="25"/>
       <x:c r="F258" s="26" t="n">
         <x:v>1.70882</x:v>
       </x:c>
@@ -9729,7 +9729,7 @@
       <x:c r="D259" s="24" t="n">
         <x:v>0.3822</x:v>
       </x:c>
-      <x:c r="E259" s="25" t="str"/>
+      <x:c r="E259" s="25"/>
       <x:c r="F259" s="26" t="n">
         <x:v>1.74921</x:v>
       </x:c>
@@ -9765,7 +9765,7 @@
       <x:c r="D260" s="24" t="n">
         <x:v>0.37752</x:v>
       </x:c>
-      <x:c r="E260" s="25" t="str"/>
+      <x:c r="E260" s="25"/>
       <x:c r="F260" s="26" t="n">
         <x:v>1.78864</x:v>
       </x:c>
@@ -9839,7 +9839,7 @@
       <x:c r="D262" s="24" t="n">
         <x:v>0.553</x:v>
       </x:c>
-      <x:c r="E262" s="25" t="str"/>
+      <x:c r="E262" s="25"/>
       <x:c r="F262" s="26" t="n">
         <x:v>1.13</x:v>
       </x:c>
@@ -9875,7 +9875,7 @@
       <x:c r="D263" s="24" t="n">
         <x:v>0.488</x:v>
       </x:c>
-      <x:c r="E263" s="25" t="str"/>
+      <x:c r="E263" s="25"/>
       <x:c r="F263" s="26" t="n">
         <x:v>1.26</x:v>
       </x:c>
@@ -9911,7 +9911,7 @@
       <x:c r="D264" s="24" t="n">
         <x:v>0.423</x:v>
       </x:c>
-      <x:c r="E264" s="25" t="str"/>
+      <x:c r="E264" s="25"/>
       <x:c r="F264" s="26" t="n">
         <x:v>1.39</x:v>
       </x:c>
@@ -9947,7 +9947,7 @@
       <x:c r="D265" s="24" t="n">
         <x:v>0.41839</x:v>
       </x:c>
-      <x:c r="E265" s="25" t="str"/>
+      <x:c r="E265" s="25"/>
       <x:c r="F265" s="26" t="n">
         <x:v>1.39394</x:v>
       </x:c>
@@ -9983,7 +9983,7 @@
       <x:c r="D266" s="24" t="n">
         <x:v>0.41377</x:v>
       </x:c>
-      <x:c r="E266" s="25" t="str"/>
+      <x:c r="E266" s="25"/>
       <x:c r="F266" s="26" t="n">
         <x:v>1.42215</x:v>
       </x:c>
@@ -10019,7 +10019,7 @@
       <x:c r="D267" s="24" t="n">
         <x:v>0.40916</x:v>
       </x:c>
-      <x:c r="E267" s="25" t="str"/>
+      <x:c r="E267" s="25"/>
       <x:c r="F267" s="26" t="n">
         <x:v>1.45852</x:v>
       </x:c>
@@ -10055,7 +10055,7 @@
       <x:c r="D268" s="24" t="n">
         <x:v>0.40454</x:v>
       </x:c>
-      <x:c r="E268" s="25" t="str"/>
+      <x:c r="E268" s="25"/>
       <x:c r="F268" s="26" t="n">
         <x:v>1.49869</x:v>
       </x:c>
@@ -10091,7 +10091,7 @@
       <x:c r="D269" s="24" t="n">
         <x:v>0.39993</x:v>
       </x:c>
-      <x:c r="E269" s="25" t="str"/>
+      <x:c r="E269" s="25"/>
       <x:c r="F269" s="26" t="n">
         <x:v>1.5406</x:v>
       </x:c>
@@ -10127,7 +10127,7 @@
       <x:c r="D270" s="24" t="n">
         <x:v>0.39531</x:v>
       </x:c>
-      <x:c r="E270" s="25" t="str"/>
+      <x:c r="E270" s="25"/>
       <x:c r="F270" s="26" t="n">
         <x:v>1.58312</x:v>
       </x:c>
@@ -10163,7 +10163,7 @@
       <x:c r="D271" s="24" t="n">
         <x:v>0.3907</x:v>
       </x:c>
-      <x:c r="E271" s="25" t="str"/>
+      <x:c r="E271" s="25"/>
       <x:c r="F271" s="26" t="n">
         <x:v>1.62558</x:v>
       </x:c>
@@ -10199,7 +10199,7 @@
       <x:c r="D272" s="24" t="n">
         <x:v>0.38608</x:v>
       </x:c>
-      <x:c r="E272" s="25" t="str"/>
+      <x:c r="E272" s="25"/>
       <x:c r="F272" s="26" t="n">
         <x:v>1.66756</x:v>
       </x:c>
@@ -10235,7 +10235,7 @@
       <x:c r="D273" s="24" t="n">
         <x:v>0.38147</x:v>
       </x:c>
-      <x:c r="E273" s="25" t="str"/>
+      <x:c r="E273" s="25"/>
       <x:c r="F273" s="26" t="n">
         <x:v>1.70882</x:v>
       </x:c>
@@ -10271,7 +10271,7 @@
       <x:c r="D274" s="24" t="n">
         <x:v>0.37685</x:v>
       </x:c>
-      <x:c r="E274" s="25" t="str"/>
+      <x:c r="E274" s="25"/>
       <x:c r="F274" s="26" t="n">
         <x:v>1.74921</x:v>
       </x:c>
@@ -10307,7 +10307,7 @@
       <x:c r="D275" s="24" t="n">
         <x:v>0.37224</x:v>
       </x:c>
-      <x:c r="E275" s="25" t="str"/>
+      <x:c r="E275" s="25"/>
       <x:c r="F275" s="26" t="n">
         <x:v>1.78864</x:v>
       </x:c>
@@ -10381,7 +10381,7 @@
       <x:c r="D277" s="24" t="n">
         <x:v>0.547</x:v>
       </x:c>
-      <x:c r="E277" s="25" t="str"/>
+      <x:c r="E277" s="25"/>
       <x:c r="F277" s="26" t="n">
         <x:v>1.035</x:v>
       </x:c>
@@ -10417,7 +10417,7 @@
       <x:c r="D278" s="24" t="n">
         <x:v>0.482</x:v>
       </x:c>
-      <x:c r="E278" s="25" t="str"/>
+      <x:c r="E278" s="25"/>
       <x:c r="F278" s="26" t="n">
         <x:v>1.07</x:v>
       </x:c>
@@ -10453,7 +10453,7 @@
       <x:c r="D279" s="24" t="n">
         <x:v>0.417</x:v>
       </x:c>
-      <x:c r="E279" s="25" t="str"/>
+      <x:c r="E279" s="25"/>
       <x:c r="F279" s="26" t="n">
         <x:v>1.105</x:v>
       </x:c>
@@ -10489,7 +10489,7 @@
       <x:c r="D280" s="24" t="n">
         <x:v>0.41245</x:v>
       </x:c>
-      <x:c r="E280" s="25" t="str"/>
+      <x:c r="E280" s="25"/>
       <x:c r="F280" s="26" t="n">
         <x:v>1.10813</x:v>
       </x:c>
@@ -10525,7 +10525,7 @@
       <x:c r="D281" s="24" t="n">
         <x:v>0.4079</x:v>
       </x:c>
-      <x:c r="E281" s="25" t="str"/>
+      <x:c r="E281" s="25"/>
       <x:c r="F281" s="26" t="n">
         <x:v>1.13056</x:v>
       </x:c>
@@ -10561,7 +10561,7 @@
       <x:c r="D282" s="24" t="n">
         <x:v>0.40335</x:v>
       </x:c>
-      <x:c r="E282" s="25" t="str"/>
+      <x:c r="E282" s="25"/>
       <x:c r="F282" s="26" t="n">
         <x:v>1.15947</x:v>
       </x:c>
@@ -10597,7 +10597,7 @@
       <x:c r="D283" s="24" t="n">
         <x:v>0.3988</x:v>
       </x:c>
-      <x:c r="E283" s="25" t="str"/>
+      <x:c r="E283" s="25"/>
       <x:c r="F283" s="26" t="n">
         <x:v>1.1914</x:v>
       </x:c>
@@ -10633,7 +10633,7 @@
       <x:c r="D284" s="24" t="n">
         <x:v>0.39425</x:v>
       </x:c>
-      <x:c r="E284" s="25" t="str"/>
+      <x:c r="E284" s="25"/>
       <x:c r="F284" s="26" t="n">
         <x:v>1.22472</x:v>
       </x:c>
@@ -10669,7 +10669,7 @@
       <x:c r="D285" s="24" t="n">
         <x:v>0.38971</x:v>
       </x:c>
-      <x:c r="E285" s="25" t="str"/>
+      <x:c r="E285" s="25"/>
       <x:c r="F285" s="26" t="n">
         <x:v>1.25853</x:v>
       </x:c>
@@ -10705,7 +10705,7 @@
       <x:c r="D286" s="24" t="n">
         <x:v>0.38516</x:v>
       </x:c>
-      <x:c r="E286" s="25" t="str"/>
+      <x:c r="E286" s="25"/>
       <x:c r="F286" s="26" t="n">
         <x:v>1.29228</x:v>
       </x:c>
@@ -10741,7 +10741,7 @@
       <x:c r="D287" s="24" t="n">
         <x:v>0.38061</x:v>
       </x:c>
-      <x:c r="E287" s="25" t="str"/>
+      <x:c r="E287" s="25"/>
       <x:c r="F287" s="26" t="n">
         <x:v>1.32565</x:v>
       </x:c>
@@ -10777,7 +10777,7 @@
       <x:c r="D288" s="24" t="n">
         <x:v>0.37606</x:v>
       </x:c>
-      <x:c r="E288" s="25" t="str"/>
+      <x:c r="E288" s="25"/>
       <x:c r="F288" s="26" t="n">
         <x:v>1.35845</x:v>
       </x:c>
@@ -10813,7 +10813,7 @@
       <x:c r="D289" s="24" t="n">
         <x:v>0.37151</x:v>
       </x:c>
-      <x:c r="E289" s="25" t="str"/>
+      <x:c r="E289" s="25"/>
       <x:c r="F289" s="26" t="n">
         <x:v>1.39056</x:v>
       </x:c>
@@ -10849,7 +10849,7 @@
       <x:c r="D290" s="24" t="n">
         <x:v>0.36696</x:v>
       </x:c>
-      <x:c r="E290" s="25" t="str"/>
+      <x:c r="E290" s="25"/>
       <x:c r="F290" s="26" t="n">
         <x:v>1.42191</x:v>
       </x:c>
@@ -10999,7 +10999,7 @@
       <x:c r="D294" s="24" t="n">
         <x:v>0.52</x:v>
       </x:c>
-      <x:c r="E294" s="25" t="str"/>
+      <x:c r="E294" s="25"/>
       <x:c r="F294" s="26" t="n">
         <x:v>1.39</x:v>
       </x:c>
@@ -11035,7 +11035,7 @@
       <x:c r="D295" s="24" t="n">
         <x:v>0.4</x:v>
       </x:c>
-      <x:c r="E295" s="25" t="str"/>
+      <x:c r="E295" s="25"/>
       <x:c r="F295" s="26" t="n">
         <x:v>1.52</x:v>
       </x:c>
@@ -11071,7 +11071,7 @@
       <x:c r="D296" s="24" t="n">
         <x:v>0.3968</x:v>
       </x:c>
-      <x:c r="E296" s="25" t="str"/>
+      <x:c r="E296" s="25"/>
       <x:c r="F296" s="26" t="n">
         <x:v>1.49985</x:v>
       </x:c>
@@ -11107,7 +11107,7 @@
       <x:c r="D297" s="24" t="n">
         <x:v>0.3936</x:v>
       </x:c>
-      <x:c r="E297" s="25" t="str"/>
+      <x:c r="E297" s="25"/>
       <x:c r="F297" s="26" t="n">
         <x:v>1.50064</x:v>
       </x:c>
@@ -11143,7 +11143,7 @@
       <x:c r="D298" s="24" t="n">
         <x:v>0.3904</x:v>
       </x:c>
-      <x:c r="E298" s="25" t="str"/>
+      <x:c r="E298" s="25"/>
       <x:c r="F298" s="26" t="n">
         <x:v>1.50988</x:v>
       </x:c>
@@ -11179,7 +11179,7 @@
       <x:c r="D299" s="24" t="n">
         <x:v>0.3872</x:v>
       </x:c>
-      <x:c r="E299" s="25" t="str"/>
+      <x:c r="E299" s="25"/>
       <x:c r="F299" s="26" t="n">
         <x:v>1.52397</x:v>
       </x:c>
@@ -11215,7 +11215,7 @@
       <x:c r="D300" s="24" t="n">
         <x:v>0.384</x:v>
       </x:c>
-      <x:c r="E300" s="25" t="str"/>
+      <x:c r="E300" s="25"/>
       <x:c r="F300" s="26" t="n">
         <x:v>1.54107</x:v>
       </x:c>
@@ -11251,7 +11251,7 @@
       <x:c r="D301" s="24" t="n">
         <x:v>0.3808</x:v>
       </x:c>
-      <x:c r="E301" s="25" t="str"/>
+      <x:c r="E301" s="25"/>
       <x:c r="F301" s="26" t="n">
         <x:v>1.56012</x:v>
       </x:c>
@@ -11287,7 +11287,7 @@
       <x:c r="D302" s="24" t="n">
         <x:v>0.3776</x:v>
       </x:c>
-      <x:c r="E302" s="25" t="str"/>
+      <x:c r="E302" s="25"/>
       <x:c r="F302" s="26" t="n">
         <x:v>1.58039</x:v>
       </x:c>
@@ -11323,7 +11323,7 @@
       <x:c r="D303" s="24" t="n">
         <x:v>0.3744</x:v>
       </x:c>
-      <x:c r="E303" s="25" t="str"/>
+      <x:c r="E303" s="25"/>
       <x:c r="F303" s="26" t="n">
         <x:v>1.60143</x:v>
       </x:c>
@@ -11359,7 +11359,7 @@
       <x:c r="D304" s="24" t="n">
         <x:v>0.3712</x:v>
       </x:c>
-      <x:c r="E304" s="25" t="str"/>
+      <x:c r="E304" s="25"/>
       <x:c r="F304" s="26" t="n">
         <x:v>1.6229</x:v>
       </x:c>
@@ -11395,7 +11395,7 @@
       <x:c r="D305" s="24" t="n">
         <x:v>0.368</x:v>
       </x:c>
-      <x:c r="E305" s="25" t="str"/>
+      <x:c r="E305" s="25"/>
       <x:c r="F305" s="26" t="n">
         <x:v>1.64457</x:v>
       </x:c>
@@ -11431,7 +11431,7 @@
       <x:c r="D306" s="24" t="n">
         <x:v>0.3648</x:v>
       </x:c>
-      <x:c r="E306" s="25" t="str"/>
+      <x:c r="E306" s="25"/>
       <x:c r="F306" s="26" t="n">
         <x:v>1.66629</x:v>
       </x:c>
@@ -11467,7 +11467,7 @@
       <x:c r="D307" s="24" t="n">
         <x:v>0.3616</x:v>
       </x:c>
-      <x:c r="E307" s="25" t="str"/>
+      <x:c r="E307" s="25"/>
       <x:c r="F307" s="26" t="n">
         <x:v>1.68793</x:v>
       </x:c>
@@ -11503,7 +11503,7 @@
       <x:c r="D308" s="24" t="n">
         <x:v>0.3584</x:v>
       </x:c>
-      <x:c r="E308" s="25" t="str"/>
+      <x:c r="E308" s="25"/>
       <x:c r="F308" s="26" t="n">
         <x:v>1.7094</x:v>
       </x:c>
@@ -11539,7 +11539,7 @@
       <x:c r="D309" s="24" t="n">
         <x:v>0.3552</x:v>
       </x:c>
-      <x:c r="E309" s="25" t="str"/>
+      <x:c r="E309" s="25"/>
       <x:c r="F309" s="26" t="n">
         <x:v>1.73064</x:v>
       </x:c>
@@ -11613,7 +11613,7 @@
       <x:c r="D311" s="24" t="n">
         <x:v>0.65</x:v>
       </x:c>
-      <x:c r="E311" s="25" t="str"/>
+      <x:c r="E311" s="25"/>
       <x:c r="F311" s="26" t="n">
         <x:v>1.1</x:v>
       </x:c>
@@ -11649,7 +11649,7 @@
       <x:c r="D312" s="24" t="n">
         <x:v>0.64208</x:v>
       </x:c>
-      <x:c r="E312" s="25" t="str"/>
+      <x:c r="E312" s="25"/>
       <x:c r="F312" s="26" t="n">
         <x:v>1.34138</x:v>
       </x:c>
@@ -11685,7 +11685,7 @@
       <x:c r="D313" s="24" t="n">
         <x:v>0.63417</x:v>
       </x:c>
-      <x:c r="E313" s="25" t="str"/>
+      <x:c r="E313" s="25"/>
       <x:c r="F313" s="26" t="n">
         <x:v>1.58276</x:v>
       </x:c>
@@ -11721,7 +11721,7 @@
       <x:c r="D314" s="24" t="n">
         <x:v>0.6262</x:v>
       </x:c>
-      <x:c r="E314" s="25" t="str"/>
+      <x:c r="E314" s="25"/>
       <x:c r="F314" s="26" t="n">
         <x:v>1.95862</x:v>
       </x:c>
@@ -11757,7 +11757,7 @@
       <x:c r="D315" s="24" t="n">
         <x:v>0.61824</x:v>
       </x:c>
-      <x:c r="E315" s="25" t="str"/>
+      <x:c r="E315" s="25"/>
       <x:c r="F315" s="26" t="n">
         <x:v>2.34483</x:v>
       </x:c>
@@ -11793,7 +11793,7 @@
       <x:c r="D316" s="24" t="n">
         <x:v>0.61031</x:v>
       </x:c>
-      <x:c r="E316" s="25" t="str"/>
+      <x:c r="E316" s="25"/>
       <x:c r="F316" s="26" t="n">
         <x:v>2.81379</x:v>
       </x:c>
@@ -11829,7 +11829,7 @@
       <x:c r="D317" s="24" t="n">
         <x:v>0.6024</x:v>
       </x:c>
-      <x:c r="E317" s="25" t="str"/>
+      <x:c r="E317" s="25"/>
       <x:c r="F317" s="26" t="n">
         <x:v>3.29655</x:v>
       </x:c>
@@ -11865,7 +11865,7 @@
       <x:c r="D318" s="24" t="n">
         <x:v>0.59448</x:v>
       </x:c>
-      <x:c r="E318" s="25" t="str"/>
+      <x:c r="E318" s="25"/>
       <x:c r="F318" s="26" t="n">
         <x:v>3.62759</x:v>
       </x:c>
@@ -11901,7 +11901,7 @@
       <x:c r="D319" s="24" t="n">
         <x:v>0.58656</x:v>
       </x:c>
-      <x:c r="E319" s="25" t="str"/>
+      <x:c r="E319" s="25"/>
       <x:c r="F319" s="26" t="n">
         <x:v>3.91724</x:v>
       </x:c>
@@ -11975,7 +11975,7 @@
       <x:c r="D321" s="24" t="n">
         <x:v>0.57073</x:v>
       </x:c>
-      <x:c r="E321" s="25" t="str"/>
+      <x:c r="E321" s="25"/>
       <x:c r="F321" s="26" t="n">
         <x:v>5.24138</x:v>
       </x:c>
@@ -12011,7 +12011,7 @@
       <x:c r="D322" s="24" t="n">
         <x:v>0.56278</x:v>
       </x:c>
-      <x:c r="E322" s="25" t="str"/>
+      <x:c r="E322" s="25"/>
       <x:c r="F322" s="26" t="n">
         <x:v>5.65517</x:v>
       </x:c>
@@ -12047,7 +12047,7 @@
       <x:c r="D323" s="24" t="n">
         <x:v>0.55481</x:v>
       </x:c>
-      <x:c r="E323" s="25" t="str"/>
+      <x:c r="E323" s="25"/>
       <x:c r="F323" s="26" t="n">
         <x:v>5.89655</x:v>
       </x:c>
@@ -12083,7 +12083,7 @@
       <x:c r="D324" s="24" t="n">
         <x:v>0.54688</x:v>
       </x:c>
-      <x:c r="E324" s="25" t="str"/>
+      <x:c r="E324" s="25"/>
       <x:c r="F324" s="26" t="n">
         <x:v>6.13793</x:v>
       </x:c>
@@ -12119,9 +12119,9 @@
       <x:c r="D325" s="24" t="n">
         <x:v>0.53896</x:v>
       </x:c>
-      <x:c r="E325" s="25" t="str"/>
+      <x:c r="E325" s="25"/>
       <x:c r="F325" s="26" t="n">
-        <x:v>6.37931</x:v>
+        <x:v>6.49414</x:v>
       </x:c>
       <x:c r="G325" t="n">
         <x:v>7.04607</x:v>
@@ -12155,9 +12155,9 @@
       <x:c r="D326" s="24" t="n">
         <x:v>0.53104</x:v>
       </x:c>
-      <x:c r="E326" s="25" t="str"/>
+      <x:c r="E326" s="25"/>
       <x:c r="F326" s="26" t="n">
-        <x:v>6.62069</x:v>
+        <x:v>6.85903</x:v>
       </x:c>
       <x:c r="G326" t="n">
         <x:v>7.38593</x:v>
@@ -12191,9 +12191,9 @@
       <x:c r="D327" s="24" t="n">
         <x:v>0.52312</x:v>
       </x:c>
-      <x:c r="E327" s="25" t="str"/>
+      <x:c r="E327" s="25"/>
       <x:c r="F327" s="26" t="n">
-        <x:v>6.86207</x:v>
+        <x:v>7.23262</x:v>
       </x:c>
       <x:c r="G327" t="n">
         <x:v>7.72579</x:v>
@@ -12227,9 +12227,9 @@
       <x:c r="D328" s="24" t="n">
         <x:v>0.51519</x:v>
       </x:c>
-      <x:c r="E328" s="25" t="str"/>
+      <x:c r="E328" s="25"/>
       <x:c r="F328" s="26" t="n">
-        <x:v>7.2069</x:v>
+        <x:v>7.7258</x:v>
       </x:c>
       <x:c r="G328" t="n">
         <x:v>8.46621</x:v>
@@ -12263,9 +12263,9 @@
       <x:c r="D329" s="24" t="n">
         <x:v>0.50722</x:v>
       </x:c>
-      <x:c r="E329" s="25" t="str"/>
+      <x:c r="E329" s="25"/>
       <x:c r="F329" s="26" t="n">
-        <x:v>7.68966</x:v>
+        <x:v>8.38173</x:v>
       </x:c>
       <x:c r="G329" t="n">
         <x:v>9.74069</x:v>
@@ -12303,10 +12303,10 @@
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F330" s="26" t="n">
-        <x:v>8.2069</x:v>
+        <x:v>9.09325</x:v>
       </x:c>
       <x:c r="G330" t="n">
-        <x:v>10.43862</x:v>
+        <x:v>12.00441</x:v>
       </x:c>
       <x:c r="H330" t="n">
         <x:v>0</x:v>
@@ -12337,9 +12337,9 @@
       <x:c r="D331" s="24" t="n">
         <x:v>0.49136</x:v>
       </x:c>
-      <x:c r="E331" s="25" t="str"/>
+      <x:c r="E331" s="25"/>
       <x:c r="F331" s="26" t="n">
-        <x:v>8.78621</x:v>
+        <x:v>9.89327</x:v>
       </x:c>
       <x:c r="G331" t="n">
         <x:v>10.09876</x:v>
@@ -12373,9 +12373,9 @@
       <x:c r="D332" s="24" t="n">
         <x:v>0.48344</x:v>
       </x:c>
-      <x:c r="E332" s="25" t="str"/>
+      <x:c r="E332" s="25"/>
       <x:c r="F332" s="26" t="n">
-        <x:v>9.31034</x:v>
+        <x:v>10.65103</x:v>
       </x:c>
       <x:c r="G332" t="n">
         <x:v>10.00166</x:v>
@@ -12409,9 +12409,9 @@
       <x:c r="D333" s="24" t="n">
         <x:v>0.47552</x:v>
       </x:c>
-      <x:c r="E333" s="25" t="str"/>
+      <x:c r="E333" s="25"/>
       <x:c r="F333" s="26" t="n">
-        <x:v>9.69655</x:v>
+        <x:v>11.26739</x:v>
       </x:c>
       <x:c r="G333" t="n">
         <x:v>10.51145</x:v>
@@ -12445,9 +12445,9 @@
       <x:c r="D334" s="24" t="n">
         <x:v>0.4676</x:v>
       </x:c>
-      <x:c r="E334" s="25" t="str"/>
+      <x:c r="E334" s="25"/>
       <x:c r="F334" s="26" t="n">
-        <x:v>10.07241</x:v>
+        <x:v>11.88544</x:v>
       </x:c>
       <x:c r="G334" t="n">
         <x:v>11.03945</x:v>
@@ -12481,9 +12481,9 @@
       <x:c r="D335" s="24" t="n">
         <x:v>0.45969</x:v>
       </x:c>
-      <x:c r="E335" s="25" t="str"/>
+      <x:c r="E335" s="25"/>
       <x:c r="F335" s="26" t="n">
-        <x:v>10.41034</x:v>
+        <x:v>12.2842</x:v>
       </x:c>
       <x:c r="G335" t="n">
         <x:v>11.63421</x:v>
@@ -12517,9 +12517,9 @@
       <x:c r="D336" s="24" t="n">
         <x:v>0.45176</x:v>
       </x:c>
-      <x:c r="E336" s="25" t="str"/>
+      <x:c r="E336" s="25"/>
       <x:c r="F336" s="26" t="n">
-        <x:v>10.74828</x:v>
+        <x:v>12.68297</x:v>
       </x:c>
       <x:c r="G336" t="n">
         <x:v>12.22897</x:v>
@@ -12553,9 +12553,9 @@
       <x:c r="D337" s="24" t="n">
         <x:v>0.4438</x:v>
       </x:c>
-      <x:c r="E337" s="25" t="str"/>
+      <x:c r="E337" s="25"/>
       <x:c r="F337" s="26" t="n">
-        <x:v>11.08621</x:v>
+        <x:v>13.08173</x:v>
       </x:c>
       <x:c r="G337" t="n">
         <x:v>12.82372</x:v>
@@ -12589,9 +12589,9 @@
       <x:c r="D338" s="24" t="n">
         <x:v>0.43583</x:v>
       </x:c>
-      <x:c r="E338" s="25" t="str"/>
+      <x:c r="E338" s="25"/>
       <x:c r="F338" s="26" t="n">
-        <x:v>11.42759</x:v>
+        <x:v>13.48456</x:v>
       </x:c>
       <x:c r="G338" t="n">
         <x:v>13.52166</x:v>
@@ -12625,9 +12625,9 @@
       <x:c r="D339" s="24" t="n">
         <x:v>0.42792</x:v>
       </x:c>
-      <x:c r="E339" s="25" t="str"/>
+      <x:c r="E339" s="25"/>
       <x:c r="F339" s="26" t="n">
-        <x:v>11.81379</x:v>
+        <x:v>13.94027</x:v>
       </x:c>
       <x:c r="G339" t="n">
         <x:v>15.56083</x:v>
@@ -12665,10 +12665,10 @@
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F340" s="26" t="n">
-        <x:v>12.2</x:v>
+        <x:v>14.396</x:v>
       </x:c>
       <x:c r="G340" t="n">
-        <x:v>17.6</x:v>
+        <x:v>26.4</x:v>
       </x:c>
       <x:c r="H340" t="n">
         <x:v>0</x:v>
@@ -12699,7 +12699,7 @@
       <x:c r="D341" s="24" t="n">
         <x:v>0.65</x:v>
       </x:c>
-      <x:c r="E341" s="25" t="str"/>
+      <x:c r="E341" s="25"/>
       <x:c r="F341" s="26" t="n">
         <x:v>1.21</x:v>
       </x:c>
@@ -12735,7 +12735,7 @@
       <x:c r="D342" s="24" t="n">
         <x:v>0.64208</x:v>
       </x:c>
-      <x:c r="E342" s="25" t="str"/>
+      <x:c r="E342" s="25"/>
       <x:c r="F342" s="26" t="n">
         <x:v>1.47552</x:v>
       </x:c>
@@ -12771,7 +12771,7 @@
       <x:c r="D343" s="24" t="n">
         <x:v>0.63417</x:v>
       </x:c>
-      <x:c r="E343" s="25" t="str"/>
+      <x:c r="E343" s="25"/>
       <x:c r="F343" s="26" t="n">
         <x:v>1.74103</x:v>
       </x:c>
@@ -12807,7 +12807,7 @@
       <x:c r="D344" s="24" t="n">
         <x:v>0.6262</x:v>
       </x:c>
-      <x:c r="E344" s="25" t="str"/>
+      <x:c r="E344" s="25"/>
       <x:c r="F344" s="26" t="n">
         <x:v>2.15448</x:v>
       </x:c>
@@ -12843,7 +12843,7 @@
       <x:c r="D345" s="24" t="n">
         <x:v>0.61824</x:v>
       </x:c>
-      <x:c r="E345" s="25" t="str"/>
+      <x:c r="E345" s="25"/>
       <x:c r="F345" s="26" t="n">
         <x:v>2.57931</x:v>
       </x:c>
@@ -12879,7 +12879,7 @@
       <x:c r="D346" s="24" t="n">
         <x:v>0.61031</x:v>
       </x:c>
-      <x:c r="E346" s="25" t="str"/>
+      <x:c r="E346" s="25"/>
       <x:c r="F346" s="26" t="n">
         <x:v>3.09517</x:v>
       </x:c>
@@ -12915,7 +12915,7 @@
       <x:c r="D347" s="24" t="n">
         <x:v>0.6024</x:v>
       </x:c>
-      <x:c r="E347" s="25" t="str"/>
+      <x:c r="E347" s="25"/>
       <x:c r="F347" s="26" t="n">
         <x:v>3.62621</x:v>
       </x:c>
@@ -12951,7 +12951,7 @@
       <x:c r="D348" s="24" t="n">
         <x:v>0.59448</x:v>
       </x:c>
-      <x:c r="E348" s="25" t="str"/>
+      <x:c r="E348" s="25"/>
       <x:c r="F348" s="26" t="n">
         <x:v>3.99034</x:v>
       </x:c>
@@ -12987,7 +12987,7 @@
       <x:c r="D349" s="24" t="n">
         <x:v>0.58656</x:v>
       </x:c>
-      <x:c r="E349" s="25" t="str"/>
+      <x:c r="E349" s="25"/>
       <x:c r="F349" s="26" t="n">
         <x:v>4.30897</x:v>
       </x:c>
@@ -13061,7 +13061,7 @@
       <x:c r="D351" s="24" t="n">
         <x:v>0.57073</x:v>
       </x:c>
-      <x:c r="E351" s="25" t="str"/>
+      <x:c r="E351" s="25"/>
       <x:c r="F351" s="26" t="n">
         <x:v>5.76552</x:v>
       </x:c>
@@ -13097,7 +13097,7 @@
       <x:c r="D352" s="24" t="n">
         <x:v>0.56278</x:v>
       </x:c>
-      <x:c r="E352" s="25" t="str"/>
+      <x:c r="E352" s="25"/>
       <x:c r="F352" s="26" t="n">
         <x:v>6.22069</x:v>
       </x:c>
@@ -13133,7 +13133,7 @@
       <x:c r="D353" s="24" t="n">
         <x:v>0.55481</x:v>
       </x:c>
-      <x:c r="E353" s="25" t="str"/>
+      <x:c r="E353" s="25"/>
       <x:c r="F353" s="26" t="n">
         <x:v>6.48621</x:v>
       </x:c>
@@ -13169,7 +13169,7 @@
       <x:c r="D354" s="24" t="n">
         <x:v>0.54688</x:v>
       </x:c>
-      <x:c r="E354" s="25" t="str"/>
+      <x:c r="E354" s="25"/>
       <x:c r="F354" s="26" t="n">
         <x:v>6.75172</x:v>
       </x:c>
@@ -13205,9 +13205,9 @@
       <x:c r="D355" s="24" t="n">
         <x:v>0.53896</x:v>
       </x:c>
-      <x:c r="E355" s="25" t="str"/>
+      <x:c r="E355" s="25"/>
       <x:c r="F355" s="26" t="n">
-        <x:v>7.01724</x:v>
+        <x:v>7.14355</x:v>
       </x:c>
       <x:c r="G355" t="n">
         <x:v>8.99658</x:v>
@@ -13241,9 +13241,9 @@
       <x:c r="D356" s="24" t="n">
         <x:v>0.53104</x:v>
       </x:c>
-      <x:c r="E356" s="25" t="str"/>
+      <x:c r="E356" s="25"/>
       <x:c r="F356" s="26" t="n">
-        <x:v>7.28276</x:v>
+        <x:v>7.54494</x:v>
       </x:c>
       <x:c r="G356" t="n">
         <x:v>9.98344</x:v>
@@ -13277,9 +13277,9 @@
       <x:c r="D357" s="24" t="n">
         <x:v>0.52312</x:v>
       </x:c>
-      <x:c r="E357" s="25" t="str"/>
+      <x:c r="E357" s="25"/>
       <x:c r="F357" s="26" t="n">
-        <x:v>7.54828</x:v>
+        <x:v>7.95589</x:v>
       </x:c>
       <x:c r="G357" t="n">
         <x:v>11.09851</x:v>
@@ -13313,9 +13313,9 @@
       <x:c r="D358" s="24" t="n">
         <x:v>0.51519</x:v>
       </x:c>
-      <x:c r="E358" s="25" t="str"/>
+      <x:c r="E358" s="25"/>
       <x:c r="F358" s="26" t="n">
-        <x:v>7.92759</x:v>
+        <x:v>8.49838</x:v>
       </x:c>
       <x:c r="G358" t="n">
         <x:v>13.03747</x:v>
@@ -13349,9 +13349,9 @@
       <x:c r="D359" s="24" t="n">
         <x:v>0.50722</x:v>
       </x:c>
-      <x:c r="E359" s="25" t="str"/>
+      <x:c r="E359" s="25"/>
       <x:c r="F359" s="26" t="n">
-        <x:v>8.45862</x:v>
+        <x:v>9.2199</x:v>
       </x:c>
       <x:c r="G359" t="n">
         <x:v>16.07494</x:v>
@@ -13389,10 +13389,10 @@
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F360" s="26" t="n">
-        <x:v>9.02759</x:v>
+        <x:v>10.00257</x:v>
       </x:c>
       <x:c r="G360" t="n">
-        <x:v>18.29869</x:v>
+        <x:v>21.04349</x:v>
       </x:c>
       <x:c r="H360" t="n">
         <x:v>0</x:v>
@@ -13423,9 +13423,9 @@
       <x:c r="D361" s="24" t="n">
         <x:v>0.49136</x:v>
       </x:c>
-      <x:c r="E361" s="25" t="str"/>
+      <x:c r="E361" s="25"/>
       <x:c r="F361" s="26" t="n">
-        <x:v>9.66483</x:v>
+        <x:v>10.8826</x:v>
       </x:c>
       <x:c r="G361" t="n">
         <x:v>19.05773</x:v>
@@ -13459,9 +13459,9 @@
       <x:c r="D362" s="24" t="n">
         <x:v>0.48344</x:v>
       </x:c>
-      <x:c r="E362" s="25" t="str"/>
+      <x:c r="E362" s="25"/>
       <x:c r="F362" s="26" t="n">
-        <x:v>10.24138</x:v>
+        <x:v>11.71614</x:v>
       </x:c>
       <x:c r="G362" t="n">
         <x:v>20.40699</x:v>
@@ -13495,9 +13495,9 @@
       <x:c r="D363" s="24" t="n">
         <x:v>0.47552</x:v>
       </x:c>
-      <x:c r="E363" s="25" t="str"/>
+      <x:c r="E363" s="25"/>
       <x:c r="F363" s="26" t="n">
-        <x:v>10.66621</x:v>
+        <x:v>12.39414</x:v>
       </x:c>
       <x:c r="G363" t="n">
         <x:v>23.2318</x:v>
@@ -13531,9 +13531,9 @@
       <x:c r="D364" s="24" t="n">
         <x:v>0.4676</x:v>
       </x:c>
-      <x:c r="E364" s="25" t="str"/>
+      <x:c r="E364" s="25"/>
       <x:c r="F364" s="26" t="n">
-        <x:v>11.07966</x:v>
+        <x:v>13.074</x:v>
       </x:c>
       <x:c r="G364" t="n">
         <x:v>26.26658</x:v>
@@ -13567,9 +13567,9 @@
       <x:c r="D365" s="24" t="n">
         <x:v>0.45969</x:v>
       </x:c>
-      <x:c r="E365" s="25" t="str"/>
+      <x:c r="E365" s="25"/>
       <x:c r="F365" s="26" t="n">
-        <x:v>11.45138</x:v>
+        <x:v>13.51263</x:v>
       </x:c>
       <x:c r="G365" t="n">
         <x:v>30.0712</x:v>
@@ -13603,9 +13603,9 @@
       <x:c r="D366" s="24" t="n">
         <x:v>0.45176</x:v>
       </x:c>
-      <x:c r="E366" s="25" t="str"/>
+      <x:c r="E366" s="25"/>
       <x:c r="F366" s="26" t="n">
-        <x:v>11.8231</x:v>
+        <x:v>13.95126</x:v>
       </x:c>
       <x:c r="G366" t="n">
         <x:v>34.01487</x:v>
@@ -13639,9 +13639,9 @@
       <x:c r="D367" s="24" t="n">
         <x:v>0.4438</x:v>
       </x:c>
-      <x:c r="E367" s="25" t="str"/>
+      <x:c r="E367" s="25"/>
       <x:c r="F367" s="26" t="n">
-        <x:v>12.19483</x:v>
+        <x:v>14.3899</x:v>
       </x:c>
       <x:c r="G367" t="n">
         <x:v>38.79282</x:v>
@@ -13675,9 +13675,9 @@
       <x:c r="D368" s="24" t="n">
         <x:v>0.43583</x:v>
       </x:c>
-      <x:c r="E368" s="25" t="str"/>
+      <x:c r="E368" s="25"/>
       <x:c r="F368" s="26" t="n">
-        <x:v>12.57034</x:v>
+        <x:v>14.833</x:v>
       </x:c>
       <x:c r="G368" t="n">
         <x:v>44.04503</x:v>
@@ -13711,9 +13711,9 @@
       <x:c r="D369" s="24" t="n">
         <x:v>0.42792</x:v>
       </x:c>
-      <x:c r="E369" s="25" t="str"/>
+      <x:c r="E369" s="25"/>
       <x:c r="F369" s="26" t="n">
-        <x:v>12.99517</x:v>
+        <x:v>15.3343</x:v>
       </x:c>
       <x:c r="G369" t="n">
         <x:v>55.46252</x:v>
@@ -13751,10 +13751,10 @@
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F370" s="26" t="n">
-        <x:v>13.42</x:v>
+        <x:v>15.8356</x:v>
       </x:c>
       <x:c r="G370" t="n">
-        <x:v>66.88</x:v>
+        <x:v>100.32</x:v>
       </x:c>
       <x:c r="H370" t="n">
         <x:v>0</x:v>
@@ -13785,7 +13785,7 @@
       <x:c r="D371" s="24" t="n">
         <x:v>0.65</x:v>
       </x:c>
-      <x:c r="E371" s="25" t="str"/>
+      <x:c r="E371" s="25"/>
       <x:c r="F371" s="26" t="n">
         <x:v>0.715</x:v>
       </x:c>
@@ -13821,7 +13821,7 @@
       <x:c r="D372" s="24" t="n">
         <x:v>0.64208</x:v>
       </x:c>
-      <x:c r="E372" s="25" t="str"/>
+      <x:c r="E372" s="25"/>
       <x:c r="F372" s="26" t="n">
         <x:v>0.8719</x:v>
       </x:c>
@@ -13857,7 +13857,7 @@
       <x:c r="D373" s="24" t="n">
         <x:v>0.63417</x:v>
       </x:c>
-      <x:c r="E373" s="25" t="str"/>
+      <x:c r="E373" s="25"/>
       <x:c r="F373" s="26" t="n">
         <x:v>1.02879</x:v>
       </x:c>
@@ -13893,7 +13893,7 @@
       <x:c r="D374" s="24" t="n">
         <x:v>0.6262</x:v>
       </x:c>
-      <x:c r="E374" s="25" t="str"/>
+      <x:c r="E374" s="25"/>
       <x:c r="F374" s="26" t="n">
         <x:v>1.2731</x:v>
       </x:c>
@@ -13929,7 +13929,7 @@
       <x:c r="D375" s="24" t="n">
         <x:v>0.61824</x:v>
       </x:c>
-      <x:c r="E375" s="25" t="str"/>
+      <x:c r="E375" s="25"/>
       <x:c r="F375" s="26" t="n">
         <x:v>1.52414</x:v>
       </x:c>
@@ -13965,7 +13965,7 @@
       <x:c r="D376" s="24" t="n">
         <x:v>0.61031</x:v>
       </x:c>
-      <x:c r="E376" s="25" t="str"/>
+      <x:c r="E376" s="25"/>
       <x:c r="F376" s="26" t="n">
         <x:v>1.82897</x:v>
       </x:c>
@@ -14001,7 +14001,7 @@
       <x:c r="D377" s="24" t="n">
         <x:v>0.6024</x:v>
       </x:c>
-      <x:c r="E377" s="25" t="str"/>
+      <x:c r="E377" s="25"/>
       <x:c r="F377" s="26" t="n">
         <x:v>2.14276</x:v>
       </x:c>
@@ -14037,7 +14037,7 @@
       <x:c r="D378" s="24" t="n">
         <x:v>0.59448</x:v>
       </x:c>
-      <x:c r="E378" s="25" t="str"/>
+      <x:c r="E378" s="25"/>
       <x:c r="F378" s="26" t="n">
         <x:v>2.35793</x:v>
       </x:c>
@@ -14073,7 +14073,7 @@
       <x:c r="D379" s="24" t="n">
         <x:v>0.58656</x:v>
       </x:c>
-      <x:c r="E379" s="25" t="str"/>
+      <x:c r="E379" s="25"/>
       <x:c r="F379" s="26" t="n">
         <x:v>2.54621</x:v>
       </x:c>
@@ -14147,7 +14147,7 @@
       <x:c r="D381" s="24" t="n">
         <x:v>0.57073</x:v>
       </x:c>
-      <x:c r="E381" s="25" t="str"/>
+      <x:c r="E381" s="25"/>
       <x:c r="F381" s="26" t="n">
         <x:v>3.4069</x:v>
       </x:c>
@@ -14183,7 +14183,7 @@
       <x:c r="D382" s="24" t="n">
         <x:v>0.56278</x:v>
       </x:c>
-      <x:c r="E382" s="25" t="str"/>
+      <x:c r="E382" s="25"/>
       <x:c r="F382" s="26" t="n">
         <x:v>3.67586</x:v>
       </x:c>
@@ -14219,7 +14219,7 @@
       <x:c r="D383" s="24" t="n">
         <x:v>0.55481</x:v>
       </x:c>
-      <x:c r="E383" s="25" t="str"/>
+      <x:c r="E383" s="25"/>
       <x:c r="F383" s="26" t="n">
         <x:v>3.83276</x:v>
       </x:c>
@@ -14255,7 +14255,7 @@
       <x:c r="D384" s="24" t="n">
         <x:v>0.54688</x:v>
       </x:c>
-      <x:c r="E384" s="25" t="str"/>
+      <x:c r="E384" s="25"/>
       <x:c r="F384" s="26" t="n">
         <x:v>3.98966</x:v>
       </x:c>
@@ -14291,9 +14291,9 @@
       <x:c r="D385" s="24" t="n">
         <x:v>0.53896</x:v>
       </x:c>
-      <x:c r="E385" s="25" t="str"/>
+      <x:c r="E385" s="25"/>
       <x:c r="F385" s="26" t="n">
-        <x:v>4.14655</x:v>
+        <x:v>4.22119</x:v>
       </x:c>
       <x:c r="G385" t="n">
         <x:v>7.04607</x:v>
@@ -14327,9 +14327,9 @@
       <x:c r="D386" s="24" t="n">
         <x:v>0.53104</x:v>
       </x:c>
-      <x:c r="E386" s="25" t="str"/>
+      <x:c r="E386" s="25"/>
       <x:c r="F386" s="26" t="n">
-        <x:v>4.30345</x:v>
+        <x:v>4.45837</x:v>
       </x:c>
       <x:c r="G386" t="n">
         <x:v>7.38593</x:v>
@@ -14363,9 +14363,9 @@
       <x:c r="D387" s="24" t="n">
         <x:v>0.52312</x:v>
       </x:c>
-      <x:c r="E387" s="25" t="str"/>
+      <x:c r="E387" s="25"/>
       <x:c r="F387" s="26" t="n">
-        <x:v>4.46034</x:v>
+        <x:v>4.7012</x:v>
       </x:c>
       <x:c r="G387" t="n">
         <x:v>7.72579</x:v>
@@ -14399,9 +14399,9 @@
       <x:c r="D388" s="24" t="n">
         <x:v>0.51519</x:v>
       </x:c>
-      <x:c r="E388" s="25" t="str"/>
+      <x:c r="E388" s="25"/>
       <x:c r="F388" s="26" t="n">
-        <x:v>4.68448</x:v>
+        <x:v>5.02176</x:v>
       </x:c>
       <x:c r="G388" t="n">
         <x:v>8.46621</x:v>
@@ -14435,9 +14435,9 @@
       <x:c r="D389" s="24" t="n">
         <x:v>0.50722</x:v>
       </x:c>
-      <x:c r="E389" s="25" t="str"/>
+      <x:c r="E389" s="25"/>
       <x:c r="F389" s="26" t="n">
-        <x:v>4.99828</x:v>
+        <x:v>5.44813</x:v>
       </x:c>
       <x:c r="G389" t="n">
         <x:v>9.74069</x:v>
@@ -14475,10 +14475,10 @@
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F390" s="26" t="n">
-        <x:v>5.33448</x:v>
+        <x:v>5.9106</x:v>
       </x:c>
       <x:c r="G390" t="n">
-        <x:v>10.43862</x:v>
+        <x:v>12.00441</x:v>
       </x:c>
       <x:c r="H390" t="n">
         <x:v>0</x:v>
@@ -14509,9 +14509,9 @@
       <x:c r="D391" s="24" t="n">
         <x:v>0.49136</x:v>
       </x:c>
-      <x:c r="E391" s="25" t="str"/>
+      <x:c r="E391" s="25"/>
       <x:c r="F391" s="26" t="n">
-        <x:v>5.71103</x:v>
+        <x:v>6.43062</x:v>
       </x:c>
       <x:c r="G391" t="n">
         <x:v>10.09876</x:v>
@@ -14545,9 +14545,9 @@
       <x:c r="D392" s="24" t="n">
         <x:v>0.48344</x:v>
       </x:c>
-      <x:c r="E392" s="25" t="str"/>
+      <x:c r="E392" s="25"/>
       <x:c r="F392" s="26" t="n">
-        <x:v>6.05172</x:v>
+        <x:v>6.92317</x:v>
       </x:c>
       <x:c r="G392" t="n">
         <x:v>10.00166</x:v>
@@ -14581,9 +14581,9 @@
       <x:c r="D393" s="24" t="n">
         <x:v>0.47552</x:v>
       </x:c>
-      <x:c r="E393" s="25" t="str"/>
+      <x:c r="E393" s="25"/>
       <x:c r="F393" s="26" t="n">
-        <x:v>6.30276</x:v>
+        <x:v>7.32381</x:v>
       </x:c>
       <x:c r="G393" t="n">
         <x:v>10.51145</x:v>
@@ -14617,9 +14617,9 @@
       <x:c r="D394" s="24" t="n">
         <x:v>0.4676</x:v>
       </x:c>
-      <x:c r="E394" s="25" t="str"/>
+      <x:c r="E394" s="25"/>
       <x:c r="F394" s="26" t="n">
-        <x:v>6.54707</x:v>
+        <x:v>7.72554</x:v>
       </x:c>
       <x:c r="G394" t="n">
         <x:v>11.03945</x:v>
@@ -14653,9 +14653,9 @@
       <x:c r="D395" s="24" t="n">
         <x:v>0.45969</x:v>
       </x:c>
-      <x:c r="E395" s="25" t="str"/>
+      <x:c r="E395" s="25"/>
       <x:c r="F395" s="26" t="n">
-        <x:v>6.76672</x:v>
+        <x:v>7.98473</x:v>
       </x:c>
       <x:c r="G395" t="n">
         <x:v>11.63421</x:v>
@@ -14689,9 +14689,9 @@
       <x:c r="D396" s="24" t="n">
         <x:v>0.45176</x:v>
       </x:c>
-      <x:c r="E396" s="25" t="str"/>
+      <x:c r="E396" s="25"/>
       <x:c r="F396" s="26" t="n">
-        <x:v>6.98638</x:v>
+        <x:v>8.24393</x:v>
       </x:c>
       <x:c r="G396" t="n">
         <x:v>12.22897</x:v>
@@ -14725,9 +14725,9 @@
       <x:c r="D397" s="24" t="n">
         <x:v>0.4438</x:v>
       </x:c>
-      <x:c r="E397" s="25" t="str"/>
+      <x:c r="E397" s="25"/>
       <x:c r="F397" s="26" t="n">
-        <x:v>7.20603</x:v>
+        <x:v>8.50312</x:v>
       </x:c>
       <x:c r="G397" t="n">
         <x:v>12.82372</x:v>
@@ -14761,9 +14761,9 @@
       <x:c r="D398" s="24" t="n">
         <x:v>0.43583</x:v>
       </x:c>
-      <x:c r="E398" s="25" t="str"/>
+      <x:c r="E398" s="25"/>
       <x:c r="F398" s="26" t="n">
-        <x:v>7.42793</x:v>
+        <x:v>8.76496</x:v>
       </x:c>
       <x:c r="G398" t="n">
         <x:v>13.52166</x:v>
@@ -14797,9 +14797,9 @@
       <x:c r="D399" s="24" t="n">
         <x:v>0.42792</x:v>
       </x:c>
-      <x:c r="E399" s="25" t="str"/>
+      <x:c r="E399" s="25"/>
       <x:c r="F399" s="26" t="n">
-        <x:v>7.67897</x:v>
+        <x:v>9.06118</x:v>
       </x:c>
       <x:c r="G399" t="n">
         <x:v>15.56083</x:v>
@@ -14837,10 +14837,10 @@
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F400" s="26" t="n">
-        <x:v>7.93</x:v>
+        <x:v>9.3574</x:v>
       </x:c>
       <x:c r="G400" t="n">
-        <x:v>17.6</x:v>
+        <x:v>26.4</x:v>
       </x:c>
       <x:c r="H400" t="n">
         <x:v>0</x:v>
@@ -14871,7 +14871,7 @@
       <x:c r="D401" s="24" t="n">
         <x:v>0.65</x:v>
       </x:c>
-      <x:c r="E401" s="25" t="str"/>
+      <x:c r="E401" s="25"/>
       <x:c r="F401" s="26" t="n">
         <x:v>0.715</x:v>
       </x:c>
@@ -14907,7 +14907,7 @@
       <x:c r="D402" s="24" t="n">
         <x:v>0.64208</x:v>
       </x:c>
-      <x:c r="E402" s="25" t="str"/>
+      <x:c r="E402" s="25"/>
       <x:c r="F402" s="26" t="n">
         <x:v>0.8719</x:v>
       </x:c>
@@ -14943,7 +14943,7 @@
       <x:c r="D403" s="24" t="n">
         <x:v>0.63417</x:v>
       </x:c>
-      <x:c r="E403" s="25" t="str"/>
+      <x:c r="E403" s="25"/>
       <x:c r="F403" s="26" t="n">
         <x:v>1.02879</x:v>
       </x:c>
@@ -14979,7 +14979,7 @@
       <x:c r="D404" s="24" t="n">
         <x:v>0.6262</x:v>
       </x:c>
-      <x:c r="E404" s="25" t="str"/>
+      <x:c r="E404" s="25"/>
       <x:c r="F404" s="26" t="n">
         <x:v>1.2731</x:v>
       </x:c>
@@ -15015,7 +15015,7 @@
       <x:c r="D405" s="24" t="n">
         <x:v>0.61824</x:v>
       </x:c>
-      <x:c r="E405" s="25" t="str"/>
+      <x:c r="E405" s="25"/>
       <x:c r="F405" s="26" t="n">
         <x:v>1.52414</x:v>
       </x:c>
@@ -15051,7 +15051,7 @@
       <x:c r="D406" s="24" t="n">
         <x:v>0.61031</x:v>
       </x:c>
-      <x:c r="E406" s="25" t="str"/>
+      <x:c r="E406" s="25"/>
       <x:c r="F406" s="26" t="n">
         <x:v>1.82897</x:v>
       </x:c>
@@ -15087,7 +15087,7 @@
       <x:c r="D407" s="24" t="n">
         <x:v>0.6024</x:v>
       </x:c>
-      <x:c r="E407" s="25" t="str"/>
+      <x:c r="E407" s="25"/>
       <x:c r="F407" s="26" t="n">
         <x:v>2.14276</x:v>
       </x:c>
@@ -15123,7 +15123,7 @@
       <x:c r="D408" s="24" t="n">
         <x:v>0.59448</x:v>
       </x:c>
-      <x:c r="E408" s="25" t="str"/>
+      <x:c r="E408" s="25"/>
       <x:c r="F408" s="26" t="n">
         <x:v>2.35793</x:v>
       </x:c>
@@ -15159,7 +15159,7 @@
       <x:c r="D409" s="24" t="n">
         <x:v>0.58656</x:v>
       </x:c>
-      <x:c r="E409" s="25" t="str"/>
+      <x:c r="E409" s="25"/>
       <x:c r="F409" s="26" t="n">
         <x:v>2.54621</x:v>
       </x:c>
@@ -15233,7 +15233,7 @@
       <x:c r="D411" s="24" t="n">
         <x:v>0.57073</x:v>
       </x:c>
-      <x:c r="E411" s="25" t="str"/>
+      <x:c r="E411" s="25"/>
       <x:c r="F411" s="26" t="n">
         <x:v>3.4069</x:v>
       </x:c>
@@ -15269,7 +15269,7 @@
       <x:c r="D412" s="24" t="n">
         <x:v>0.56278</x:v>
       </x:c>
-      <x:c r="E412" s="25" t="str"/>
+      <x:c r="E412" s="25"/>
       <x:c r="F412" s="26" t="n">
         <x:v>3.67586</x:v>
       </x:c>
@@ -15305,7 +15305,7 @@
       <x:c r="D413" s="24" t="n">
         <x:v>0.55481</x:v>
       </x:c>
-      <x:c r="E413" s="25" t="str"/>
+      <x:c r="E413" s="25"/>
       <x:c r="F413" s="26" t="n">
         <x:v>3.83276</x:v>
       </x:c>
@@ -15341,7 +15341,7 @@
       <x:c r="D414" s="24" t="n">
         <x:v>0.54688</x:v>
       </x:c>
-      <x:c r="E414" s="25" t="str"/>
+      <x:c r="E414" s="25"/>
       <x:c r="F414" s="26" t="n">
         <x:v>3.98966</x:v>
       </x:c>
@@ -15377,9 +15377,9 @@
       <x:c r="D415" s="24" t="n">
         <x:v>0.53896</x:v>
       </x:c>
-      <x:c r="E415" s="25" t="str"/>
+      <x:c r="E415" s="25"/>
       <x:c r="F415" s="26" t="n">
-        <x:v>4.14655</x:v>
+        <x:v>4.22119</x:v>
       </x:c>
       <x:c r="G415" t="n">
         <x:v>7.18697</x:v>
@@ -15413,9 +15413,9 @@
       <x:c r="D416" s="24" t="n">
         <x:v>0.53104</x:v>
       </x:c>
-      <x:c r="E416" s="25" t="str"/>
+      <x:c r="E416" s="25"/>
       <x:c r="F416" s="26" t="n">
-        <x:v>4.30345</x:v>
+        <x:v>4.45837</x:v>
       </x:c>
       <x:c r="G416" t="n">
         <x:v>7.53363</x:v>
@@ -15449,9 +15449,9 @@
       <x:c r="D417" s="24" t="n">
         <x:v>0.52312</x:v>
       </x:c>
-      <x:c r="E417" s="25" t="str"/>
+      <x:c r="E417" s="25"/>
       <x:c r="F417" s="26" t="n">
-        <x:v>4.46034</x:v>
+        <x:v>4.7012</x:v>
       </x:c>
       <x:c r="G417" t="n">
         <x:v>7.8803</x:v>
@@ -15485,9 +15485,9 @@
       <x:c r="D418" s="24" t="n">
         <x:v>0.51519</x:v>
       </x:c>
-      <x:c r="E418" s="25" t="str"/>
+      <x:c r="E418" s="25"/>
       <x:c r="F418" s="26" t="n">
-        <x:v>4.68448</x:v>
+        <x:v>5.02176</x:v>
       </x:c>
       <x:c r="G418" t="n">
         <x:v>8.63553</x:v>
@@ -15521,9 +15521,9 @@
       <x:c r="D419" s="24" t="n">
         <x:v>0.50722</x:v>
       </x:c>
-      <x:c r="E419" s="25" t="str"/>
+      <x:c r="E419" s="25"/>
       <x:c r="F419" s="26" t="n">
-        <x:v>4.99828</x:v>
+        <x:v>5.44813</x:v>
       </x:c>
       <x:c r="G419" t="n">
         <x:v>9.9355</x:v>
@@ -15561,10 +15561,10 @@
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F420" s="26" t="n">
-        <x:v>5.33448</x:v>
+        <x:v>5.9106</x:v>
       </x:c>
       <x:c r="G420" t="n">
-        <x:v>10.64739</x:v>
+        <x:v>12.2445</x:v>
       </x:c>
       <x:c r="H420" t="n">
         <x:v>0</x:v>
@@ -15595,9 +15595,9 @@
       <x:c r="D421" s="24" t="n">
         <x:v>0.49136</x:v>
       </x:c>
-      <x:c r="E421" s="25" t="str"/>
+      <x:c r="E421" s="25"/>
       <x:c r="F421" s="26" t="n">
-        <x:v>5.71103</x:v>
+        <x:v>6.43062</x:v>
       </x:c>
       <x:c r="G421" t="n">
         <x:v>10.30072</x:v>
@@ -15631,9 +15631,9 @@
       <x:c r="D422" s="24" t="n">
         <x:v>0.48344</x:v>
       </x:c>
-      <x:c r="E422" s="25" t="str"/>
+      <x:c r="E422" s="25"/>
       <x:c r="F422" s="26" t="n">
-        <x:v>6.05172</x:v>
+        <x:v>6.92317</x:v>
       </x:c>
       <x:c r="G422" t="n">
         <x:v>10.20167</x:v>
@@ -15667,9 +15667,9 @@
       <x:c r="D423" s="24" t="n">
         <x:v>0.47552</x:v>
       </x:c>
-      <x:c r="E423" s="25" t="str"/>
+      <x:c r="E423" s="25"/>
       <x:c r="F423" s="26" t="n">
-        <x:v>6.30276</x:v>
+        <x:v>7.32381</x:v>
       </x:c>
       <x:c r="G423" t="n">
         <x:v>10.72164</x:v>
@@ -15703,9 +15703,9 @@
       <x:c r="D424" s="24" t="n">
         <x:v>0.4676</x:v>
       </x:c>
-      <x:c r="E424" s="25" t="str"/>
+      <x:c r="E424" s="25"/>
       <x:c r="F424" s="26" t="n">
-        <x:v>6.54707</x:v>
+        <x:v>7.72554</x:v>
       </x:c>
       <x:c r="G424" t="n">
         <x:v>11.2602</x:v>
@@ -15739,9 +15739,9 @@
       <x:c r="D425" s="24" t="n">
         <x:v>0.45969</x:v>
       </x:c>
-      <x:c r="E425" s="25" t="str"/>
+      <x:c r="E425" s="25"/>
       <x:c r="F425" s="26" t="n">
-        <x:v>6.76672</x:v>
+        <x:v>7.98473</x:v>
       </x:c>
       <x:c r="G425" t="n">
         <x:v>11.86689</x:v>
@@ -15775,9 +15775,9 @@
       <x:c r="D426" s="24" t="n">
         <x:v>0.45176</x:v>
       </x:c>
-      <x:c r="E426" s="25" t="str"/>
+      <x:c r="E426" s="25"/>
       <x:c r="F426" s="26" t="n">
-        <x:v>6.98638</x:v>
+        <x:v>8.24393</x:v>
       </x:c>
       <x:c r="G426" t="n">
         <x:v>12.47356</x:v>
@@ -15811,9 +15811,9 @@
       <x:c r="D427" s="24" t="n">
         <x:v>0.4438</x:v>
       </x:c>
-      <x:c r="E427" s="25" t="str"/>
+      <x:c r="E427" s="25"/>
       <x:c r="F427" s="26" t="n">
-        <x:v>7.20603</x:v>
+        <x:v>8.50312</x:v>
       </x:c>
       <x:c r="G427" t="n">
         <x:v>13.0802</x:v>
@@ -15847,9 +15847,9 @@
       <x:c r="D428" s="24" t="n">
         <x:v>0.43583</x:v>
       </x:c>
-      <x:c r="E428" s="25" t="str"/>
+      <x:c r="E428" s="25"/>
       <x:c r="F428" s="26" t="n">
-        <x:v>7.42793</x:v>
+        <x:v>8.76496</x:v>
       </x:c>
       <x:c r="G428" t="n">
         <x:v>13.79207</x:v>
@@ -15883,9 +15883,9 @@
       <x:c r="D429" s="24" t="n">
         <x:v>0.42792</x:v>
       </x:c>
-      <x:c r="E429" s="25" t="str"/>
+      <x:c r="E429" s="25"/>
       <x:c r="F429" s="26" t="n">
-        <x:v>7.67897</x:v>
+        <x:v>9.06118</x:v>
       </x:c>
       <x:c r="G429" t="n">
         <x:v>15.87203</x:v>
@@ -15923,10 +15923,10 @@
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F430" s="26" t="n">
-        <x:v>7.93</x:v>
+        <x:v>9.3574</x:v>
       </x:c>
       <x:c r="G430" t="n">
-        <x:v>17.952</x:v>
+        <x:v>26.928</x:v>
       </x:c>
       <x:c r="H430" t="n">
         <x:v>0</x:v>
@@ -15957,7 +15957,7 @@
       <x:c r="D431" s="24" t="n">
         <x:v>0.65</x:v>
       </x:c>
-      <x:c r="E431" s="25" t="str"/>
+      <x:c r="E431" s="25"/>
       <x:c r="F431" s="26" t="n">
         <x:v>0.9</x:v>
       </x:c>
@@ -15993,7 +15993,7 @@
       <x:c r="D432" s="24" t="n">
         <x:v>0.64208</x:v>
       </x:c>
-      <x:c r="E432" s="25" t="str"/>
+      <x:c r="E432" s="25"/>
       <x:c r="F432" s="26" t="n">
         <x:v>1.0931</x:v>
       </x:c>
@@ -16029,7 +16029,7 @@
       <x:c r="D433" s="24" t="n">
         <x:v>0.63417</x:v>
       </x:c>
-      <x:c r="E433" s="25" t="str"/>
+      <x:c r="E433" s="25"/>
       <x:c r="F433" s="26" t="n">
         <x:v>1.28621</x:v>
       </x:c>
@@ -16065,7 +16065,7 @@
       <x:c r="D434" s="24" t="n">
         <x:v>0.6262</x:v>
       </x:c>
-      <x:c r="E434" s="25" t="str"/>
+      <x:c r="E434" s="25"/>
       <x:c r="F434" s="26" t="n">
         <x:v>1.56897</x:v>
       </x:c>
@@ -16101,7 +16101,7 @@
       <x:c r="D435" s="24" t="n">
         <x:v>0.61824</x:v>
       </x:c>
-      <x:c r="E435" s="25" t="str"/>
+      <x:c r="E435" s="25"/>
       <x:c r="F435" s="26" t="n">
         <x:v>1.85862</x:v>
       </x:c>
@@ -16137,7 +16137,7 @@
       <x:c r="D436" s="24" t="n">
         <x:v>0.61031</x:v>
       </x:c>
-      <x:c r="E436" s="25" t="str"/>
+      <x:c r="E436" s="25"/>
       <x:c r="F436" s="26" t="n">
         <x:v>2.18966</x:v>
       </x:c>
@@ -16173,7 +16173,7 @@
       <x:c r="D437" s="24" t="n">
         <x:v>0.6024</x:v>
       </x:c>
-      <x:c r="E437" s="25" t="str"/>
+      <x:c r="E437" s="25"/>
       <x:c r="F437" s="26" t="n">
         <x:v>2.52759</x:v>
       </x:c>
@@ -16209,7 +16209,7 @@
       <x:c r="D438" s="24" t="n">
         <x:v>0.59448</x:v>
       </x:c>
-      <x:c r="E438" s="25" t="str"/>
+      <x:c r="E438" s="25"/>
       <x:c r="F438" s="26" t="n">
         <x:v>2.82759</x:v>
       </x:c>
@@ -16245,7 +16245,7 @@
       <x:c r="D439" s="24" t="n">
         <x:v>0.58656</x:v>
       </x:c>
-      <x:c r="E439" s="25" t="str"/>
+      <x:c r="E439" s="25"/>
       <x:c r="F439" s="26" t="n">
         <x:v>3.11724</x:v>
       </x:c>
@@ -16319,7 +16319,7 @@
       <x:c r="D441" s="24" t="n">
         <x:v>0.57073</x:v>
       </x:c>
-      <x:c r="E441" s="25" t="str"/>
+      <x:c r="E441" s="25"/>
       <x:c r="F441" s="26" t="n">
         <x:v>4.11034</x:v>
       </x:c>
@@ -16355,7 +16355,7 @@
       <x:c r="D442" s="24" t="n">
         <x:v>0.56278</x:v>
       </x:c>
-      <x:c r="E442" s="25" t="str"/>
+      <x:c r="E442" s="25"/>
       <x:c r="F442" s="26" t="n">
         <x:v>4.51724</x:v>
       </x:c>
@@ -16391,7 +16391,7 @@
       <x:c r="D443" s="24" t="n">
         <x:v>0.55481</x:v>
       </x:c>
-      <x:c r="E443" s="25" t="str"/>
+      <x:c r="E443" s="25"/>
       <x:c r="F443" s="26" t="n">
         <x:v>4.85517</x:v>
       </x:c>
@@ -16427,7 +16427,7 @@
       <x:c r="D444" s="24" t="n">
         <x:v>0.54688</x:v>
       </x:c>
-      <x:c r="E444" s="25" t="str"/>
+      <x:c r="E444" s="25"/>
       <x:c r="F444" s="26" t="n">
         <x:v>5.22069</x:v>
       </x:c>
@@ -16463,9 +16463,9 @@
       <x:c r="D445" s="24" t="n">
         <x:v>0.53896</x:v>
       </x:c>
-      <x:c r="E445" s="25" t="str"/>
+      <x:c r="E445" s="25"/>
       <x:c r="F445" s="26" t="n">
-        <x:v>5.6069</x:v>
+        <x:v>5.70782</x:v>
       </x:c>
       <x:c r="G445" t="n">
         <x:v>7.25748</x:v>
@@ -16499,9 +16499,9 @@
       <x:c r="D446" s="24" t="n">
         <x:v>0.53104</x:v>
       </x:c>
-      <x:c r="E446" s="25" t="str"/>
+      <x:c r="E446" s="25"/>
       <x:c r="F446" s="26" t="n">
-        <x:v>6.04138</x:v>
+        <x:v>6.25887</x:v>
       </x:c>
       <x:c r="G446" t="n">
         <x:v>7.60752</x:v>
@@ -16535,9 +16535,9 @@
       <x:c r="D447" s="24" t="n">
         <x:v>0.52312</x:v>
       </x:c>
-      <x:c r="E447" s="25" t="str"/>
+      <x:c r="E447" s="25"/>
       <x:c r="F447" s="26" t="n">
-        <x:v>6.52414</x:v>
+        <x:v>6.87644</x:v>
       </x:c>
       <x:c r="G447" t="n">
         <x:v>7.95757</x:v>
@@ -16571,9 +16571,9 @@
       <x:c r="D448" s="24" t="n">
         <x:v>0.51519</x:v>
       </x:c>
-      <x:c r="E448" s="25" t="str"/>
+      <x:c r="E448" s="25"/>
       <x:c r="F448" s="26" t="n">
-        <x:v>7.0069</x:v>
+        <x:v>7.5114</x:v>
       </x:c>
       <x:c r="G448" t="n">
         <x:v>8.72019</x:v>
@@ -16607,9 +16607,9 @@
       <x:c r="D449" s="24" t="n">
         <x:v>0.50722</x:v>
       </x:c>
-      <x:c r="E449" s="25" t="str"/>
+      <x:c r="E449" s="25"/>
       <x:c r="F449" s="26" t="n">
-        <x:v>7.48966</x:v>
+        <x:v>8.16373</x:v>
       </x:c>
       <x:c r="G449" t="n">
         <x:v>10.03291</x:v>
@@ -16647,10 +16647,10 @@
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F450" s="26" t="n">
-        <x:v>8.0069</x:v>
+        <x:v>8.87165</x:v>
       </x:c>
       <x:c r="G450" t="n">
-        <x:v>10.75178</x:v>
+        <x:v>12.36455</x:v>
       </x:c>
       <x:c r="H450" t="n">
         <x:v>0</x:v>
@@ -16681,9 +16681,9 @@
       <x:c r="D451" s="24" t="n">
         <x:v>0.49136</x:v>
       </x:c>
-      <x:c r="E451" s="25" t="str"/>
+      <x:c r="E451" s="25"/>
       <x:c r="F451" s="26" t="n">
-        <x:v>8.58621</x:v>
+        <x:v>9.66807</x:v>
       </x:c>
       <x:c r="G451" t="n">
         <x:v>10.40173</x:v>
@@ -16717,9 +16717,9 @@
       <x:c r="D452" s="24" t="n">
         <x:v>0.48344</x:v>
       </x:c>
-      <x:c r="E452" s="25" t="str"/>
+      <x:c r="E452" s="25"/>
       <x:c r="F452" s="26" t="n">
-        <x:v>9.13793</x:v>
+        <x:v>10.45379</x:v>
       </x:c>
       <x:c r="G452" t="n">
         <x:v>10.30173</x:v>
@@ -16753,9 +16753,9 @@
       <x:c r="D453" s="24" t="n">
         <x:v>0.47552</x:v>
       </x:c>
-      <x:c r="E453" s="25" t="str"/>
+      <x:c r="E453" s="25"/>
       <x:c r="F453" s="26" t="n">
-        <x:v>9.62069</x:v>
+        <x:v>11.17924</x:v>
       </x:c>
       <x:c r="G453" t="n">
         <x:v>10.82682</x:v>
@@ -16789,9 +16789,9 @@
       <x:c r="D454" s="24" t="n">
         <x:v>0.4676</x:v>
       </x:c>
-      <x:c r="E454" s="25" t="str"/>
+      <x:c r="E454" s="25"/>
       <x:c r="F454" s="26" t="n">
-        <x:v>10.10345</x:v>
+        <x:v>11.92207</x:v>
       </x:c>
       <x:c r="G454" t="n">
         <x:v>11.37067</x:v>
@@ -16825,9 +16825,9 @@
       <x:c r="D455" s="24" t="n">
         <x:v>0.45969</x:v>
       </x:c>
-      <x:c r="E455" s="25" t="str"/>
+      <x:c r="E455" s="25"/>
       <x:c r="F455" s="26" t="n">
-        <x:v>10.58621</x:v>
+        <x:v>12.49173</x:v>
       </x:c>
       <x:c r="G455" t="n">
         <x:v>11.98324</x:v>
@@ -16861,9 +16861,9 @@
       <x:c r="D456" s="24" t="n">
         <x:v>0.45176</x:v>
       </x:c>
-      <x:c r="E456" s="25" t="str"/>
+      <x:c r="E456" s="25"/>
       <x:c r="F456" s="26" t="n">
-        <x:v>11.06897</x:v>
+        <x:v>13.06138</x:v>
       </x:c>
       <x:c r="G456" t="n">
         <x:v>12.59582</x:v>
@@ -16897,9 +16897,9 @@
       <x:c r="D457" s="24" t="n">
         <x:v>0.4438</x:v>
       </x:c>
-      <x:c r="E457" s="25" t="str"/>
+      <x:c r="E457" s="25"/>
       <x:c r="F457" s="26" t="n">
-        <x:v>11.55172</x:v>
+        <x:v>13.63103</x:v>
       </x:c>
       <x:c r="G457" t="n">
         <x:v>13.20844</x:v>
@@ -16933,9 +16933,9 @@
       <x:c r="D458" s="24" t="n">
         <x:v>0.43583</x:v>
       </x:c>
-      <x:c r="E458" s="25" t="str"/>
+      <x:c r="E458" s="25"/>
       <x:c r="F458" s="26" t="n">
-        <x:v>12.03448</x:v>
+        <x:v>14.20069</x:v>
       </x:c>
       <x:c r="G458" t="n">
         <x:v>13.92732</x:v>
@@ -16969,9 +16969,9 @@
       <x:c r="D459" s="24" t="n">
         <x:v>0.42792</x:v>
       </x:c>
-      <x:c r="E459" s="25" t="str"/>
+      <x:c r="E459" s="25"/>
       <x:c r="F459" s="26" t="n">
-        <x:v>12.51724</x:v>
+        <x:v>14.77034</x:v>
       </x:c>
       <x:c r="G459" t="n">
         <x:v>16.02766</x:v>
@@ -17009,10 +17009,10 @@
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F460" s="26" t="n">
-        <x:v>13</x:v>
+        <x:v>15.34</x:v>
       </x:c>
       <x:c r="G460" t="n">
-        <x:v>18.128</x:v>
+        <x:v>27.192</x:v>
       </x:c>
       <x:c r="H460" t="n">
         <x:v>0</x:v>
@@ -17043,7 +17043,7 @@
       <x:c r="D461" s="24" t="n">
         <x:v>0.65</x:v>
       </x:c>
-      <x:c r="E461" s="25" t="str"/>
+      <x:c r="E461" s="25"/>
       <x:c r="F461" s="26" t="n">
         <x:v>0.9</x:v>
       </x:c>
@@ -17079,7 +17079,7 @@
       <x:c r="D462" s="24" t="n">
         <x:v>0.64208</x:v>
       </x:c>
-      <x:c r="E462" s="25" t="str"/>
+      <x:c r="E462" s="25"/>
       <x:c r="F462" s="26" t="n">
         <x:v>0.99655</x:v>
       </x:c>
@@ -17115,7 +17115,7 @@
       <x:c r="D463" s="24" t="n">
         <x:v>0.63417</x:v>
       </x:c>
-      <x:c r="E463" s="25" t="str"/>
+      <x:c r="E463" s="25"/>
       <x:c r="F463" s="26" t="n">
         <x:v>1.0931</x:v>
       </x:c>
@@ -17151,7 +17151,7 @@
       <x:c r="D464" s="24" t="n">
         <x:v>0.6262</x:v>
       </x:c>
-      <x:c r="E464" s="25" t="str"/>
+      <x:c r="E464" s="25"/>
       <x:c r="F464" s="26" t="n">
         <x:v>1.27931</x:v>
       </x:c>
@@ -17187,7 +17187,7 @@
       <x:c r="D465" s="24" t="n">
         <x:v>0.61824</x:v>
       </x:c>
-      <x:c r="E465" s="25" t="str"/>
+      <x:c r="E465" s="25"/>
       <x:c r="F465" s="26" t="n">
         <x:v>1.47241</x:v>
       </x:c>
@@ -17223,7 +17223,7 @@
       <x:c r="D466" s="24" t="n">
         <x:v>0.61031</x:v>
       </x:c>
-      <x:c r="E466" s="25" t="str"/>
+      <x:c r="E466" s="25"/>
       <x:c r="F466" s="26" t="n">
         <x:v>1.66552</x:v>
       </x:c>
@@ -17259,7 +17259,7 @@
       <x:c r="D467" s="24" t="n">
         <x:v>0.6024</x:v>
       </x:c>
-      <x:c r="E467" s="25" t="str"/>
+      <x:c r="E467" s="25"/>
       <x:c r="F467" s="26" t="n">
         <x:v>1.85862</x:v>
       </x:c>
@@ -17295,7 +17295,7 @@
       <x:c r="D468" s="24" t="n">
         <x:v>0.59448</x:v>
       </x:c>
-      <x:c r="E468" s="25" t="str"/>
+      <x:c r="E468" s="25"/>
       <x:c r="F468" s="26" t="n">
         <x:v>2.08966</x:v>
       </x:c>
@@ -17331,7 +17331,7 @@
       <x:c r="D469" s="24" t="n">
         <x:v>0.58656</x:v>
       </x:c>
-      <x:c r="E469" s="25" t="str"/>
+      <x:c r="E469" s="25"/>
       <x:c r="F469" s="26" t="n">
         <x:v>2.33103</x:v>
       </x:c>
@@ -17405,7 +17405,7 @@
       <x:c r="D471" s="24" t="n">
         <x:v>0.57073</x:v>
       </x:c>
-      <x:c r="E471" s="25" t="str"/>
+      <x:c r="E471" s="25"/>
       <x:c r="F471" s="26" t="n">
         <x:v>3.06207</x:v>
       </x:c>
@@ -17441,7 +17441,7 @@
       <x:c r="D472" s="24" t="n">
         <x:v>0.56278</x:v>
       </x:c>
-      <x:c r="E472" s="25" t="str"/>
+      <x:c r="E472" s="25"/>
       <x:c r="F472" s="26" t="n">
         <x:v>3.44828</x:v>
       </x:c>
@@ -17477,7 +17477,7 @@
       <x:c r="D473" s="24" t="n">
         <x:v>0.55481</x:v>
       </x:c>
-      <x:c r="E473" s="25" t="str"/>
+      <x:c r="E473" s="25"/>
       <x:c r="F473" s="26" t="n">
         <x:v>3.83448</x:v>
       </x:c>
@@ -17513,7 +17513,7 @@
       <x:c r="D474" s="24" t="n">
         <x:v>0.54688</x:v>
       </x:c>
-      <x:c r="E474" s="25" t="str"/>
+      <x:c r="E474" s="25"/>
       <x:c r="F474" s="26" t="n">
         <x:v>4.27586</x:v>
       </x:c>
@@ -17549,9 +17549,9 @@
       <x:c r="D475" s="24" t="n">
         <x:v>0.53896</x:v>
       </x:c>
-      <x:c r="E475" s="25" t="str"/>
+      <x:c r="E475" s="25"/>
       <x:c r="F475" s="26" t="n">
-        <x:v>4.75862</x:v>
+        <x:v>4.84428</x:v>
       </x:c>
       <x:c r="G475" t="n">
         <x:v>7.46886</x:v>
@@ -17585,9 +17585,9 @@
       <x:c r="D476" s="24" t="n">
         <x:v>0.53104</x:v>
       </x:c>
-      <x:c r="E476" s="25" t="str"/>
+      <x:c r="E476" s="25"/>
       <x:c r="F476" s="26" t="n">
-        <x:v>5.24138</x:v>
+        <x:v>5.43007</x:v>
       </x:c>
       <x:c r="G476" t="n">
         <x:v>7.82912</x:v>
@@ -17621,9 +17621,9 @@
       <x:c r="D477" s="24" t="n">
         <x:v>0.52312</x:v>
       </x:c>
-      <x:c r="E477" s="25" t="str"/>
+      <x:c r="E477" s="25"/>
       <x:c r="F477" s="26" t="n">
-        <x:v>5.72414</x:v>
+        <x:v>6.03324</x:v>
       </x:c>
       <x:c r="G477" t="n">
         <x:v>8.18935</x:v>
@@ -17657,9 +17657,9 @@
       <x:c r="D478" s="24" t="n">
         <x:v>0.51519</x:v>
       </x:c>
-      <x:c r="E478" s="25" t="str"/>
+      <x:c r="E478" s="25"/>
       <x:c r="F478" s="26" t="n">
-        <x:v>6.2069</x:v>
+        <x:v>6.6538</x:v>
       </x:c>
       <x:c r="G478" t="n">
         <x:v>8.97418</x:v>
@@ -17693,9 +17693,9 @@
       <x:c r="D479" s="24" t="n">
         <x:v>0.50722</x:v>
       </x:c>
-      <x:c r="E479" s="25" t="str"/>
+      <x:c r="E479" s="25"/>
       <x:c r="F479" s="26" t="n">
-        <x:v>6.68966</x:v>
+        <x:v>7.29173</x:v>
       </x:c>
       <x:c r="G479" t="n">
         <x:v>10.32513</x:v>
@@ -17733,10 +17733,10 @@
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F480" s="26" t="n">
-        <x:v>7.17241</x:v>
+        <x:v>7.94703</x:v>
       </x:c>
       <x:c r="G480" t="n">
-        <x:v>11.06494</x:v>
+        <x:v>12.72468</x:v>
       </x:c>
       <x:c r="H480" t="n">
         <x:v>0</x:v>
@@ -17767,9 +17767,9 @@
       <x:c r="D481" s="24" t="n">
         <x:v>0.49136</x:v>
       </x:c>
-      <x:c r="E481" s="25" t="str"/>
+      <x:c r="E481" s="25"/>
       <x:c r="F481" s="26" t="n">
-        <x:v>7.65517</x:v>
+        <x:v>8.61972</x:v>
       </x:c>
       <x:c r="G481" t="n">
         <x:v>10.70471</x:v>
@@ -17803,9 +17803,9 @@
       <x:c r="D482" s="24" t="n">
         <x:v>0.48344</x:v>
       </x:c>
-      <x:c r="E482" s="25" t="str"/>
+      <x:c r="E482" s="25"/>
       <x:c r="F482" s="26" t="n">
-        <x:v>8.13793</x:v>
+        <x:v>9.30979</x:v>
       </x:c>
       <x:c r="G482" t="n">
         <x:v>10.60179</x:v>
@@ -17839,9 +17839,9 @@
       <x:c r="D483" s="24" t="n">
         <x:v>0.47552</x:v>
       </x:c>
-      <x:c r="E483" s="25" t="str"/>
+      <x:c r="E483" s="25"/>
       <x:c r="F483" s="26" t="n">
-        <x:v>8.62069</x:v>
+        <x:v>10.01724</x:v>
       </x:c>
       <x:c r="G483" t="n">
         <x:v>11.14214</x:v>
@@ -17875,9 +17875,9 @@
       <x:c r="D484" s="24" t="n">
         <x:v>0.4676</x:v>
       </x:c>
-      <x:c r="E484" s="25" t="str"/>
+      <x:c r="E484" s="25"/>
       <x:c r="F484" s="26" t="n">
-        <x:v>9.10345</x:v>
+        <x:v>10.74207</x:v>
       </x:c>
       <x:c r="G484" t="n">
         <x:v>11.70179</x:v>
@@ -17911,9 +17911,9 @@
       <x:c r="D485" s="24" t="n">
         <x:v>0.45969</x:v>
       </x:c>
-      <x:c r="E485" s="25" t="str"/>
+      <x:c r="E485" s="25"/>
       <x:c r="F485" s="26" t="n">
-        <x:v>9.58621</x:v>
+        <x:v>11.31173</x:v>
       </x:c>
       <x:c r="G485" t="n">
         <x:v>12.33223</x:v>
@@ -17947,9 +17947,9 @@
       <x:c r="D486" s="24" t="n">
         <x:v>0.45176</x:v>
       </x:c>
-      <x:c r="E486" s="25" t="str"/>
+      <x:c r="E486" s="25"/>
       <x:c r="F486" s="26" t="n">
-        <x:v>10.06897</x:v>
+        <x:v>11.88138</x:v>
       </x:c>
       <x:c r="G486" t="n">
         <x:v>12.96267</x:v>
@@ -17983,9 +17983,9 @@
       <x:c r="D487" s="24" t="n">
         <x:v>0.4438</x:v>
       </x:c>
-      <x:c r="E487" s="25" t="str"/>
+      <x:c r="E487" s="25"/>
       <x:c r="F487" s="26" t="n">
-        <x:v>10.55172</x:v>
+        <x:v>12.45103</x:v>
       </x:c>
       <x:c r="G487" t="n">
         <x:v>13.59315</x:v>
@@ -18019,9 +18019,9 @@
       <x:c r="D488" s="24" t="n">
         <x:v>0.43583</x:v>
       </x:c>
-      <x:c r="E488" s="25" t="str"/>
+      <x:c r="E488" s="25"/>
       <x:c r="F488" s="26" t="n">
-        <x:v>11.03448</x:v>
+        <x:v>13.02069</x:v>
       </x:c>
       <x:c r="G488" t="n">
         <x:v>14.33299</x:v>
@@ -18055,9 +18055,9 @@
       <x:c r="D489" s="24" t="n">
         <x:v>0.42792</x:v>
       </x:c>
-      <x:c r="E489" s="25" t="str"/>
+      <x:c r="E489" s="25"/>
       <x:c r="F489" s="26" t="n">
-        <x:v>11.51724</x:v>
+        <x:v>13.59034</x:v>
       </x:c>
       <x:c r="G489" t="n">
         <x:v>16.4945</x:v>
@@ -18095,10 +18095,10 @@
         <x:v>challenge.bossWave</x:v>
       </x:c>
       <x:c r="F490" s="26" t="n">
-        <x:v>12</x:v>
+        <x:v>14.16</x:v>
       </x:c>
       <x:c r="G490" t="n">
-        <x:v>18.656</x:v>
+        <x:v>27.984</x:v>
       </x:c>
       <x:c r="H490" t="n">
         <x:v>0</x:v>

--- a/design/tables/Wave.xlsx
+++ b/design/tables/Wave.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wave" sheetId="1" r:id="R2084ce9055bd4e5f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wave" sheetId="1" r:id="R87610f4b591046e9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -689,7 +689,7 @@
       </x:c>
       <x:c r="E9" s="25"/>
       <x:c r="F9" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.03525</x:v>
       </x:c>
       <x:c r="G9" t="n">
         <x:v>1</x:v>
@@ -725,7 +725,7 @@
       </x:c>
       <x:c r="E10" s="25"/>
       <x:c r="F10" s="26" t="n">
-        <x:v>1.02838</x:v>
+        <x:v>1.08394</x:v>
       </x:c>
       <x:c r="G10" t="n">
         <x:v>1</x:v>
@@ -761,7 +761,7 @@
       </x:c>
       <x:c r="E11" s="25"/>
       <x:c r="F11" s="26" t="n">
-        <x:v>1.07848</x:v>
+        <x:v>1.14238</x:v>
       </x:c>
       <x:c r="G11" t="n">
         <x:v>1</x:v>
@@ -797,7 +797,7 @@
       </x:c>
       <x:c r="E12" s="25"/>
       <x:c r="F12" s="26" t="n">
-        <x:v>1.13446</x:v>
+        <x:v>1.21022</x:v>
       </x:c>
       <x:c r="G12" t="n">
         <x:v>1</x:v>
@@ -835,7 +835,7 @@
         <x:v>wave.104.announcement</x:v>
       </x:c>
       <x:c r="F13" s="26" t="n">
-        <x:v>1.19231</x:v>
+        <x:v>1.28769</x:v>
       </x:c>
       <x:c r="G13" t="n">
         <x:v>1</x:v>
@@ -979,7 +979,7 @@
       </x:c>
       <x:c r="E17" s="25"/>
       <x:c r="F17" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.01713</x:v>
       </x:c>
       <x:c r="G17" t="n">
         <x:v>1</x:v>
@@ -1015,7 +1015,7 @@
       </x:c>
       <x:c r="E18" s="25"/>
       <x:c r="F18" s="26" t="n">
-        <x:v>1.00504</x:v>
+        <x:v>1.01929</x:v>
       </x:c>
       <x:c r="G18" t="n">
         <x:v>1</x:v>
@@ -1051,7 +1051,7 @@
       </x:c>
       <x:c r="E19" s="25"/>
       <x:c r="F19" s="26" t="n">
-        <x:v>1.02791</x:v>
+        <x:v>1.10166</x:v>
       </x:c>
       <x:c r="G19" t="n">
         <x:v>1</x:v>
@@ -1087,7 +1087,7 @@
       </x:c>
       <x:c r="E20" s="25"/>
       <x:c r="F20" s="26" t="n">
-        <x:v>1.05665</x:v>
+        <x:v>1.07404</x:v>
       </x:c>
       <x:c r="G20" t="n">
         <x:v>1</x:v>
@@ -1123,7 +1123,7 @@
       </x:c>
       <x:c r="E21" s="25"/>
       <x:c r="F21" s="26" t="n">
-        <x:v>1.08805</x:v>
+        <x:v>1.1805</x:v>
       </x:c>
       <x:c r="G21" t="n">
         <x:v>1</x:v>
@@ -1159,7 +1159,7 @@
       </x:c>
       <x:c r="E22" s="25"/>
       <x:c r="F22" s="26" t="n">
-        <x:v>1.12061</x:v>
+        <x:v>1.16558</x:v>
       </x:c>
       <x:c r="G22" t="n">
         <x:v>1</x:v>
@@ -1197,7 +1197,7 @@
         <x:v>wave.204.announcement</x:v>
       </x:c>
       <x:c r="F23" s="26" t="n">
-        <x:v>1.15349</x:v>
+        <x:v>1.29191</x:v>
       </x:c>
       <x:c r="G23" t="n">
         <x:v>1</x:v>
@@ -1341,7 +1341,7 @@
       </x:c>
       <x:c r="E27" s="25"/>
       <x:c r="F27" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>1.006</x:v>
       </x:c>
       <x:c r="G27" t="n">
         <x:v>1</x:v>
@@ -1377,7 +1377,7 @@
       </x:c>
       <x:c r="E28" s="25"/>
       <x:c r="F28" s="26" t="n">
-        <x:v>0.99362</x:v>
+        <x:v>1.00636</x:v>
       </x:c>
       <x:c r="G28" t="n">
         <x:v>1</x:v>
@@ -1413,7 +1413,7 @@
       </x:c>
       <x:c r="E29" s="25"/>
       <x:c r="F29" s="26" t="n">
-        <x:v>1.00318</x:v>
+        <x:v>1.05766</x:v>
       </x:c>
       <x:c r="G29" t="n">
         <x:v>1</x:v>
@@ -1449,7 +1449,7 @@
       </x:c>
       <x:c r="E30" s="25"/>
       <x:c r="F30" s="26" t="n">
-        <x:v>1.0186</x:v>
+        <x:v>1.04776</x:v>
       </x:c>
       <x:c r="G30" t="n">
         <x:v>1</x:v>
@@ -1485,7 +1485,7 @@
       </x:c>
       <x:c r="E31" s="25"/>
       <x:c r="F31" s="26" t="n">
-        <x:v>1.03706</x:v>
+        <x:v>1.11918</x:v>
       </x:c>
       <x:c r="G31" t="n">
         <x:v>1</x:v>
@@ -1521,7 +1521,7 @@
       </x:c>
       <x:c r="E32" s="25"/>
       <x:c r="F32" s="26" t="n">
-        <x:v>1.05721</x:v>
+        <x:v>1.10898</x:v>
       </x:c>
       <x:c r="G32" t="n">
         <x:v>1</x:v>
@@ -1557,7 +1557,7 @@
       </x:c>
       <x:c r="E33" s="25"/>
       <x:c r="F33" s="26" t="n">
-        <x:v>1.07826</x:v>
+        <x:v>1.20017</x:v>
       </x:c>
       <x:c r="G33" t="n">
         <x:v>1</x:v>
@@ -1593,7 +1593,7 @@
       </x:c>
       <x:c r="E34" s="25"/>
       <x:c r="F34" s="26" t="n">
-        <x:v>1.09971</x:v>
+        <x:v>1.19918</x:v>
       </x:c>
       <x:c r="G34" t="n">
         <x:v>1</x:v>
@@ -1631,7 +1631,7 @@
         <x:v>wave.304.announcement</x:v>
       </x:c>
       <x:c r="F35" s="26" t="n">
-        <x:v>1.12128</x:v>
+        <x:v>1.28947</x:v>
       </x:c>
       <x:c r="G35" t="n">
         <x:v>1</x:v>
@@ -1775,7 +1775,7 @@
       </x:c>
       <x:c r="E39" s="25"/>
       <x:c r="F39" s="26" t="n">
-        <x:v>1.15</x:v>
+        <x:v>1.07079</x:v>
       </x:c>
       <x:c r="G39" t="n">
         <x:v>1</x:v>
@@ -1811,7 +1811,7 @@
       </x:c>
       <x:c r="E40" s="25"/>
       <x:c r="F40" s="26" t="n">
-        <x:v>1.15326</x:v>
+        <x:v>1.10982</x:v>
       </x:c>
       <x:c r="G40" t="n">
         <x:v>1</x:v>
@@ -1847,7 +1847,7 @@
       </x:c>
       <x:c r="E41" s="25"/>
       <x:c r="F41" s="26" t="n">
-        <x:v>1.1766</x:v>
+        <x:v>1.07205</x:v>
       </x:c>
       <x:c r="G41" t="n">
         <x:v>1</x:v>
@@ -1883,7 +1883,7 @@
       </x:c>
       <x:c r="E42" s="25"/>
       <x:c r="F42" s="26" t="n">
-        <x:v>1.20669</x:v>
+        <x:v>1.23983</x:v>
       </x:c>
       <x:c r="G42" t="n">
         <x:v>1</x:v>
@@ -1919,7 +1919,7 @@
       </x:c>
       <x:c r="E43" s="25"/>
       <x:c r="F43" s="26" t="n">
-        <x:v>1.23992</x:v>
+        <x:v>1.27284</x:v>
       </x:c>
       <x:c r="G43" t="n">
         <x:v>1</x:v>
@@ -1955,7 +1955,7 @@
       </x:c>
       <x:c r="E44" s="25"/>
       <x:c r="F44" s="26" t="n">
-        <x:v>1.2746</x:v>
+        <x:v>1.26811</x:v>
       </x:c>
       <x:c r="G44" t="n">
         <x:v>1</x:v>
@@ -1991,7 +1991,7 @@
       </x:c>
       <x:c r="E45" s="25"/>
       <x:c r="F45" s="26" t="n">
-        <x:v>1.30978</x:v>
+        <x:v>1.47383</x:v>
       </x:c>
       <x:c r="G45" t="n">
         <x:v>1</x:v>
@@ -2027,7 +2027,7 @@
       </x:c>
       <x:c r="E46" s="25"/>
       <x:c r="F46" s="26" t="n">
-        <x:v>1.3449</x:v>
+        <x:v>1.53543</x:v>
       </x:c>
       <x:c r="G46" t="n">
         <x:v>1</x:v>
@@ -2063,7 +2063,7 @@
       </x:c>
       <x:c r="E47" s="25"/>
       <x:c r="F47" s="26" t="n">
-        <x:v>1.37964</x:v>
+        <x:v>1.42856</x:v>
       </x:c>
       <x:c r="G47" t="n">
         <x:v>1</x:v>
@@ -2099,7 +2099,7 @@
       </x:c>
       <x:c r="E48" s="25"/>
       <x:c r="F48" s="26" t="n">
-        <x:v>1.41377</x:v>
+        <x:v>1.8</x:v>
       </x:c>
       <x:c r="G48" t="n">
         <x:v>1</x:v>
@@ -2135,7 +2135,7 @@
       </x:c>
       <x:c r="E49" s="25"/>
       <x:c r="F49" s="26" t="n">
-        <x:v>1.44719</x:v>
+        <x:v>1.86908</x:v>
       </x:c>
       <x:c r="G49" t="n">
         <x:v>1</x:v>
@@ -2173,7 +2173,7 @@
         <x:v>wave.404.announcement</x:v>
       </x:c>
       <x:c r="F50" s="26" t="n">
-        <x:v>1.47981</x:v>
+        <x:v>1.77577</x:v>
       </x:c>
       <x:c r="G50" t="n">
         <x:v>1</x:v>
@@ -2317,7 +2317,7 @@
       </x:c>
       <x:c r="E54" s="25"/>
       <x:c r="F54" s="26" t="n">
-        <x:v>1.15</x:v>
+        <x:v>1.12852</x:v>
       </x:c>
       <x:c r="G54" t="n">
         <x:v>1</x:v>
@@ -2353,7 +2353,7 @@
       </x:c>
       <x:c r="E55" s="25"/>
       <x:c r="F55" s="26" t="n">
-        <x:v>1.12684</x:v>
+        <x:v>1.13099</x:v>
       </x:c>
       <x:c r="G55" t="n">
         <x:v>1</x:v>
@@ -2389,7 +2389,7 @@
       </x:c>
       <x:c r="E56" s="25"/>
       <x:c r="F56" s="26" t="n">
-        <x:v>1.11937</x:v>
+        <x:v>1.17904</x:v>
       </x:c>
       <x:c r="G56" t="n">
         <x:v>1</x:v>
@@ -2425,7 +2425,7 @@
       </x:c>
       <x:c r="E57" s="25"/>
       <x:c r="F57" s="26" t="n">
-        <x:v>1.11862</x:v>
+        <x:v>1.06787</x:v>
       </x:c>
       <x:c r="G57" t="n">
         <x:v>1</x:v>
@@ -2461,7 +2461,7 @@
       </x:c>
       <x:c r="E58" s="25"/>
       <x:c r="F58" s="26" t="n">
-        <x:v>1.12193</x:v>
+        <x:v>1.1905</x:v>
       </x:c>
       <x:c r="G58" t="n">
         <x:v>1</x:v>
@@ -2497,7 +2497,7 @@
       </x:c>
       <x:c r="E59" s="25"/>
       <x:c r="F59" s="26" t="n">
-        <x:v>1.1279</x:v>
+        <x:v>1.25399</x:v>
       </x:c>
       <x:c r="G59" t="n">
         <x:v>1</x:v>
@@ -2533,7 +2533,7 @@
       </x:c>
       <x:c r="E60" s="25"/>
       <x:c r="F60" s="26" t="n">
-        <x:v>1.1357</x:v>
+        <x:v>1.17398</x:v>
       </x:c>
       <x:c r="G60" t="n">
         <x:v>1</x:v>
@@ -2569,7 +2569,7 @@
       </x:c>
       <x:c r="E61" s="25"/>
       <x:c r="F61" s="26" t="n">
-        <x:v>1.14476</x:v>
+        <x:v>1.29159</x:v>
       </x:c>
       <x:c r="G61" t="n">
         <x:v>1</x:v>
@@ -2605,7 +2605,7 @@
       </x:c>
       <x:c r="E62" s="25"/>
       <x:c r="F62" s="26" t="n">
-        <x:v>1.1547</x:v>
+        <x:v>1.38979</x:v>
       </x:c>
       <x:c r="G62" t="n">
         <x:v>1</x:v>
@@ -2641,7 +2641,7 @@
       </x:c>
       <x:c r="E63" s="25"/>
       <x:c r="F63" s="26" t="n">
-        <x:v>1.16527</x:v>
+        <x:v>1.29601</x:v>
       </x:c>
       <x:c r="G63" t="n">
         <x:v>1</x:v>
@@ -2677,7 +2677,7 @@
       </x:c>
       <x:c r="E64" s="25"/>
       <x:c r="F64" s="26" t="n">
-        <x:v>1.17625</x:v>
+        <x:v>1.4527</x:v>
       </x:c>
       <x:c r="G64" t="n">
         <x:v>1</x:v>
@@ -2713,7 +2713,7 @@
       </x:c>
       <x:c r="E65" s="25"/>
       <x:c r="F65" s="26" t="n">
-        <x:v>1.18751</x:v>
+        <x:v>1.54081</x:v>
       </x:c>
       <x:c r="G65" t="n">
         <x:v>1</x:v>
@@ -2749,7 +2749,7 @@
       </x:c>
       <x:c r="E66" s="25"/>
       <x:c r="F66" s="26" t="n">
-        <x:v>1.19893</x:v>
+        <x:v>1.36498</x:v>
       </x:c>
       <x:c r="G66" t="n">
         <x:v>1</x:v>
@@ -2785,7 +2785,7 @@
       </x:c>
       <x:c r="E67" s="25"/>
       <x:c r="F67" s="26" t="n">
-        <x:v>1.21044</x:v>
+        <x:v>1.63618</x:v>
       </x:c>
       <x:c r="G67" t="n">
         <x:v>1</x:v>
@@ -2821,7 +2821,7 @@
       </x:c>
       <x:c r="E68" s="25"/>
       <x:c r="F68" s="26" t="n">
-        <x:v>1.22197</x:v>
+        <x:v>1.77099</x:v>
       </x:c>
       <x:c r="G68" t="n">
         <x:v>1</x:v>
@@ -2857,7 +2857,7 @@
       </x:c>
       <x:c r="E69" s="25"/>
       <x:c r="F69" s="26" t="n">
-        <x:v>1.23347</x:v>
+        <x:v>1.58257</x:v>
       </x:c>
       <x:c r="G69" t="n">
         <x:v>1</x:v>
@@ -2895,10 +2895,10 @@
         <x:v>wave.504.announcement</x:v>
       </x:c>
       <x:c r="F70" s="26" t="n">
-        <x:v>1.55615</x:v>
+        <x:v>1.86738</x:v>
       </x:c>
       <x:c r="G70" t="n">
-        <x:v>1</x:v>
+        <x:v>1.35</x:v>
       </x:c>
       <x:c r="H70" t="n">
         <x:v>0.25</x:v>
@@ -3039,7 +3039,7 @@
       </x:c>
       <x:c r="E74" s="25"/>
       <x:c r="F74" s="26" t="n">
-        <x:v>1.075</x:v>
+        <x:v>1.01311</x:v>
       </x:c>
       <x:c r="G74" t="n">
         <x:v>1</x:v>
@@ -3075,7 +3075,7 @@
       </x:c>
       <x:c r="E75" s="25"/>
       <x:c r="F75" s="26" t="n">
-        <x:v>1.07805</x:v>
+        <x:v>0.99582</x:v>
       </x:c>
       <x:c r="G75" t="n">
         <x:v>1</x:v>
@@ -3111,7 +3111,7 @@
       </x:c>
       <x:c r="E76" s="25"/>
       <x:c r="F76" s="26" t="n">
-        <x:v>1.09987</x:v>
+        <x:v>1.08068</x:v>
       </x:c>
       <x:c r="G76" t="n">
         <x:v>1</x:v>
@@ -3147,7 +3147,7 @@
       </x:c>
       <x:c r="E77" s="25"/>
       <x:c r="F77" s="26" t="n">
-        <x:v>1.12799</x:v>
+        <x:v>1.1588</x:v>
       </x:c>
       <x:c r="G77" t="n">
         <x:v>1</x:v>
@@ -3183,7 +3183,7 @@
       </x:c>
       <x:c r="E78" s="25"/>
       <x:c r="F78" s="26" t="n">
-        <x:v>1.15906</x:v>
+        <x:v>1.04282</x:v>
       </x:c>
       <x:c r="G78" t="n">
         <x:v>1</x:v>
@@ -3219,7 +3219,7 @@
       </x:c>
       <x:c r="E79" s="25"/>
       <x:c r="F79" s="26" t="n">
-        <x:v>1.19147</x:v>
+        <x:v>1.17252</x:v>
       </x:c>
       <x:c r="G79" t="n">
         <x:v>1</x:v>
@@ -3255,7 +3255,7 @@
       </x:c>
       <x:c r="E80" s="25"/>
       <x:c r="F80" s="26" t="n">
-        <x:v>1.22436</x:v>
+        <x:v>1.30104</x:v>
       </x:c>
       <x:c r="G80" t="n">
         <x:v>1</x:v>
@@ -3291,7 +3291,7 @@
       </x:c>
       <x:c r="E81" s="25"/>
       <x:c r="F81" s="26" t="n">
-        <x:v>1.25719</x:v>
+        <x:v>1.39694</x:v>
       </x:c>
       <x:c r="G81" t="n">
         <x:v>1</x:v>
@@ -3327,7 +3327,7 @@
       </x:c>
       <x:c r="E82" s="25"/>
       <x:c r="F82" s="26" t="n">
-        <x:v>1.28966</x:v>
+        <x:v>1.23633</x:v>
       </x:c>
       <x:c r="G82" t="n">
         <x:v>1</x:v>
@@ -3363,7 +3363,7 @@
       </x:c>
       <x:c r="E83" s="25"/>
       <x:c r="F83" s="26" t="n">
-        <x:v>1.32157</x:v>
+        <x:v>1.36639</x:v>
       </x:c>
       <x:c r="G83" t="n">
         <x:v>1</x:v>
@@ -3399,7 +3399,7 @@
       </x:c>
       <x:c r="E84" s="25"/>
       <x:c r="F84" s="26" t="n">
-        <x:v>1.35281</x:v>
+        <x:v>1.58683</x:v>
       </x:c>
       <x:c r="G84" t="n">
         <x:v>1</x:v>
@@ -3437,7 +3437,7 @@
         <x:v>wave.604.announcement</x:v>
       </x:c>
       <x:c r="F85" s="26" t="n">
-        <x:v>1.3833</x:v>
+        <x:v>1.65996</x:v>
       </x:c>
       <x:c r="G85" t="n">
         <x:v>1</x:v>
@@ -3581,7 +3581,7 @@
       </x:c>
       <x:c r="E89" s="26"/>
       <x:c r="F89" s="26" t="n">
-        <x:v>1.15</x:v>
+        <x:v>1.0765</x:v>
       </x:c>
       <x:c r="G89" t="n">
         <x:v>1</x:v>
@@ -3617,7 +3617,7 @@
       </x:c>
       <x:c r="E90" s="26"/>
       <x:c r="F90" s="26" t="n">
-        <x:v>1.15326</x:v>
+        <x:v>1.06201</x:v>
       </x:c>
       <x:c r="G90" t="n">
         <x:v>1</x:v>
@@ -3653,7 +3653,7 @@
       </x:c>
       <x:c r="E91" s="26"/>
       <x:c r="F91" s="26" t="n">
-        <x:v>1.1766</x:v>
+        <x:v>1.14877</x:v>
       </x:c>
       <x:c r="G91" t="n">
         <x:v>1</x:v>
@@ -3689,7 +3689,7 @@
       </x:c>
       <x:c r="E92" s="26"/>
       <x:c r="F92" s="26" t="n">
-        <x:v>1.20669</x:v>
+        <x:v>1.2482</x:v>
       </x:c>
       <x:c r="G92" t="n">
         <x:v>1</x:v>
@@ -3725,7 +3725,7 @@
       </x:c>
       <x:c r="E93" s="26"/>
       <x:c r="F93" s="26" t="n">
-        <x:v>1.23992</x:v>
+        <x:v>1.13833</x:v>
       </x:c>
       <x:c r="G93" t="n">
         <x:v>1</x:v>
@@ -3761,7 +3761,7 @@
       </x:c>
       <x:c r="E94" s="26"/>
       <x:c r="F94" s="26" t="n">
-        <x:v>1.2746</x:v>
+        <x:v>1.23241</x:v>
       </x:c>
       <x:c r="G94" t="n">
         <x:v>1</x:v>
@@ -3797,7 +3797,7 @@
       </x:c>
       <x:c r="E95" s="26"/>
       <x:c r="F95" s="26" t="n">
-        <x:v>1.30978</x:v>
+        <x:v>1.38443</x:v>
       </x:c>
       <x:c r="G95" t="n">
         <x:v>1</x:v>
@@ -3833,7 +3833,7 @@
       </x:c>
       <x:c r="E96" s="26"/>
       <x:c r="F96" s="26" t="n">
-        <x:v>1.3449</x:v>
+        <x:v>1.50553</x:v>
       </x:c>
       <x:c r="G96" t="n">
         <x:v>1</x:v>
@@ -3869,7 +3869,7 @@
       </x:c>
       <x:c r="E97" s="26"/>
       <x:c r="F97" s="26" t="n">
-        <x:v>1.37964</x:v>
+        <x:v>1.37833</x:v>
       </x:c>
       <x:c r="G97" t="n">
         <x:v>1</x:v>
@@ -3905,7 +3905,7 @@
       </x:c>
       <x:c r="E98" s="26"/>
       <x:c r="F98" s="26" t="n">
-        <x:v>1.41377</x:v>
+        <x:v>1.44845</x:v>
       </x:c>
       <x:c r="G98" t="n">
         <x:v>1</x:v>
@@ -3941,7 +3941,7 @@
       </x:c>
       <x:c r="E99" s="26"/>
       <x:c r="F99" s="26" t="n">
-        <x:v>1.44719</x:v>
+        <x:v>1.70749</x:v>
       </x:c>
       <x:c r="G99" t="n">
         <x:v>1</x:v>
@@ -3979,7 +3979,7 @@
         <x:v>wave.704.announcement</x:v>
       </x:c>
       <x:c r="F100" s="26" t="n">
-        <x:v>1.47981</x:v>
+        <x:v>1.77577</x:v>
       </x:c>
       <x:c r="G100" t="n">
         <x:v>1</x:v>
@@ -4127,7 +4127,7 @@
       </x:c>
       <x:c r="E104" s="26"/>
       <x:c r="F104" s="26" t="n">
-        <x:v>1.24</x:v>
+        <x:v>1.18543</x:v>
       </x:c>
       <x:c r="G104" t="n">
         <x:v>1</x:v>
@@ -4163,7 +4163,7 @@
       </x:c>
       <x:c r="E105" s="26"/>
       <x:c r="F105" s="26" t="n">
-        <x:v>1.24351</x:v>
+        <x:v>1.24039</x:v>
       </x:c>
       <x:c r="G105" t="n">
         <x:v>1</x:v>
@@ -4199,7 +4199,7 @@
       </x:c>
       <x:c r="E106" s="26"/>
       <x:c r="F106" s="26" t="n">
-        <x:v>1.26868</x:v>
+        <x:v>1.19955</x:v>
       </x:c>
       <x:c r="G106" t="n">
         <x:v>1</x:v>
@@ -4235,7 +4235,7 @@
       </x:c>
       <x:c r="E107" s="26"/>
       <x:c r="F107" s="26" t="n">
-        <x:v>1.30112</x:v>
+        <x:v>1.347</x:v>
       </x:c>
       <x:c r="G107" t="n">
         <x:v>1</x:v>
@@ -4271,7 +4271,7 @@
       </x:c>
       <x:c r="E108" s="26"/>
       <x:c r="F108" s="26" t="n">
-        <x:v>1.33696</x:v>
+        <x:v>1.28841</x:v>
       </x:c>
       <x:c r="G108" t="n">
         <x:v>1</x:v>
@@ -4307,7 +4307,7 @@
       </x:c>
       <x:c r="E109" s="26"/>
       <x:c r="F109" s="26" t="n">
-        <x:v>1.37435</x:v>
+        <x:v>1.44666</x:v>
       </x:c>
       <x:c r="G109" t="n">
         <x:v>1</x:v>
@@ -4343,7 +4343,7 @@
       </x:c>
       <x:c r="E110"/>
       <x:c r="F110" t="n">
-        <x:v>1.41228</x:v>
+        <x:v>1.39259</x:v>
       </x:c>
       <x:c r="G110" t="n">
         <x:v>1</x:v>
@@ -4379,7 +4379,7 @@
       </x:c>
       <x:c r="E111"/>
       <x:c r="F111" t="n">
-        <x:v>1.45016</x:v>
+        <x:v>1.64629</x:v>
       </x:c>
       <x:c r="G111" t="n">
         <x:v>1</x:v>
@@ -4415,7 +4415,7 @@
       </x:c>
       <x:c r="E112"/>
       <x:c r="F112" t="n">
-        <x:v>1.48761</x:v>
+        <x:v>1.54084</x:v>
       </x:c>
       <x:c r="G112" t="n">
         <x:v>1</x:v>
@@ -4451,7 +4451,7 @@
       </x:c>
       <x:c r="E113"/>
       <x:c r="F113" t="n">
-        <x:v>1.52442</x:v>
+        <x:v>1.79751</x:v>
       </x:c>
       <x:c r="G113" t="n">
         <x:v>1</x:v>
@@ -4487,7 +4487,7 @@
       </x:c>
       <x:c r="E114"/>
       <x:c r="F114" t="n">
-        <x:v>1.56045</x:v>
+        <x:v>1.70259</x:v>
       </x:c>
       <x:c r="G114" t="n">
         <x:v>1</x:v>
@@ -4525,7 +4525,7 @@
         <x:v>wave.804.announcement</x:v>
       </x:c>
       <x:c r="F115" t="n">
-        <x:v>1.59562</x:v>
+        <x:v>2.04753</x:v>
       </x:c>
       <x:c r="G115" t="n">
         <x:v>1</x:v>
@@ -4669,7 +4669,7 @@
       </x:c>
       <x:c r="E119"/>
       <x:c r="F119" t="n">
-        <x:v>1.24</x:v>
+        <x:v>1.0881</x:v>
       </x:c>
       <x:c r="G119" t="n">
         <x:v>1</x:v>
@@ -4705,7 +4705,7 @@
       </x:c>
       <x:c r="E120"/>
       <x:c r="F120" t="n">
-        <x:v>1.24351</x:v>
+        <x:v>1.07645</x:v>
       </x:c>
       <x:c r="G120" t="n">
         <x:v>1</x:v>
@@ -4741,7 +4741,7 @@
       </x:c>
       <x:c r="E121"/>
       <x:c r="F121" t="n">
-        <x:v>1.26868</x:v>
+        <x:v>1.24439</x:v>
       </x:c>
       <x:c r="G121" t="n">
         <x:v>1</x:v>
@@ -4777,7 +4777,7 @@
       </x:c>
       <x:c r="E122"/>
       <x:c r="F122" t="n">
-        <x:v>1.30112</x:v>
+        <x:v>1.25052</x:v>
       </x:c>
       <x:c r="G122" t="n">
         <x:v>1</x:v>
@@ -4813,7 +4813,7 @@
       </x:c>
       <x:c r="E123"/>
       <x:c r="F123" t="n">
-        <x:v>1.33696</x:v>
+        <x:v>1.1497</x:v>
       </x:c>
       <x:c r="G123" t="n">
         <x:v>1</x:v>
@@ -4849,7 +4849,7 @@
       </x:c>
       <x:c r="E124"/>
       <x:c r="F124" t="n">
-        <x:v>1.37435</x:v>
+        <x:v>1.23861</x:v>
       </x:c>
       <x:c r="G124" t="n">
         <x:v>1</x:v>
@@ -4885,7 +4885,7 @@
       </x:c>
       <x:c r="E125"/>
       <x:c r="F125" t="n">
-        <x:v>1.41228</x:v>
+        <x:v>1.43017</x:v>
       </x:c>
       <x:c r="G125" t="n">
         <x:v>1</x:v>
@@ -4921,7 +4921,7 @@
       </x:c>
       <x:c r="E126"/>
       <x:c r="F126" t="n">
-        <x:v>1.45016</x:v>
+        <x:v>1.55584</x:v>
       </x:c>
       <x:c r="G126" t="n">
         <x:v>1</x:v>
@@ -4957,7 +4957,7 @@
       </x:c>
       <x:c r="E127"/>
       <x:c r="F127" t="n">
-        <x:v>1.48761</x:v>
+        <x:v>1.37522</x:v>
       </x:c>
       <x:c r="G127" t="n">
         <x:v>1</x:v>
@@ -4993,7 +4993,7 @@
       </x:c>
       <x:c r="E128"/>
       <x:c r="F128" t="n">
-        <x:v>1.52442</x:v>
+        <x:v>1.54755</x:v>
       </x:c>
       <x:c r="G128" t="n">
         <x:v>1</x:v>
@@ -5029,7 +5029,7 @@
       </x:c>
       <x:c r="E129"/>
       <x:c r="F129" t="n">
-        <x:v>1.56045</x:v>
+        <x:v>1.76362</x:v>
       </x:c>
       <x:c r="G129" t="n">
         <x:v>1</x:v>
@@ -5067,7 +5067,7 @@
         <x:v>wave.904.announcement</x:v>
       </x:c>
       <x:c r="F130" t="n">
-        <x:v>1.59562</x:v>
+        <x:v>1.91474</x:v>
       </x:c>
       <x:c r="G130" t="n">
         <x:v>1</x:v>
@@ -5211,7 +5211,7 @@
       </x:c>
       <x:c r="E134"/>
       <x:c r="F134" t="n">
-        <x:v>1.24</x:v>
+        <x:v>1.09499</x:v>
       </x:c>
       <x:c r="G134" t="n">
         <x:v>1</x:v>
@@ -5247,7 +5247,7 @@
       </x:c>
       <x:c r="E135"/>
       <x:c r="F135" t="n">
-        <x:v>1.32</x:v>
+        <x:v>1.2355</x:v>
       </x:c>
       <x:c r="G135" t="n">
         <x:v>1</x:v>
@@ -5283,7 +5283,7 @@
       </x:c>
       <x:c r="E136"/>
       <x:c r="F136" t="n">
-        <x:v>1.3025</x:v>
+        <x:v>1.00815</x:v>
       </x:c>
       <x:c r="G136" t="n">
         <x:v>1</x:v>
@@ -5319,7 +5319,7 @@
       </x:c>
       <x:c r="E137"/>
       <x:c r="F137" t="n">
-        <x:v>1.30319</x:v>
+        <x:v>1.13408</x:v>
       </x:c>
       <x:c r="G137" t="n">
         <x:v>1</x:v>
@@ -5355,7 +5355,7 @@
       </x:c>
       <x:c r="E138"/>
       <x:c r="F138" t="n">
-        <x:v>1.31121</x:v>
+        <x:v>1.2002</x:v>
       </x:c>
       <x:c r="G138" t="n">
         <x:v>1</x:v>
@@ -5391,7 +5391,7 @@
       </x:c>
       <x:c r="E139"/>
       <x:c r="F139" t="n">
-        <x:v>1.32344</x:v>
+        <x:v>1.13657</x:v>
       </x:c>
       <x:c r="G139" t="n">
         <x:v>1</x:v>
@@ -5427,7 +5427,7 @@
       </x:c>
       <x:c r="E140"/>
       <x:c r="F140" t="n">
-        <x:v>1.3383</x:v>
+        <x:v>1.15679</x:v>
       </x:c>
       <x:c r="G140" t="n">
         <x:v>1</x:v>
@@ -5463,7 +5463,7 @@
       </x:c>
       <x:c r="E141"/>
       <x:c r="F141" t="n">
-        <x:v>1.35484</x:v>
+        <x:v>1.36766</x:v>
       </x:c>
       <x:c r="G141" t="n">
         <x:v>1</x:v>
@@ -5499,7 +5499,7 @@
       </x:c>
       <x:c r="E142"/>
       <x:c r="F142" t="n">
-        <x:v>1.37244</x:v>
+        <x:v>1.46112</x:v>
       </x:c>
       <x:c r="G142" t="n">
         <x:v>1</x:v>
@@ -5535,7 +5535,7 @@
       </x:c>
       <x:c r="E143"/>
       <x:c r="F143" t="n">
-        <x:v>1.39071</x:v>
+        <x:v>1.37623</x:v>
       </x:c>
       <x:c r="G143" t="n">
         <x:v>1</x:v>
@@ -5571,7 +5571,7 @@
       </x:c>
       <x:c r="E144"/>
       <x:c r="F144" t="n">
-        <x:v>1.40936</x:v>
+        <x:v>1.48278</x:v>
       </x:c>
       <x:c r="G144" t="n">
         <x:v>1</x:v>
@@ -5607,7 +5607,7 @@
       </x:c>
       <x:c r="E145"/>
       <x:c r="F145" t="n">
-        <x:v>1.42818</x:v>
+        <x:v>1.71257</x:v>
       </x:c>
       <x:c r="G145" t="n">
         <x:v>1</x:v>
@@ -5643,7 +5643,7 @@
       </x:c>
       <x:c r="E146"/>
       <x:c r="F146" t="n">
-        <x:v>1.44704</x:v>
+        <x:v>1.85898</x:v>
       </x:c>
       <x:c r="G146" t="n">
         <x:v>1</x:v>
@@ -5679,7 +5679,7 @@
       </x:c>
       <x:c r="E147"/>
       <x:c r="F147" t="n">
-        <x:v>1.46583</x:v>
+        <x:v>1.77074</x:v>
       </x:c>
       <x:c r="G147" t="n">
         <x:v>1</x:v>
@@ -5715,7 +5715,7 @@
       </x:c>
       <x:c r="E148"/>
       <x:c r="F148" t="n">
-        <x:v>1.48448</x:v>
+        <x:v>1.84092</x:v>
       </x:c>
       <x:c r="G148" t="n">
         <x:v>1</x:v>
@@ -5751,7 +5751,7 @@
       </x:c>
       <x:c r="E149"/>
       <x:c r="F149" t="n">
-        <x:v>1.50293</x:v>
+        <x:v>2.17626</x:v>
       </x:c>
       <x:c r="G149" t="n">
         <x:v>1</x:v>
@@ -5789,10 +5789,10 @@
         <x:v>wave.1005.announcement</x:v>
       </x:c>
       <x:c r="F150" t="n">
-        <x:v>1.90142</x:v>
+        <x:v>2.37677</x:v>
       </x:c>
       <x:c r="G150" t="n">
-        <x:v>1</x:v>
+        <x:v>1.35</x:v>
       </x:c>
       <x:c r="H150" t="n">
         <x:v>0.375</x:v>
@@ -5935,7 +5935,7 @@
       </x:c>
       <x:c r="E154"/>
       <x:c r="F154" t="n">
-        <x:v>1.24</x:v>
+        <x:v>1.19936</x:v>
       </x:c>
       <x:c r="G154" t="n">
         <x:v>1</x:v>
@@ -5971,7 +5971,7 @@
       </x:c>
       <x:c r="E155"/>
       <x:c r="F155" t="n">
-        <x:v>1.24351</x:v>
+        <x:v>1.25394</x:v>
       </x:c>
       <x:c r="G155" t="n">
         <x:v>1</x:v>
@@ -6007,7 +6007,7 @@
       </x:c>
       <x:c r="E156"/>
       <x:c r="F156" t="n">
-        <x:v>1.26868</x:v>
+        <x:v>1.31104</x:v>
       </x:c>
       <x:c r="G156" t="n">
         <x:v>1</x:v>
@@ -6043,7 +6043,7 @@
       </x:c>
       <x:c r="E157"/>
       <x:c r="F157" t="n">
-        <x:v>1.30112</x:v>
+        <x:v>1.26854</x:v>
       </x:c>
       <x:c r="G157" t="n">
         <x:v>1</x:v>
@@ -6079,7 +6079,7 @@
       </x:c>
       <x:c r="E158"/>
       <x:c r="F158" t="n">
-        <x:v>1.33696</x:v>
+        <x:v>1.35423</x:v>
       </x:c>
       <x:c r="G158" t="n">
         <x:v>1</x:v>
@@ -6115,7 +6115,7 @@
       </x:c>
       <x:c r="E159"/>
       <x:c r="F159" t="n">
-        <x:v>1.37435</x:v>
+        <x:v>1.40381</x:v>
       </x:c>
       <x:c r="G159" t="n">
         <x:v>1</x:v>
@@ -6151,7 +6151,7 @@
       </x:c>
       <x:c r="E160"/>
       <x:c r="F160" t="n">
-        <x:v>1.41228</x:v>
+        <x:v>1.54733</x:v>
       </x:c>
       <x:c r="G160" t="n">
         <x:v>1</x:v>
@@ -6187,7 +6187,7 @@
       </x:c>
       <x:c r="E161"/>
       <x:c r="F161" t="n">
-        <x:v>1.45016</x:v>
+        <x:v>1.6756</x:v>
       </x:c>
       <x:c r="G161" t="n">
         <x:v>1</x:v>
@@ -6223,7 +6223,7 @@
       </x:c>
       <x:c r="E162"/>
       <x:c r="F162" t="n">
-        <x:v>1.48761</x:v>
+        <x:v>1.55022</x:v>
       </x:c>
       <x:c r="G162" t="n">
         <x:v>1</x:v>
@@ -6259,7 +6259,7 @@
       </x:c>
       <x:c r="E163"/>
       <x:c r="F163" t="n">
-        <x:v>1.52442</x:v>
+        <x:v>1.68874</x:v>
       </x:c>
       <x:c r="G163" t="n">
         <x:v>1</x:v>
@@ -6295,7 +6295,7 @@
       </x:c>
       <x:c r="E164"/>
       <x:c r="F164" t="n">
-        <x:v>1.56045</x:v>
+        <x:v>1.7715</x:v>
       </x:c>
       <x:c r="G164" t="n">
         <x:v>1</x:v>
@@ -6331,7 +6331,7 @@
       </x:c>
       <x:c r="E165"/>
       <x:c r="F165" t="n">
-        <x:v>1.59562</x:v>
+        <x:v>2.04746</x:v>
       </x:c>
       <x:c r="G165" t="n">
         <x:v>1</x:v>
@@ -6477,7 +6477,7 @@
       </x:c>
       <x:c r="E169"/>
       <x:c r="F169" t="n">
-        <x:v>1.24</x:v>
+        <x:v>1.19936</x:v>
       </x:c>
       <x:c r="G169" t="n">
         <x:v>1</x:v>
@@ -6513,7 +6513,7 @@
       </x:c>
       <x:c r="E170"/>
       <x:c r="F170" t="n">
-        <x:v>1.24351</x:v>
+        <x:v>1.25394</x:v>
       </x:c>
       <x:c r="G170" t="n">
         <x:v>1</x:v>
@@ -6549,7 +6549,7 @@
       </x:c>
       <x:c r="E171"/>
       <x:c r="F171" t="n">
-        <x:v>1.26868</x:v>
+        <x:v>1.31104</x:v>
       </x:c>
       <x:c r="G171" t="n">
         <x:v>1</x:v>
@@ -6585,7 +6585,7 @@
       </x:c>
       <x:c r="E172"/>
       <x:c r="F172" t="n">
-        <x:v>1.30112</x:v>
+        <x:v>1.26854</x:v>
       </x:c>
       <x:c r="G172" t="n">
         <x:v>1</x:v>
@@ -6621,7 +6621,7 @@
       </x:c>
       <x:c r="E173"/>
       <x:c r="F173" t="n">
-        <x:v>1.33696</x:v>
+        <x:v>1.35423</x:v>
       </x:c>
       <x:c r="G173" t="n">
         <x:v>1</x:v>
@@ -6657,7 +6657,7 @@
       </x:c>
       <x:c r="E174"/>
       <x:c r="F174" t="n">
-        <x:v>1.37435</x:v>
+        <x:v>1.40381</x:v>
       </x:c>
       <x:c r="G174" t="n">
         <x:v>1</x:v>
@@ -6693,7 +6693,7 @@
       </x:c>
       <x:c r="E175"/>
       <x:c r="F175" t="n">
-        <x:v>1.41228</x:v>
+        <x:v>1.54733</x:v>
       </x:c>
       <x:c r="G175" t="n">
         <x:v>1</x:v>
@@ -6729,7 +6729,7 @@
       </x:c>
       <x:c r="E176"/>
       <x:c r="F176" t="n">
-        <x:v>1.45016</x:v>
+        <x:v>1.6756</x:v>
       </x:c>
       <x:c r="G176" t="n">
         <x:v>1</x:v>
@@ -6765,7 +6765,7 @@
       </x:c>
       <x:c r="E177"/>
       <x:c r="F177" t="n">
-        <x:v>1.48761</x:v>
+        <x:v>1.55022</x:v>
       </x:c>
       <x:c r="G177" t="n">
         <x:v>1</x:v>
@@ -6801,7 +6801,7 @@
       </x:c>
       <x:c r="E178"/>
       <x:c r="F178" t="n">
-        <x:v>1.52442</x:v>
+        <x:v>1.68874</x:v>
       </x:c>
       <x:c r="G178" t="n">
         <x:v>1</x:v>
@@ -6837,7 +6837,7 @@
       </x:c>
       <x:c r="E179" s="25"/>
       <x:c r="F179" s="26" t="n">
-        <x:v>1.56045</x:v>
+        <x:v>1.7715</x:v>
       </x:c>
       <x:c r="G179" t="n">
         <x:v>1</x:v>
@@ -6873,7 +6873,7 @@
       </x:c>
       <x:c r="E180" s="25"/>
       <x:c r="F180" s="26" t="n">
-        <x:v>1.59562</x:v>
+        <x:v>2.04746</x:v>
       </x:c>
       <x:c r="G180" t="n">
         <x:v>1</x:v>
@@ -7019,7 +7019,7 @@
       </x:c>
       <x:c r="E184" s="25"/>
       <x:c r="F184" s="26" t="n">
-        <x:v>1.12</x:v>
+        <x:v>1.13972</x:v>
       </x:c>
       <x:c r="G184" t="n">
         <x:v>1</x:v>
@@ -7055,7 +7055,7 @@
       </x:c>
       <x:c r="E185" s="25"/>
       <x:c r="F185" s="26" t="n">
-        <x:v>1.12317</x:v>
+        <x:v>1.17141</x:v>
       </x:c>
       <x:c r="G185" t="n">
         <x:v>1</x:v>
@@ -7091,7 +7091,7 @@
       </x:c>
       <x:c r="E186" s="25"/>
       <x:c r="F186" s="26" t="n">
-        <x:v>1.14591</x:v>
+        <x:v>1.23828</x:v>
       </x:c>
       <x:c r="G186" t="n">
         <x:v>1</x:v>
@@ -7127,7 +7127,7 @@
       </x:c>
       <x:c r="E187" s="25"/>
       <x:c r="F187" s="26" t="n">
-        <x:v>1.17521</x:v>
+        <x:v>1.1863</x:v>
       </x:c>
       <x:c r="G187" t="n">
         <x:v>1</x:v>
@@ -7163,7 +7163,7 @@
       </x:c>
       <x:c r="E188" s="25"/>
       <x:c r="F188" s="26" t="n">
-        <x:v>1.20758</x:v>
+        <x:v>1.27832</x:v>
       </x:c>
       <x:c r="G188" t="n">
         <x:v>1</x:v>
@@ -7199,7 +7199,7 @@
       </x:c>
       <x:c r="E189" s="25"/>
       <x:c r="F189" s="26" t="n">
-        <x:v>1.24135</x:v>
+        <x:v>1.32691</x:v>
       </x:c>
       <x:c r="G189" t="n">
         <x:v>1</x:v>
@@ -7235,7 +7235,7 @@
       </x:c>
       <x:c r="E190" s="25"/>
       <x:c r="F190" s="26" t="n">
-        <x:v>1.27561</x:v>
+        <x:v>1.42676</x:v>
       </x:c>
       <x:c r="G190" t="n">
         <x:v>1</x:v>
@@ -7271,7 +7271,7 @@
       </x:c>
       <x:c r="E191" s="25"/>
       <x:c r="F191" s="26" t="n">
-        <x:v>1.30982</x:v>
+        <x:v>1.5324</x:v>
       </x:c>
       <x:c r="G191" t="n">
         <x:v>1</x:v>
@@ -7307,7 +7307,7 @@
       </x:c>
       <x:c r="E192" s="25"/>
       <x:c r="F192" s="26" t="n">
-        <x:v>1.34365</x:v>
+        <x:v>1.41453</x:v>
       </x:c>
       <x:c r="G192" t="n">
         <x:v>1</x:v>
@@ -7343,7 +7343,7 @@
       </x:c>
       <x:c r="E193" s="25"/>
       <x:c r="F193" s="26" t="n">
-        <x:v>1.37689</x:v>
+        <x:v>1.53683</x:v>
       </x:c>
       <x:c r="G193" t="n">
         <x:v>1</x:v>
@@ -7379,7 +7379,7 @@
       </x:c>
       <x:c r="E194" s="25"/>
       <x:c r="F194" s="26" t="n">
-        <x:v>1.40944</x:v>
+        <x:v>1.60748</x:v>
       </x:c>
       <x:c r="G194" t="n">
         <x:v>1</x:v>
@@ -7415,7 +7415,7 @@
       </x:c>
       <x:c r="E195" s="25"/>
       <x:c r="F195" s="26" t="n">
-        <x:v>1.44121</x:v>
+        <x:v>1.87014</x:v>
       </x:c>
       <x:c r="G195" t="n">
         <x:v>1</x:v>
@@ -7561,7 +7561,7 @@
       </x:c>
       <x:c r="E199" s="25"/>
       <x:c r="F199" s="26" t="n">
-        <x:v>1.24</x:v>
+        <x:v>1.19744</x:v>
       </x:c>
       <x:c r="G199" t="n">
         <x:v>1</x:v>
@@ -7597,7 +7597,7 @@
       </x:c>
       <x:c r="E200" s="25"/>
       <x:c r="F200" s="26" t="n">
-        <x:v>1.24351</x:v>
+        <x:v>1.25123</x:v>
       </x:c>
       <x:c r="G200" t="n">
         <x:v>1</x:v>
@@ -7633,7 +7633,7 @@
       </x:c>
       <x:c r="E201" s="25"/>
       <x:c r="F201" s="26" t="n">
-        <x:v>1.26868</x:v>
+        <x:v>1.30774</x:v>
       </x:c>
       <x:c r="G201" t="n">
         <x:v>1</x:v>
@@ -7669,7 +7669,7 @@
       </x:c>
       <x:c r="E202" s="25"/>
       <x:c r="F202" s="26" t="n">
-        <x:v>1.30112</x:v>
+        <x:v>1.25064</x:v>
       </x:c>
       <x:c r="G202" t="n">
         <x:v>1</x:v>
@@ -7705,7 +7705,7 @@
       </x:c>
       <x:c r="E203" s="25"/>
       <x:c r="F203" s="26" t="n">
-        <x:v>1.33696</x:v>
+        <x:v>1.36719</x:v>
       </x:c>
       <x:c r="G203" t="n">
         <x:v>1</x:v>
@@ -7741,7 +7741,7 @@
       </x:c>
       <x:c r="E204" s="25"/>
       <x:c r="F204" s="26" t="n">
-        <x:v>1.37435</x:v>
+        <x:v>1.40231</x:v>
       </x:c>
       <x:c r="G204" t="n">
         <x:v>1</x:v>
@@ -7777,7 +7777,7 @@
       </x:c>
       <x:c r="E205" s="25"/>
       <x:c r="F205" s="26" t="n">
-        <x:v>1.41228</x:v>
+        <x:v>1.54389</x:v>
       </x:c>
       <x:c r="G205" t="n">
         <x:v>1</x:v>
@@ -7813,7 +7813,7 @@
       </x:c>
       <x:c r="E206" s="25"/>
       <x:c r="F206" s="26" t="n">
-        <x:v>1.45016</x:v>
+        <x:v>1.67772</x:v>
       </x:c>
       <x:c r="G206" t="n">
         <x:v>1</x:v>
@@ -7849,7 +7849,7 @@
       </x:c>
       <x:c r="E207" s="25"/>
       <x:c r="F207" s="26" t="n">
-        <x:v>1.48761</x:v>
+        <x:v>1.55052</x:v>
       </x:c>
       <x:c r="G207" t="n">
         <x:v>1</x:v>
@@ -7885,7 +7885,7 @@
       </x:c>
       <x:c r="E208" s="25"/>
       <x:c r="F208" s="26" t="n">
-        <x:v>1.52442</x:v>
+        <x:v>1.68809</x:v>
       </x:c>
       <x:c r="G208" t="n">
         <x:v>1</x:v>
@@ -7921,7 +7921,7 @@
       </x:c>
       <x:c r="E209" s="25"/>
       <x:c r="F209" s="26" t="n">
-        <x:v>1.56045</x:v>
+        <x:v>1.77103</x:v>
       </x:c>
       <x:c r="G209" t="n">
         <x:v>1</x:v>
@@ -7957,7 +7957,7 @@
       </x:c>
       <x:c r="E210" s="25"/>
       <x:c r="F210" s="26" t="n">
-        <x:v>1.59562</x:v>
+        <x:v>2.067</x:v>
       </x:c>
       <x:c r="G210" t="n">
         <x:v>1</x:v>
@@ -8105,7 +8105,7 @@
       </x:c>
       <x:c r="E214" s="25"/>
       <x:c r="F214" s="26" t="n">
-        <x:v>1.39</x:v>
+        <x:v>1.30633</x:v>
       </x:c>
       <x:c r="G214" t="n">
         <x:v>1</x:v>
@@ -8141,7 +8141,7 @@
       </x:c>
       <x:c r="E215" s="25"/>
       <x:c r="F215" s="26" t="n">
-        <x:v>1.52</x:v>
+        <x:v>1.62215</x:v>
       </x:c>
       <x:c r="G215" t="n">
         <x:v>1</x:v>
@@ -8177,7 +8177,7 @@
       </x:c>
       <x:c r="E216" s="25"/>
       <x:c r="F216" s="26" t="n">
-        <x:v>1.49985</x:v>
+        <x:v>1.49024</x:v>
       </x:c>
       <x:c r="G216" t="n">
         <x:v>1</x:v>
@@ -8213,7 +8213,7 @@
       </x:c>
       <x:c r="E217" s="25"/>
       <x:c r="F217" s="26" t="n">
-        <x:v>1.50064</x:v>
+        <x:v>1.36418</x:v>
       </x:c>
       <x:c r="G217" t="n">
         <x:v>1</x:v>
@@ -8249,7 +8249,7 @@
       </x:c>
       <x:c r="E218" s="25"/>
       <x:c r="F218" s="26" t="n">
-        <x:v>1.50988</x:v>
+        <x:v>1.42158</x:v>
       </x:c>
       <x:c r="G218" t="n">
         <x:v>1</x:v>
@@ -8285,7 +8285,7 @@
       </x:c>
       <x:c r="E219" s="25"/>
       <x:c r="F219" s="26" t="n">
-        <x:v>1.52397</x:v>
+        <x:v>1.60136</x:v>
       </x:c>
       <x:c r="G219" t="n">
         <x:v>1</x:v>
@@ -8321,7 +8321,7 @@
       </x:c>
       <x:c r="E220" s="25"/>
       <x:c r="F220" s="26" t="n">
-        <x:v>1.54107</x:v>
+        <x:v>1.54223</x:v>
       </x:c>
       <x:c r="G220" t="n">
         <x:v>1</x:v>
@@ -8357,7 +8357,7 @@
       </x:c>
       <x:c r="E221" s="25"/>
       <x:c r="F221" s="26" t="n">
-        <x:v>1.56012</x:v>
+        <x:v>1.76409</x:v>
       </x:c>
       <x:c r="G221" t="n">
         <x:v>1</x:v>
@@ -8393,7 +8393,7 @@
       </x:c>
       <x:c r="E222" s="25"/>
       <x:c r="F222" s="26" t="n">
-        <x:v>1.58039</x:v>
+        <x:v>1.77577</x:v>
       </x:c>
       <x:c r="G222" t="n">
         <x:v>1</x:v>
@@ -8429,7 +8429,7 @@
       </x:c>
       <x:c r="E223" s="25"/>
       <x:c r="F223" s="26" t="n">
-        <x:v>1.60143</x:v>
+        <x:v>1.89545</x:v>
       </x:c>
       <x:c r="G223" t="n">
         <x:v>1</x:v>
@@ -8465,7 +8465,7 @@
       </x:c>
       <x:c r="E224" s="25"/>
       <x:c r="F224" s="26" t="n">
-        <x:v>1.6229</x:v>
+        <x:v>2.12881</x:v>
       </x:c>
       <x:c r="G224" t="n">
         <x:v>1</x:v>
@@ -8501,7 +8501,7 @@
       </x:c>
       <x:c r="E225" s="25"/>
       <x:c r="F225" s="26" t="n">
-        <x:v>1.64457</x:v>
+        <x:v>2.07778</x:v>
       </x:c>
       <x:c r="G225" t="n">
         <x:v>1</x:v>
@@ -8537,7 +8537,7 @@
       </x:c>
       <x:c r="E226" s="25"/>
       <x:c r="F226" s="26" t="n">
-        <x:v>1.66629</x:v>
+        <x:v>2.38533</x:v>
       </x:c>
       <x:c r="G226" t="n">
         <x:v>1</x:v>
@@ -8573,7 +8573,7 @@
       </x:c>
       <x:c r="E227" s="25"/>
       <x:c r="F227" s="26" t="n">
-        <x:v>1.68793</x:v>
+        <x:v>2.45923</x:v>
       </x:c>
       <x:c r="G227" t="n">
         <x:v>1</x:v>
@@ -8609,7 +8609,7 @@
       </x:c>
       <x:c r="E228" s="25"/>
       <x:c r="F228" s="26" t="n">
-        <x:v>1.7094</x:v>
+        <x:v>2.6647</x:v>
       </x:c>
       <x:c r="G228" t="n">
         <x:v>1</x:v>
@@ -8645,7 +8645,7 @@
       </x:c>
       <x:c r="E229" s="25"/>
       <x:c r="F229" s="26" t="n">
-        <x:v>1.73064</x:v>
+        <x:v>3.02546</x:v>
       </x:c>
       <x:c r="G229" t="n">
         <x:v>1</x:v>
@@ -8683,10 +8683,10 @@
         <x:v>wave.1505.announcement</x:v>
       </x:c>
       <x:c r="F230" s="26" t="n">
-        <x:v>2.18952</x:v>
+        <x:v>2.84638</x:v>
       </x:c>
       <x:c r="G230" t="n">
-        <x:v>1</x:v>
+        <x:v>1.35</x:v>
       </x:c>
       <x:c r="H230" t="n">
         <x:v>0.525</x:v>
@@ -8829,7 +8829,7 @@
       </x:c>
       <x:c r="E234" s="25"/>
       <x:c r="F234" s="26" t="n">
-        <x:v>1.39</x:v>
+        <x:v>1.27307</x:v>
       </x:c>
       <x:c r="G234" t="n">
         <x:v>1</x:v>
@@ -8865,7 +8865,7 @@
       </x:c>
       <x:c r="E235" s="25"/>
       <x:c r="F235" s="26" t="n">
-        <x:v>1.39394</x:v>
+        <x:v>1.35032</x:v>
       </x:c>
       <x:c r="G235" t="n">
         <x:v>1</x:v>
@@ -8901,7 +8901,7 @@
       </x:c>
       <x:c r="E236" s="25"/>
       <x:c r="F236" s="26" t="n">
-        <x:v>1.42215</x:v>
+        <x:v>1.42846</x:v>
       </x:c>
       <x:c r="G236" t="n">
         <x:v>1</x:v>
@@ -8937,7 +8937,7 @@
       </x:c>
       <x:c r="E237" s="25"/>
       <x:c r="F237" s="26" t="n">
-        <x:v>1.45852</x:v>
+        <x:v>1.35544</x:v>
       </x:c>
       <x:c r="G237" t="n">
         <x:v>1</x:v>
@@ -8973,7 +8973,7 @@
       </x:c>
       <x:c r="E238" s="25"/>
       <x:c r="F238" s="26" t="n">
-        <x:v>1.49869</x:v>
+        <x:v>1.50732</x:v>
       </x:c>
       <x:c r="G238" t="n">
         <x:v>1</x:v>
@@ -9009,7 +9009,7 @@
       </x:c>
       <x:c r="E239" s="25"/>
       <x:c r="F239" s="26" t="n">
-        <x:v>1.5406</x:v>
+        <x:v>1.6034</x:v>
       </x:c>
       <x:c r="G239" t="n">
         <x:v>1</x:v>
@@ -9045,7 +9045,7 @@
       </x:c>
       <x:c r="E240" s="25"/>
       <x:c r="F240" s="26" t="n">
-        <x:v>1.58312</x:v>
+        <x:v>1.73713</x:v>
       </x:c>
       <x:c r="G240" t="n">
         <x:v>1</x:v>
@@ -9081,7 +9081,7 @@
       </x:c>
       <x:c r="E241" s="25"/>
       <x:c r="F241" s="26" t="n">
-        <x:v>1.62558</x:v>
+        <x:v>1.8826</x:v>
       </x:c>
       <x:c r="G241" t="n">
         <x:v>1</x:v>
@@ -9117,7 +9117,7 @@
       </x:c>
       <x:c r="E242" s="25"/>
       <x:c r="F242" s="26" t="n">
-        <x:v>1.66756</x:v>
+        <x:v>1.95247</x:v>
       </x:c>
       <x:c r="G242" t="n">
         <x:v>1</x:v>
@@ -9153,7 +9153,7 @@
       </x:c>
       <x:c r="E243" s="25"/>
       <x:c r="F243" s="26" t="n">
-        <x:v>1.70882</x:v>
+        <x:v>1.92577</x:v>
       </x:c>
       <x:c r="G243" t="n">
         <x:v>1</x:v>
@@ -9189,7 +9189,7 @@
       </x:c>
       <x:c r="E244" s="25"/>
       <x:c r="F244" s="26" t="n">
-        <x:v>1.74921</x:v>
+        <x:v>2.15446</x:v>
       </x:c>
       <x:c r="G244" t="n">
         <x:v>1</x:v>
@@ -9225,7 +9225,7 @@
       </x:c>
       <x:c r="E245" s="25"/>
       <x:c r="F245" s="26" t="n">
-        <x:v>1.78864</x:v>
+        <x:v>2.32523</x:v>
       </x:c>
       <x:c r="G245" t="n">
         <x:v>1</x:v>
@@ -9371,7 +9371,7 @@
       </x:c>
       <x:c r="E249" s="25"/>
       <x:c r="F249" s="26" t="n">
-        <x:v>1.39</x:v>
+        <x:v>1.2714</x:v>
       </x:c>
       <x:c r="G249" t="n">
         <x:v>1</x:v>
@@ -9407,7 +9407,7 @@
       </x:c>
       <x:c r="E250" s="25"/>
       <x:c r="F250" s="26" t="n">
-        <x:v>1.25454</x:v>
+        <x:v>1.34748</x:v>
       </x:c>
       <x:c r="G250" t="n">
         <x:v>1</x:v>
@@ -9443,7 +9443,7 @@
       </x:c>
       <x:c r="E251" s="25"/>
       <x:c r="F251" s="26" t="n">
-        <x:v>1.32734</x:v>
+        <x:v>1.42461</x:v>
       </x:c>
       <x:c r="G251" t="n">
         <x:v>1</x:v>
@@ -9479,7 +9479,7 @@
       </x:c>
       <x:c r="E252" s="25"/>
       <x:c r="F252" s="26" t="n">
-        <x:v>1.4099</x:v>
+        <x:v>1.37015</x:v>
       </x:c>
       <x:c r="G252" t="n">
         <x:v>1</x:v>
@@ -9515,7 +9515,7 @@
       </x:c>
       <x:c r="E253" s="25"/>
       <x:c r="F253" s="26" t="n">
-        <x:v>1.49869</x:v>
+        <x:v>1.50367</x:v>
       </x:c>
       <x:c r="G253" t="n">
         <x:v>1</x:v>
@@ -9551,7 +9551,7 @@
       </x:c>
       <x:c r="E254" s="25"/>
       <x:c r="F254" s="26" t="n">
-        <x:v>1.5406</x:v>
+        <x:v>1.59897</x:v>
       </x:c>
       <x:c r="G254" t="n">
         <x:v>1</x:v>
@@ -9587,7 +9587,7 @@
       </x:c>
       <x:c r="E255" s="25"/>
       <x:c r="F255" s="26" t="n">
-        <x:v>1.58312</x:v>
+        <x:v>1.73134</x:v>
       </x:c>
       <x:c r="G255" t="n">
         <x:v>1</x:v>
@@ -9623,7 +9623,7 @@
       </x:c>
       <x:c r="E256" s="25"/>
       <x:c r="F256" s="26" t="n">
-        <x:v>1.62558</x:v>
+        <x:v>1.88254</x:v>
       </x:c>
       <x:c r="G256" t="n">
         <x:v>1</x:v>
@@ -9659,7 +9659,7 @@
       </x:c>
       <x:c r="E257" s="25"/>
       <x:c r="F257" s="26" t="n">
-        <x:v>1.66756</x:v>
+        <x:v>1.94488</x:v>
       </x:c>
       <x:c r="G257" t="n">
         <x:v>1</x:v>
@@ -9695,7 +9695,7 @@
       </x:c>
       <x:c r="E258" s="25"/>
       <x:c r="F258" s="26" t="n">
-        <x:v>1.70882</x:v>
+        <x:v>1.92973</x:v>
       </x:c>
       <x:c r="G258" t="n">
         <x:v>1</x:v>
@@ -9731,7 +9731,7 @@
       </x:c>
       <x:c r="E259" s="25"/>
       <x:c r="F259" s="26" t="n">
-        <x:v>1.74921</x:v>
+        <x:v>2.12993</x:v>
       </x:c>
       <x:c r="G259" t="n">
         <x:v>1</x:v>
@@ -9767,7 +9767,7 @@
       </x:c>
       <x:c r="E260" s="25"/>
       <x:c r="F260" s="26" t="n">
-        <x:v>1.78864</x:v>
+        <x:v>2.32523</x:v>
       </x:c>
       <x:c r="G260" t="n">
         <x:v>1</x:v>
@@ -9913,7 +9913,7 @@
       </x:c>
       <x:c r="E264" s="25"/>
       <x:c r="F264" s="26" t="n">
-        <x:v>1.39</x:v>
+        <x:v>1.2714</x:v>
       </x:c>
       <x:c r="G264" t="n">
         <x:v>1</x:v>
@@ -9949,7 +9949,7 @@
       </x:c>
       <x:c r="E265" s="25"/>
       <x:c r="F265" s="26" t="n">
-        <x:v>1.39394</x:v>
+        <x:v>1.34748</x:v>
       </x:c>
       <x:c r="G265" t="n">
         <x:v>1</x:v>
@@ -9985,7 +9985,7 @@
       </x:c>
       <x:c r="E266" s="25"/>
       <x:c r="F266" s="26" t="n">
-        <x:v>1.42215</x:v>
+        <x:v>1.42461</x:v>
       </x:c>
       <x:c r="G266" t="n">
         <x:v>1</x:v>
@@ -10021,7 +10021,7 @@
       </x:c>
       <x:c r="E267" s="25"/>
       <x:c r="F267" s="26" t="n">
-        <x:v>1.45852</x:v>
+        <x:v>1.37015</x:v>
       </x:c>
       <x:c r="G267" t="n">
         <x:v>1</x:v>
@@ -10057,7 +10057,7 @@
       </x:c>
       <x:c r="E268" s="25"/>
       <x:c r="F268" s="26" t="n">
-        <x:v>1.49869</x:v>
+        <x:v>1.50367</x:v>
       </x:c>
       <x:c r="G268" t="n">
         <x:v>1</x:v>
@@ -10093,7 +10093,7 @@
       </x:c>
       <x:c r="E269" s="25"/>
       <x:c r="F269" s="26" t="n">
-        <x:v>1.5406</x:v>
+        <x:v>1.59897</x:v>
       </x:c>
       <x:c r="G269" t="n">
         <x:v>1</x:v>
@@ -10129,7 +10129,7 @@
       </x:c>
       <x:c r="E270" s="25"/>
       <x:c r="F270" s="26" t="n">
-        <x:v>1.58312</x:v>
+        <x:v>1.73134</x:v>
       </x:c>
       <x:c r="G270" t="n">
         <x:v>1</x:v>
@@ -10165,7 +10165,7 @@
       </x:c>
       <x:c r="E271" s="25"/>
       <x:c r="F271" s="26" t="n">
-        <x:v>1.62558</x:v>
+        <x:v>1.88254</x:v>
       </x:c>
       <x:c r="G271" t="n">
         <x:v>1</x:v>
@@ -10201,7 +10201,7 @@
       </x:c>
       <x:c r="E272" s="25"/>
       <x:c r="F272" s="26" t="n">
-        <x:v>1.66756</x:v>
+        <x:v>1.94488</x:v>
       </x:c>
       <x:c r="G272" t="n">
         <x:v>1</x:v>
@@ -10237,7 +10237,7 @@
       </x:c>
       <x:c r="E273" s="25"/>
       <x:c r="F273" s="26" t="n">
-        <x:v>1.70882</x:v>
+        <x:v>1.92973</x:v>
       </x:c>
       <x:c r="G273" t="n">
         <x:v>1</x:v>
@@ -10273,7 +10273,7 @@
       </x:c>
       <x:c r="E274" s="25"/>
       <x:c r="F274" s="26" t="n">
-        <x:v>1.74921</x:v>
+        <x:v>2.12993</x:v>
       </x:c>
       <x:c r="G274" t="n">
         <x:v>1</x:v>
@@ -10309,7 +10309,7 @@
       </x:c>
       <x:c r="E275" s="25"/>
       <x:c r="F275" s="26" t="n">
-        <x:v>1.78864</x:v>
+        <x:v>2.32523</x:v>
       </x:c>
       <x:c r="G275" t="n">
         <x:v>1</x:v>
@@ -10455,7 +10455,7 @@
       </x:c>
       <x:c r="E279" s="25"/>
       <x:c r="F279" s="26" t="n">
-        <x:v>1.105</x:v>
+        <x:v>1.12783</x:v>
       </x:c>
       <x:c r="G279" t="n">
         <x:v>1</x:v>
@@ -10491,7 +10491,7 @@
       </x:c>
       <x:c r="E280" s="25"/>
       <x:c r="F280" s="26" t="n">
-        <x:v>1.10813</x:v>
+        <x:v>1.1727</x:v>
       </x:c>
       <x:c r="G280" t="n">
         <x:v>1</x:v>
@@ -10527,7 +10527,7 @@
       </x:c>
       <x:c r="E281" s="25"/>
       <x:c r="F281" s="26" t="n">
-        <x:v>1.13056</x:v>
+        <x:v>1.23783</x:v>
       </x:c>
       <x:c r="G281" t="n">
         <x:v>1</x:v>
@@ -10563,7 +10563,7 @@
       </x:c>
       <x:c r="E282" s="25"/>
       <x:c r="F282" s="26" t="n">
-        <x:v>1.15947</x:v>
+        <x:v>1.21619</x:v>
       </x:c>
       <x:c r="G282" t="n">
         <x:v>1</x:v>
@@ -10599,7 +10599,7 @@
       </x:c>
       <x:c r="E283" s="25"/>
       <x:c r="F283" s="26" t="n">
-        <x:v>1.1914</x:v>
+        <x:v>1.27785</x:v>
       </x:c>
       <x:c r="G283" t="n">
         <x:v>1</x:v>
@@ -10635,7 +10635,7 @@
       </x:c>
       <x:c r="E284" s="25"/>
       <x:c r="F284" s="26" t="n">
-        <x:v>1.22472</x:v>
+        <x:v>1.36669</x:v>
       </x:c>
       <x:c r="G284" t="n">
         <x:v>1</x:v>
@@ -10671,7 +10671,7 @@
       </x:c>
       <x:c r="E285" s="25"/>
       <x:c r="F285" s="26" t="n">
-        <x:v>1.25853</x:v>
+        <x:v>1.46069</x:v>
       </x:c>
       <x:c r="G285" t="n">
         <x:v>1</x:v>
@@ -10707,7 +10707,7 @@
       </x:c>
       <x:c r="E286" s="25"/>
       <x:c r="F286" s="26" t="n">
-        <x:v>1.29228</x:v>
+        <x:v>1.56686</x:v>
       </x:c>
       <x:c r="G286" t="n">
         <x:v>1</x:v>
@@ -10743,7 +10743,7 @@
       </x:c>
       <x:c r="E287" s="25"/>
       <x:c r="F287" s="26" t="n">
-        <x:v>1.32565</x:v>
+        <x:v>1.64335</x:v>
       </x:c>
       <x:c r="G287" t="n">
         <x:v>1</x:v>
@@ -10779,7 +10779,7 @@
       </x:c>
       <x:c r="E288" s="25"/>
       <x:c r="F288" s="26" t="n">
-        <x:v>1.35845</x:v>
+        <x:v>1.6001</x:v>
       </x:c>
       <x:c r="G288" t="n">
         <x:v>1</x:v>
@@ -10815,7 +10815,7 @@
       </x:c>
       <x:c r="E289" s="25"/>
       <x:c r="F289" s="26" t="n">
-        <x:v>1.39056</x:v>
+        <x:v>1.70822</x:v>
       </x:c>
       <x:c r="G289" t="n">
         <x:v>1</x:v>
@@ -10851,7 +10851,7 @@
       </x:c>
       <x:c r="E290" s="25"/>
       <x:c r="F290" s="26" t="n">
-        <x:v>1.42191</x:v>
+        <x:v>1.84848</x:v>
       </x:c>
       <x:c r="G290" t="n">
         <x:v>1</x:v>
@@ -11001,7 +11001,7 @@
       </x:c>
       <x:c r="E294" s="25"/>
       <x:c r="F294" s="26" t="n">
-        <x:v>1.39</x:v>
+        <x:v>1.27667</x:v>
       </x:c>
       <x:c r="G294" t="n">
         <x:v>1</x:v>
@@ -11037,7 +11037,7 @@
       </x:c>
       <x:c r="E295" s="25"/>
       <x:c r="F295" s="26" t="n">
-        <x:v>1.52</x:v>
+        <x:v>1.56166</x:v>
       </x:c>
       <x:c r="G295" t="n">
         <x:v>1</x:v>
@@ -11073,7 +11073,7 @@
       </x:c>
       <x:c r="E296" s="25"/>
       <x:c r="F296" s="26" t="n">
-        <x:v>1.49985</x:v>
+        <x:v>1.35999</x:v>
       </x:c>
       <x:c r="G296" t="n">
         <x:v>1</x:v>
@@ -11109,7 +11109,7 @@
       </x:c>
       <x:c r="E297" s="25"/>
       <x:c r="F297" s="26" t="n">
-        <x:v>1.50064</x:v>
+        <x:v>1.36972</x:v>
       </x:c>
       <x:c r="G297" t="n">
         <x:v>1</x:v>
@@ -11145,7 +11145,7 @@
       </x:c>
       <x:c r="E298" s="25"/>
       <x:c r="F298" s="26" t="n">
-        <x:v>1.50988</x:v>
+        <x:v>1.4135</x:v>
       </x:c>
       <x:c r="G298" t="n">
         <x:v>1</x:v>
@@ -11181,7 +11181,7 @@
       </x:c>
       <x:c r="E299" s="25"/>
       <x:c r="F299" s="26" t="n">
-        <x:v>1.52397</x:v>
+        <x:v>1.55153</x:v>
       </x:c>
       <x:c r="G299" t="n">
         <x:v>1</x:v>
@@ -11217,7 +11217,7 @@
       </x:c>
       <x:c r="E300" s="25"/>
       <x:c r="F300" s="26" t="n">
-        <x:v>1.54107</x:v>
+        <x:v>1.53606</x:v>
       </x:c>
       <x:c r="G300" t="n">
         <x:v>1</x:v>
@@ -11253,7 +11253,7 @@
       </x:c>
       <x:c r="E301" s="25"/>
       <x:c r="F301" s="26" t="n">
-        <x:v>1.56012</x:v>
+        <x:v>1.67988</x:v>
       </x:c>
       <x:c r="G301" t="n">
         <x:v>1</x:v>
@@ -11289,7 +11289,7 @@
       </x:c>
       <x:c r="E302" s="25"/>
       <x:c r="F302" s="26" t="n">
-        <x:v>1.58039</x:v>
+        <x:v>1.81799</x:v>
       </x:c>
       <x:c r="G302" t="n">
         <x:v>1</x:v>
@@ -11325,7 +11325,7 @@
       </x:c>
       <x:c r="E303" s="25"/>
       <x:c r="F303" s="26" t="n">
-        <x:v>1.60143</x:v>
+        <x:v>1.84189</x:v>
       </x:c>
       <x:c r="G303" t="n">
         <x:v>1</x:v>
@@ -11361,7 +11361,7 @@
       </x:c>
       <x:c r="E304" s="25"/>
       <x:c r="F304" s="26" t="n">
-        <x:v>1.6229</x:v>
+        <x:v>1.96026</x:v>
       </x:c>
       <x:c r="G304" t="n">
         <x:v>1</x:v>
@@ -11397,7 +11397,7 @@
       </x:c>
       <x:c r="E305" s="25"/>
       <x:c r="F305" s="26" t="n">
-        <x:v>1.64457</x:v>
+        <x:v>2.19974</x:v>
       </x:c>
       <x:c r="G305" t="n">
         <x:v>1</x:v>
@@ -11433,7 +11433,7 @@
       </x:c>
       <x:c r="E306" s="25"/>
       <x:c r="F306" s="26" t="n">
-        <x:v>1.66629</x:v>
+        <x:v>2.19255</x:v>
       </x:c>
       <x:c r="G306" t="n">
         <x:v>1</x:v>
@@ -11469,7 +11469,7 @@
       </x:c>
       <x:c r="E307" s="25"/>
       <x:c r="F307" s="26" t="n">
-        <x:v>1.68793</x:v>
+        <x:v>2.39462</x:v>
       </x:c>
       <x:c r="G307" t="n">
         <x:v>1</x:v>
@@ -11505,7 +11505,7 @@
       </x:c>
       <x:c r="E308" s="25"/>
       <x:c r="F308" s="26" t="n">
-        <x:v>1.7094</x:v>
+        <x:v>2.61751</x:v>
       </x:c>
       <x:c r="G308" t="n">
         <x:v>1</x:v>
@@ -11541,7 +11541,7 @@
       </x:c>
       <x:c r="E309" s="25"/>
       <x:c r="F309" s="26" t="n">
-        <x:v>1.73064</x:v>
+        <x:v>2.6922</x:v>
       </x:c>
       <x:c r="G309" t="n">
         <x:v>1</x:v>
@@ -11579,10 +11579,10 @@
         <x:v>wave.2005.announcement</x:v>
       </x:c>
       <x:c r="F310" s="26" t="n">
-        <x:v>2.18952</x:v>
+        <x:v>2.84638</x:v>
       </x:c>
       <x:c r="G310" t="n">
-        <x:v>1</x:v>
+        <x:v>1.35</x:v>
       </x:c>
       <x:c r="H310" t="n">
         <x:v>0.525</x:v>

--- a/design/tables/Wave.xlsx
+++ b/design/tables/Wave.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wave" sheetId="1" r:id="R20440da37a864a13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wave" sheetId="1" r:id="R4e20855e2122418c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1667,10 +1667,10 @@
       </x:c>
       <x:c r="E36" s="25" t="str"/>
       <x:c r="F36" s="26" t="n">
-        <x:v>1.06</x:v>
+        <x:v>0.583</x:v>
       </x:c>
       <x:c r="G36" t="n">
-        <x:v>1.03773585</x:v>
+        <x:v>1.88679245</x:v>
       </x:c>
       <x:c r="H36" t="n">
         <x:v>0</x:v>
@@ -1703,10 +1703,10 @@
       </x:c>
       <x:c r="E37" s="25" t="str"/>
       <x:c r="F37" s="26" t="n">
-        <x:v>1.1265</x:v>
+        <x:v>0.6759</x:v>
       </x:c>
       <x:c r="G37" t="n">
-        <x:v>1.03861518</x:v>
+        <x:v>1.7310253</x:v>
       </x:c>
       <x:c r="H37" t="n">
         <x:v>0.06666666666666667</x:v>
@@ -1739,10 +1739,10 @@
       </x:c>
       <x:c r="E38" s="25" t="str"/>
       <x:c r="F38" s="26" t="n">
-        <x:v>1.19428571</x:v>
+        <x:v>0.77628571</x:v>
       </x:c>
       <x:c r="G38" t="n">
-        <x:v>1.03947368</x:v>
+        <x:v>1.59919028</x:v>
       </x:c>
       <x:c r="H38" t="n">
         <x:v>0.13333333333333333</x:v>
@@ -1775,10 +1775,10 @@
       </x:c>
       <x:c r="E39" s="25" t="str"/>
       <x:c r="F39" s="26" t="n">
-        <x:v>1.1763393</x:v>
+        <x:v>0.82343751</x:v>
       </x:c>
       <x:c r="G39" t="n">
-        <x:v>1.04031209</x:v>
+        <x:v>1.48616013</x:v>
       </x:c>
       <x:c r="H39" t="n">
         <x:v>0.20000000000000004</x:v>
@@ -1811,10 +1811,10 @@
       </x:c>
       <x:c r="E40" s="25" t="str"/>
       <x:c r="F40" s="26" t="n">
-        <x:v>1.23348566</x:v>
+        <x:v>0.92511425</x:v>
       </x:c>
       <x:c r="G40" t="n">
-        <x:v>1.04113111</x:v>
+        <x:v>1.38817481</x:v>
       </x:c>
       <x:c r="H40" t="n">
         <x:v>0.20455</x:v>
@@ -1847,10 +1847,10 @@
       </x:c>
       <x:c r="E41" s="25" t="str"/>
       <x:c r="F41" s="26" t="n">
-        <x:v>1.2052905</x:v>
+        <x:v>0.9642324</x:v>
       </x:c>
       <x:c r="G41" t="n">
-        <x:v>1.04193139</x:v>
+        <x:v>1.30241424</x:v>
       </x:c>
       <x:c r="H41" t="n">
         <x:v>0.20909</x:v>
@@ -1883,10 +1883,10 @@
       </x:c>
       <x:c r="E42" s="25" t="str"/>
       <x:c r="F42" s="26" t="n">
-        <x:v>1.40986383</x:v>
+        <x:v>1.19838426</x:v>
       </x:c>
       <x:c r="G42" t="n">
-        <x:v>1.04271357</x:v>
+        <x:v>1.22672185</x:v>
       </x:c>
       <x:c r="H42" t="n">
         <x:v>0.21364</x:v>
@@ -1919,10 +1919,10 @@
       </x:c>
       <x:c r="E43" s="25" t="str"/>
       <x:c r="F43" s="26" t="n">
-        <x:v>1.463766</x:v>
+        <x:v>1.3173894</x:v>
       </x:c>
       <x:c r="G43" t="n">
-        <x:v>1.04347826</x:v>
+        <x:v>1.15942029</x:v>
       </x:c>
       <x:c r="H43" t="n">
         <x:v>0.21818</x:v>
@@ -1955,10 +1955,10 @@
       </x:c>
       <x:c r="E44" s="25" t="str"/>
       <x:c r="F44" s="26" t="n">
-        <x:v>1.47463077</x:v>
+        <x:v>1.40089923</x:v>
       </x:c>
       <x:c r="G44" t="n">
-        <x:v>1.04422604</x:v>
+        <x:v>1.09918531</x:v>
       </x:c>
       <x:c r="H44" t="n">
         <x:v>0.22273</x:v>
@@ -2209,10 +2209,10 @@
       </x:c>
       <x:c r="E51" s="25" t="str"/>
       <x:c r="F51" s="26" t="n">
-        <x:v>1.06</x:v>
+        <x:v>0.583</x:v>
       </x:c>
       <x:c r="G51" t="n">
-        <x:v>1.03773585</x:v>
+        <x:v>1.88679245</x:v>
       </x:c>
       <x:c r="H51" t="n">
         <x:v>0</x:v>
@@ -2245,10 +2245,10 @@
       </x:c>
       <x:c r="E52" s="25" t="str"/>
       <x:c r="F52" s="26" t="n">
-        <x:v>1.12294737</x:v>
+        <x:v>0.67376842</x:v>
       </x:c>
       <x:c r="G52" t="n">
-        <x:v>1.03838583</x:v>
+        <x:v>1.73064305</x:v>
       </x:c>
       <x:c r="H52" t="n">
         <x:v>0.06666666666666667</x:v>
@@ -2281,10 +2281,10 @@
       </x:c>
       <x:c r="E53" s="25" t="str"/>
       <x:c r="F53" s="26" t="n">
-        <x:v>1.18684211</x:v>
+        <x:v>0.77144737</x:v>
       </x:c>
       <x:c r="G53" t="n">
-        <x:v>1.03902439</x:v>
+        <x:v>1.59849906</x:v>
       </x:c>
       <x:c r="H53" t="n">
         <x:v>0.13333333333333333</x:v>
@@ -2317,10 +2317,10 @@
       </x:c>
       <x:c r="E54" s="25" t="str"/>
       <x:c r="F54" s="26" t="n">
-        <x:v>1.22830493</x:v>
+        <x:v>0.85981345</x:v>
       </x:c>
       <x:c r="G54" t="n">
-        <x:v>1.03965184</x:v>
+        <x:v>1.48521691</x:v>
       </x:c>
       <x:c r="H54" t="n">
         <x:v>0.20000000000000004</x:v>
@@ -2353,10 +2353,10 @@
       </x:c>
       <x:c r="E55" s="25" t="str"/>
       <x:c r="F55" s="26" t="n">
-        <x:v>1.24170797</x:v>
+        <x:v>0.93128098</x:v>
       </x:c>
       <x:c r="G55" t="n">
-        <x:v>1.04026846</x:v>
+        <x:v>1.38702461</x:v>
       </x:c>
       <x:c r="H55" t="n">
         <x:v>0.20313</x:v>
@@ -2389,10 +2389,10 @@
       </x:c>
       <x:c r="E56" s="25" t="str"/>
       <x:c r="F56" s="26" t="n">
-        <x:v>1.30563166</x:v>
+        <x:v>1.04450533</x:v>
       </x:c>
       <x:c r="G56" t="n">
-        <x:v>1.04087452</x:v>
+        <x:v>1.30109315</x:v>
       </x:c>
       <x:c r="H56" t="n">
         <x:v>0.20625</x:v>
@@ -2425,10 +2425,10 @@
       </x:c>
       <x:c r="E57" s="25" t="str"/>
       <x:c r="F57" s="26" t="n">
-        <x:v>1.19264218</x:v>
+        <x:v>1.01374585</x:v>
       </x:c>
       <x:c r="G57" t="n">
-        <x:v>1.04147031</x:v>
+        <x:v>1.22525919</x:v>
       </x:c>
       <x:c r="H57" t="n">
         <x:v>0.20938</x:v>
@@ -2461,10 +2461,10 @@
       </x:c>
       <x:c r="E58" s="25" t="str"/>
       <x:c r="F58" s="26" t="n">
-        <x:v>1.34087895</x:v>
+        <x:v>1.20679106</x:v>
       </x:c>
       <x:c r="G58" t="n">
-        <x:v>1.04205607</x:v>
+        <x:v>1.15784008</x:v>
       </x:c>
       <x:c r="H58" t="n">
         <x:v>0.2125</x:v>
@@ -2497,10 +2497,10 @@
       </x:c>
       <x:c r="E59" s="25" t="str"/>
       <x:c r="F59" s="26" t="n">
-        <x:v>1.42426864</x:v>
+        <x:v>1.35305521</x:v>
       </x:c>
       <x:c r="G59" t="n">
-        <x:v>1.04263207</x:v>
+        <x:v>1.09750744</x:v>
       </x:c>
       <x:c r="H59" t="n">
         <x:v>0.21563</x:v>
@@ -2931,10 +2931,10 @@
       </x:c>
       <x:c r="E71" s="25" t="str"/>
       <x:c r="F71" s="26" t="n">
-        <x:v>1.06</x:v>
+        <x:v>0.583</x:v>
       </x:c>
       <x:c r="G71" t="n">
-        <x:v>1.03773585</x:v>
+        <x:v>1.88679245</x:v>
       </x:c>
       <x:c r="H71" t="n">
         <x:v>0</x:v>
@@ -2967,10 +2967,10 @@
       </x:c>
       <x:c r="E72" s="25" t="str"/>
       <x:c r="F72" s="26" t="n">
-        <x:v>1.09967857</x:v>
+        <x:v>0.65980714</x:v>
       </x:c>
       <x:c r="G72" t="n">
-        <x:v>1.03861518</x:v>
+        <x:v>1.7310253</x:v>
       </x:c>
       <x:c r="H72" t="n">
         <x:v>0.03333333333333333</x:v>
@@ -3003,10 +3003,10 @@
       </x:c>
       <x:c r="E73" s="25" t="str"/>
       <x:c r="F73" s="26" t="n">
-        <x:v>1.14</x:v>
+        <x:v>0.741</x:v>
       </x:c>
       <x:c r="G73" t="n">
-        <x:v>1.03947368</x:v>
+        <x:v>1.59919028</x:v>
       </x:c>
       <x:c r="H73" t="n">
         <x:v>0.06666666666666667</x:v>
@@ -3039,10 +3039,10 @@
       </x:c>
       <x:c r="E74" s="25" t="str"/>
       <x:c r="F74" s="26" t="n">
-        <x:v>1.1129737</x:v>
+        <x:v>0.77908159</x:v>
       </x:c>
       <x:c r="G74" t="n">
-        <x:v>1.04031209</x:v>
+        <x:v>1.48616013</x:v>
       </x:c>
       <x:c r="H74" t="n">
         <x:v>0.10000000000000002</x:v>
@@ -3075,10 +3075,10 @@
       </x:c>
       <x:c r="E75" s="25" t="str"/>
       <x:c r="F75" s="26" t="n">
-        <x:v>1.1067828</x:v>
+        <x:v>0.8300871</x:v>
       </x:c>
       <x:c r="G75" t="n">
-        <x:v>1.04113111</x:v>
+        <x:v>1.38817481</x:v>
       </x:c>
       <x:c r="H75" t="n">
         <x:v>0.10227</x:v>
@@ -3111,10 +3111,10 @@
       </x:c>
       <x:c r="E76" s="25" t="str"/>
       <x:c r="F76" s="26" t="n">
-        <x:v>1.21499309</x:v>
+        <x:v>0.97199447</x:v>
       </x:c>
       <x:c r="G76" t="n">
-        <x:v>1.04193139</x:v>
+        <x:v>1.30241424</x:v>
       </x:c>
       <x:c r="H76" t="n">
         <x:v>0.10455</x:v>
@@ -3147,10 +3147,10 @@
       </x:c>
       <x:c r="E77" s="25" t="str"/>
       <x:c r="F77" s="26" t="n">
-        <x:v>1.31772114</x:v>
+        <x:v>1.12006297</x:v>
       </x:c>
       <x:c r="G77" t="n">
-        <x:v>1.04271357</x:v>
+        <x:v>1.22672185</x:v>
       </x:c>
       <x:c r="H77" t="n">
         <x:v>0.10682</x:v>
@@ -3183,10 +3183,10 @@
       </x:c>
       <x:c r="E78" s="25" t="str"/>
       <x:c r="F78" s="26" t="n">
-        <x:v>1.199243</x:v>
+        <x:v>1.0793187</x:v>
       </x:c>
       <x:c r="G78" t="n">
-        <x:v>1.04347826</x:v>
+        <x:v>1.15942029</x:v>
       </x:c>
       <x:c r="H78" t="n">
         <x:v>0.10909</x:v>
@@ -3219,10 +3219,10 @@
       </x:c>
       <x:c r="E79" s="25" t="str"/>
       <x:c r="F79" s="26" t="n">
-        <x:v>1.36347326</x:v>
+        <x:v>1.2952996</x:v>
       </x:c>
       <x:c r="G79" t="n">
-        <x:v>1.04422604</x:v>
+        <x:v>1.09918531</x:v>
       </x:c>
       <x:c r="H79" t="n">
         <x:v>0.11136</x:v>
@@ -3473,10 +3473,10 @@
       </x:c>
       <x:c r="E86" s="25" t="str"/>
       <x:c r="F86" s="26" t="n">
-        <x:v>1.06</x:v>
+        <x:v>0.583</x:v>
       </x:c>
       <x:c r="G86" t="n">
-        <x:v>1.03773585</x:v>
+        <x:v>1.88679245</x:v>
       </x:c>
       <x:c r="H86" t="n">
         <x:v>0</x:v>
@@ -3509,10 +3509,10 @@
       </x:c>
       <x:c r="E87" s="25" t="str"/>
       <x:c r="F87" s="26" t="n">
-        <x:v>1.1265</x:v>
+        <x:v>0.6759</x:v>
       </x:c>
       <x:c r="G87" t="n">
-        <x:v>1.03861518</x:v>
+        <x:v>1.7310253</x:v>
       </x:c>
       <x:c r="H87" t="n">
         <x:v>0.06666666666666667</x:v>
@@ -3545,10 +3545,10 @@
       </x:c>
       <x:c r="E88" s="25" t="str"/>
       <x:c r="F88" s="26" t="n">
-        <x:v>1.19428571</x:v>
+        <x:v>0.77628571</x:v>
       </x:c>
       <x:c r="G88" t="n">
-        <x:v>1.03947368</x:v>
+        <x:v>1.59919028</x:v>
       </x:c>
       <x:c r="H88" t="n">
         <x:v>0.13333333333333333</x:v>
@@ -3581,10 +3581,10 @@
       </x:c>
       <x:c r="E89" s="26" t="str"/>
       <x:c r="F89" s="26" t="n">
-        <x:v>1.18261214</x:v>
+        <x:v>0.8278285</x:v>
       </x:c>
       <x:c r="G89" t="n">
-        <x:v>1.04031209</x:v>
+        <x:v>1.48616013</x:v>
       </x:c>
       <x:c r="H89" t="n">
         <x:v>0.20000000000000004</x:v>
@@ -3617,10 +3617,10 @@
       </x:c>
       <x:c r="E90" s="26" t="str"/>
       <x:c r="F90" s="26" t="n">
-        <x:v>1.18034826</x:v>
+        <x:v>0.8852612</x:v>
       </x:c>
       <x:c r="G90" t="n">
-        <x:v>1.04113111</x:v>
+        <x:v>1.38817481</x:v>
       </x:c>
       <x:c r="H90" t="n">
         <x:v>0.20455</x:v>
@@ -3653,10 +3653,10 @@
       </x:c>
       <x:c r="E91" s="26" t="str"/>
       <x:c r="F91" s="26" t="n">
-        <x:v>1.2915457</x:v>
+        <x:v>1.03323656</x:v>
       </x:c>
       <x:c r="G91" t="n">
-        <x:v>1.04193139</x:v>
+        <x:v>1.30241424</x:v>
       </x:c>
       <x:c r="H91" t="n">
         <x:v>0.20909</x:v>
@@ -3689,10 +3689,10 @@
       </x:c>
       <x:c r="E92" s="26" t="str"/>
       <x:c r="F92" s="26" t="n">
-        <x:v>1.41938171</x:v>
+        <x:v>1.20647445</x:v>
       </x:c>
       <x:c r="G92" t="n">
-        <x:v>1.04271357</x:v>
+        <x:v>1.22672185</x:v>
       </x:c>
       <x:c r="H92" t="n">
         <x:v>0.21364</x:v>
@@ -3725,10 +3725,10 @@
       </x:c>
       <x:c r="E93" s="26" t="str"/>
       <x:c r="F93" s="26" t="n">
-        <x:v>1.3090795</x:v>
+        <x:v>1.17817155</x:v>
       </x:c>
       <x:c r="G93" t="n">
-        <x:v>1.04347826</x:v>
+        <x:v>1.15942029</x:v>
       </x:c>
       <x:c r="H93" t="n">
         <x:v>0.21818</x:v>
@@ -3761,10 +3761,10 @@
       </x:c>
       <x:c r="E94" s="26" t="str"/>
       <x:c r="F94" s="26" t="n">
-        <x:v>1.43311677</x:v>
+        <x:v>1.36146093</x:v>
       </x:c>
       <x:c r="G94" t="n">
-        <x:v>1.04422604</x:v>
+        <x:v>1.09918531</x:v>
       </x:c>
       <x:c r="H94" t="n">
         <x:v>0.22273</x:v>
@@ -4017,10 +4017,10 @@
         <x:v>wave.801.announcement</x:v>
       </x:c>
       <x:c r="F101" s="26" t="n">
-        <x:v>1.06</x:v>
+        <x:v>0.583</x:v>
       </x:c>
       <x:c r="G101" t="n">
-        <x:v>1.03773585</x:v>
+        <x:v>1.88679245</x:v>
       </x:c>
       <x:c r="H101" t="n">
         <x:v>0</x:v>
@@ -4053,10 +4053,10 @@
       </x:c>
       <x:c r="E102" s="26" t="str"/>
       <x:c r="F102" s="26" t="n">
-        <x:v>1.15868571</x:v>
+        <x:v>0.69521143</x:v>
       </x:c>
       <x:c r="G102" t="n">
-        <x:v>1.03861518</x:v>
+        <x:v>1.7310253</x:v>
       </x:c>
       <x:c r="H102" t="n">
         <x:v>0.09999999999999999</x:v>
@@ -4091,10 +4091,10 @@
         <x:v>wave.803.announcement</x:v>
       </x:c>
       <x:c r="F103" s="26" t="n">
-        <x:v>1.25942857</x:v>
+        <x:v>0.81862857</x:v>
       </x:c>
       <x:c r="G103" t="n">
-        <x:v>1.03947368</x:v>
+        <x:v>1.59919028</x:v>
       </x:c>
       <x:c r="H103" t="n">
         <x:v>0.19999999999999998</x:v>
@@ -4127,10 +4127,10 @@
       </x:c>
       <x:c r="E104" s="26" t="str"/>
       <x:c r="F104" s="26" t="n">
-        <x:v>1.30227953</x:v>
+        <x:v>0.91159567</x:v>
       </x:c>
       <x:c r="G104" t="n">
-        <x:v>1.04031209</x:v>
+        <x:v>1.48616013</x:v>
       </x:c>
       <x:c r="H104" t="n">
         <x:v>0.3</x:v>
@@ -4163,10 +4163,10 @@
       </x:c>
       <x:c r="E105" s="26" t="str"/>
       <x:c r="F105" s="26" t="n">
-        <x:v>1.37860489</x:v>
+        <x:v>1.03395367</x:v>
       </x:c>
       <x:c r="G105" t="n">
-        <x:v>1.04113111</x:v>
+        <x:v>1.38817481</x:v>
       </x:c>
       <x:c r="H105" t="n">
         <x:v>0.30682</x:v>
@@ -4199,10 +4199,10 @@
       </x:c>
       <x:c r="E106" s="26" t="str"/>
       <x:c r="F106" s="26" t="n">
-        <x:v>1.34863693</x:v>
+        <x:v>1.07890954</x:v>
       </x:c>
       <x:c r="G106" t="n">
-        <x:v>1.04193139</x:v>
+        <x:v>1.30241424</x:v>
       </x:c>
       <x:c r="H106" t="n">
         <x:v>0.31364</x:v>
@@ -4235,10 +4235,10 @@
       </x:c>
       <x:c r="E107" s="26" t="str"/>
       <x:c r="F107" s="26" t="n">
-        <x:v>1.53173143</x:v>
+        <x:v>1.30197172</x:v>
       </x:c>
       <x:c r="G107" t="n">
-        <x:v>1.04271357</x:v>
+        <x:v>1.22672185</x:v>
       </x:c>
       <x:c r="H107" t="n">
         <x:v>0.32045</x:v>
@@ -4271,10 +4271,10 @@
       </x:c>
       <x:c r="E108" s="26" t="str"/>
       <x:c r="F108" s="26" t="n">
-        <x:v>1.4816715</x:v>
+        <x:v>1.33350435</x:v>
       </x:c>
       <x:c r="G108" t="n">
-        <x:v>1.04347826</x:v>
+        <x:v>1.15942029</x:v>
       </x:c>
       <x:c r="H108" t="n">
         <x:v>0.32727</x:v>
@@ -4307,10 +4307,10 @@
       </x:c>
       <x:c r="E109" s="26" t="str"/>
       <x:c r="F109" s="26" t="n">
-        <x:v>1.68225891</x:v>
+        <x:v>1.59814596</x:v>
       </x:c>
       <x:c r="G109" t="n">
-        <x:v>1.04422604</x:v>
+        <x:v>1.09918531</x:v>
       </x:c>
       <x:c r="H109" t="n">
         <x:v>0.33409</x:v>
@@ -4561,10 +4561,10 @@
       </x:c>
       <x:c r="E116" t="str"/>
       <x:c r="F116" t="n">
-        <x:v>1.06</x:v>
+        <x:v>0.583</x:v>
       </x:c>
       <x:c r="G116" t="n">
-        <x:v>1.03773585</x:v>
+        <x:v>1.88679245</x:v>
       </x:c>
       <x:c r="H116" t="n">
         <x:v>0</x:v>
@@ -4597,10 +4597,10 @@
       </x:c>
       <x:c r="E117" t="str"/>
       <x:c r="F117" t="n">
-        <x:v>1.15868571</x:v>
+        <x:v>0.69521143</x:v>
       </x:c>
       <x:c r="G117" t="n">
-        <x:v>1.03861518</x:v>
+        <x:v>1.7310253</x:v>
       </x:c>
       <x:c r="H117" t="n">
         <x:v>0.09999999999999999</x:v>
@@ -4633,10 +4633,10 @@
       </x:c>
       <x:c r="E118" t="str"/>
       <x:c r="F118" t="n">
-        <x:v>1.25942857</x:v>
+        <x:v>0.81862857</x:v>
       </x:c>
       <x:c r="G118" t="n">
-        <x:v>1.03947368</x:v>
+        <x:v>1.59919028</x:v>
       </x:c>
       <x:c r="H118" t="n">
         <x:v>0.19999999999999998</x:v>
@@ -4669,10 +4669,10 @@
       </x:c>
       <x:c r="E119" t="str"/>
       <x:c r="F119" t="n">
-        <x:v>1.19535557</x:v>
+        <x:v>0.8367489</x:v>
       </x:c>
       <x:c r="G119" t="n">
-        <x:v>1.04031209</x:v>
+        <x:v>1.48616013</x:v>
       </x:c>
       <x:c r="H119" t="n">
         <x:v>0.3</x:v>
@@ -4705,10 +4705,10 @@
       </x:c>
       <x:c r="E120" t="str"/>
       <x:c r="F120" t="n">
-        <x:v>1.19639729</x:v>
+        <x:v>0.89729797</x:v>
       </x:c>
       <x:c r="G120" t="n">
-        <x:v>1.04113111</x:v>
+        <x:v>1.38817481</x:v>
       </x:c>
       <x:c r="H120" t="n">
         <x:v>0.30682</x:v>
@@ -4741,10 +4741,10 @@
       </x:c>
       <x:c r="E121" t="str"/>
       <x:c r="F121" t="n">
-        <x:v>1.3990499</x:v>
+        <x:v>1.11923992</x:v>
       </x:c>
       <x:c r="G121" t="n">
-        <x:v>1.04193139</x:v>
+        <x:v>1.30241424</x:v>
       </x:c>
       <x:c r="H121" t="n">
         <x:v>0.31364</x:v>
@@ -4777,10 +4777,10 @@
       </x:c>
       <x:c r="E122" t="str"/>
       <x:c r="F122" t="n">
-        <x:v>1.42201989</x:v>
+        <x:v>1.20871691</x:v>
       </x:c>
       <x:c r="G122" t="n">
-        <x:v>1.04271357</x:v>
+        <x:v>1.22672185</x:v>
       </x:c>
       <x:c r="H122" t="n">
         <x:v>0.32045</x:v>
@@ -4813,10 +4813,10 @@
       </x:c>
       <x:c r="E123" t="str"/>
       <x:c r="F123" t="n">
-        <x:v>1.322155</x:v>
+        <x:v>1.1899395</x:v>
       </x:c>
       <x:c r="G123" t="n">
-        <x:v>1.04347826</x:v>
+        <x:v>1.15942029</x:v>
       </x:c>
       <x:c r="H123" t="n">
         <x:v>0.32727</x:v>
@@ -4849,10 +4849,10 @@
       </x:c>
       <x:c r="E124" t="str"/>
       <x:c r="F124" t="n">
-        <x:v>1.44032649</x:v>
+        <x:v>1.36831017</x:v>
       </x:c>
       <x:c r="G124" t="n">
-        <x:v>1.04422604</x:v>
+        <x:v>1.09918531</x:v>
       </x:c>
       <x:c r="H124" t="n">
         <x:v>0.33409</x:v>
@@ -5103,10 +5103,10 @@
       </x:c>
       <x:c r="E131" t="str"/>
       <x:c r="F131" t="n">
-        <x:v>1.06</x:v>
+        <x:v>0.583</x:v>
       </x:c>
       <x:c r="G131" t="n">
-        <x:v>1.03773585</x:v>
+        <x:v>1.88679245</x:v>
       </x:c>
       <x:c r="H131" t="n">
         <x:v>0</x:v>
@@ -5139,10 +5139,10 @@
       </x:c>
       <x:c r="E132" t="str"/>
       <x:c r="F132" t="n">
-        <x:v>1.15503158</x:v>
+        <x:v>0.69301895</x:v>
       </x:c>
       <x:c r="G132" t="n">
-        <x:v>1.03838583</x:v>
+        <x:v>1.73064305</x:v>
       </x:c>
       <x:c r="H132" t="n">
         <x:v>0.075</x:v>
@@ -5175,10 +5175,10 @@
       </x:c>
       <x:c r="E133" t="str"/>
       <x:c r="F133" t="n">
-        <x:v>1.25157895</x:v>
+        <x:v>0.81352632</x:v>
       </x:c>
       <x:c r="G133" t="n">
-        <x:v>1.03902439</x:v>
+        <x:v>1.59849906</x:v>
       </x:c>
       <x:c r="H133" t="n">
         <x:v>0.15</x:v>
@@ -5211,10 +5211,10 @@
       </x:c>
       <x:c r="E134" t="str"/>
       <x:c r="F134" t="n">
-        <x:v>1.19181017</x:v>
+        <x:v>0.83426712</x:v>
       </x:c>
       <x:c r="G134" t="n">
-        <x:v>1.03965184</x:v>
+        <x:v>1.48521691</x:v>
       </x:c>
       <x:c r="H134" t="n">
         <x:v>0.22499999999999998</x:v>
@@ -5247,10 +5247,10 @@
       </x:c>
       <x:c r="E135" t="str"/>
       <x:c r="F135" t="n">
-        <x:v>1.35644895</x:v>
+        <x:v>1.01733671</x:v>
       </x:c>
       <x:c r="G135" t="n">
-        <x:v>1.04026846</x:v>
+        <x:v>1.38702461</x:v>
       </x:c>
       <x:c r="H135" t="n">
         <x:v>0.3</x:v>
@@ -5283,10 +5283,10 @@
       </x:c>
       <x:c r="E136" t="str"/>
       <x:c r="F136" t="n">
-        <x:v>1.11639347</x:v>
+        <x:v>0.89311478</x:v>
       </x:c>
       <x:c r="G136" t="n">
-        <x:v>1.04087452</x:v>
+        <x:v>1.30109315</x:v>
       </x:c>
       <x:c r="H136" t="n">
         <x:v>0.305</x:v>
@@ -5319,10 +5319,10 @@
       </x:c>
       <x:c r="E137" t="str"/>
       <x:c r="F137" t="n">
-        <x:v>1.26658829</x:v>
+        <x:v>1.07660005</x:v>
       </x:c>
       <x:c r="G137" t="n">
-        <x:v>1.04147031</x:v>
+        <x:v>1.22525919</x:v>
       </x:c>
       <x:c r="H137" t="n">
         <x:v>0.31</x:v>
@@ -5355,10 +5355,10 @@
       </x:c>
       <x:c r="E138" t="str"/>
       <x:c r="F138" t="n">
-        <x:v>1.35180421</x:v>
+        <x:v>1.21662379</x:v>
       </x:c>
       <x:c r="G138" t="n">
-        <x:v>1.04205607</x:v>
+        <x:v>1.15784008</x:v>
       </x:c>
       <x:c r="H138" t="n">
         <x:v>0.315</x:v>
@@ -5391,10 +5391,10 @@
       </x:c>
       <x:c r="E139" t="str"/>
       <x:c r="F139" t="n">
-        <x:v>1.29090424</x:v>
+        <x:v>1.22635903</x:v>
       </x:c>
       <x:c r="G139" t="n">
-        <x:v>1.04263207</x:v>
+        <x:v>1.09750744</x:v>
       </x:c>
       <x:c r="H139" t="n">
         <x:v>0.32</x:v>
